--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G7" s="18">
         <f>Assumptions!D16*Assumptions!D22*(1+Assumptions!D23)^4</f>
-        <v>4979187.94</v>
+        <v>4979187.936</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -1621,11 +1621,11 @@
       </c>
       <c r="F8" s="18">
         <f>Assumptions!D15*Assumptions!D24*(1+Assumptions!D25)^3</f>
-        <v>122931.79</v>
+        <v>122931.7875</v>
       </c>
       <c r="G8" s="18">
         <f>Assumptions!D16*Assumptions!D24*(1+Assumptions!D25)^4</f>
-        <v>135061.06</v>
+        <v>135061.0572</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="F10" s="20">
         <f>F6+F7+F8+F9</f>
-        <v>4829391.29</v>
+        <v>4829391.2875</v>
       </c>
       <c r="G10" s="20">
         <f>G6+G7+G8+G9</f>
-        <v>5244248.99</v>
+        <v>5244248.9932</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -1717,15 +1717,15 @@
       </c>
       <c r="E13" s="18">
         <f>E12*Assumptions!D33*(1+Assumptions!D34)^2</f>
-        <v>1211203.01</v>
+        <v>1211203.0075</v>
       </c>
       <c r="F13" s="18">
         <f>F12*Assumptions!D33*(1+Assumptions!D34)^3</f>
-        <v>1596850.05</v>
+        <v>1596850.045088</v>
       </c>
       <c r="G13" s="18">
         <f>G12*Assumptions!D33*(1+Assumptions!D34)^4</f>
-        <v>1747552.77</v>
+        <v>1747552.76809318</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="G14" s="18">
         <f>Assumptions!D39*Assumptions!D40*(1+Assumptions!D41)^4</f>
-        <v>551499.32</v>
+        <v>551499.3169</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
@@ -1759,23 +1759,23 @@
       </c>
       <c r="C15" s="18">
         <f>(C13+C14)*Assumptions!D42</f>
-        <v>253497.19</v>
+        <v>253497.18888889</v>
       </c>
       <c r="D15" s="18">
         <f>(D13+D14)*Assumptions!D42</f>
-        <v>349270.37</v>
+        <v>349270.36663333</v>
       </c>
       <c r="E15" s="18">
         <f>(E13+E14)*Assumptions!D42</f>
-        <v>463535.12</v>
+        <v>463535.11756389</v>
       </c>
       <c r="F15" s="18">
         <f>(F13+F14)*Assumptions!D42</f>
-        <v>570978.88</v>
+        <v>570978.88032912</v>
       </c>
       <c r="G15" s="18">
         <f>(G13+G14)*Assumptions!D42</f>
-        <v>615635.06</v>
+        <v>615635.05831484</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
@@ -1784,23 +1784,23 @@
       </c>
       <c r="C16" s="20">
         <f>C13+C14+C15</f>
-        <v>1200167.19</v>
+        <v>1200167.18888889</v>
       </c>
       <c r="D16" s="20">
         <f>D13+D14+D15</f>
-        <v>1653599.54</v>
+        <v>1653599.53663333</v>
       </c>
       <c r="E16" s="20">
         <f>E13+E14+E15</f>
-        <v>2194579.13</v>
+        <v>2194579.12506389</v>
       </c>
       <c r="F16" s="20">
         <f>F13+F14+F15</f>
-        <v>2703265.16</v>
+        <v>2703265.15541712</v>
       </c>
       <c r="G16" s="20">
         <f>G13+G14+G15</f>
-        <v>2914687.14</v>
+        <v>2914687.14330802</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -1821,11 +1821,11 @@
       </c>
       <c r="F18" s="18">
         <f>Assumptions!D46*(1+Assumptions!D47)^3</f>
-        <v>308149.01</v>
+        <v>308149.014</v>
       </c>
       <c r="G18" s="18">
         <f>Assumptions!D46*(1+Assumptions!D47)^4</f>
-        <v>317393.48</v>
+        <v>317393.48442</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
@@ -1863,19 +1863,19 @@
       </c>
       <c r="D20" s="18">
         <f>Assumptions!D13*Assumptions!D50*(1+Assumptions!D51)^1</f>
-        <v>240333.33</v>
+        <v>240333.33333333</v>
       </c>
       <c r="E20" s="18">
         <f>Assumptions!D14*Assumptions!D50*(1+Assumptions!D51)^2</f>
-        <v>618858.33</v>
+        <v>618858.33333333</v>
       </c>
       <c r="F20" s="18">
         <f>Assumptions!D15*Assumptions!D50*(1+Assumptions!D51)^3</f>
-        <v>1327966.84</v>
+        <v>1327966.84027778</v>
       </c>
       <c r="G20" s="18">
         <f>Assumptions!D16*Assumptions!D50*(1+Assumptions!D51)^4</f>
-        <v>2431654.84</v>
+        <v>2431654.83641975</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
@@ -1892,15 +1892,15 @@
       </c>
       <c r="E21" s="18">
         <f>Assumptions!D52*(1+Assumptions!D53)^2</f>
-        <v>713160.56</v>
+        <v>713160.55555556</v>
       </c>
       <c r="F21" s="18">
         <f>Assumptions!D52*(1+Assumptions!D53)^3</f>
-        <v>1122237.37</v>
+        <v>1122237.3742284</v>
       </c>
       <c r="G21" s="18">
         <f>Assumptions!D52*(1+Assumptions!D53)^4</f>
-        <v>1765965.2</v>
+        <v>1765965.20138996</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -1913,19 +1913,19 @@
       </c>
       <c r="D22" s="20">
         <f>D18+D19+D20+D21</f>
-        <v>983993.33</v>
+        <v>983993.33333333</v>
       </c>
       <c r="E22" s="20">
         <f>E18+E19+E20+E21</f>
-        <v>1631192.69</v>
+        <v>1631192.68888889</v>
       </c>
       <c r="F22" s="20">
         <f>F18+F19+F20+F21</f>
-        <v>2758353.23</v>
+        <v>2758353.22850617</v>
       </c>
       <c r="G22" s="20">
         <f>G18+G19+G20+G21</f>
-        <v>4515013.52</v>
+        <v>4515013.52222971</v>
       </c>
     </row>
   </sheetData>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="G7" s="18">
         <f>Drivers!G7</f>
-        <v>4979187.94</v>
+        <v>4979187.936</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -2075,11 +2075,11 @@
       </c>
       <c r="F8" s="18">
         <f>Drivers!F8</f>
-        <v>122931.79</v>
+        <v>122931.7875</v>
       </c>
       <c r="G8" s="18">
         <f>Drivers!G8</f>
-        <v>135061.06</v>
+        <v>135061.0572</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
@@ -2125,11 +2125,11 @@
       </c>
       <c r="F10" s="20">
         <f>Drivers!F10</f>
-        <v>4829391.29</v>
+        <v>4829391.2875</v>
       </c>
       <c r="G10" s="20">
         <f>Drivers!G10</f>
-        <v>5244248.99</v>
+        <v>5244248.9932</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -2138,23 +2138,23 @@
       </c>
       <c r="C12" s="18">
         <f>Drivers!C16</f>
-        <v>1200167.19</v>
+        <v>1200167.18888889</v>
       </c>
       <c r="D12" s="18">
         <f>Drivers!D16</f>
-        <v>1653599.54</v>
+        <v>1653599.53663333</v>
       </c>
       <c r="E12" s="18">
         <f>Drivers!E16</f>
-        <v>2194579.13</v>
+        <v>2194579.12506389</v>
       </c>
       <c r="F12" s="18">
         <f>Drivers!F16</f>
-        <v>2703265.16</v>
+        <v>2703265.15541712</v>
       </c>
       <c r="G12" s="18">
         <f>Drivers!G16</f>
-        <v>2914687.14</v>
+        <v>2914687.14330802</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
@@ -2167,19 +2167,19 @@
       </c>
       <c r="D13" s="18">
         <f>Drivers!D22</f>
-        <v>983993.33</v>
+        <v>983993.33333333</v>
       </c>
       <c r="E13" s="18">
         <f>Drivers!E22</f>
-        <v>1631192.69</v>
+        <v>1631192.68888889</v>
       </c>
       <c r="F13" s="18">
         <f>Drivers!F22</f>
-        <v>2758353.23</v>
+        <v>2758353.22850617</v>
       </c>
       <c r="G13" s="18">
         <f>Drivers!G22</f>
-        <v>4515013.52</v>
+        <v>4515013.52222971</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
@@ -2188,23 +2188,23 @@
       </c>
       <c r="C15" s="20">
         <f>C12+C13</f>
-        <v>1854167.19</v>
+        <v>1854167.18888889</v>
       </c>
       <c r="D15" s="20">
         <f>D12+D13</f>
-        <v>2637592.87</v>
+        <v>2637592.86996667</v>
       </c>
       <c r="E15" s="20">
         <f>E12+E13</f>
-        <v>3825771.81</v>
+        <v>3825771.81395278</v>
       </c>
       <c r="F15" s="20">
         <f>F12+F13</f>
-        <v>5461618.38</v>
+        <v>5461618.38392329</v>
       </c>
       <c r="G15" s="20">
         <f>G12+G13</f>
-        <v>7429700.67</v>
+        <v>7429700.66553774</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
@@ -2213,23 +2213,23 @@
       </c>
       <c r="C16" s="21">
         <f>C10-C15</f>
-        <v>-308167.19</v>
+        <v>-308167.18888889</v>
       </c>
       <c r="D16" s="21">
         <f>D10-D15</f>
-        <v>-99792.87</v>
+        <v>-99792.86996667</v>
       </c>
       <c r="E16" s="21">
         <f>E10-E15</f>
-        <v>-10910.81</v>
+        <v>-10910.81395278</v>
       </c>
       <c r="F16" s="21">
         <f>F10-F15</f>
-        <v>-632227.1</v>
+        <v>-632227.09642329</v>
       </c>
       <c r="G16" s="21">
         <f>G10-G15</f>
-        <v>-2185451.67</v>
+        <v>-2185451.67233774</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
@@ -2238,23 +2238,23 @@
       </c>
       <c r="C17" s="22">
         <f>IF(C10&gt;0,C16/C10,0)</f>
-        <v>-0.2</v>
+        <v>-0.19933195</v>
       </c>
       <c r="D17" s="22">
         <f>IF(D10&gt;0,D16/D10,0)</f>
-        <v>-0.04</v>
-      </c>
-      <c r="E17" s="22" t="str">
+        <v>-0.03932259</v>
+      </c>
+      <c r="E17" s="22">
         <f>IF(E10&gt;0,E16/E10,0)</f>
-        <v>0</v>
+        <v>-0.00286008</v>
       </c>
       <c r="F17" s="22">
         <f>IF(F10&gt;0,F16/F10,0)</f>
-        <v>-0.13</v>
+        <v>-0.13091238</v>
       </c>
       <c r="G17" s="22">
         <f>IF(G10&gt;0,G16/G10,0)</f>
-        <v>-0.42</v>
+        <v>-0.41673301</v>
       </c>
     </row>
   </sheetData>
@@ -2317,23 +2317,23 @@
       </c>
       <c r="C4" s="18">
         <f>'5-Year P&amp;L'!C16</f>
-        <v>-308167.19</v>
+        <v>-308167.18888889</v>
       </c>
       <c r="D4" s="18">
         <f>'5-Year P&amp;L'!D16</f>
-        <v>-99792.87</v>
+        <v>-99792.86996667</v>
       </c>
       <c r="E4" s="18">
         <f>'5-Year P&amp;L'!E16</f>
-        <v>-10910.81</v>
+        <v>-10910.81395278</v>
       </c>
       <c r="F4" s="18">
         <f>'5-Year P&amp;L'!F16</f>
-        <v>-632227.1</v>
+        <v>-632227.09642329</v>
       </c>
       <c r="G4" s="18">
         <f>'5-Year P&amp;L'!G16</f>
-        <v>-2185451.67</v>
+        <v>-2185451.67233774</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
@@ -2367,23 +2367,23 @@
       </c>
       <c r="C7" s="18">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
-        <v>49824.61</v>
+        <v>49824.60522118</v>
       </c>
       <c r="D7" s="18">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
-        <v>49824.61</v>
+        <v>49824.60522118</v>
       </c>
       <c r="E7" s="18">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
-        <v>49824.61</v>
+        <v>49824.60522118</v>
       </c>
       <c r="F7" s="18">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
-        <v>49824.61</v>
+        <v>49824.60522118</v>
       </c>
       <c r="G7" s="18">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
-        <v>49824.61</v>
+        <v>49824.60522118</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -2392,23 +2392,23 @@
       </c>
       <c r="C8" s="20">
         <f>C6+C7</f>
-        <v>164824.61</v>
+        <v>164824.60522118</v>
       </c>
       <c r="D8" s="20">
         <f>D6+D7</f>
-        <v>164824.61</v>
+        <v>164824.60522118</v>
       </c>
       <c r="E8" s="20">
         <f>E6+E7</f>
-        <v>164824.61</v>
+        <v>164824.60522118</v>
       </c>
       <c r="F8" s="20">
         <f>F6+F7</f>
-        <v>164824.61</v>
+        <v>164824.60522118</v>
       </c>
       <c r="G8" s="20">
         <f>G6+G7</f>
-        <v>164824.61</v>
+        <v>164824.60522118</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -2417,23 +2417,23 @@
       </c>
       <c r="C10" s="23">
         <f>IF(C8&gt;0,C4/C8,IF(C4&gt;0,99.9,0))</f>
-        <v>-1.87</v>
+        <v>-1.86966739</v>
       </c>
       <c r="D10" s="23">
         <f>IF(D8&gt;0,D4/D8,IF(D4&gt;0,99.9,0))</f>
-        <v>-0.61</v>
+        <v>-0.60544886</v>
       </c>
       <c r="E10" s="23">
         <f>IF(E8&gt;0,E4/E8,IF(E4&gt;0,99.9,0))</f>
-        <v>-0.07</v>
+        <v>-0.06619651</v>
       </c>
       <c r="F10" s="23">
         <f>IF(F8&gt;0,F4/F8,IF(F4&gt;0,99.9,0))</f>
-        <v>-3.84</v>
+        <v>-3.83575678</v>
       </c>
       <c r="G10" s="23">
         <f>IF(G8&gt;0,G4/G8,IF(G4&gt;0,99.9,0))</f>
-        <v>-13.26</v>
+        <v>-13.25925622</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -2442,23 +2442,23 @@
       </c>
       <c r="C12" s="18">
         <f>C4-C8</f>
-        <v>-472991.79</v>
+        <v>-472991.79411007</v>
       </c>
       <c r="D12" s="18">
         <f>D4-D8</f>
-        <v>-264617.48</v>
+        <v>-264617.47518785</v>
       </c>
       <c r="E12" s="18">
         <f>E4-E8</f>
-        <v>-175735.42</v>
+        <v>-175735.41917396</v>
       </c>
       <c r="F12" s="18">
         <f>F4-F8</f>
-        <v>-797051.7</v>
+        <v>-797051.70164447</v>
       </c>
       <c r="G12" s="18">
         <f>G4-G8</f>
-        <v>-2350276.28</v>
+        <v>-2350276.27755892</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
@@ -2467,23 +2467,23 @@
       </c>
       <c r="C14" s="24">
         <f>Assumptions!D57+C12</f>
-        <v>-472991.79</v>
+        <v>-472991.79411007</v>
       </c>
       <c r="D14" s="24">
         <f>C14+D12</f>
-        <v>-737609.27</v>
+        <v>-737609.26929791</v>
       </c>
       <c r="E14" s="24">
         <f>D14+E12</f>
-        <v>-913344.69</v>
+        <v>-913344.68847187</v>
       </c>
       <c r="F14" s="24">
         <f>E14+F12</f>
-        <v>-1710396.39</v>
+        <v>-1710396.39011634</v>
       </c>
       <c r="G14" s="24">
         <f>F14+G12</f>
-        <v>-4060672.67</v>
+        <v>-4060672.66767526</v>
       </c>
     </row>
   </sheetData>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="C4" s="22">
         <f>Assumptions!D60</f>
-        <v>0.06</v>
+        <v>0.0575</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="C6" s="26">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
-        <v>49824.61</v>
+        <v>49824.60522118</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="C8" s="23">
         <f>'Cash Flow &amp; DSCR'!C10</f>
-        <v>-1.87</v>
+        <v>-1.86966739</v>
       </c>
     </row>
   </sheetData>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="C9" s="18">
         <f>Drivers!G10</f>
-        <v>5244248.99</v>
+        <v>5244248.9932</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="C10" s="24">
         <f>'5-Year P&amp;L'!G16</f>
-        <v>-2185451.67</v>
+        <v>-2185451.67233774</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
@@ -53,7 +53,7 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>Generated March 16, 2026</t>
+    <t>Generated March 17, 2026</t>
   </si>
   <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>
@@ -412,13 +412,13 @@
     <font>
       <u/>
       <color rgb="FF0563C1"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <i/>
       <color rgb="FF6B7280"/>
-      <sz val="9"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -435,12 +435,12 @@
     </font>
     <font>
       <color rgb="FF374151"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <color rgb="FF1E293B"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
@@ -59,7 +59,7 @@
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>
   </si>
   <si>
-    <t>SchoolStack Budget — Lender Pro Forma Assumptions</t>
+    <t>SchoolStack Budget - Lender Pro Forma Assumptions</t>
   </si>
   <si>
     <t>SCHOOL PROFILE</t>
@@ -143,19 +143,19 @@
     <t>Teacher Salary Growth %</t>
   </si>
   <si>
-    <t>Admin FTE — Year 1</t>
-  </si>
-  <si>
-    <t>Admin FTE — Year 2</t>
-  </si>
-  <si>
-    <t>Admin FTE — Year 3</t>
-  </si>
-  <si>
-    <t>Admin FTE — Year 4</t>
-  </si>
-  <si>
-    <t>Admin FTE — Year 5</t>
+    <t>Admin FTE - Year 1</t>
+  </si>
+  <si>
+    <t>Admin FTE - Year 2</t>
+  </si>
+  <si>
+    <t>Admin FTE - Year 3</t>
+  </si>
+  <si>
+    <t>Admin FTE - Year 4</t>
+  </si>
+  <si>
+    <t>Admin FTE - Year 5</t>
   </si>
   <si>
     <t>Avg Admin Salary (Year 1)</t>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
@@ -53,7 +53,7 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>Generated March 17, 2026</t>
+    <t>Generated March 18, 2026</t>
   </si>
   <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
@@ -5,20 +5,22 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="Cover" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Assumptions" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Drivers" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="5-Year P&amp;L" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Cash Flow &amp; DSCR" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="Staffing" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Loan Snapshot" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="Summary" state="visible" r:id="rId11"/>
+    <sheet sheetId="2" name="Instructions" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Assumptions" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Drivers" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="5-Year P&amp;L" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Cash Flow &amp; DSCR" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Staffing" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Loan Snapshot" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Summary" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="Financial Health" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="178">
   <si>
     <t>SCHOOLSTACK BUDGET</t>
   </si>
@@ -53,12 +55,81 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>Generated March 18, 2026</t>
+    <t>Generated March 26, 2026</t>
   </si>
   <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>
   </si>
   <si>
+    <t>How to Use This Workbook</t>
+  </si>
+  <si>
+    <t>Cell Color Legend</t>
+  </si>
+  <si>
+    <t>Blue cells are editable inputs — change these to update your model.</t>
+  </si>
+  <si>
+    <t>White cells contain formulas — do not edit (they recalculate automatically).</t>
+  </si>
+  <si>
+    <t>Green cells are key outputs and summary metrics.</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Navigation</t>
+  </si>
+  <si>
+    <t>The Assumptions tab is the central control panel — all other tabs reference it.</t>
+  </si>
+  <si>
+    <t>Structure</t>
+  </si>
+  <si>
+    <t>Assumptions &amp; Drivers: Model inputs and calculations</t>
+  </si>
+  <si>
+    <t>5-Year P&amp;L &amp; Cash Flow: Financial projections</t>
+  </si>
+  <si>
+    <t>Staffing &amp; Loan Snapshot: Personnel and debt detail</t>
+  </si>
+  <si>
+    <t>Summary &amp; Financial Health: Key metrics dashboard</t>
+  </si>
+  <si>
+    <t>Debt Service Convention</t>
+  </si>
+  <si>
+    <t>operating expense on the Operating Statement. This is a standard</t>
+  </si>
+  <si>
+    <t>simplification used in school financial underwriting that ensures internal</t>
+  </si>
+  <si>
+    <t>consistency across all tabs.</t>
+  </si>
+  <si>
+    <t>Tips</t>
+  </si>
+  <si>
+    <t>Check the Financial Health dashboard for an at-a-glance assessment.</t>
+  </si>
+  <si>
+    <t>Review key metrics: net margin, cash runway, and DSCR.</t>
+  </si>
+  <si>
+    <t>Disclaimer</t>
+  </si>
+  <si>
+    <t>a loan commitment, or a guarantee of funding. All projections are based on</t>
+  </si>
+  <si>
+    <t>user-provided assumptions and should be independently verified.</t>
+  </si>
+  <si>
     <t>SchoolStack Budget - Lender Pro Forma Assumptions</t>
   </si>
   <si>
@@ -366,6 +437,123 @@
   </si>
   <si>
     <t>Generated by SchoolStack Budget (budget.schoolstack.ai)</t>
+  </si>
+  <si>
+    <t>Civic Scholars Charter — Financial Health Dashboard</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>Personnel</t>
+  </si>
+  <si>
+    <t>Operating Expenses</t>
+  </si>
+  <si>
+    <t>Debt Service</t>
+  </si>
+  <si>
+    <t>Net Income</t>
+  </si>
+  <si>
+    <t>Ending Cash</t>
+  </si>
+  <si>
+    <t>Net Margin</t>
+  </si>
+  <si>
+    <t>FINANCIAL HEALTH SIGNALS</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Assessment</t>
+  </si>
+  <si>
+    <t>Watch Item</t>
+  </si>
+  <si>
+    <t>Viability</t>
+  </si>
+  <si>
+    <t>○ Needs attention</t>
+  </si>
+  <si>
+    <t>The model does not reach break-even within 5 years. This needs to be addressed before approaching lenders.</t>
+  </si>
+  <si>
+    <t>Revisit revenue assumptions and cost structure to build a clear path to break-even.</t>
+  </si>
+  <si>
+    <t>Liquidity</t>
+  </si>
+  <si>
+    <t>Cash goes negative in month 0. The school will need outside funding to continue operating.</t>
+  </si>
+  <si>
+    <t>Secure a line of credit or bridge funding before operations begin.</t>
+  </si>
+  <si>
+    <t>Staffing Burden</t>
+  </si>
+  <si>
+    <t>◐ Watch closely</t>
+  </si>
+  <si>
+    <t>Staffing at 56% of revenue is within range but leaves limited margin for other costs.</t>
+  </si>
+  <si>
+    <t>Phase new hires with enrollment growth to prevent staffing from exceeding 65%.</t>
+  </si>
+  <si>
+    <t>Facility Burden</t>
+  </si>
+  <si>
+    <t>Facility costs at 26% of revenue are high. Fixed costs this size create rigidity in your budget.</t>
+  </si>
+  <si>
+    <t>Explore shared space, renegotiate terms, or consider a smaller facility.</t>
+  </si>
+  <si>
+    <t>Debt Affordability</t>
+  </si>
+  <si>
+    <t>DSCR of -13.26x means operating income does not cover debt payments. This must be resolved.</t>
+  </si>
+  <si>
+    <t>Reduce loan amounts, extend terms, or increase revenue before committing to this debt.</t>
+  </si>
+  <si>
+    <t>Revenue Concentration</t>
+  </si>
+  <si>
+    <t>● Healthy</t>
+  </si>
+  <si>
+    <t>Revenue is anchored to enrollment-driven income — the strongest foundation for a school model. A focused revenue stream is a strength when backed by dependable demand.</t>
+  </si>
+  <si>
+    <t>Continue to pressure-test enrollment assumptions: recruitment pipeline, waitlist depth, retention rates, and collection reliability.</t>
+  </si>
+  <si>
+    <t>Reserve Strength</t>
+  </si>
+  <si>
+    <t>Less than 1 month of reserves by Year 5. The school has no financial cushion.</t>
+  </si>
+  <si>
+    <t>Prioritize building reserves — even a small surplus each year compounds into meaningful protection.</t>
+  </si>
+  <si>
+    <t>1 Healthy  |  1 Watch  |  5 Needs Attention</t>
+  </si>
+  <si>
+    <t>Built by SchoolStack Budget  •  budget.schoolstack.ai</t>
   </si>
 </sst>
 </file>
@@ -378,7 +566,7 @@
     <numFmt numFmtId="166" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -422,6 +610,10 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FF1E293B"/>
       <sz val="14"/>
@@ -444,16 +636,36 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color rgb="FFDC2626"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFD97706"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF16A34A"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF9CA3AF"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -473,6 +685,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCE4EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EDF2"/>
       </patternFill>
     </fill>
   </fills>
@@ -536,7 +753,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -544,32 +761,34 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="11" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -579,7 +798,7 @@
     <xf numFmtId="165" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="12" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -593,6 +812,32 @@
     </xf>
     <xf numFmtId="165" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1043,7 +1288,556 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:G26"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="G5" s="30" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="19">
+        <v>120</v>
+      </c>
+      <c r="D6" s="19">
+        <v>200</v>
+      </c>
+      <c r="E6" s="19">
+        <v>300</v>
+      </c>
+      <c r="F6" s="19">
+        <v>375</v>
+      </c>
+      <c r="G6" s="19">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="C7" s="20">
+        <v>1546000</v>
+      </c>
+      <c r="D7" s="20">
+        <v>2537800</v>
+      </c>
+      <c r="E7" s="20">
+        <v>3814861</v>
+      </c>
+      <c r="F7" s="20">
+        <v>4829391.287500001</v>
+      </c>
+      <c r="G7" s="20">
+        <v>5244248.993199999</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="C8" s="20">
+        <v>1200167.1888888888</v>
+      </c>
+      <c r="D8" s="20">
+        <v>1653599.5366333332</v>
+      </c>
+      <c r="E8" s="20">
+        <v>2194579.1250638887</v>
+      </c>
+      <c r="F8" s="20">
+        <v>2703265.15541712</v>
+      </c>
+      <c r="G8" s="20">
+        <v>2914687.143308021</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="C9" s="20">
+        <v>654000</v>
+      </c>
+      <c r="D9" s="20">
+        <v>983993.3333333334</v>
+      </c>
+      <c r="E9" s="20">
+        <v>1631192.688888889</v>
+      </c>
+      <c r="F9" s="20">
+        <v>2758353.228506173</v>
+      </c>
+      <c r="G9" s="20">
+        <v>4515013.522229714</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="C10" s="20">
+        <v>164824.60522117943</v>
+      </c>
+      <c r="D10" s="20">
+        <v>164824.60522117943</v>
+      </c>
+      <c r="E10" s="20">
+        <v>164824.60522117943</v>
+      </c>
+      <c r="F10" s="20">
+        <v>164824.60522117943</v>
+      </c>
+      <c r="G10" s="20">
+        <v>164824.60522117943</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="C11" s="23">
+        <v>-472991.79411006824</v>
+      </c>
+      <c r="D11" s="23">
+        <v>-264617.4751878461</v>
+      </c>
+      <c r="E11" s="23">
+        <v>-175735.41917395697</v>
+      </c>
+      <c r="F11" s="23">
+        <v>-797051.701644472</v>
+      </c>
+      <c r="G11" s="23">
+        <v>-2350276.2775589153</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="C12" s="23">
+        <v>-472991.79411006824</v>
+      </c>
+      <c r="D12" s="23">
+        <v>-737609.2692979143</v>
+      </c>
+      <c r="E12" s="23">
+        <v>-913344.6884718713</v>
+      </c>
+      <c r="F12" s="23">
+        <v>-1710396.3901163433</v>
+      </c>
+      <c r="G12" s="23">
+        <v>-4060672.6676752586</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="C13" s="31">
+        <v>-0.3059455330595525</v>
+      </c>
+      <c r="D13" s="31">
+        <v>-0.10427042130500674</v>
+      </c>
+      <c r="E13" s="31">
+        <v>-0.046066008479458874</v>
+      </c>
+      <c r="F13" s="31">
+        <v>-0.16504185604249857</v>
+      </c>
+      <c r="G13" s="31">
+        <v>-0.44816260261601254</v>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="C15" s="29" t="s">
+        <v>149</v>
+      </c>
+      <c r="D15" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="G15" s="29"/>
+    </row>
+    <row r="16" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="D16" s="34" t="s">
+        <v>154</v>
+      </c>
+      <c r="E16" s="34"/>
+      <c r="F16" s="35" t="s">
+        <v>155</v>
+      </c>
+      <c r="G16" s="35"/>
+    </row>
+    <row r="17" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="32" t="s">
+        <v>156</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="D17" s="34" t="s">
+        <v>157</v>
+      </c>
+      <c r="E17" s="34"/>
+      <c r="F17" s="35" t="s">
+        <v>158</v>
+      </c>
+      <c r="G17" s="35"/>
+    </row>
+    <row r="18" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="C18" s="36" t="s">
+        <v>160</v>
+      </c>
+      <c r="D18" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="E18" s="34"/>
+      <c r="F18" s="35" t="s">
+        <v>162</v>
+      </c>
+      <c r="G18" s="35"/>
+    </row>
+    <row r="19" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="C19" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="D19" s="34" t="s">
+        <v>164</v>
+      </c>
+      <c r="E19" s="34"/>
+      <c r="F19" s="35" t="s">
+        <v>165</v>
+      </c>
+      <c r="G19" s="35"/>
+    </row>
+    <row r="20" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="32" t="s">
+        <v>166</v>
+      </c>
+      <c r="C20" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="D20" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="E20" s="34"/>
+      <c r="F20" s="35" t="s">
+        <v>168</v>
+      </c>
+      <c r="G20" s="35"/>
+    </row>
+    <row r="21" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="C21" s="37" t="s">
+        <v>170</v>
+      </c>
+      <c r="D21" s="34" t="s">
+        <v>171</v>
+      </c>
+      <c r="E21" s="34"/>
+      <c r="F21" s="35" t="s">
+        <v>172</v>
+      </c>
+      <c r="G21" s="35"/>
+    </row>
+    <row r="22" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="32" t="s">
+        <v>173</v>
+      </c>
+      <c r="C22" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="D22" s="34" t="s">
+        <v>174</v>
+      </c>
+      <c r="E22" s="34"/>
+      <c r="F22" s="35" t="s">
+        <v>175</v>
+      </c>
+      <c r="G22" s="35"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="C26" s="38"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="38"/>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="B26:G26"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:B29"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B2" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B8" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B9" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B10" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B11" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B12" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B13" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B16" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B22" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFD97706"/>
@@ -1059,387 +1853,387 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B1" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
+      <c r="B1" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
+      <c r="B3" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C5" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="10" t="s">
+      <c r="C5" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C6" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>17</v>
+      <c r="C6" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C7" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>19</v>
+      <c r="C7" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C8" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="10">
+      <c r="C8" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="12">
         <v>2026</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
+      <c r="B10" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C12" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="11">
+      <c r="C12" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="13">
         <v>120</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C13" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="11">
+      <c r="C13" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="13">
         <v>200</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C14" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="11">
+      <c r="C14" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="13">
         <v>300</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C15" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="11">
+      <c r="C15" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="13">
         <v>375</v>
       </c>
     </row>
     <row r="16" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C16" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" s="11">
+      <c r="C16" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="13">
         <v>400</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
+      <c r="B18" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
     </row>
     <row r="20" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C20" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20" s="12">
+      <c r="C20" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C21" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" s="13">
+      <c r="C21" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="15">
         <v>0.03</v>
       </c>
     </row>
     <row r="22" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C22" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" s="12">
+      <c r="C22" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="14">
         <v>11500</v>
       </c>
     </row>
     <row r="23" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C23" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D23" s="13">
+      <c r="C23" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" s="15">
         <v>0.02</v>
       </c>
     </row>
     <row r="24" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C24" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" s="12">
+      <c r="C24" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" s="14">
         <v>300</v>
       </c>
     </row>
     <row r="25" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C25" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D25" s="13">
+      <c r="C25" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="15">
         <v>0.03</v>
       </c>
     </row>
     <row r="26" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C26" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D26" s="13">
+      <c r="C26" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" s="15">
         <v>0.95</v>
       </c>
     </row>
     <row r="27" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C27" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D27" s="12">
+      <c r="C27" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" s="14">
         <v>130000</v>
       </c>
     </row>
     <row r="28" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C28" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D28" s="13">
+      <c r="C28" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B30" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
+      <c r="B30" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
     </row>
     <row r="32" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C32" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D32" s="11">
+      <c r="C32" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D32" s="13">
         <v>12</v>
       </c>
     </row>
     <row r="33" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C33" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D33" s="12">
+      <c r="C33" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D33" s="14">
         <v>45667</v>
       </c>
     </row>
     <row r="34" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C34" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D34" s="13">
+      <c r="C34" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D34" s="15">
         <v>0.03</v>
       </c>
     </row>
     <row r="35" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C35" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D35" s="11">
+      <c r="C35" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D35" s="13">
         <v>7</v>
       </c>
     </row>
     <row r="36" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C36" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" s="11">
+      <c r="C36" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D36" s="13">
         <v>7</v>
       </c>
     </row>
     <row r="37" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C37" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" s="11">
+      <c r="C37" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D37" s="13">
         <v>7</v>
       </c>
     </row>
     <row r="38" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C38" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" s="11">
+      <c r="C38" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D38" s="13">
         <v>7</v>
       </c>
     </row>
     <row r="39" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C39" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" s="11">
+      <c r="C39" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" s="13">
         <v>7</v>
       </c>
     </row>
     <row r="40" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C40" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D40" s="12">
+      <c r="C40" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D40" s="14">
         <v>70000</v>
       </c>
     </row>
     <row r="41" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C41" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D41" s="13">
+      <c r="C41" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D41" s="15">
         <v>0.03</v>
       </c>
     </row>
     <row r="42" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C42" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="D42" s="13">
+      <c r="C42" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D42" s="15">
         <v>0.2677777777777778</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B44" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
+      <c r="B44" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C44" s="10"/>
+      <c r="D44" s="10"/>
     </row>
     <row r="46" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C46" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D46" s="12">
+      <c r="C46" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D46" s="14">
         <v>282000</v>
       </c>
     </row>
     <row r="47" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C47" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D47" s="13">
+      <c r="C47" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D47" s="15">
         <v>0.03</v>
       </c>
     </row>
     <row r="48" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C48" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D48" s="12">
+      <c r="C48" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D48" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C49" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="D49" s="13">
+      <c r="C49" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D49" s="15">
         <v>0.03</v>
       </c>
     </row>
     <row r="50" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C50" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D50" s="12">
+      <c r="C50" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D50" s="14">
         <v>700</v>
       </c>
     </row>
     <row r="51" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C51" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D51" s="13">
+      <c r="C51" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D51" s="15">
         <v>0.7166666666666667</v>
       </c>
     </row>
     <row r="52" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C52" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D52" s="12">
+      <c r="C52" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D52" s="14">
         <v>288000</v>
       </c>
     </row>
     <row r="53" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C53" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="D53" s="13">
+      <c r="C53" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D53" s="15">
         <v>0.5736111111111111</v>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B55" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
+      <c r="B55" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C55" s="10"/>
+      <c r="D55" s="10"/>
     </row>
     <row r="57" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C57" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="D57" s="12">
+      <c r="C57" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D57" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C58" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D58" s="12">
+      <c r="C58" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D58" s="14">
         <v>115000</v>
       </c>
     </row>
     <row r="59" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C59" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D59" s="12">
+      <c r="C59" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D59" s="14">
         <v>500000</v>
       </c>
     </row>
     <row r="60" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C60" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D60" s="13">
+      <c r="C60" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D60" s="15">
         <v>0.0575</v>
       </c>
     </row>
     <row r="61" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C61" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D61" s="11">
+      <c r="C61" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="D61" s="13">
         <v>15</v>
       </c>
     </row>
@@ -1461,7 +2255,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF0D9488"/>
@@ -1476,785 +2270,456 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
+      <c r="B1" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="14"/>
-      <c r="C3" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>69</v>
+      <c r="B3" s="16"/>
+      <c r="C3" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" s="17">
+      <c r="B4" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" s="19">
         <f>Assumptions!D12</f>
         <v>120</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="19">
         <f>Assumptions!D13</f>
         <v>200</v>
       </c>
-      <c r="E4" s="17">
+      <c r="E4" s="19">
         <f>Assumptions!D14</f>
         <v>300</v>
       </c>
-      <c r="F4" s="17">
+      <c r="F4" s="19">
         <f>Assumptions!D15</f>
         <v>375</v>
       </c>
-      <c r="G4" s="17">
+      <c r="G4" s="19">
         <f>Assumptions!D16</f>
         <v>400</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="C5" s="18" t="str">
+      <c r="B5" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" s="20" t="str">
         <f>Assumptions!D12*Assumptions!D20</f>
         <v>0</v>
       </c>
-      <c r="D5" s="18" t="str">
+      <c r="D5" s="20" t="str">
         <f>Assumptions!D13*Assumptions!D20*(1+Assumptions!D21)^1</f>
         <v>0</v>
       </c>
-      <c r="E5" s="18" t="str">
+      <c r="E5" s="20" t="str">
         <f>Assumptions!D14*Assumptions!D20*(1+Assumptions!D21)^2</f>
         <v>0</v>
       </c>
-      <c r="F5" s="18" t="str">
+      <c r="F5" s="20" t="str">
         <f>Assumptions!D15*Assumptions!D20*(1+Assumptions!D21)^3</f>
         <v>0</v>
       </c>
-      <c r="G5" s="18" t="str">
+      <c r="G5" s="20" t="str">
         <f>Assumptions!D16*Assumptions!D20*(1+Assumptions!D21)^4</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" s="18" t="str">
+      <c r="B6" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="20" t="str">
         <f>C5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="D6" s="18" t="str">
+      <c r="D6" s="20" t="str">
         <f>D5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="E6" s="18" t="str">
+      <c r="E6" s="20" t="str">
         <f>E5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="F6" s="18" t="str">
+      <c r="F6" s="20" t="str">
         <f>F5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="G6" s="18" t="str">
+      <c r="G6" s="20" t="str">
         <f>G5*Assumptions!D26</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" s="18">
+      <c r="B7" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="20">
         <f>Assumptions!D12*Assumptions!D22</f>
         <v>1380000</v>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="20">
         <f>Assumptions!D13*Assumptions!D22*(1+Assumptions!D23)^1</f>
         <v>2346000</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="20">
         <f>Assumptions!D14*Assumptions!D22*(1+Assumptions!D23)^2</f>
         <v>3589380</v>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="20">
         <f>Assumptions!D15*Assumptions!D22*(1+Assumptions!D23)^3</f>
         <v>4576459.5</v>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="20">
         <f>Assumptions!D16*Assumptions!D22*(1+Assumptions!D23)^4</f>
         <v>4979187.936</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" s="18">
+      <c r="B8" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="20">
         <f>Assumptions!D12*Assumptions!D24</f>
         <v>36000</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="20">
         <f>Assumptions!D13*Assumptions!D24*(1+Assumptions!D25)^1</f>
         <v>61800</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="20">
         <f>Assumptions!D14*Assumptions!D24*(1+Assumptions!D25)^2</f>
         <v>95481</v>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="20">
         <f>Assumptions!D15*Assumptions!D24*(1+Assumptions!D25)^3</f>
         <v>122931.7875</v>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="20">
         <f>Assumptions!D16*Assumptions!D24*(1+Assumptions!D25)^4</f>
         <v>135061.0572</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="C9" s="18">
+      <c r="B9" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="20">
         <f>Assumptions!D27</f>
         <v>130000</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="20">
         <f>Assumptions!D27*(1+Assumptions!D28)^1</f>
         <v>130000</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="20">
         <f>Assumptions!D27*(1+Assumptions!D28)^2</f>
         <v>130000</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="20">
         <f>Assumptions!D27*(1+Assumptions!D28)^3</f>
         <v>130000</v>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="20">
         <f>Assumptions!D27*(1+Assumptions!D28)^4</f>
         <v>130000</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="C10" s="20">
+      <c r="B10" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="22">
         <f>C6+C7+C8+C9</f>
         <v>1546000</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="22">
         <f>D6+D7+D8+D9</f>
         <v>2537800</v>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="22">
         <f>E6+E7+E8+E9</f>
         <v>3814861</v>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="22">
         <f>F6+F7+F8+F9</f>
         <v>4829391.2875</v>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="22">
         <f>G6+G7+G8+G9</f>
         <v>5244248.9932</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" s="17">
+      <c r="B12" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="C12" s="19">
         <f>CEILING(Assumptions!D12/Assumptions!D32,1)</f>
         <v>10</v>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="19">
         <f>CEILING(Assumptions!D13/Assumptions!D32,1)</f>
         <v>17</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="19">
         <f>CEILING(Assumptions!D14/Assumptions!D32,1)</f>
         <v>25</v>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="19">
         <f>CEILING(Assumptions!D15/Assumptions!D32,1)</f>
         <v>32</v>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="19">
         <f>CEILING(Assumptions!D16/Assumptions!D32,1)</f>
         <v>34</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" s="18">
+      <c r="B13" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="20">
         <f>C12*Assumptions!D33</f>
         <v>456670</v>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="20">
         <f>D12*Assumptions!D33*(1+Assumptions!D34)^1</f>
         <v>799629.17</v>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="20">
         <f>E12*Assumptions!D33*(1+Assumptions!D34)^2</f>
         <v>1211203.0075</v>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="20">
         <f>F12*Assumptions!D33*(1+Assumptions!D34)^3</f>
         <v>1596850.045088</v>
       </c>
-      <c r="G13" s="18">
+      <c r="G13" s="20">
         <f>G12*Assumptions!D33*(1+Assumptions!D34)^4</f>
         <v>1747552.76809318</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C14" s="18">
+      <c r="B14" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C14" s="20">
         <f>Assumptions!D35*Assumptions!D40</f>
         <v>490000</v>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="20">
         <f>Assumptions!D36*Assumptions!D40*(1+Assumptions!D41)^1</f>
         <v>504700</v>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="20">
         <f>Assumptions!D37*Assumptions!D40*(1+Assumptions!D41)^2</f>
         <v>519841</v>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="20">
         <f>Assumptions!D38*Assumptions!D40*(1+Assumptions!D41)^3</f>
         <v>535436.23</v>
       </c>
-      <c r="G14" s="18">
+      <c r="G14" s="20">
         <f>Assumptions!D39*Assumptions!D40*(1+Assumptions!D41)^4</f>
         <v>551499.3169</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="C15" s="18">
+      <c r="B15" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" s="20">
         <f>(C13+C14)*Assumptions!D42</f>
         <v>253497.18888889</v>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="20">
         <f>(D13+D14)*Assumptions!D42</f>
         <v>349270.36663333</v>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="20">
         <f>(E13+E14)*Assumptions!D42</f>
         <v>463535.11756389</v>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="20">
         <f>(F13+F14)*Assumptions!D42</f>
         <v>570978.88032912</v>
       </c>
-      <c r="G15" s="18">
+      <c r="G15" s="20">
         <f>(G13+G14)*Assumptions!D42</f>
         <v>615635.05831484</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="C16" s="20">
+      <c r="B16" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" s="22">
         <f>C13+C14+C15</f>
         <v>1200167.18888889</v>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="22">
         <f>D13+D14+D15</f>
         <v>1653599.53663333</v>
       </c>
-      <c r="E16" s="20">
+      <c r="E16" s="22">
         <f>E13+E14+E15</f>
         <v>2194579.12506389</v>
       </c>
-      <c r="F16" s="20">
+      <c r="F16" s="22">
         <f>F13+F14+F15</f>
         <v>2703265.15541712</v>
       </c>
-      <c r="G16" s="20">
+      <c r="G16" s="22">
         <f>G13+G14+G15</f>
         <v>2914687.14330802</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="C18" s="18">
+      <c r="B18" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" s="20">
         <f>Assumptions!D46</f>
         <v>282000</v>
       </c>
-      <c r="D18" s="18">
+      <c r="D18" s="20">
         <f>Assumptions!D46*(1+Assumptions!D47)^1</f>
         <v>290460</v>
       </c>
-      <c r="E18" s="18">
+      <c r="E18" s="20">
         <f>Assumptions!D46*(1+Assumptions!D47)^2</f>
         <v>299173.8</v>
       </c>
-      <c r="F18" s="18">
+      <c r="F18" s="20">
         <f>Assumptions!D46*(1+Assumptions!D47)^3</f>
         <v>308149.014</v>
       </c>
-      <c r="G18" s="18">
+      <c r="G18" s="20">
         <f>Assumptions!D46*(1+Assumptions!D47)^4</f>
         <v>317393.48442</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C19" s="18" t="str">
+      <c r="B19" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" s="20" t="str">
         <f>Assumptions!D48</f>
         <v>0</v>
       </c>
-      <c r="D19" s="18" t="str">
+      <c r="D19" s="20" t="str">
         <f>Assumptions!D48*(1+Assumptions!D49)^1</f>
         <v>0</v>
       </c>
-      <c r="E19" s="18" t="str">
+      <c r="E19" s="20" t="str">
         <f>Assumptions!D48*(1+Assumptions!D49)^2</f>
         <v>0</v>
       </c>
-      <c r="F19" s="18" t="str">
+      <c r="F19" s="20" t="str">
         <f>Assumptions!D48*(1+Assumptions!D49)^3</f>
         <v>0</v>
       </c>
-      <c r="G19" s="18" t="str">
+      <c r="G19" s="20" t="str">
         <f>Assumptions!D48*(1+Assumptions!D49)^4</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="C20" s="18">
+      <c r="B20" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C20" s="20">
         <f>Assumptions!D12*Assumptions!D50</f>
         <v>84000</v>
       </c>
-      <c r="D20" s="18">
+      <c r="D20" s="20">
         <f>Assumptions!D13*Assumptions!D50*(1+Assumptions!D51)^1</f>
         <v>240333.33333333</v>
       </c>
-      <c r="E20" s="18">
+      <c r="E20" s="20">
         <f>Assumptions!D14*Assumptions!D50*(1+Assumptions!D51)^2</f>
         <v>618858.33333333</v>
       </c>
-      <c r="F20" s="18">
+      <c r="F20" s="20">
         <f>Assumptions!D15*Assumptions!D50*(1+Assumptions!D51)^3</f>
         <v>1327966.84027778</v>
       </c>
-      <c r="G20" s="18">
+      <c r="G20" s="20">
         <f>Assumptions!D16*Assumptions!D50*(1+Assumptions!D51)^4</f>
         <v>2431654.83641975</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C21" s="18">
+      <c r="B21" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" s="20">
         <f>Assumptions!D52</f>
         <v>288000</v>
       </c>
-      <c r="D21" s="18">
+      <c r="D21" s="20">
         <f>Assumptions!D52*(1+Assumptions!D53)^1</f>
         <v>453200</v>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="20">
         <f>Assumptions!D52*(1+Assumptions!D53)^2</f>
         <v>713160.55555556</v>
       </c>
-      <c r="F21" s="18">
+      <c r="F21" s="20">
         <f>Assumptions!D52*(1+Assumptions!D53)^3</f>
         <v>1122237.3742284</v>
       </c>
-      <c r="G21" s="18">
+      <c r="G21" s="20">
         <f>Assumptions!D52*(1+Assumptions!D53)^4</f>
         <v>1765965.20138996</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="C22" s="20">
+      <c r="B22" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="C22" s="22">
         <f>C18+C19+C20+C21</f>
         <v>654000</v>
       </c>
-      <c r="D22" s="20">
+      <c r="D22" s="22">
         <f>D18+D19+D20+D21</f>
         <v>983993.33333333</v>
       </c>
-      <c r="E22" s="20">
+      <c r="E22" s="22">
         <f>E18+E19+E20+E21</f>
         <v>1631192.68888889</v>
       </c>
-      <c r="F22" s="20">
+      <c r="F22" s="22">
         <f>F18+F19+F20+F21</f>
         <v>2758353.22850617</v>
       </c>
-      <c r="G22" s="20">
+      <c r="G22" s="22">
         <f>G18+G19+G20+G21</f>
         <v>4515013.52222971</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
-  <headerFooter>
-    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor rgb="FF328555"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="B1:G17"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="7" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-    </row>
-    <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="14"/>
-      <c r="C3" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" s="17">
-        <f>Drivers!C4</f>
-        <v>120</v>
-      </c>
-      <c r="D5" s="17">
-        <f>Drivers!D4</f>
-        <v>200</v>
-      </c>
-      <c r="E5" s="17">
-        <f>Drivers!E4</f>
-        <v>300</v>
-      </c>
-      <c r="F5" s="17">
-        <f>Drivers!F4</f>
-        <v>375</v>
-      </c>
-      <c r="G5" s="17">
-        <f>Drivers!G4</f>
-        <v>400</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="18" t="str">
-        <f>Drivers!C6</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="18" t="str">
-        <f>Drivers!D6</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="18" t="str">
-        <f>Drivers!E6</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="18" t="str">
-        <f>Drivers!F6</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="18" t="str">
-        <f>Drivers!G6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="C7" s="18">
-        <f>Drivers!C7</f>
-        <v>1380000</v>
-      </c>
-      <c r="D7" s="18">
-        <f>Drivers!D7</f>
-        <v>2346000</v>
-      </c>
-      <c r="E7" s="18">
-        <f>Drivers!E7</f>
-        <v>3589380</v>
-      </c>
-      <c r="F7" s="18">
-        <f>Drivers!F7</f>
-        <v>4576459.5</v>
-      </c>
-      <c r="G7" s="18">
-        <f>Drivers!G7</f>
-        <v>4979187.936</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="C8" s="18">
-        <f>Drivers!C8</f>
-        <v>36000</v>
-      </c>
-      <c r="D8" s="18">
-        <f>Drivers!D8</f>
-        <v>61800</v>
-      </c>
-      <c r="E8" s="18">
-        <f>Drivers!E8</f>
-        <v>95481</v>
-      </c>
-      <c r="F8" s="18">
-        <f>Drivers!F8</f>
-        <v>122931.7875</v>
-      </c>
-      <c r="G8" s="18">
-        <f>Drivers!G8</f>
-        <v>135061.0572</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="C9" s="18">
-        <f>Drivers!C9</f>
-        <v>130000</v>
-      </c>
-      <c r="D9" s="18">
-        <f>Drivers!D9</f>
-        <v>130000</v>
-      </c>
-      <c r="E9" s="18">
-        <f>Drivers!E9</f>
-        <v>130000</v>
-      </c>
-      <c r="F9" s="18">
-        <f>Drivers!F9</f>
-        <v>130000</v>
-      </c>
-      <c r="G9" s="18">
-        <f>Drivers!G9</f>
-        <v>130000</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="C10" s="20">
-        <f>Drivers!C10</f>
-        <v>1546000</v>
-      </c>
-      <c r="D10" s="20">
-        <f>Drivers!D10</f>
-        <v>2537800</v>
-      </c>
-      <c r="E10" s="20">
-        <f>Drivers!E10</f>
-        <v>3814861</v>
-      </c>
-      <c r="F10" s="20">
-        <f>Drivers!F10</f>
-        <v>4829391.2875</v>
-      </c>
-      <c r="G10" s="20">
-        <f>Drivers!G10</f>
-        <v>5244248.9932</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="C12" s="18">
-        <f>Drivers!C16</f>
-        <v>1200167.18888889</v>
-      </c>
-      <c r="D12" s="18">
-        <f>Drivers!D16</f>
-        <v>1653599.53663333</v>
-      </c>
-      <c r="E12" s="18">
-        <f>Drivers!E16</f>
-        <v>2194579.12506389</v>
-      </c>
-      <c r="F12" s="18">
-        <f>Drivers!F16</f>
-        <v>2703265.15541712</v>
-      </c>
-      <c r="G12" s="18">
-        <f>Drivers!G16</f>
-        <v>2914687.14330802</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" s="18">
-        <f>Drivers!C22</f>
-        <v>654000</v>
-      </c>
-      <c r="D13" s="18">
-        <f>Drivers!D22</f>
-        <v>983993.33333333</v>
-      </c>
-      <c r="E13" s="18">
-        <f>Drivers!E22</f>
-        <v>1631192.68888889</v>
-      </c>
-      <c r="F13" s="18">
-        <f>Drivers!F22</f>
-        <v>2758353.22850617</v>
-      </c>
-      <c r="G13" s="18">
-        <f>Drivers!G22</f>
-        <v>4515013.52222971</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="C15" s="20">
-        <f>C12+C13</f>
-        <v>1854167.18888889</v>
-      </c>
-      <c r="D15" s="20">
-        <f>D12+D13</f>
-        <v>2637592.86996667</v>
-      </c>
-      <c r="E15" s="20">
-        <f>E12+E13</f>
-        <v>3825771.81395278</v>
-      </c>
-      <c r="F15" s="20">
-        <f>F12+F13</f>
-        <v>5461618.38392329</v>
-      </c>
-      <c r="G15" s="20">
-        <f>G12+G13</f>
-        <v>7429700.66553774</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="C16" s="21">
-        <f>C10-C15</f>
-        <v>-308167.18888889</v>
-      </c>
-      <c r="D16" s="21">
-        <f>D10-D15</f>
-        <v>-99792.86996667</v>
-      </c>
-      <c r="E16" s="21">
-        <f>E10-E15</f>
-        <v>-10910.81395278</v>
-      </c>
-      <c r="F16" s="21">
-        <f>F10-F15</f>
-        <v>-632227.09642329</v>
-      </c>
-      <c r="G16" s="21">
-        <f>G10-G15</f>
-        <v>-2185451.67233774</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="C17" s="22">
-        <f>IF(C10&gt;0,C16/C10,0)</f>
-        <v>-0.19933195</v>
-      </c>
-      <c r="D17" s="22">
-        <f>IF(D10&gt;0,D16/D10,0)</f>
-        <v>-0.03932259</v>
-      </c>
-      <c r="E17" s="22">
-        <f>IF(E10&gt;0,E16/E10,0)</f>
-        <v>-0.00286008</v>
-      </c>
-      <c r="F17" s="22">
-        <f>IF(F10&gt;0,F16/F10,0)</f>
-        <v>-0.13091238</v>
-      </c>
-      <c r="G17" s="22">
-        <f>IF(G10&gt;0,G16/G10,0)</f>
-        <v>-0.41673301</v>
       </c>
     </row>
   </sheetData>
@@ -2272,10 +2737,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FFD97706"/>
+    <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:G14"/>
+  <dimension ref="B1:G17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -2284,206 +2749,306 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="16"/>
+      <c r="C3" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" s="19">
+        <f>Drivers!C4</f>
+        <v>120</v>
+      </c>
+      <c r="D5" s="19">
+        <f>Drivers!D4</f>
+        <v>200</v>
+      </c>
+      <c r="E5" s="19">
+        <f>Drivers!E4</f>
+        <v>300</v>
+      </c>
+      <c r="F5" s="19">
+        <f>Drivers!F4</f>
+        <v>375</v>
+      </c>
+      <c r="G5" s="19">
+        <f>Drivers!G4</f>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-    </row>
-    <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="14"/>
-      <c r="C3" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="C4" s="18">
-        <f>'5-Year P&amp;L'!C16</f>
+      <c r="C6" s="20" t="str">
+        <f>Drivers!C6</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="20" t="str">
+        <f>Drivers!D6</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="20" t="str">
+        <f>Drivers!E6</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="20" t="str">
+        <f>Drivers!F6</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="20" t="str">
+        <f>Drivers!G6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" s="20">
+        <f>Drivers!C7</f>
+        <v>1380000</v>
+      </c>
+      <c r="D7" s="20">
+        <f>Drivers!D7</f>
+        <v>2346000</v>
+      </c>
+      <c r="E7" s="20">
+        <f>Drivers!E7</f>
+        <v>3589380</v>
+      </c>
+      <c r="F7" s="20">
+        <f>Drivers!F7</f>
+        <v>4576459.5</v>
+      </c>
+      <c r="G7" s="20">
+        <f>Drivers!G7</f>
+        <v>4979187.936</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" s="20">
+        <f>Drivers!C8</f>
+        <v>36000</v>
+      </c>
+      <c r="D8" s="20">
+        <f>Drivers!D8</f>
+        <v>61800</v>
+      </c>
+      <c r="E8" s="20">
+        <f>Drivers!E8</f>
+        <v>95481</v>
+      </c>
+      <c r="F8" s="20">
+        <f>Drivers!F8</f>
+        <v>122931.7875</v>
+      </c>
+      <c r="G8" s="20">
+        <f>Drivers!G8</f>
+        <v>135061.0572</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="20">
+        <f>Drivers!C9</f>
+        <v>130000</v>
+      </c>
+      <c r="D9" s="20">
+        <f>Drivers!D9</f>
+        <v>130000</v>
+      </c>
+      <c r="E9" s="20">
+        <f>Drivers!E9</f>
+        <v>130000</v>
+      </c>
+      <c r="F9" s="20">
+        <f>Drivers!F9</f>
+        <v>130000</v>
+      </c>
+      <c r="G9" s="20">
+        <f>Drivers!G9</f>
+        <v>130000</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="22">
+        <f>Drivers!C10</f>
+        <v>1546000</v>
+      </c>
+      <c r="D10" s="22">
+        <f>Drivers!D10</f>
+        <v>2537800</v>
+      </c>
+      <c r="E10" s="22">
+        <f>Drivers!E10</f>
+        <v>3814861</v>
+      </c>
+      <c r="F10" s="22">
+        <f>Drivers!F10</f>
+        <v>4829391.2875</v>
+      </c>
+      <c r="G10" s="22">
+        <f>Drivers!G10</f>
+        <v>5244248.9932</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="C12" s="20">
+        <f>Drivers!C16</f>
+        <v>1200167.18888889</v>
+      </c>
+      <c r="D12" s="20">
+        <f>Drivers!D16</f>
+        <v>1653599.53663333</v>
+      </c>
+      <c r="E12" s="20">
+        <f>Drivers!E16</f>
+        <v>2194579.12506389</v>
+      </c>
+      <c r="F12" s="20">
+        <f>Drivers!F16</f>
+        <v>2703265.15541712</v>
+      </c>
+      <c r="G12" s="20">
+        <f>Drivers!G16</f>
+        <v>2914687.14330802</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="C13" s="20">
+        <f>Drivers!C22</f>
+        <v>654000</v>
+      </c>
+      <c r="D13" s="20">
+        <f>Drivers!D22</f>
+        <v>983993.33333333</v>
+      </c>
+      <c r="E13" s="20">
+        <f>Drivers!E22</f>
+        <v>1631192.68888889</v>
+      </c>
+      <c r="F13" s="20">
+        <f>Drivers!F22</f>
+        <v>2758353.22850617</v>
+      </c>
+      <c r="G13" s="20">
+        <f>Drivers!G22</f>
+        <v>4515013.52222971</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="C15" s="22">
+        <f>C12+C13</f>
+        <v>1854167.18888889</v>
+      </c>
+      <c r="D15" s="22">
+        <f>D12+D13</f>
+        <v>2637592.86996667</v>
+      </c>
+      <c r="E15" s="22">
+        <f>E12+E13</f>
+        <v>3825771.81395278</v>
+      </c>
+      <c r="F15" s="22">
+        <f>F12+F13</f>
+        <v>5461618.38392329</v>
+      </c>
+      <c r="G15" s="22">
+        <f>G12+G13</f>
+        <v>7429700.66553774</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" s="23">
+        <f>C10-C15</f>
         <v>-308167.18888889</v>
       </c>
-      <c r="D4" s="18">
-        <f>'5-Year P&amp;L'!D16</f>
+      <c r="D16" s="23">
+        <f>D10-D15</f>
         <v>-99792.86996667</v>
       </c>
-      <c r="E4" s="18">
-        <f>'5-Year P&amp;L'!E16</f>
+      <c r="E16" s="23">
+        <f>E10-E15</f>
         <v>-10910.81395278</v>
       </c>
-      <c r="F4" s="18">
-        <f>'5-Year P&amp;L'!F16</f>
+      <c r="F16" s="23">
+        <f>F10-F15</f>
         <v>-632227.09642329</v>
       </c>
-      <c r="G4" s="18">
-        <f>'5-Year P&amp;L'!G16</f>
+      <c r="G16" s="23">
+        <f>G10-G15</f>
         <v>-2185451.67233774</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="C6" s="18">
-        <f>Assumptions!D58</f>
-        <v>115000</v>
-      </c>
-      <c r="D6" s="18">
-        <f>Assumptions!D58</f>
-        <v>115000</v>
-      </c>
-      <c r="E6" s="18">
-        <f>Assumptions!D58</f>
-        <v>115000</v>
-      </c>
-      <c r="F6" s="18">
-        <f>Assumptions!D58</f>
-        <v>115000</v>
-      </c>
-      <c r="G6" s="18">
-        <f>Assumptions!D58</f>
-        <v>115000</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="C7" s="18">
-        <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
-        <v>49824.60522118</v>
-      </c>
-      <c r="D7" s="18">
-        <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
-        <v>49824.60522118</v>
-      </c>
-      <c r="E7" s="18">
-        <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
-        <v>49824.60522118</v>
-      </c>
-      <c r="F7" s="18">
-        <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
-        <v>49824.60522118</v>
-      </c>
-      <c r="G7" s="18">
-        <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
-        <v>49824.60522118</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="C8" s="20">
-        <f>C6+C7</f>
-        <v>164824.60522118</v>
-      </c>
-      <c r="D8" s="20">
-        <f>D6+D7</f>
-        <v>164824.60522118</v>
-      </c>
-      <c r="E8" s="20">
-        <f>E6+E7</f>
-        <v>164824.60522118</v>
-      </c>
-      <c r="F8" s="20">
-        <f>F6+F7</f>
-        <v>164824.60522118</v>
-      </c>
-      <c r="G8" s="20">
-        <f>G6+G7</f>
-        <v>164824.60522118</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="C10" s="23">
-        <f>IF(C8&gt;0,C4/C8,IF(C4&gt;0,99.9,0))</f>
-        <v>-1.86966739</v>
-      </c>
-      <c r="D10" s="23">
-        <f>IF(D8&gt;0,D4/D8,IF(D4&gt;0,99.9,0))</f>
-        <v>-0.60544886</v>
-      </c>
-      <c r="E10" s="23">
-        <f>IF(E8&gt;0,E4/E8,IF(E4&gt;0,99.9,0))</f>
-        <v>-0.06619651</v>
-      </c>
-      <c r="F10" s="23">
-        <f>IF(F8&gt;0,F4/F8,IF(F4&gt;0,99.9,0))</f>
-        <v>-3.83575678</v>
-      </c>
-      <c r="G10" s="23">
-        <f>IF(G8&gt;0,G4/G8,IF(G4&gt;0,99.9,0))</f>
-        <v>-13.25925622</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="C12" s="18">
-        <f>C4-C8</f>
-        <v>-472991.79411007</v>
-      </c>
-      <c r="D12" s="18">
-        <f>D4-D8</f>
-        <v>-264617.47518785</v>
-      </c>
-      <c r="E12" s="18">
-        <f>E4-E8</f>
-        <v>-175735.41917396</v>
-      </c>
-      <c r="F12" s="18">
-        <f>F4-F8</f>
-        <v>-797051.70164447</v>
-      </c>
-      <c r="G12" s="18">
-        <f>G4-G8</f>
-        <v>-2350276.27755892</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="C14" s="24">
-        <f>Assumptions!D57+C12</f>
-        <v>-472991.79411007</v>
-      </c>
-      <c r="D14" s="24">
-        <f>C14+D12</f>
-        <v>-737609.26929791</v>
-      </c>
-      <c r="E14" s="24">
-        <f>D14+E12</f>
-        <v>-913344.68847187</v>
-      </c>
-      <c r="F14" s="24">
-        <f>E14+F12</f>
-        <v>-1710396.39011634</v>
-      </c>
-      <c r="G14" s="24">
-        <f>F14+G12</f>
-        <v>-4060672.66767526</v>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="C17" s="24">
+        <f>IF(C10&gt;0,C16/C10,0)</f>
+        <v>-0.19933195</v>
+      </c>
+      <c r="D17" s="24">
+        <f>IF(D10&gt;0,D16/D10,0)</f>
+        <v>-0.03932259</v>
+      </c>
+      <c r="E17" s="24">
+        <f>IF(E10&gt;0,E16/E10,0)</f>
+        <v>-0.00286008</v>
+      </c>
+      <c r="F17" s="24">
+        <f>IF(F10&gt;0,F16/F10,0)</f>
+        <v>-0.13091238</v>
+      </c>
+      <c r="G17" s="24">
+        <f>IF(G10&gt;0,G16/G10,0)</f>
+        <v>-0.41673301</v>
       </c>
     </row>
   </sheetData>
@@ -2501,10 +3066,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FF0D9488"/>
+    <tabColor rgb="FFD97706"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:G6"/>
+  <dimension ref="B1:G14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -2513,106 +3078,206 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
+      <c r="B1" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="14"/>
-      <c r="C3" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>69</v>
+      <c r="B3" s="16"/>
+      <c r="C3" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="C4" s="17">
-        <f>Drivers!C12</f>
-        <v>10</v>
-      </c>
-      <c r="D4" s="17">
-        <f>Drivers!D12</f>
-        <v>17</v>
-      </c>
-      <c r="E4" s="17">
-        <f>Drivers!E12</f>
-        <v>25</v>
-      </c>
-      <c r="F4" s="17">
-        <f>Drivers!F12</f>
-        <v>32</v>
-      </c>
-      <c r="G4" s="17">
-        <f>Drivers!G12</f>
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="C5" s="17">
-        <f>Assumptions!D35</f>
-        <v>7</v>
-      </c>
-      <c r="D5" s="17">
-        <f>Assumptions!D36</f>
-        <v>7</v>
-      </c>
-      <c r="E5" s="17">
-        <f>Assumptions!D37</f>
-        <v>7</v>
-      </c>
-      <c r="F5" s="17">
-        <f>Assumptions!D38</f>
-        <v>7</v>
-      </c>
-      <c r="G5" s="17">
-        <f>Assumptions!D39</f>
-        <v>7</v>
+      <c r="B4" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4" s="20">
+        <f>'5-Year P&amp;L'!C16</f>
+        <v>-308167.18888889</v>
+      </c>
+      <c r="D4" s="20">
+        <f>'5-Year P&amp;L'!D16</f>
+        <v>-99792.86996667</v>
+      </c>
+      <c r="E4" s="20">
+        <f>'5-Year P&amp;L'!E16</f>
+        <v>-10910.81395278</v>
+      </c>
+      <c r="F4" s="20">
+        <f>'5-Year P&amp;L'!F16</f>
+        <v>-632227.09642329</v>
+      </c>
+      <c r="G4" s="20">
+        <f>'5-Year P&amp;L'!G16</f>
+        <v>-2185451.67233774</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="C6" s="25">
-        <f>C4+C5</f>
-        <v>17</v>
-      </c>
-      <c r="D6" s="25">
-        <f>D4+D5</f>
-        <v>24</v>
-      </c>
-      <c r="E6" s="25">
-        <f>E4+E5</f>
-        <v>32</v>
-      </c>
-      <c r="F6" s="25">
-        <f>F4+F5</f>
-        <v>39</v>
-      </c>
-      <c r="G6" s="25">
-        <f>G4+G5</f>
-        <v>41</v>
+      <c r="B6" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" s="20">
+        <f>Assumptions!D58</f>
+        <v>115000</v>
+      </c>
+      <c r="D6" s="20">
+        <f>Assumptions!D58</f>
+        <v>115000</v>
+      </c>
+      <c r="E6" s="20">
+        <f>Assumptions!D58</f>
+        <v>115000</v>
+      </c>
+      <c r="F6" s="20">
+        <f>Assumptions!D58</f>
+        <v>115000</v>
+      </c>
+      <c r="G6" s="20">
+        <f>Assumptions!D58</f>
+        <v>115000</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" s="20">
+        <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
+        <v>49824.60522118</v>
+      </c>
+      <c r="D7" s="20">
+        <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
+        <v>49824.60522118</v>
+      </c>
+      <c r="E7" s="20">
+        <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
+        <v>49824.60522118</v>
+      </c>
+      <c r="F7" s="20">
+        <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
+        <v>49824.60522118</v>
+      </c>
+      <c r="G7" s="20">
+        <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
+        <v>49824.60522118</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8" s="22">
+        <f>C6+C7</f>
+        <v>164824.60522118</v>
+      </c>
+      <c r="D8" s="22">
+        <f>D6+D7</f>
+        <v>164824.60522118</v>
+      </c>
+      <c r="E8" s="22">
+        <f>E6+E7</f>
+        <v>164824.60522118</v>
+      </c>
+      <c r="F8" s="22">
+        <f>F6+F7</f>
+        <v>164824.60522118</v>
+      </c>
+      <c r="G8" s="22">
+        <f>G6+G7</f>
+        <v>164824.60522118</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" s="25">
+        <f>IF(C8&gt;0,C4/C8,IF(C4&gt;0,99.9,0))</f>
+        <v>-1.86966739</v>
+      </c>
+      <c r="D10" s="25">
+        <f>IF(D8&gt;0,D4/D8,IF(D4&gt;0,99.9,0))</f>
+        <v>-0.60544886</v>
+      </c>
+      <c r="E10" s="25">
+        <f>IF(E8&gt;0,E4/E8,IF(E4&gt;0,99.9,0))</f>
+        <v>-0.06619651</v>
+      </c>
+      <c r="F10" s="25">
+        <f>IF(F8&gt;0,F4/F8,IF(F4&gt;0,99.9,0))</f>
+        <v>-3.83575678</v>
+      </c>
+      <c r="G10" s="25">
+        <f>IF(G8&gt;0,G4/G8,IF(G4&gt;0,99.9,0))</f>
+        <v>-13.25925622</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="C12" s="20">
+        <f>C4-C8</f>
+        <v>-472991.79411007</v>
+      </c>
+      <c r="D12" s="20">
+        <f>D4-D8</f>
+        <v>-264617.47518785</v>
+      </c>
+      <c r="E12" s="20">
+        <f>E4-E8</f>
+        <v>-175735.41917396</v>
+      </c>
+      <c r="F12" s="20">
+        <f>F4-F8</f>
+        <v>-797051.70164447</v>
+      </c>
+      <c r="G12" s="20">
+        <f>G4-G8</f>
+        <v>-2350276.27755892</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="C14" s="26">
+        <f>Assumptions!D57+C12</f>
+        <v>-472991.79411007</v>
+      </c>
+      <c r="D14" s="26">
+        <f>C14+D12</f>
+        <v>-737609.26929791</v>
+      </c>
+      <c r="E14" s="26">
+        <f>D14+E12</f>
+        <v>-913344.68847187</v>
+      </c>
+      <c r="F14" s="26">
+        <f>E14+F12</f>
+        <v>-1710396.39011634</v>
+      </c>
+      <c r="G14" s="26">
+        <f>F14+G12</f>
+        <v>-4060672.66767526</v>
       </c>
     </row>
   </sheetData>
@@ -2630,6 +3295,135 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <tabColor rgb="FF0D9488"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:G6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="7" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B1" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="16"/>
+      <c r="C3" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" s="19">
+        <f>Drivers!C12</f>
+        <v>10</v>
+      </c>
+      <c r="D4" s="19">
+        <f>Drivers!D12</f>
+        <v>17</v>
+      </c>
+      <c r="E4" s="19">
+        <f>Drivers!E12</f>
+        <v>25</v>
+      </c>
+      <c r="F4" s="19">
+        <f>Drivers!F12</f>
+        <v>32</v>
+      </c>
+      <c r="G4" s="19">
+        <f>Drivers!G12</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="C5" s="19">
+        <f>Assumptions!D35</f>
+        <v>7</v>
+      </c>
+      <c r="D5" s="19">
+        <f>Assumptions!D36</f>
+        <v>7</v>
+      </c>
+      <c r="E5" s="19">
+        <f>Assumptions!D37</f>
+        <v>7</v>
+      </c>
+      <c r="F5" s="19">
+        <f>Assumptions!D38</f>
+        <v>7</v>
+      </c>
+      <c r="G5" s="19">
+        <f>Assumptions!D39</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="C6" s="27">
+        <f>C4+C5</f>
+        <v>17</v>
+      </c>
+      <c r="D6" s="27">
+        <f>D4+D5</f>
+        <v>24</v>
+      </c>
+      <c r="E6" s="27">
+        <f>E4+E5</f>
+        <v>32</v>
+      </c>
+      <c r="F6" s="27">
+        <f>F4+F5</f>
+        <v>39</v>
+      </c>
+      <c r="G6" s="27">
+        <f>G4+G5</f>
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
     <tabColor rgb="FFD97706"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2642,52 +3436,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C1" s="7"/>
+      <c r="B1" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="C1" s="9"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="C3" s="18">
+      <c r="B3" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="C3" s="20">
         <f>Assumptions!D59</f>
         <v>500000</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="C4" s="22">
+      <c r="B4" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" s="24">
         <f>Assumptions!D60</f>
         <v>0.0575</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="C5" s="17">
+      <c r="B5" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="19">
         <f>Assumptions!D61</f>
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="C6" s="26">
+      <c r="B6" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="C6" s="28">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>49824.60522118</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="C8" s="23">
+      <c r="B8" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="C8" s="25">
         <f>'Cash Flow &amp; DSCR'!C10</f>
         <v>-1.86966739</v>
       </c>
@@ -2704,7 +3498,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF328555"/>
@@ -2719,77 +3513,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C1" s="7"/>
+      <c r="B1" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1" s="9"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="16" t="str">
+      <c r="B3" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="18" t="str">
         <f>Assumptions!D5</f>
         <v>Civic Scholars Charter</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="16" t="str">
+      <c r="B4" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="18" t="str">
         <f>Assumptions!D7</f>
         <v>Charter School</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="16" t="str">
+      <c r="B5" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="18" t="str">
         <f>Assumptions!D6</f>
         <v>OH</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="C6" s="16">
+      <c r="B6" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="C6" s="18">
         <f>Assumptions!D8</f>
         <v>2026</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="17">
+      <c r="B8" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="19">
         <f>Assumptions!D16</f>
         <v>400</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="C9" s="18">
+      <c r="B9" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="C9" s="20">
         <f>Drivers!G10</f>
         <v>5244248.9932</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="C10" s="24">
+      <c r="B10" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="C10" s="26">
         <f>'5-Year P&amp;L'!G16</f>
         <v>-2185451.67233774</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="C12" s="6"/>
     </row>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="187">
   <si>
     <t>SCHOOLSTACK BUDGET</t>
   </si>
@@ -133,6 +133,9 @@
     <t>SchoolStack Budget - Lender Pro Forma Assumptions</t>
   </si>
   <si>
+    <t>Blue cells are editable inputs</t>
+  </si>
+  <si>
     <t>SCHOOL PROFILE</t>
   </si>
   <si>
@@ -464,6 +467,30 @@
   </si>
   <si>
     <t>Net Margin</t>
+  </si>
+  <si>
+    <t>Revenue per Student</t>
+  </si>
+  <si>
+    <t>Payroll %</t>
+  </si>
+  <si>
+    <t>Facility %</t>
+  </si>
+  <si>
+    <t>DSCR</t>
+  </si>
+  <si>
+    <t>Break-even Year</t>
+  </si>
+  <si>
+    <t>Not reached</t>
+  </si>
+  <si>
+    <t>Cash Runway</t>
+  </si>
+  <si>
+    <t>0 months</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -566,7 +593,7 @@
     <numFmt numFmtId="166" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -620,6 +647,12 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <i/>
+      <color rgb="FF666666"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
@@ -631,7 +664,7 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="FF1E293B"/>
+      <color rgb="FF1E3A5F"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -665,7 +698,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -674,12 +707,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1E293B"/>
+        <fgColor rgb="FFDBEAFE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFDE8"/>
+        <fgColor rgb="FF1E293B"/>
       </patternFill>
     </fill>
     <fill>
@@ -690,6 +723,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE8EDF2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF8E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -753,7 +796,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -764,24 +807,26 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -791,37 +836,47 @@
     <xf numFmtId="165" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="166" fontId="13" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -830,13 +885,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1293,7 +1348,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:G26"/>
+  <dimension ref="B2:G33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1304,7 +1359,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -1323,355 +1378,481 @@
       <c r="G3" s="6"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="C5" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="D5" s="30" t="s">
+      <c r="B5" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="C5" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="D5" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="F5" s="30" t="s">
+      <c r="E5" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="G5" s="30" t="s">
+      <c r="F5" s="32" t="s">
         <v>92</v>
       </c>
+      <c r="G5" s="32" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="C6" s="19">
+      <c r="B6" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="21">
         <v>120</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="21">
         <v>200</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="21">
         <v>300</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="21">
         <v>375</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="21">
         <v>400</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="C7" s="20">
+      <c r="B7" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="C7" s="22">
         <v>1546000</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="22">
         <v>2537800</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="22">
         <v>3814861</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="22">
         <v>4829391.287500001</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="22">
         <v>5244248.993199999</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="C8" s="20">
+      <c r="B8" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8" s="22">
         <v>1200167.1888888888</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="22">
         <v>1653599.5366333332</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="22">
         <v>2194579.1250638887</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="22">
         <v>2703265.15541712</v>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="22">
         <v>2914687.143308021</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="C9" s="20">
+      <c r="B9" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="C9" s="22">
         <v>654000</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="22">
         <v>983993.3333333334</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="22">
         <v>1631192.688888889</v>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="22">
         <v>2758353.228506173</v>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="22">
         <v>4515013.522229714</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="C10" s="20">
+      <c r="B10" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="C10" s="22">
         <v>164824.60522117943</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="22">
         <v>164824.60522117943</v>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="22">
         <v>164824.60522117943</v>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="22">
         <v>164824.60522117943</v>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="22">
         <v>164824.60522117943</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="C11" s="23">
+      <c r="B11" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="C11" s="25">
         <v>-472991.79411006824</v>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="25">
         <v>-264617.4751878461</v>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="25">
         <v>-175735.41917395697</v>
       </c>
-      <c r="F11" s="23">
+      <c r="F11" s="25">
         <v>-797051.701644472</v>
       </c>
-      <c r="G11" s="23">
+      <c r="G11" s="25">
         <v>-2350276.2775589153</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="C12" s="23">
+      <c r="B12" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="C12" s="25">
         <v>-472991.79411006824</v>
       </c>
-      <c r="D12" s="23">
+      <c r="D12" s="25">
         <v>-737609.2692979143</v>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="25">
         <v>-913344.6884718713</v>
       </c>
-      <c r="F12" s="23">
+      <c r="F12" s="25">
         <v>-1710396.3901163433</v>
       </c>
-      <c r="G12" s="23">
+      <c r="G12" s="25">
         <v>-4060672.6676752586</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="C13" s="31">
+      <c r="B13" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="C13" s="33">
         <v>-0.3059455330595525</v>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="33">
         <v>-0.10427042130500674</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="33">
         <v>-0.046066008479458874</v>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="33">
         <v>-0.16504185604249857</v>
       </c>
-      <c r="G13" s="31">
+      <c r="G13" s="33">
         <v>-0.44816260261601254</v>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="29" t="s">
-        <v>148</v>
-      </c>
-      <c r="C15" s="29" t="s">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="23" t="s">
         <v>149</v>
       </c>
-      <c r="D15" s="29" t="s">
+      <c r="C14" s="22">
+        <v>12883.333333333334</v>
+      </c>
+      <c r="D14" s="22">
+        <v>12689</v>
+      </c>
+      <c r="E14" s="22">
+        <v>12716.203333333333</v>
+      </c>
+      <c r="F14" s="22">
+        <v>12878.376766666668</v>
+      </c>
+      <c r="G14" s="22">
+        <v>13110.622483</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="23" t="s">
         <v>150</v>
       </c>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29" t="s">
+      <c r="C15" s="33">
+        <v>0.7763047793589191</v>
+      </c>
+      <c r="D15" s="33">
+        <v>0.6515878070113221</v>
+      </c>
+      <c r="E15" s="34">
+        <v>0.5752710583855843</v>
+      </c>
+      <c r="F15" s="34">
+        <v>0.5597527709991174</v>
+      </c>
+      <c r="G15" s="34">
+        <v>0.5557873295275215</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="23" t="s">
         <v>151</v>
       </c>
-      <c r="G15" s="29"/>
-    </row>
-    <row r="16" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="32" t="s">
+      <c r="C16" s="35">
+        <v>0.12690815006468306</v>
+      </c>
+      <c r="D16" s="35">
+        <v>0.1163204350224604</v>
+      </c>
+      <c r="E16" s="35">
+        <v>0.1282767069800621</v>
+      </c>
+      <c r="F16" s="34">
+        <v>0.1713478820185269</v>
+      </c>
+      <c r="G16" s="33">
+        <v>0.25828370438269493</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="C17" s="33">
+        <v>-0.19933194624119585</v>
+      </c>
+      <c r="D17" s="33">
+        <v>-0.039322590419523434</v>
+      </c>
+      <c r="E17" s="33">
+        <v>-0.0028600816524580494</v>
+      </c>
+      <c r="F17" s="33">
+        <v>-0.13091237772754036</v>
+      </c>
+      <c r="G17" s="33">
+        <v>-0.4167330108031714</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="23" t="s">
         <v>152</v>
       </c>
-      <c r="C16" s="33" t="s">
+      <c r="C18" s="36">
+        <v>-1.8696673865856184</v>
+      </c>
+      <c r="D18" s="36">
+        <v>-0.6054488638559378</v>
+      </c>
+      <c r="E18" s="36">
+        <v>-0.06619651197184098</v>
+      </c>
+      <c r="F18" s="36">
+        <v>-3.8357567765741165</v>
+      </c>
+      <c r="G18" s="36">
+        <v>-13.259256222122064</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="23" t="s">
         <v>153</v>
       </c>
-      <c r="D16" s="34" t="s">
+      <c r="C19" s="37" t="s">
         <v>154</v>
       </c>
-      <c r="E16" s="34"/>
-      <c r="F16" s="35" t="s">
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="37"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="23" t="s">
         <v>155</v>
       </c>
-      <c r="G16" s="35"/>
-    </row>
-    <row r="17" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="32" t="s">
+      <c r="C20" s="37" t="s">
         <v>156</v>
       </c>
-      <c r="C17" s="33" t="s">
-        <v>153</v>
-      </c>
-      <c r="D17" s="34" t="s">
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="37"/>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="31" t="s">
         <v>157</v>
       </c>
-      <c r="E17" s="34"/>
-      <c r="F17" s="35" t="s">
+      <c r="C22" s="31" t="s">
         <v>158</v>
       </c>
-      <c r="G17" s="35"/>
-    </row>
-    <row r="18" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="32" t="s">
+      <c r="D22" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="C18" s="36" t="s">
+      <c r="E22" s="31"/>
+      <c r="F22" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="D18" s="34" t="s">
+      <c r="G22" s="31"/>
+    </row>
+    <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="38" t="s">
         <v>161</v>
       </c>
-      <c r="E18" s="34"/>
-      <c r="F18" s="35" t="s">
+      <c r="C23" s="39" t="s">
         <v>162</v>
       </c>
-      <c r="G18" s="35"/>
-    </row>
-    <row r="19" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="32" t="s">
+      <c r="D23" s="40" t="s">
         <v>163</v>
       </c>
-      <c r="C19" s="33" t="s">
-        <v>153</v>
-      </c>
-      <c r="D19" s="34" t="s">
+      <c r="E23" s="40"/>
+      <c r="F23" s="41" t="s">
         <v>164</v>
       </c>
-      <c r="E19" s="34"/>
-      <c r="F19" s="35" t="s">
+      <c r="G23" s="41"/>
+    </row>
+    <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="38" t="s">
         <v>165</v>
       </c>
-      <c r="G19" s="35"/>
-    </row>
-    <row r="20" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="32" t="s">
+      <c r="C24" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="D24" s="40" t="s">
         <v>166</v>
       </c>
-      <c r="C20" s="33" t="s">
-        <v>153</v>
-      </c>
-      <c r="D20" s="34" t="s">
+      <c r="E24" s="40"/>
+      <c r="F24" s="41" t="s">
         <v>167</v>
       </c>
-      <c r="E20" s="34"/>
-      <c r="F20" s="35" t="s">
+      <c r="G24" s="41"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="38" t="s">
         <v>168</v>
       </c>
-      <c r="G20" s="35"/>
-    </row>
-    <row r="21" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="32" t="s">
+      <c r="C25" s="42" t="s">
         <v>169</v>
       </c>
-      <c r="C21" s="37" t="s">
+      <c r="D25" s="40" t="s">
         <v>170</v>
       </c>
-      <c r="D21" s="34" t="s">
+      <c r="E25" s="40"/>
+      <c r="F25" s="41" t="s">
         <v>171</v>
       </c>
-      <c r="E21" s="34"/>
-      <c r="F21" s="35" t="s">
+      <c r="G25" s="41"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="G21" s="35"/>
-    </row>
-    <row r="22" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="32" t="s">
+      <c r="C26" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="D26" s="40" t="s">
         <v>173</v>
       </c>
-      <c r="C22" s="33" t="s">
-        <v>153</v>
-      </c>
-      <c r="D22" s="34" t="s">
+      <c r="E26" s="40"/>
+      <c r="F26" s="41" t="s">
         <v>174</v>
       </c>
-      <c r="E22" s="34"/>
-      <c r="F22" s="35" t="s">
+      <c r="G26" s="41"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="38" t="s">
         <v>175</v>
       </c>
-      <c r="G22" s="35"/>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B24" s="32" t="s">
+      <c r="C27" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="D27" s="40" t="s">
+        <v>176</v>
+      </c>
+      <c r="E27" s="40"/>
+      <c r="F27" s="41" t="s">
+        <v>177</v>
+      </c>
+      <c r="G27" s="41"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="38" t="s">
+        <v>178</v>
+      </c>
+      <c r="C28" s="43" t="s">
+        <v>179</v>
+      </c>
+      <c r="D28" s="40" t="s">
+        <v>180</v>
+      </c>
+      <c r="E28" s="40"/>
+      <c r="F28" s="41" t="s">
+        <v>181</v>
+      </c>
+      <c r="G28" s="41"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="38" t="s">
+        <v>182</v>
+      </c>
+      <c r="C29" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="D29" s="40" t="s">
+        <v>183</v>
+      </c>
+      <c r="E29" s="40"/>
+      <c r="F29" s="41" t="s">
+        <v>184</v>
+      </c>
+      <c r="G29" s="41"/>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B31" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="38" t="s">
-        <v>177</v>
-      </c>
-      <c r="C26" s="38"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="38"/>
+      <c r="C31" s="23" t="s">
+        <v>185</v>
+      </c>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B33" s="44" t="s">
+        <v>186</v>
+      </c>
+      <c r="C33" s="44"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="44"/>
+      <c r="F33" s="44"/>
+      <c r="G33" s="44"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="22">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B3:G3"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C20:G20"/>
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="F22:G22"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="B33:G33"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -1859,381 +2040,389 @@
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
     </row>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
     <row r="3" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
+      <c r="B3" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C5" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="12" t="s">
+      <c r="C5" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="14" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C6" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="12" t="s">
+      <c r="C6" s="13" t="s">
         <v>40</v>
       </c>
+      <c r="D6" s="14" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C7" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="12" t="s">
+      <c r="C7" s="13" t="s">
         <v>42</v>
       </c>
+      <c r="D7" s="14" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C8" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="12">
+      <c r="C8" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="14">
         <v>2026</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
+      <c r="B10" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C12" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="13">
+      <c r="C12" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="15">
         <v>120</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C13" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" s="13">
+      <c r="C13" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="15">
         <v>200</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C14" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="13">
+      <c r="C14" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="15">
         <v>300</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C15" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" s="13">
+      <c r="C15" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="15">
         <v>375</v>
       </c>
     </row>
     <row r="16" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C16" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" s="13">
+      <c r="C16" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="15">
         <v>400</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
+      <c r="B18" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
     </row>
     <row r="20" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C20" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D20" s="14">
+      <c r="C20" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C21" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" s="15">
+      <c r="C21" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="17">
         <v>0.03</v>
       </c>
     </row>
     <row r="22" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C22" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="D22" s="14">
+      <c r="C22" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="16">
         <v>11500</v>
       </c>
     </row>
     <row r="23" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C23" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="D23" s="15">
+      <c r="C23" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="17">
         <v>0.02</v>
       </c>
     </row>
     <row r="24" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C24" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="D24" s="14">
+      <c r="C24" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="16">
         <v>300</v>
       </c>
     </row>
     <row r="25" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C25" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D25" s="15">
+      <c r="C25" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" s="17">
         <v>0.03</v>
       </c>
     </row>
     <row r="26" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C26" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="D26" s="15">
+      <c r="C26" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" s="17">
         <v>0.95</v>
       </c>
     </row>
     <row r="27" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C27" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="D27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" s="16">
         <v>130000</v>
       </c>
     </row>
     <row r="28" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C28" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="D28" s="15">
+      <c r="C28" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D28" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B30" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
+      <c r="B30" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
     </row>
     <row r="32" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C32" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="D32" s="13">
+      <c r="C32" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32" s="15">
         <v>12</v>
       </c>
     </row>
     <row r="33" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C33" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="D33" s="14">
+      <c r="C33" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D33" s="16">
         <v>45667</v>
       </c>
     </row>
     <row r="34" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C34" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="D34" s="15">
+      <c r="C34" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D34" s="17">
         <v>0.03</v>
       </c>
     </row>
     <row r="35" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C35" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D35" s="13">
+      <c r="C35" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D35" s="15">
         <v>7</v>
       </c>
     </row>
     <row r="36" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C36" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D36" s="13">
+      <c r="C36" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D36" s="15">
         <v>7</v>
       </c>
     </row>
     <row r="37" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C37" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D37" s="13">
+      <c r="C37" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D37" s="15">
         <v>7</v>
       </c>
     </row>
     <row r="38" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C38" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="D38" s="13">
+      <c r="C38" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D38" s="15">
         <v>7</v>
       </c>
     </row>
     <row r="39" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C39" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="D39" s="13">
+      <c r="C39" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D39" s="15">
         <v>7</v>
       </c>
     </row>
     <row r="40" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C40" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="D40" s="14">
+      <c r="C40" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D40" s="16">
         <v>70000</v>
       </c>
     </row>
     <row r="41" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C41" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D41" s="15">
+      <c r="C41" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D41" s="17">
         <v>0.03</v>
       </c>
     </row>
     <row r="42" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C42" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="D42" s="15">
+      <c r="C42" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D42" s="17">
         <v>0.2677777777777778</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B44" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C44" s="10"/>
-      <c r="D44" s="10"/>
+      <c r="B44" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
     </row>
     <row r="46" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C46" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="D46" s="14">
+      <c r="C46" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D46" s="16">
         <v>282000</v>
       </c>
     </row>
     <row r="47" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C47" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="D47" s="15">
+      <c r="C47" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D47" s="17">
         <v>0.03</v>
       </c>
     </row>
     <row r="48" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C48" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="D48" s="14">
+      <c r="C48" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D48" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C49" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="D49" s="15">
+      <c r="C49" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D49" s="17">
         <v>0.03</v>
       </c>
     </row>
     <row r="50" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C50" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="D50" s="14">
+      <c r="C50" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="D50" s="16">
         <v>700</v>
       </c>
     </row>
     <row r="51" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C51" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="D51" s="15">
+      <c r="C51" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="D51" s="17">
         <v>0.7166666666666667</v>
       </c>
     </row>
     <row r="52" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C52" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D52" s="14">
+      <c r="C52" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D52" s="16">
         <v>288000</v>
       </c>
     </row>
     <row r="53" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C53" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D53" s="15">
+      <c r="C53" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D53" s="17">
         <v>0.5736111111111111</v>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B55" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C55" s="10"/>
-      <c r="D55" s="10"/>
+      <c r="B55" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C55" s="12"/>
+      <c r="D55" s="12"/>
     </row>
     <row r="57" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C57" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D57" s="14">
+      <c r="C57" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="D57" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C58" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D58" s="14">
+      <c r="C58" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D58" s="16">
         <v>115000</v>
       </c>
     </row>
     <row r="59" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C59" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D59" s="14">
+      <c r="C59" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="D59" s="16">
         <v>500000</v>
       </c>
     </row>
     <row r="60" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C60" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="D60" s="15">
+      <c r="C60" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D60" s="17">
         <v>0.0575</v>
       </c>
     </row>
     <row r="61" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C61" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="D61" s="13">
+      <c r="C61" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D61" s="15">
         <v>15</v>
       </c>
     </row>
@@ -2271,7 +2460,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -2280,444 +2469,444 @@
       <c r="G1" s="9"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="16"/>
-      <c r="C3" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="D3" s="17" t="s">
+      <c r="B3" s="18"/>
+      <c r="C3" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="D3" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="E3" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="F3" s="19" t="s">
         <v>92</v>
       </c>
+      <c r="G3" s="19" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="C4" s="19">
+      <c r="B4" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="21">
         <f>Assumptions!D12</f>
         <v>120</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="21">
         <f>Assumptions!D13</f>
         <v>200</v>
       </c>
-      <c r="E4" s="19">
+      <c r="E4" s="21">
         <f>Assumptions!D14</f>
         <v>300</v>
       </c>
-      <c r="F4" s="19">
+      <c r="F4" s="21">
         <f>Assumptions!D15</f>
         <v>375</v>
       </c>
-      <c r="G4" s="19">
+      <c r="G4" s="21">
         <f>Assumptions!D16</f>
         <v>400</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="C5" s="20" t="str">
+      <c r="B5" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" s="22" t="str">
         <f>Assumptions!D12*Assumptions!D20</f>
         <v>0</v>
       </c>
-      <c r="D5" s="20" t="str">
+      <c r="D5" s="22" t="str">
         <f>Assumptions!D13*Assumptions!D20*(1+Assumptions!D21)^1</f>
         <v>0</v>
       </c>
-      <c r="E5" s="20" t="str">
+      <c r="E5" s="22" t="str">
         <f>Assumptions!D14*Assumptions!D20*(1+Assumptions!D21)^2</f>
         <v>0</v>
       </c>
-      <c r="F5" s="20" t="str">
+      <c r="F5" s="22" t="str">
         <f>Assumptions!D15*Assumptions!D20*(1+Assumptions!D21)^3</f>
         <v>0</v>
       </c>
-      <c r="G5" s="20" t="str">
+      <c r="G5" s="22" t="str">
         <f>Assumptions!D16*Assumptions!D20*(1+Assumptions!D21)^4</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="C6" s="20" t="str">
+      <c r="B6" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="C6" s="22" t="str">
         <f>C5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="D6" s="20" t="str">
+      <c r="D6" s="22" t="str">
         <f>D5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="E6" s="20" t="str">
+      <c r="E6" s="22" t="str">
         <f>E5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="F6" s="20" t="str">
+      <c r="F6" s="22" t="str">
         <f>F5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="G6" s="20" t="str">
+      <c r="G6" s="22" t="str">
         <f>G5*Assumptions!D26</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="C7" s="20">
+      <c r="B7" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" s="22">
         <f>Assumptions!D12*Assumptions!D22</f>
         <v>1380000</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="22">
         <f>Assumptions!D13*Assumptions!D22*(1+Assumptions!D23)^1</f>
         <v>2346000</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="22">
         <f>Assumptions!D14*Assumptions!D22*(1+Assumptions!D23)^2</f>
         <v>3589380</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="22">
         <f>Assumptions!D15*Assumptions!D22*(1+Assumptions!D23)^3</f>
         <v>4576459.5</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="22">
         <f>Assumptions!D16*Assumptions!D22*(1+Assumptions!D23)^4</f>
         <v>4979187.936</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="C8" s="20">
+      <c r="B8" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="22">
         <f>Assumptions!D12*Assumptions!D24</f>
         <v>36000</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="22">
         <f>Assumptions!D13*Assumptions!D24*(1+Assumptions!D25)^1</f>
         <v>61800</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="22">
         <f>Assumptions!D14*Assumptions!D24*(1+Assumptions!D25)^2</f>
         <v>95481</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="22">
         <f>Assumptions!D15*Assumptions!D24*(1+Assumptions!D25)^3</f>
         <v>122931.7875</v>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="22">
         <f>Assumptions!D16*Assumptions!D24*(1+Assumptions!D25)^4</f>
         <v>135061.0572</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="C9" s="20">
+      <c r="B9" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="22">
         <f>Assumptions!D27</f>
         <v>130000</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="22">
         <f>Assumptions!D27*(1+Assumptions!D28)^1</f>
         <v>130000</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="22">
         <f>Assumptions!D27*(1+Assumptions!D28)^2</f>
         <v>130000</v>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="22">
         <f>Assumptions!D27*(1+Assumptions!D28)^3</f>
         <v>130000</v>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="22">
         <f>Assumptions!D27*(1+Assumptions!D28)^4</f>
         <v>130000</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="C10" s="22">
+      <c r="B10" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="24">
         <f>C6+C7+C8+C9</f>
         <v>1546000</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="24">
         <f>D6+D7+D8+D9</f>
         <v>2537800</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="24">
         <f>E6+E7+E8+E9</f>
         <v>3814861</v>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="24">
         <f>F6+F7+F8+F9</f>
         <v>4829391.2875</v>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="24">
         <f>G6+G7+G8+G9</f>
         <v>5244248.9932</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="C12" s="19">
+      <c r="B12" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" s="21">
         <f>CEILING(Assumptions!D12/Assumptions!D32,1)</f>
         <v>10</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="21">
         <f>CEILING(Assumptions!D13/Assumptions!D32,1)</f>
         <v>17</v>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="21">
         <f>CEILING(Assumptions!D14/Assumptions!D32,1)</f>
         <v>25</v>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="21">
         <f>CEILING(Assumptions!D15/Assumptions!D32,1)</f>
         <v>32</v>
       </c>
-      <c r="G12" s="19">
+      <c r="G12" s="21">
         <f>CEILING(Assumptions!D16/Assumptions!D32,1)</f>
         <v>34</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="C13" s="20">
+      <c r="B13" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="C13" s="22">
         <f>C12*Assumptions!D33</f>
         <v>456670</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="22">
         <f>D12*Assumptions!D33*(1+Assumptions!D34)^1</f>
         <v>799629.17</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="22">
         <f>E12*Assumptions!D33*(1+Assumptions!D34)^2</f>
         <v>1211203.0075</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="22">
         <f>F12*Assumptions!D33*(1+Assumptions!D34)^3</f>
         <v>1596850.045088</v>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="22">
         <f>G12*Assumptions!D33*(1+Assumptions!D34)^4</f>
         <v>1747552.76809318</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="C14" s="20">
+      <c r="B14" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="C14" s="22">
         <f>Assumptions!D35*Assumptions!D40</f>
         <v>490000</v>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="22">
         <f>Assumptions!D36*Assumptions!D40*(1+Assumptions!D41)^1</f>
         <v>504700</v>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="22">
         <f>Assumptions!D37*Assumptions!D40*(1+Assumptions!D41)^2</f>
         <v>519841</v>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="22">
         <f>Assumptions!D38*Assumptions!D40*(1+Assumptions!D41)^3</f>
         <v>535436.23</v>
       </c>
-      <c r="G14" s="20">
+      <c r="G14" s="22">
         <f>Assumptions!D39*Assumptions!D40*(1+Assumptions!D41)^4</f>
         <v>551499.3169</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="C15" s="20">
+      <c r="B15" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" s="22">
         <f>(C13+C14)*Assumptions!D42</f>
         <v>253497.18888889</v>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="22">
         <f>(D13+D14)*Assumptions!D42</f>
         <v>349270.36663333</v>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="22">
         <f>(E13+E14)*Assumptions!D42</f>
         <v>463535.11756389</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="22">
         <f>(F13+F14)*Assumptions!D42</f>
         <v>570978.88032912</v>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="22">
         <f>(G13+G14)*Assumptions!D42</f>
         <v>615635.05831484</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="C16" s="22">
+      <c r="B16" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" s="24">
         <f>C13+C14+C15</f>
         <v>1200167.18888889</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="24">
         <f>D13+D14+D15</f>
         <v>1653599.53663333</v>
       </c>
-      <c r="E16" s="22">
+      <c r="E16" s="24">
         <f>E13+E14+E15</f>
         <v>2194579.12506389</v>
       </c>
-      <c r="F16" s="22">
+      <c r="F16" s="24">
         <f>F13+F14+F15</f>
         <v>2703265.15541712</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="24">
         <f>G13+G14+G15</f>
         <v>2914687.14330802</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="C18" s="20">
+      <c r="B18" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="C18" s="22">
         <f>Assumptions!D46</f>
         <v>282000</v>
       </c>
-      <c r="D18" s="20">
+      <c r="D18" s="22">
         <f>Assumptions!D46*(1+Assumptions!D47)^1</f>
         <v>290460</v>
       </c>
-      <c r="E18" s="20">
+      <c r="E18" s="22">
         <f>Assumptions!D46*(1+Assumptions!D47)^2</f>
         <v>299173.8</v>
       </c>
-      <c r="F18" s="20">
+      <c r="F18" s="22">
         <f>Assumptions!D46*(1+Assumptions!D47)^3</f>
         <v>308149.014</v>
       </c>
-      <c r="G18" s="20">
+      <c r="G18" s="22">
         <f>Assumptions!D46*(1+Assumptions!D47)^4</f>
         <v>317393.48442</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="C19" s="20" t="str">
+      <c r="B19" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="C19" s="22" t="str">
         <f>Assumptions!D48</f>
         <v>0</v>
       </c>
-      <c r="D19" s="20" t="str">
+      <c r="D19" s="22" t="str">
         <f>Assumptions!D48*(1+Assumptions!D49)^1</f>
         <v>0</v>
       </c>
-      <c r="E19" s="20" t="str">
+      <c r="E19" s="22" t="str">
         <f>Assumptions!D48*(1+Assumptions!D49)^2</f>
         <v>0</v>
       </c>
-      <c r="F19" s="20" t="str">
+      <c r="F19" s="22" t="str">
         <f>Assumptions!D48*(1+Assumptions!D49)^3</f>
         <v>0</v>
       </c>
-      <c r="G19" s="20" t="str">
+      <c r="G19" s="22" t="str">
         <f>Assumptions!D48*(1+Assumptions!D49)^4</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="C20" s="20">
+      <c r="B20" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" s="22">
         <f>Assumptions!D12*Assumptions!D50</f>
         <v>84000</v>
       </c>
-      <c r="D20" s="20">
+      <c r="D20" s="22">
         <f>Assumptions!D13*Assumptions!D50*(1+Assumptions!D51)^1</f>
         <v>240333.33333333</v>
       </c>
-      <c r="E20" s="20">
+      <c r="E20" s="22">
         <f>Assumptions!D14*Assumptions!D50*(1+Assumptions!D51)^2</f>
         <v>618858.33333333</v>
       </c>
-      <c r="F20" s="20">
+      <c r="F20" s="22">
         <f>Assumptions!D15*Assumptions!D50*(1+Assumptions!D51)^3</f>
         <v>1327966.84027778</v>
       </c>
-      <c r="G20" s="20">
+      <c r="G20" s="22">
         <f>Assumptions!D16*Assumptions!D50*(1+Assumptions!D51)^4</f>
         <v>2431654.83641975</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="C21" s="20">
+      <c r="B21" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="C21" s="22">
         <f>Assumptions!D52</f>
         <v>288000</v>
       </c>
-      <c r="D21" s="20">
+      <c r="D21" s="22">
         <f>Assumptions!D52*(1+Assumptions!D53)^1</f>
         <v>453200</v>
       </c>
-      <c r="E21" s="20">
+      <c r="E21" s="22">
         <f>Assumptions!D52*(1+Assumptions!D53)^2</f>
         <v>713160.55555556</v>
       </c>
-      <c r="F21" s="20">
+      <c r="F21" s="22">
         <f>Assumptions!D52*(1+Assumptions!D53)^3</f>
         <v>1122237.3742284</v>
       </c>
-      <c r="G21" s="20">
+      <c r="G21" s="22">
         <f>Assumptions!D52*(1+Assumptions!D53)^4</f>
         <v>1765965.20138996</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="C22" s="22">
+      <c r="B22" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="C22" s="24">
         <f>C18+C19+C20+C21</f>
         <v>654000</v>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="24">
         <f>D18+D19+D20+D21</f>
         <v>983993.33333333</v>
       </c>
-      <c r="E22" s="22">
+      <c r="E22" s="24">
         <f>E18+E19+E20+E21</f>
         <v>1631192.68888889</v>
       </c>
-      <c r="F22" s="22">
+      <c r="F22" s="24">
         <f>F18+F19+F20+F21</f>
         <v>2758353.22850617</v>
       </c>
-      <c r="G22" s="22">
+      <c r="G22" s="24">
         <f>G18+G19+G20+G21</f>
         <v>4515013.52222971</v>
       </c>
@@ -2750,7 +2939,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -2759,294 +2948,294 @@
       <c r="G1" s="9"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="16"/>
-      <c r="C3" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="D3" s="17" t="s">
+      <c r="B3" s="18"/>
+      <c r="C3" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="D3" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="E3" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="F3" s="19" t="s">
         <v>92</v>
       </c>
+      <c r="G3" s="19" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="C5" s="19">
+      <c r="B5" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" s="21">
         <f>Drivers!C4</f>
         <v>120</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="21">
         <f>Drivers!D4</f>
         <v>200</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="21">
         <f>Drivers!E4</f>
         <v>300</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="21">
         <f>Drivers!F4</f>
         <v>375</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="21">
         <f>Drivers!G4</f>
         <v>400</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="C6" s="20" t="str">
+      <c r="B6" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="22" t="str">
         <f>Drivers!C6</f>
         <v>0</v>
       </c>
-      <c r="D6" s="20" t="str">
+      <c r="D6" s="22" t="str">
         <f>Drivers!D6</f>
         <v>0</v>
       </c>
-      <c r="E6" s="20" t="str">
+      <c r="E6" s="22" t="str">
         <f>Drivers!E6</f>
         <v>0</v>
       </c>
-      <c r="F6" s="20" t="str">
+      <c r="F6" s="22" t="str">
         <f>Drivers!F6</f>
         <v>0</v>
       </c>
-      <c r="G6" s="20" t="str">
+      <c r="G6" s="22" t="str">
         <f>Drivers!G6</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="C7" s="20">
+      <c r="B7" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="C7" s="22">
         <f>Drivers!C7</f>
         <v>1380000</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="22">
         <f>Drivers!D7</f>
         <v>2346000</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="22">
         <f>Drivers!E7</f>
         <v>3589380</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="22">
         <f>Drivers!F7</f>
         <v>4576459.5</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="22">
         <f>Drivers!G7</f>
         <v>4979187.936</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="C8" s="20">
+      <c r="B8" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="C8" s="22">
         <f>Drivers!C8</f>
         <v>36000</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="22">
         <f>Drivers!D8</f>
         <v>61800</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="22">
         <f>Drivers!E8</f>
         <v>95481</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="22">
         <f>Drivers!F8</f>
         <v>122931.7875</v>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="22">
         <f>Drivers!G8</f>
         <v>135061.0572</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="C9" s="20">
+      <c r="B9" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="22">
         <f>Drivers!C9</f>
         <v>130000</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="22">
         <f>Drivers!D9</f>
         <v>130000</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="22">
         <f>Drivers!E9</f>
         <v>130000</v>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="22">
         <f>Drivers!F9</f>
         <v>130000</v>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="22">
         <f>Drivers!G9</f>
         <v>130000</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="C10" s="22">
+      <c r="B10" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="24">
         <f>Drivers!C10</f>
         <v>1546000</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="24">
         <f>Drivers!D10</f>
         <v>2537800</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="24">
         <f>Drivers!E10</f>
         <v>3814861</v>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="24">
         <f>Drivers!F10</f>
         <v>4829391.2875</v>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="24">
         <f>Drivers!G10</f>
         <v>5244248.9932</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="C12" s="20">
+      <c r="B12" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="C12" s="22">
         <f>Drivers!C16</f>
         <v>1200167.18888889</v>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="22">
         <f>Drivers!D16</f>
         <v>1653599.53663333</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="22">
         <f>Drivers!E16</f>
         <v>2194579.12506389</v>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="22">
         <f>Drivers!F16</f>
         <v>2703265.15541712</v>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="22">
         <f>Drivers!G16</f>
         <v>2914687.14330802</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="C13" s="20">
+      <c r="B13" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="C13" s="22">
         <f>Drivers!C22</f>
         <v>654000</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="22">
         <f>Drivers!D22</f>
         <v>983993.33333333</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="22">
         <f>Drivers!E22</f>
         <v>1631192.68888889</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="22">
         <f>Drivers!F22</f>
         <v>2758353.22850617</v>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="22">
         <f>Drivers!G22</f>
         <v>4515013.52222971</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="C15" s="22">
+      <c r="B15" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="C15" s="24">
         <f>C12+C13</f>
         <v>1854167.18888889</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="24">
         <f>D12+D13</f>
         <v>2637592.86996667</v>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="24">
         <f>E12+E13</f>
         <v>3825771.81395278</v>
       </c>
-      <c r="F15" s="22">
+      <c r="F15" s="24">
         <f>F12+F13</f>
         <v>5461618.38392329</v>
       </c>
-      <c r="G15" s="22">
+      <c r="G15" s="24">
         <f>G12+G13</f>
         <v>7429700.66553774</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="C16" s="23">
+      <c r="B16" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="C16" s="25">
         <f>C10-C15</f>
         <v>-308167.18888889</v>
       </c>
-      <c r="D16" s="23">
+      <c r="D16" s="25">
         <f>D10-D15</f>
         <v>-99792.86996667</v>
       </c>
-      <c r="E16" s="23">
+      <c r="E16" s="25">
         <f>E10-E15</f>
         <v>-10910.81395278</v>
       </c>
-      <c r="F16" s="23">
+      <c r="F16" s="25">
         <f>F10-F15</f>
         <v>-632227.09642329</v>
       </c>
-      <c r="G16" s="23">
+      <c r="G16" s="25">
         <f>G10-G15</f>
         <v>-2185451.67233774</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="C17" s="24">
+      <c r="B17" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="C17" s="26">
         <f>IF(C10&gt;0,C16/C10,0)</f>
         <v>-0.19933195</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D17" s="26">
         <f>IF(D10&gt;0,D16/D10,0)</f>
         <v>-0.03932259</v>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="26">
         <f>IF(E10&gt;0,E16/E10,0)</f>
         <v>-0.00286008</v>
       </c>
-      <c r="F17" s="24">
+      <c r="F17" s="26">
         <f>IF(F10&gt;0,F16/F10,0)</f>
         <v>-0.13091238</v>
       </c>
-      <c r="G17" s="24">
+      <c r="G17" s="26">
         <f>IF(G10&gt;0,G16/G10,0)</f>
         <v>-0.41673301</v>
       </c>
@@ -3079,7 +3268,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -3088,194 +3277,194 @@
       <c r="G1" s="9"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="16"/>
-      <c r="C3" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="D3" s="17" t="s">
+      <c r="B3" s="18"/>
+      <c r="C3" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="D3" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="E3" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="F3" s="19" t="s">
         <v>92</v>
       </c>
+      <c r="G3" s="19" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="C4" s="20">
+      <c r="B4" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="C4" s="22">
         <f>'5-Year P&amp;L'!C16</f>
         <v>-308167.18888889</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="22">
         <f>'5-Year P&amp;L'!D16</f>
         <v>-99792.86996667</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="22">
         <f>'5-Year P&amp;L'!E16</f>
         <v>-10910.81395278</v>
       </c>
-      <c r="F4" s="20">
+      <c r="F4" s="22">
         <f>'5-Year P&amp;L'!F16</f>
         <v>-632227.09642329</v>
       </c>
-      <c r="G4" s="20">
+      <c r="G4" s="22">
         <f>'5-Year P&amp;L'!G16</f>
         <v>-2185451.67233774</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="C6" s="20">
+      <c r="B6" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" s="22">
         <f>Assumptions!D58</f>
         <v>115000</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="22">
         <f>Assumptions!D58</f>
         <v>115000</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="22">
         <f>Assumptions!D58</f>
         <v>115000</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="22">
         <f>Assumptions!D58</f>
         <v>115000</v>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="22">
         <f>Assumptions!D58</f>
         <v>115000</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="C7" s="20">
+      <c r="B7" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="C7" s="22">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>49824.60522118</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="22">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>49824.60522118</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="22">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>49824.60522118</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="22">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>49824.60522118</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="22">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>49824.60522118</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="C8" s="22">
+      <c r="B8" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8" s="24">
         <f>C6+C7</f>
         <v>164824.60522118</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="24">
         <f>D6+D7</f>
         <v>164824.60522118</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="24">
         <f>E6+E7</f>
         <v>164824.60522118</v>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="24">
         <f>F6+F7</f>
         <v>164824.60522118</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="24">
         <f>G6+G7</f>
         <v>164824.60522118</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="C10" s="25">
+      <c r="B10" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="C10" s="27">
         <f>IF(C8&gt;0,C4/C8,IF(C4&gt;0,99.9,0))</f>
         <v>-1.86966739</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="27">
         <f>IF(D8&gt;0,D4/D8,IF(D4&gt;0,99.9,0))</f>
         <v>-0.60544886</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="27">
         <f>IF(E8&gt;0,E4/E8,IF(E4&gt;0,99.9,0))</f>
         <v>-0.06619651</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="27">
         <f>IF(F8&gt;0,F4/F8,IF(F4&gt;0,99.9,0))</f>
         <v>-3.83575678</v>
       </c>
-      <c r="G10" s="25">
+      <c r="G10" s="27">
         <f>IF(G8&gt;0,G4/G8,IF(G4&gt;0,99.9,0))</f>
         <v>-13.25925622</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="C12" s="20">
+      <c r="B12" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="C12" s="22">
         <f>C4-C8</f>
         <v>-472991.79411007</v>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="22">
         <f>D4-D8</f>
         <v>-264617.47518785</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="22">
         <f>E4-E8</f>
         <v>-175735.41917396</v>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="22">
         <f>F4-F8</f>
         <v>-797051.70164447</v>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="22">
         <f>G4-G8</f>
         <v>-2350276.27755892</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="C14" s="26">
+      <c r="B14" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="C14" s="28">
         <f>Assumptions!D57+C12</f>
         <v>-472991.79411007</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="28">
         <f>C14+D12</f>
         <v>-737609.26929791</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="28">
         <f>D14+E12</f>
         <v>-913344.68847187</v>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="28">
         <f>E14+F12</f>
         <v>-1710396.39011634</v>
       </c>
-      <c r="G14" s="26">
+      <c r="G14" s="28">
         <f>F14+G12</f>
         <v>-4060672.66767526</v>
       </c>
@@ -3308,7 +3497,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -3317,94 +3506,94 @@
       <c r="G1" s="9"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="16"/>
-      <c r="C3" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="D3" s="17" t="s">
+      <c r="B3" s="18"/>
+      <c r="C3" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="D3" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="E3" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="F3" s="19" t="s">
         <v>92</v>
       </c>
+      <c r="G3" s="19" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="C4" s="19">
+      <c r="B4" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C4" s="21">
         <f>Drivers!C12</f>
         <v>10</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="21">
         <f>Drivers!D12</f>
         <v>17</v>
       </c>
-      <c r="E4" s="19">
+      <c r="E4" s="21">
         <f>Drivers!E12</f>
         <v>25</v>
       </c>
-      <c r="F4" s="19">
+      <c r="F4" s="21">
         <f>Drivers!F12</f>
         <v>32</v>
       </c>
-      <c r="G4" s="19">
+      <c r="G4" s="21">
         <f>Drivers!G12</f>
         <v>34</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="C5" s="19">
+      <c r="B5" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="C5" s="21">
         <f>Assumptions!D35</f>
         <v>7</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="21">
         <f>Assumptions!D36</f>
         <v>7</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="21">
         <f>Assumptions!D37</f>
         <v>7</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="21">
         <f>Assumptions!D38</f>
         <v>7</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="21">
         <f>Assumptions!D39</f>
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="C6" s="27">
+      <c r="B6" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="C6" s="29">
         <f>C4+C5</f>
         <v>17</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="29">
         <f>D4+D5</f>
         <v>24</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="29">
         <f>E4+E5</f>
         <v>32</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="29">
         <f>F4+F5</f>
         <v>39</v>
       </c>
-      <c r="G6" s="27">
+      <c r="G6" s="29">
         <f>G4+G5</f>
         <v>41</v>
       </c>
@@ -3437,51 +3626,51 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C1" s="9"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="C3" s="20">
+      <c r="B3" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" s="22">
         <f>Assumptions!D59</f>
         <v>500000</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="C4" s="24">
+      <c r="B4" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="C4" s="26">
         <f>Assumptions!D60</f>
         <v>0.0575</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="C5" s="19">
+      <c r="B5" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="21">
         <f>Assumptions!D61</f>
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="C6" s="28">
+      <c r="B6" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="C6" s="30">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>49824.60522118</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="C8" s="25">
+      <c r="B8" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="C8" s="27">
         <f>'Cash Flow &amp; DSCR'!C10</f>
         <v>-1.86966739</v>
       </c>
@@ -3514,76 +3703,76 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C1" s="9"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="18" t="str">
+      <c r="B3" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="20" t="str">
         <f>Assumptions!D5</f>
         <v>Civic Scholars Charter</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="18" t="str">
+      <c r="B4" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="20" t="str">
         <f>Assumptions!D7</f>
         <v>Charter School</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="18" t="str">
+      <c r="B5" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="20" t="str">
         <f>Assumptions!D6</f>
         <v>OH</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="C6" s="18">
+      <c r="B6" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="C6" s="20">
         <f>Assumptions!D8</f>
         <v>2026</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="19">
+      <c r="B8" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="21">
         <f>Assumptions!D16</f>
         <v>400</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="C9" s="20">
+      <c r="B9" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="C9" s="22">
         <f>Drivers!G10</f>
         <v>5244248.9932</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="C10" s="26">
+      <c r="B10" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="C10" s="28">
         <f>'5-Year P&amp;L'!G16</f>
         <v>-2185451.67233774</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C12" s="6"/>
     </row>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="192">
   <si>
     <t>SCHOOLSTACK BUDGET</t>
   </si>
@@ -67,13 +67,13 @@
     <t>Cell Color Legend</t>
   </si>
   <si>
-    <t>Blue cells are editable inputs — change these to update your model.</t>
-  </si>
-  <si>
-    <t>White cells contain formulas — do not edit (they recalculate automatically).</t>
-  </si>
-  <si>
-    <t>Green cells are key outputs and summary metrics.</t>
+    <t xml:space="preserve">  Blue cells are editable inputs — change these to update your model.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  White cells contain formulas — do not edit (they recalculate automatically).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Green cells are key outputs and summary metrics.</t>
   </si>
   <si>
     <t/>
@@ -119,6 +119,21 @@
   </si>
   <si>
     <t>Review key metrics: net margin, cash runway, and DSCR.</t>
+  </si>
+  <si>
+    <t>Next Steps</t>
+  </si>
+  <si>
+    <t>2. Verify enrollment and revenue projections match your plan.</t>
+  </si>
+  <si>
+    <t>3. Check the Financial Health dashboard for risk signals.</t>
+  </si>
+  <si>
+    <t>4. Share this workbook with your lender or financial advisor.</t>
+  </si>
+  <si>
+    <t>5. Update inputs as your school's plan evolves.</t>
   </si>
   <si>
     <t>Disclaimer</t>
@@ -593,7 +608,7 @@
     <numFmt numFmtId="166" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -637,6 +652,22 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FF1E293B"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF6B7280"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF1E3A5F"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -660,11 +691,6 @@
     </font>
     <font>
       <color rgb="FF374151"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF1E3A5F"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -712,6 +738,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1E293B"/>
       </patternFill>
     </fill>
@@ -728,11 +759,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF8E1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -796,7 +822,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -804,101 +830,253 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="15" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="15" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="15" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="15" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="21">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1346,6 +1524,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <tabColor rgb="FF0D9488"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:G33"/>
@@ -1359,7 +1538,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -1378,456 +1557,456 @@
       <c r="G3" s="6"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="C5" s="32" t="s">
-        <v>89</v>
-      </c>
-      <c r="D5" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="E5" s="32" t="s">
-        <v>91</v>
-      </c>
-      <c r="F5" s="32" t="s">
-        <v>92</v>
-      </c>
-      <c r="G5" s="32" t="s">
-        <v>93</v>
+      <c r="B5" s="35" t="s">
+        <v>146</v>
+      </c>
+      <c r="C5" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="D5" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="E5" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="F5" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="G5" s="36" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="C6" s="21">
+      <c r="B6" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="25">
         <v>120</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="25">
         <v>200</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="25">
         <v>300</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="25">
         <v>375</v>
       </c>
-      <c r="G6" s="21">
+      <c r="G6" s="25">
         <v>400</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="C7" s="22">
+      <c r="B7" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="C7" s="26">
         <v>1546000</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="26">
         <v>2537800</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="26">
         <v>3814861</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="26">
         <v>4829391.287500001</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="26">
         <v>5244248.993199999</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="C8" s="22">
+      <c r="B8" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="C8" s="26">
         <v>1200167.1888888888</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="26">
         <v>1653599.5366333332</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="26">
         <v>2194579.1250638887</v>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="26">
         <v>2703265.15541712</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="26">
         <v>2914687.143308021</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="C9" s="22">
+      <c r="B9" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="C9" s="26">
         <v>654000</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="26">
         <v>983993.3333333334</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="26">
         <v>1631192.688888889</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="26">
         <v>2758353.228506173</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="26">
         <v>4515013.522229714</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="C10" s="22">
+      <c r="B10" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="C10" s="26">
         <v>164824.60522117943</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="26">
         <v>164824.60522117943</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="26">
         <v>164824.60522117943</v>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="26">
         <v>164824.60522117943</v>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="26">
         <v>164824.60522117943</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="C11" s="25">
+      <c r="B11" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="C11" s="29">
         <v>-472991.79411006824</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="29">
         <v>-264617.4751878461</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="29">
         <v>-175735.41917395697</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="29">
         <v>-797051.701644472</v>
       </c>
-      <c r="G11" s="25">
+      <c r="G11" s="29">
         <v>-2350276.2775589153</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="C12" s="25">
+      <c r="B12" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="C12" s="29">
         <v>-472991.79411006824</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="29">
         <v>-737609.2692979143</v>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="29">
         <v>-913344.6884718713</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="29">
         <v>-1710396.3901163433</v>
       </c>
-      <c r="G12" s="25">
+      <c r="G12" s="29">
         <v>-4060672.6676752586</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="23" t="s">
-        <v>148</v>
-      </c>
-      <c r="C13" s="33">
+      <c r="B13" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="C13" s="37">
         <v>-0.3059455330595525</v>
       </c>
-      <c r="D13" s="33">
+      <c r="D13" s="37">
         <v>-0.10427042130500674</v>
       </c>
-      <c r="E13" s="33">
+      <c r="E13" s="37">
         <v>-0.046066008479458874</v>
       </c>
-      <c r="F13" s="33">
+      <c r="F13" s="37">
         <v>-0.16504185604249857</v>
       </c>
-      <c r="G13" s="33">
+      <c r="G13" s="37">
         <v>-0.44816260261601254</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="C14" s="22">
+      <c r="B14" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="C14" s="26">
         <v>12883.333333333334</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="26">
         <v>12689</v>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="26">
         <v>12716.203333333333</v>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="26">
         <v>12878.376766666668</v>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="26">
         <v>13110.622483</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="23" t="s">
-        <v>150</v>
-      </c>
-      <c r="C15" s="33">
+      <c r="B15" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="C15" s="37">
         <v>0.7763047793589191</v>
       </c>
-      <c r="D15" s="33">
+      <c r="D15" s="37">
         <v>0.6515878070113221</v>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="38">
         <v>0.5752710583855843</v>
       </c>
-      <c r="F15" s="34">
+      <c r="F15" s="38">
         <v>0.5597527709991174</v>
       </c>
-      <c r="G15" s="34">
+      <c r="G15" s="38">
         <v>0.5557873295275215</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="23" t="s">
-        <v>151</v>
-      </c>
-      <c r="C16" s="35">
+      <c r="B16" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="C16" s="39">
         <v>0.12690815006468306</v>
       </c>
-      <c r="D16" s="35">
+      <c r="D16" s="39">
         <v>0.1163204350224604</v>
       </c>
-      <c r="E16" s="35">
+      <c r="E16" s="39">
         <v>0.1282767069800621</v>
       </c>
-      <c r="F16" s="34">
+      <c r="F16" s="38">
         <v>0.1713478820185269</v>
       </c>
-      <c r="G16" s="33">
+      <c r="G16" s="37">
         <v>0.25828370438269493</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="C17" s="33">
+      <c r="B17" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="C17" s="37">
         <v>-0.19933194624119585</v>
       </c>
-      <c r="D17" s="33">
+      <c r="D17" s="37">
         <v>-0.039322590419523434</v>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="37">
         <v>-0.0028600816524580494</v>
       </c>
-      <c r="F17" s="33">
+      <c r="F17" s="37">
         <v>-0.13091237772754036</v>
       </c>
-      <c r="G17" s="33">
+      <c r="G17" s="37">
         <v>-0.4167330108031714</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="23" t="s">
-        <v>152</v>
-      </c>
-      <c r="C18" s="36">
+      <c r="B18" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="C18" s="40">
         <v>-1.8696673865856184</v>
       </c>
-      <c r="D18" s="36">
+      <c r="D18" s="40">
         <v>-0.6054488638559378</v>
       </c>
-      <c r="E18" s="36">
+      <c r="E18" s="40">
         <v>-0.06619651197184098</v>
       </c>
-      <c r="F18" s="36">
+      <c r="F18" s="40">
         <v>-3.8357567765741165</v>
       </c>
-      <c r="G18" s="36">
+      <c r="G18" s="40">
         <v>-13.259256222122064</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="C19" s="37" t="s">
-        <v>154</v>
-      </c>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
+      <c r="B19" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="C19" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="23" t="s">
-        <v>155</v>
-      </c>
-      <c r="C20" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="D20" s="37"/>
-      <c r="E20" s="37"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="37"/>
+      <c r="B20" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="C20" s="41" t="s">
+        <v>161</v>
+      </c>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
     </row>
     <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="31" t="s">
-        <v>157</v>
-      </c>
-      <c r="C22" s="31" t="s">
-        <v>158</v>
-      </c>
-      <c r="D22" s="31" t="s">
-        <v>159</v>
-      </c>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31" t="s">
-        <v>160</v>
-      </c>
-      <c r="G22" s="31"/>
+      <c r="B22" s="35" t="s">
+        <v>162</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>163</v>
+      </c>
+      <c r="D22" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35" t="s">
+        <v>165</v>
+      </c>
+      <c r="G22" s="35"/>
     </row>
     <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="38" t="s">
-        <v>161</v>
-      </c>
-      <c r="C23" s="39" t="s">
-        <v>162</v>
-      </c>
-      <c r="D23" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="E23" s="40"/>
-      <c r="F23" s="41" t="s">
-        <v>164</v>
-      </c>
-      <c r="G23" s="41"/>
+      <c r="B23" s="42" t="s">
+        <v>166</v>
+      </c>
+      <c r="C23" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="D23" s="44" t="s">
+        <v>168</v>
+      </c>
+      <c r="E23" s="44"/>
+      <c r="F23" s="45" t="s">
+        <v>169</v>
+      </c>
+      <c r="G23" s="45"/>
     </row>
     <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="38" t="s">
-        <v>165</v>
-      </c>
-      <c r="C24" s="39" t="s">
-        <v>162</v>
-      </c>
-      <c r="D24" s="40" t="s">
-        <v>166</v>
-      </c>
-      <c r="E24" s="40"/>
-      <c r="F24" s="41" t="s">
+      <c r="B24" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="C24" s="43" t="s">
         <v>167</v>
       </c>
-      <c r="G24" s="41"/>
+      <c r="D24" s="44" t="s">
+        <v>171</v>
+      </c>
+      <c r="E24" s="44"/>
+      <c r="F24" s="45" t="s">
+        <v>172</v>
+      </c>
+      <c r="G24" s="45"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="38" t="s">
-        <v>168</v>
-      </c>
-      <c r="C25" s="42" t="s">
-        <v>169</v>
-      </c>
-      <c r="D25" s="40" t="s">
-        <v>170</v>
-      </c>
-      <c r="E25" s="40"/>
-      <c r="F25" s="41" t="s">
-        <v>171</v>
-      </c>
-      <c r="G25" s="41"/>
+      <c r="B25" s="42" t="s">
+        <v>173</v>
+      </c>
+      <c r="C25" s="46" t="s">
+        <v>174</v>
+      </c>
+      <c r="D25" s="44" t="s">
+        <v>175</v>
+      </c>
+      <c r="E25" s="44"/>
+      <c r="F25" s="45" t="s">
+        <v>176</v>
+      </c>
+      <c r="G25" s="45"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="38" t="s">
-        <v>172</v>
-      </c>
-      <c r="C26" s="39" t="s">
-        <v>162</v>
-      </c>
-      <c r="D26" s="40" t="s">
-        <v>173</v>
-      </c>
-      <c r="E26" s="40"/>
-      <c r="F26" s="41" t="s">
-        <v>174</v>
-      </c>
-      <c r="G26" s="41"/>
+      <c r="B26" s="42" t="s">
+        <v>177</v>
+      </c>
+      <c r="C26" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="D26" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="E26" s="44"/>
+      <c r="F26" s="45" t="s">
+        <v>179</v>
+      </c>
+      <c r="G26" s="45"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="38" t="s">
-        <v>175</v>
-      </c>
-      <c r="C27" s="39" t="s">
-        <v>162</v>
-      </c>
-      <c r="D27" s="40" t="s">
-        <v>176</v>
-      </c>
-      <c r="E27" s="40"/>
-      <c r="F27" s="41" t="s">
-        <v>177</v>
-      </c>
-      <c r="G27" s="41"/>
+      <c r="B27" s="42" t="s">
+        <v>180</v>
+      </c>
+      <c r="C27" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="D27" s="44" t="s">
+        <v>181</v>
+      </c>
+      <c r="E27" s="44"/>
+      <c r="F27" s="45" t="s">
+        <v>182</v>
+      </c>
+      <c r="G27" s="45"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="38" t="s">
-        <v>178</v>
-      </c>
-      <c r="C28" s="43" t="s">
-        <v>179</v>
-      </c>
-      <c r="D28" s="40" t="s">
-        <v>180</v>
-      </c>
-      <c r="E28" s="40"/>
-      <c r="F28" s="41" t="s">
-        <v>181</v>
-      </c>
-      <c r="G28" s="41"/>
+      <c r="B28" s="42" t="s">
+        <v>183</v>
+      </c>
+      <c r="C28" s="47" t="s">
+        <v>184</v>
+      </c>
+      <c r="D28" s="44" t="s">
+        <v>185</v>
+      </c>
+      <c r="E28" s="44"/>
+      <c r="F28" s="45" t="s">
+        <v>186</v>
+      </c>
+      <c r="G28" s="45"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="38" t="s">
-        <v>182</v>
-      </c>
-      <c r="C29" s="39" t="s">
-        <v>162</v>
-      </c>
-      <c r="D29" s="40" t="s">
-        <v>183</v>
-      </c>
-      <c r="E29" s="40"/>
-      <c r="F29" s="41" t="s">
-        <v>184</v>
-      </c>
-      <c r="G29" s="41"/>
+      <c r="B29" s="42" t="s">
+        <v>187</v>
+      </c>
+      <c r="C29" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="D29" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="E29" s="44"/>
+      <c r="F29" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="G29" s="45"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B31" s="38" t="s">
+      <c r="B31" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="23" t="s">
-        <v>185</v>
-      </c>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
+      <c r="C31" s="27" t="s">
+        <v>190</v>
+      </c>
+      <c r="D31" s="27"/>
+      <c r="E31" s="27"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="44" t="s">
-        <v>186</v>
-      </c>
-      <c r="C33" s="44"/>
-      <c r="D33" s="44"/>
-      <c r="E33" s="44"/>
-      <c r="F33" s="44"/>
-      <c r="G33" s="44"/>
+      <c r="B33" s="48" t="s">
+        <v>191</v>
+      </c>
+      <c r="C33" s="48"/>
+      <c r="D33" s="48"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="48"/>
+      <c r="G33" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -1854,6 +2033,83 @@
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="B33:G33"/>
   </mergeCells>
+  <conditionalFormatting sqref="C11:G11">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>C11&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>C11&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>C11&lt;-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C12:G12">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>C12&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>C12&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>C12&lt;-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C13:G13">
+    <cfRule type="expression" dxfId="6" priority="1">
+      <formula>C13&gt;=0.05</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="2">
+      <formula>C13&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="3">
+      <formula>C13&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C15:G15">
+    <cfRule type="expression" dxfId="9" priority="1">
+      <formula>C15&lt;=0.55</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="2">
+      <formula>C15&lt;=0.65</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="3">
+      <formula>C15&gt;0.65</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:G16">
+    <cfRule type="expression" dxfId="12" priority="1">
+      <formula>C16&lt;=0.15</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="2">
+      <formula>C16&lt;=0.25</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="3">
+      <formula>C16&gt;0.25</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C17:G17">
+    <cfRule type="expression" dxfId="15" priority="1">
+      <formula>C17&gt;=0.10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="2">
+      <formula>C17&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="3">
+      <formula>C17&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C18:G18">
+    <cfRule type="expression" dxfId="18" priority="1">
+      <formula>C18&gt;=1.25</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="2">
+      <formula>C18&gt;=1.0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="3">
+      <formula>C18&lt;1.0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
@@ -1865,9 +2121,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B29"/>
+  <dimension ref="B2:B37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1879,134 +2136,174 @@
         <v>13</v>
       </c>
     </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="8" t="s">
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="10" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="8" t="s">
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B8" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="8" t="s">
+    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B8" s="8" t="s">
+    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B10" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B9" s="7" t="s">
+    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B11" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="8" t="s">
+    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B12" s="11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="8" t="s">
+    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B13" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="7" t="s">
+    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="8" t="s">
+    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="11" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="8" t="s">
+    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B16" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B15" s="8" t="s">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B16" s="8" t="s">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="8" t="s">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="7" t="s">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="9" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B19" s="8" t="s">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="11" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="8" t="s">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B22" s="11" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B21" s="8" t="s">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="11" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B22" s="8" t="s">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="7" t="s">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B24" s="8" t="s">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="8" t="s">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="11" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B26" s="8" t="s">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B27" s="7" t="s">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="9" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B28" s="8" t="s">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B30" s="11" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B29" s="8" t="s">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B31" s="11" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B32" s="11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="11" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -2034,395 +2331,395 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B1" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
+      <c r="B1" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>37</v>
+      <c r="C2" s="15" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
+      <c r="B3" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C5" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="14" t="s">
+      <c r="C5" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="18" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C6" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>41</v>
+      <c r="C6" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C7" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>43</v>
+      <c r="C7" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C8" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="14">
+      <c r="C8" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="18">
         <v>2026</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
+      <c r="B10" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C12" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="15">
+      <c r="C12" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="19">
         <v>120</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C13" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="15">
+      <c r="C13" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="19">
         <v>200</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C14" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="15">
+      <c r="C14" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="19">
         <v>300</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C15" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="15">
+      <c r="C15" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="19">
         <v>375</v>
       </c>
     </row>
     <row r="16" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C16" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="15">
+      <c r="C16" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="19">
         <v>400</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
+      <c r="B18" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
     </row>
     <row r="20" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C20" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" s="16">
+      <c r="C20" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C21" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D21" s="17">
+      <c r="C21" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="21">
         <v>0.03</v>
       </c>
     </row>
     <row r="22" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C22" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="D22" s="16">
+      <c r="C22" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="20">
         <v>11500</v>
       </c>
     </row>
     <row r="23" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C23" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="D23" s="17">
+      <c r="C23" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="21">
         <v>0.02</v>
       </c>
     </row>
     <row r="24" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C24" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="D24" s="16">
+      <c r="C24" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" s="20">
         <v>300</v>
       </c>
     </row>
     <row r="25" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C25" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="D25" s="17">
+      <c r="C25" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="D25" s="21">
         <v>0.03</v>
       </c>
     </row>
     <row r="26" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C26" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D26" s="17">
+      <c r="C26" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" s="21">
         <v>0.95</v>
       </c>
     </row>
     <row r="27" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C27" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="D27" s="16">
+      <c r="C27" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" s="20">
         <v>130000</v>
       </c>
     </row>
     <row r="28" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C28" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="D28" s="17">
+      <c r="C28" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B30" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
+      <c r="B30" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
     </row>
     <row r="32" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C32" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="D32" s="15">
+      <c r="C32" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" s="19">
         <v>12</v>
       </c>
     </row>
     <row r="33" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C33" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="D33" s="16">
+      <c r="C33" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" s="20">
         <v>45667</v>
       </c>
     </row>
     <row r="34" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C34" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="D34" s="17">
+      <c r="C34" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D34" s="21">
         <v>0.03</v>
       </c>
     </row>
     <row r="35" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C35" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="D35" s="15">
+      <c r="C35" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35" s="19">
         <v>7</v>
       </c>
     </row>
     <row r="36" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C36" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="D36" s="15">
+      <c r="C36" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D36" s="19">
         <v>7</v>
       </c>
     </row>
     <row r="37" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C37" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="D37" s="15">
+      <c r="C37" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D37" s="19">
         <v>7</v>
       </c>
     </row>
     <row r="38" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C38" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="D38" s="15">
+      <c r="C38" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D38" s="19">
         <v>7</v>
       </c>
     </row>
     <row r="39" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C39" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="D39" s="15">
+      <c r="C39" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="D39" s="19">
         <v>7</v>
       </c>
     </row>
     <row r="40" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C40" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="D40" s="16">
+      <c r="C40" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D40" s="20">
         <v>70000</v>
       </c>
     </row>
     <row r="41" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C41" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="D41" s="17">
+      <c r="C41" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="D41" s="21">
         <v>0.03</v>
       </c>
     </row>
     <row r="42" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C42" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="D42" s="17">
+      <c r="C42" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D42" s="21">
         <v>0.2677777777777778</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B44" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
+      <c r="B44" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C44" s="16"/>
+      <c r="D44" s="16"/>
     </row>
     <row r="46" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C46" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="D46" s="16">
+      <c r="C46" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D46" s="20">
         <v>282000</v>
       </c>
     </row>
     <row r="47" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C47" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D47" s="17">
+      <c r="C47" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="D47" s="21">
         <v>0.03</v>
       </c>
     </row>
     <row r="48" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C48" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="D48" s="16">
+      <c r="C48" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="D48" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C49" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="D49" s="17">
+      <c r="C49" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D49" s="21">
         <v>0.03</v>
       </c>
     </row>
     <row r="50" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C50" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="D50" s="16">
+      <c r="C50" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="D50" s="20">
         <v>700</v>
       </c>
     </row>
     <row r="51" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C51" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="D51" s="17">
+      <c r="C51" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="D51" s="21">
         <v>0.7166666666666667</v>
       </c>
     </row>
     <row r="52" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C52" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="D52" s="16">
+      <c r="C52" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="D52" s="20">
         <v>288000</v>
       </c>
     </row>
     <row r="53" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C53" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="D53" s="17">
+      <c r="C53" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D53" s="21">
         <v>0.5736111111111111</v>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B55" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="C55" s="12"/>
-      <c r="D55" s="12"/>
+      <c r="B55" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C55" s="16"/>
+      <c r="D55" s="16"/>
     </row>
     <row r="57" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C57" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="D57" s="16">
+      <c r="C57" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="D57" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C58" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="D58" s="16">
+      <c r="C58" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D58" s="20">
         <v>115000</v>
       </c>
     </row>
     <row r="59" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C59" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D59" s="16">
+      <c r="C59" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="D59" s="20">
         <v>500000</v>
       </c>
     </row>
     <row r="60" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C60" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="D60" s="17">
+      <c r="C60" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D60" s="21">
         <v>0.0575</v>
       </c>
     </row>
     <row r="61" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C61" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="D61" s="15">
+      <c r="C61" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="D61" s="19">
         <v>15</v>
       </c>
     </row>
@@ -2459,454 +2756,454 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="B1" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="18"/>
-      <c r="C3" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>93</v>
+      <c r="B3" s="22"/>
+      <c r="C3" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="C4" s="21">
+      <c r="B4" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="25">
         <f>Assumptions!D12</f>
         <v>120</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="25">
         <f>Assumptions!D13</f>
         <v>200</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="25">
         <f>Assumptions!D14</f>
         <v>300</v>
       </c>
-      <c r="F4" s="21">
+      <c r="F4" s="25">
         <f>Assumptions!D15</f>
         <v>375</v>
       </c>
-      <c r="G4" s="21">
+      <c r="G4" s="25">
         <f>Assumptions!D16</f>
         <v>400</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="C5" s="22" t="str">
+      <c r="B5" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" s="26" t="str">
         <f>Assumptions!D12*Assumptions!D20</f>
         <v>0</v>
       </c>
-      <c r="D5" s="22" t="str">
+      <c r="D5" s="26" t="str">
         <f>Assumptions!D13*Assumptions!D20*(1+Assumptions!D21)^1</f>
         <v>0</v>
       </c>
-      <c r="E5" s="22" t="str">
+      <c r="E5" s="26" t="str">
         <f>Assumptions!D14*Assumptions!D20*(1+Assumptions!D21)^2</f>
         <v>0</v>
       </c>
-      <c r="F5" s="22" t="str">
+      <c r="F5" s="26" t="str">
         <f>Assumptions!D15*Assumptions!D20*(1+Assumptions!D21)^3</f>
         <v>0</v>
       </c>
-      <c r="G5" s="22" t="str">
+      <c r="G5" s="26" t="str">
         <f>Assumptions!D16*Assumptions!D20*(1+Assumptions!D21)^4</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="C6" s="22" t="str">
+      <c r="B6" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="26" t="str">
         <f>C5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="D6" s="22" t="str">
+      <c r="D6" s="26" t="str">
         <f>D5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="E6" s="22" t="str">
+      <c r="E6" s="26" t="str">
         <f>E5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="F6" s="22" t="str">
+      <c r="F6" s="26" t="str">
         <f>F5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="G6" s="22" t="str">
+      <c r="G6" s="26" t="str">
         <f>G5*Assumptions!D26</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="C7" s="22">
+      <c r="B7" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" s="26">
         <f>Assumptions!D12*Assumptions!D22</f>
         <v>1380000</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="26">
         <f>Assumptions!D13*Assumptions!D22*(1+Assumptions!D23)^1</f>
         <v>2346000</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="26">
         <f>Assumptions!D14*Assumptions!D22*(1+Assumptions!D23)^2</f>
         <v>3589380</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="26">
         <f>Assumptions!D15*Assumptions!D22*(1+Assumptions!D23)^3</f>
         <v>4576459.5</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="26">
         <f>Assumptions!D16*Assumptions!D22*(1+Assumptions!D23)^4</f>
         <v>4979187.936</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="C8" s="22">
+      <c r="B8" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="C8" s="26">
         <f>Assumptions!D12*Assumptions!D24</f>
         <v>36000</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="26">
         <f>Assumptions!D13*Assumptions!D24*(1+Assumptions!D25)^1</f>
         <v>61800</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="26">
         <f>Assumptions!D14*Assumptions!D24*(1+Assumptions!D25)^2</f>
         <v>95481</v>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="26">
         <f>Assumptions!D15*Assumptions!D24*(1+Assumptions!D25)^3</f>
         <v>122931.7875</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="26">
         <f>Assumptions!D16*Assumptions!D24*(1+Assumptions!D25)^4</f>
         <v>135061.0572</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="C9" s="22">
+      <c r="B9" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="26">
         <f>Assumptions!D27</f>
         <v>130000</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="26">
         <f>Assumptions!D27*(1+Assumptions!D28)^1</f>
         <v>130000</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="26">
         <f>Assumptions!D27*(1+Assumptions!D28)^2</f>
         <v>130000</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="26">
         <f>Assumptions!D27*(1+Assumptions!D28)^3</f>
         <v>130000</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="26">
         <f>Assumptions!D27*(1+Assumptions!D28)^4</f>
         <v>130000</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="C10" s="24">
+      <c r="B10" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" s="28">
         <f>C6+C7+C8+C9</f>
         <v>1546000</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="28">
         <f>D6+D7+D8+D9</f>
         <v>2537800</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="28">
         <f>E6+E7+E8+E9</f>
         <v>3814861</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="28">
         <f>F6+F7+F8+F9</f>
         <v>4829391.2875</v>
       </c>
-      <c r="G10" s="24">
+      <c r="G10" s="28">
         <f>G6+G7+G8+G9</f>
         <v>5244248.9932</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C12" s="21">
+      <c r="B12" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="C12" s="25">
         <f>CEILING(Assumptions!D12/Assumptions!D32,1)</f>
         <v>10</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="25">
         <f>CEILING(Assumptions!D13/Assumptions!D32,1)</f>
         <v>17</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="25">
         <f>CEILING(Assumptions!D14/Assumptions!D32,1)</f>
         <v>25</v>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="25">
         <f>CEILING(Assumptions!D15/Assumptions!D32,1)</f>
         <v>32</v>
       </c>
-      <c r="G12" s="21">
+      <c r="G12" s="25">
         <f>CEILING(Assumptions!D16/Assumptions!D32,1)</f>
         <v>34</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="C13" s="22">
+      <c r="B13" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" s="26">
         <f>C12*Assumptions!D33</f>
         <v>456670</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="26">
         <f>D12*Assumptions!D33*(1+Assumptions!D34)^1</f>
         <v>799629.17</v>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="26">
         <f>E12*Assumptions!D33*(1+Assumptions!D34)^2</f>
         <v>1211203.0075</v>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="26">
         <f>F12*Assumptions!D33*(1+Assumptions!D34)^3</f>
         <v>1596850.045088</v>
       </c>
-      <c r="G13" s="22">
+      <c r="G13" s="26">
         <f>G12*Assumptions!D33*(1+Assumptions!D34)^4</f>
         <v>1747552.76809318</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="C14" s="22">
+      <c r="B14" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="C14" s="26">
         <f>Assumptions!D35*Assumptions!D40</f>
         <v>490000</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="26">
         <f>Assumptions!D36*Assumptions!D40*(1+Assumptions!D41)^1</f>
         <v>504700</v>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="26">
         <f>Assumptions!D37*Assumptions!D40*(1+Assumptions!D41)^2</f>
         <v>519841</v>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="26">
         <f>Assumptions!D38*Assumptions!D40*(1+Assumptions!D41)^3</f>
         <v>535436.23</v>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="26">
         <f>Assumptions!D39*Assumptions!D40*(1+Assumptions!D41)^4</f>
         <v>551499.3169</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="C15" s="22">
+      <c r="B15" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15" s="26">
         <f>(C13+C14)*Assumptions!D42</f>
         <v>253497.18888889</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="26">
         <f>(D13+D14)*Assumptions!D42</f>
         <v>349270.36663333</v>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="26">
         <f>(E13+E14)*Assumptions!D42</f>
         <v>463535.11756389</v>
       </c>
-      <c r="F15" s="22">
+      <c r="F15" s="26">
         <f>(F13+F14)*Assumptions!D42</f>
         <v>570978.88032912</v>
       </c>
-      <c r="G15" s="22">
+      <c r="G15" s="26">
         <f>(G13+G14)*Assumptions!D42</f>
         <v>615635.05831484</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="C16" s="24">
+      <c r="B16" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="C16" s="28">
         <f>C13+C14+C15</f>
         <v>1200167.18888889</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="28">
         <f>D13+D14+D15</f>
         <v>1653599.53663333</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="28">
         <f>E13+E14+E15</f>
         <v>2194579.12506389</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="28">
         <f>F13+F14+F15</f>
         <v>2703265.15541712</v>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="28">
         <f>G13+G14+G15</f>
         <v>2914687.14330802</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="C18" s="22">
+      <c r="B18" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="C18" s="26">
         <f>Assumptions!D46</f>
         <v>282000</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="26">
         <f>Assumptions!D46*(1+Assumptions!D47)^1</f>
         <v>290460</v>
       </c>
-      <c r="E18" s="22">
+      <c r="E18" s="26">
         <f>Assumptions!D46*(1+Assumptions!D47)^2</f>
         <v>299173.8</v>
       </c>
-      <c r="F18" s="22">
+      <c r="F18" s="26">
         <f>Assumptions!D46*(1+Assumptions!D47)^3</f>
         <v>308149.014</v>
       </c>
-      <c r="G18" s="22">
+      <c r="G18" s="26">
         <f>Assumptions!D46*(1+Assumptions!D47)^4</f>
         <v>317393.48442</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="C19" s="22" t="str">
+      <c r="B19" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="C19" s="26" t="str">
         <f>Assumptions!D48</f>
         <v>0</v>
       </c>
-      <c r="D19" s="22" t="str">
+      <c r="D19" s="26" t="str">
         <f>Assumptions!D48*(1+Assumptions!D49)^1</f>
         <v>0</v>
       </c>
-      <c r="E19" s="22" t="str">
+      <c r="E19" s="26" t="str">
         <f>Assumptions!D48*(1+Assumptions!D49)^2</f>
         <v>0</v>
       </c>
-      <c r="F19" s="22" t="str">
+      <c r="F19" s="26" t="str">
         <f>Assumptions!D48*(1+Assumptions!D49)^3</f>
         <v>0</v>
       </c>
-      <c r="G19" s="22" t="str">
+      <c r="G19" s="26" t="str">
         <f>Assumptions!D48*(1+Assumptions!D49)^4</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="C20" s="22">
+      <c r="B20" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="C20" s="26">
         <f>Assumptions!D12*Assumptions!D50</f>
         <v>84000</v>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="26">
         <f>Assumptions!D13*Assumptions!D50*(1+Assumptions!D51)^1</f>
         <v>240333.33333333</v>
       </c>
-      <c r="E20" s="22">
+      <c r="E20" s="26">
         <f>Assumptions!D14*Assumptions!D50*(1+Assumptions!D51)^2</f>
         <v>618858.33333333</v>
       </c>
-      <c r="F20" s="22">
+      <c r="F20" s="26">
         <f>Assumptions!D15*Assumptions!D50*(1+Assumptions!D51)^3</f>
         <v>1327966.84027778</v>
       </c>
-      <c r="G20" s="22">
+      <c r="G20" s="26">
         <f>Assumptions!D16*Assumptions!D50*(1+Assumptions!D51)^4</f>
         <v>2431654.83641975</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="C21" s="22">
+      <c r="B21" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="C21" s="26">
         <f>Assumptions!D52</f>
         <v>288000</v>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="26">
         <f>Assumptions!D52*(1+Assumptions!D53)^1</f>
         <v>453200</v>
       </c>
-      <c r="E21" s="22">
+      <c r="E21" s="26">
         <f>Assumptions!D52*(1+Assumptions!D53)^2</f>
         <v>713160.55555556</v>
       </c>
-      <c r="F21" s="22">
+      <c r="F21" s="26">
         <f>Assumptions!D52*(1+Assumptions!D53)^3</f>
         <v>1122237.3742284</v>
       </c>
-      <c r="G21" s="22">
+      <c r="G21" s="26">
         <f>Assumptions!D52*(1+Assumptions!D53)^4</f>
         <v>1765965.20138996</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="C22" s="24">
+      <c r="B22" s="27" t="s">
+        <v>115</v>
+      </c>
+      <c r="C22" s="28">
         <f>C18+C19+C20+C21</f>
         <v>654000</v>
       </c>
-      <c r="D22" s="24">
+      <c r="D22" s="28">
         <f>D18+D19+D20+D21</f>
         <v>983993.33333333</v>
       </c>
-      <c r="E22" s="24">
+      <c r="E22" s="28">
         <f>E18+E19+E20+E21</f>
         <v>1631192.68888889</v>
       </c>
-      <c r="F22" s="24">
+      <c r="F22" s="28">
         <f>F18+F19+F20+F21</f>
         <v>2758353.22850617</v>
       </c>
-      <c r="G22" s="24">
+      <c r="G22" s="28">
         <f>G18+G19+G20+G21</f>
         <v>4515013.52222971</v>
       </c>
@@ -2938,304 +3235,304 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="B1" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="18"/>
-      <c r="C3" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>93</v>
+      <c r="B3" s="22"/>
+      <c r="C3" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="C5" s="21">
+      <c r="B5" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="25">
         <f>Drivers!C4</f>
         <v>120</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="25">
         <f>Drivers!D4</f>
         <v>200</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="25">
         <f>Drivers!E4</f>
         <v>300</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="25">
         <f>Drivers!F4</f>
         <v>375</v>
       </c>
-      <c r="G5" s="21">
+      <c r="G5" s="25">
         <f>Drivers!G4</f>
         <v>400</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="C6" s="22" t="str">
+      <c r="B6" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="26" t="str">
         <f>Drivers!C6</f>
         <v>0</v>
       </c>
-      <c r="D6" s="22" t="str">
+      <c r="D6" s="26" t="str">
         <f>Drivers!D6</f>
         <v>0</v>
       </c>
-      <c r="E6" s="22" t="str">
+      <c r="E6" s="26" t="str">
         <f>Drivers!E6</f>
         <v>0</v>
       </c>
-      <c r="F6" s="22" t="str">
+      <c r="F6" s="26" t="str">
         <f>Drivers!F6</f>
         <v>0</v>
       </c>
-      <c r="G6" s="22" t="str">
+      <c r="G6" s="26" t="str">
         <f>Drivers!G6</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="C7" s="22">
+      <c r="B7" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="C7" s="26">
         <f>Drivers!C7</f>
         <v>1380000</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="26">
         <f>Drivers!D7</f>
         <v>2346000</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="26">
         <f>Drivers!E7</f>
         <v>3589380</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="26">
         <f>Drivers!F7</f>
         <v>4576459.5</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="26">
         <f>Drivers!G7</f>
         <v>4979187.936</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="C8" s="22">
+      <c r="B8" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="C8" s="26">
         <f>Drivers!C8</f>
         <v>36000</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="26">
         <f>Drivers!D8</f>
         <v>61800</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="26">
         <f>Drivers!E8</f>
         <v>95481</v>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="26">
         <f>Drivers!F8</f>
         <v>122931.7875</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="26">
         <f>Drivers!G8</f>
         <v>135061.0572</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="C9" s="22">
+      <c r="B9" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="26">
         <f>Drivers!C9</f>
         <v>130000</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="26">
         <f>Drivers!D9</f>
         <v>130000</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="26">
         <f>Drivers!E9</f>
         <v>130000</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="26">
         <f>Drivers!F9</f>
         <v>130000</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="26">
         <f>Drivers!G9</f>
         <v>130000</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="C10" s="24">
+      <c r="B10" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" s="28">
         <f>Drivers!C10</f>
         <v>1546000</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="28">
         <f>Drivers!D10</f>
         <v>2537800</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="28">
         <f>Drivers!E10</f>
         <v>3814861</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="28">
         <f>Drivers!F10</f>
         <v>4829391.2875</v>
       </c>
-      <c r="G10" s="24">
+      <c r="G10" s="28">
         <f>Drivers!G10</f>
         <v>5244248.9932</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="20" t="s">
-        <v>114</v>
-      </c>
-      <c r="C12" s="22">
+      <c r="B12" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" s="26">
         <f>Drivers!C16</f>
         <v>1200167.18888889</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="26">
         <f>Drivers!D16</f>
         <v>1653599.53663333</v>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="26">
         <f>Drivers!E16</f>
         <v>2194579.12506389</v>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="26">
         <f>Drivers!F16</f>
         <v>2703265.15541712</v>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="26">
         <f>Drivers!G16</f>
         <v>2914687.14330802</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="C13" s="22">
+      <c r="B13" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="C13" s="26">
         <f>Drivers!C22</f>
         <v>654000</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="26">
         <f>Drivers!D22</f>
         <v>983993.33333333</v>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="26">
         <f>Drivers!E22</f>
         <v>1631192.68888889</v>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="26">
         <f>Drivers!F22</f>
         <v>2758353.22850617</v>
       </c>
-      <c r="G13" s="22">
+      <c r="G13" s="26">
         <f>Drivers!G22</f>
         <v>4515013.52222971</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="C15" s="24">
+      <c r="B15" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="C15" s="28">
         <f>C12+C13</f>
         <v>1854167.18888889</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="28">
         <f>D12+D13</f>
         <v>2637592.86996667</v>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="28">
         <f>E12+E13</f>
         <v>3825771.81395278</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="28">
         <f>F12+F13</f>
         <v>5461618.38392329</v>
       </c>
-      <c r="G15" s="24">
+      <c r="G15" s="28">
         <f>G12+G13</f>
         <v>7429700.66553774</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="C16" s="25">
+      <c r="B16" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="C16" s="29">
         <f>C10-C15</f>
         <v>-308167.18888889</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="29">
         <f>D10-D15</f>
         <v>-99792.86996667</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="29">
         <f>E10-E15</f>
         <v>-10910.81395278</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="29">
         <f>F10-F15</f>
         <v>-632227.09642329</v>
       </c>
-      <c r="G16" s="25">
+      <c r="G16" s="29">
         <f>G10-G15</f>
         <v>-2185451.67233774</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="C17" s="26">
+      <c r="B17" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="C17" s="30">
         <f>IF(C10&gt;0,C16/C10,0)</f>
         <v>-0.19933195</v>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="30">
         <f>IF(D10&gt;0,D16/D10,0)</f>
         <v>-0.03932259</v>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="30">
         <f>IF(E10&gt;0,E16/E10,0)</f>
         <v>-0.00286008</v>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="30">
         <f>IF(F10&gt;0,F16/F10,0)</f>
         <v>-0.13091238</v>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="30">
         <f>IF(G10&gt;0,G16/G10,0)</f>
         <v>-0.41673301</v>
       </c>
@@ -3267,204 +3564,204 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="B1" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="18"/>
-      <c r="C3" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>93</v>
+      <c r="B3" s="22"/>
+      <c r="C3" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="C4" s="22">
+      <c r="B4" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="C4" s="26">
         <f>'5-Year P&amp;L'!C16</f>
         <v>-308167.18888889</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="26">
         <f>'5-Year P&amp;L'!D16</f>
         <v>-99792.86996667</v>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="26">
         <f>'5-Year P&amp;L'!E16</f>
         <v>-10910.81395278</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="26">
         <f>'5-Year P&amp;L'!F16</f>
         <v>-632227.09642329</v>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="26">
         <f>'5-Year P&amp;L'!G16</f>
         <v>-2185451.67233774</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="C6" s="22">
+      <c r="B6" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6" s="26">
         <f>Assumptions!D58</f>
         <v>115000</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="26">
         <f>Assumptions!D58</f>
         <v>115000</v>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="26">
         <f>Assumptions!D58</f>
         <v>115000</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="26">
         <f>Assumptions!D58</f>
         <v>115000</v>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="26">
         <f>Assumptions!D58</f>
         <v>115000</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="C7" s="22">
+      <c r="B7" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="C7" s="26">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>49824.60522118</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="26">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>49824.60522118</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="26">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>49824.60522118</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="26">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>49824.60522118</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="26">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>49824.60522118</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="23" t="s">
-        <v>122</v>
-      </c>
-      <c r="C8" s="24">
+      <c r="B8" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="C8" s="28">
         <f>C6+C7</f>
         <v>164824.60522118</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="28">
         <f>D6+D7</f>
         <v>164824.60522118</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="28">
         <f>E6+E7</f>
         <v>164824.60522118</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="28">
         <f>F6+F7</f>
         <v>164824.60522118</v>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="28">
         <f>G6+G7</f>
         <v>164824.60522118</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="C10" s="27">
+      <c r="B10" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="C10" s="31">
         <f>IF(C8&gt;0,C4/C8,IF(C4&gt;0,99.9,0))</f>
         <v>-1.86966739</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="31">
         <f>IF(D8&gt;0,D4/D8,IF(D4&gt;0,99.9,0))</f>
         <v>-0.60544886</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="31">
         <f>IF(E8&gt;0,E4/E8,IF(E4&gt;0,99.9,0))</f>
         <v>-0.06619651</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="31">
         <f>IF(F8&gt;0,F4/F8,IF(F4&gt;0,99.9,0))</f>
         <v>-3.83575678</v>
       </c>
-      <c r="G10" s="27">
+      <c r="G10" s="31">
         <f>IF(G8&gt;0,G4/G8,IF(G4&gt;0,99.9,0))</f>
         <v>-13.25925622</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="C12" s="22">
+      <c r="B12" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="C12" s="26">
         <f>C4-C8</f>
         <v>-472991.79411007</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="26">
         <f>D4-D8</f>
         <v>-264617.47518785</v>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="26">
         <f>E4-E8</f>
         <v>-175735.41917396</v>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="26">
         <f>F4-F8</f>
         <v>-797051.70164447</v>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="26">
         <f>G4-G8</f>
         <v>-2350276.27755892</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="C14" s="28">
+      <c r="B14" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="C14" s="32">
         <f>Assumptions!D57+C12</f>
         <v>-472991.79411007</v>
       </c>
-      <c r="D14" s="28">
+      <c r="D14" s="32">
         <f>C14+D12</f>
         <v>-737609.26929791</v>
       </c>
-      <c r="E14" s="28">
+      <c r="E14" s="32">
         <f>D14+E12</f>
         <v>-913344.68847187</v>
       </c>
-      <c r="F14" s="28">
+      <c r="F14" s="32">
         <f>E14+F12</f>
         <v>-1710396.39011634</v>
       </c>
-      <c r="G14" s="28">
+      <c r="G14" s="32">
         <f>F14+G12</f>
         <v>-4060672.66767526</v>
       </c>
@@ -3496,104 +3793,104 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="B1" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="18"/>
-      <c r="C3" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>93</v>
+      <c r="B3" s="22"/>
+      <c r="C3" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="C4" s="21">
+      <c r="B4" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="C4" s="25">
         <f>Drivers!C12</f>
         <v>10</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="25">
         <f>Drivers!D12</f>
         <v>17</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="25">
         <f>Drivers!E12</f>
         <v>25</v>
       </c>
-      <c r="F4" s="21">
+      <c r="F4" s="25">
         <f>Drivers!F12</f>
         <v>32</v>
       </c>
-      <c r="G4" s="21">
+      <c r="G4" s="25">
         <f>Drivers!G12</f>
         <v>34</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="C5" s="21">
+      <c r="B5" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="C5" s="25">
         <f>Assumptions!D35</f>
         <v>7</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="25">
         <f>Assumptions!D36</f>
         <v>7</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="25">
         <f>Assumptions!D37</f>
         <v>7</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="25">
         <f>Assumptions!D38</f>
         <v>7</v>
       </c>
-      <c r="G5" s="21">
+      <c r="G5" s="25">
         <f>Assumptions!D39</f>
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="C6" s="29">
+      <c r="B6" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="C6" s="33">
         <f>C4+C5</f>
         <v>17</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="33">
         <f>D4+D5</f>
         <v>24</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="33">
         <f>E4+E5</f>
         <v>32</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="33">
         <f>F4+F5</f>
         <v>39</v>
       </c>
-      <c r="G6" s="29">
+      <c r="G6" s="33">
         <f>G4+G5</f>
         <v>41</v>
       </c>
@@ -3625,52 +3922,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="C1" s="9"/>
+      <c r="B1" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="C1" s="13"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="C3" s="22">
+      <c r="B3" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="C3" s="26">
         <f>Assumptions!D59</f>
         <v>500000</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="C4" s="26">
+      <c r="B4" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="30">
         <f>Assumptions!D60</f>
         <v>0.0575</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="C5" s="21">
+      <c r="B5" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" s="25">
         <f>Assumptions!D61</f>
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="C6" s="30">
+      <c r="B6" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="C6" s="34">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>49824.60522118</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="C8" s="27">
+      <c r="B8" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="C8" s="31">
         <f>'Cash Flow &amp; DSCR'!C10</f>
         <v>-1.86966739</v>
       </c>
@@ -3702,77 +3999,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="C1" s="9"/>
+      <c r="B1" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1" s="13"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" s="20" t="str">
+      <c r="B3" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="24" t="str">
         <f>Assumptions!D5</f>
         <v>Civic Scholars Charter</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" s="20" t="str">
+      <c r="B4" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="24" t="str">
         <f>Assumptions!D7</f>
         <v>Charter School</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="20" t="str">
+      <c r="B5" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="24" t="str">
         <f>Assumptions!D6</f>
         <v>OH</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="C6" s="20">
+      <c r="B6" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="C6" s="24">
         <f>Assumptions!D8</f>
         <v>2026</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" s="21">
+      <c r="B8" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="25">
         <f>Assumptions!D16</f>
         <v>400</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="C9" s="22">
+      <c r="B9" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="C9" s="26">
         <f>Drivers!G10</f>
         <v>5244248.9932</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="C10" s="28">
+      <c r="B10" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="C10" s="32">
         <f>'5-Year P&amp;L'!G16</f>
         <v>-2185451.67233774</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C12" s="6"/>
     </row>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
@@ -4,8 +4,8 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Cover" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Instructions" state="visible" r:id="rId5"/>
+    <sheet sheetId="1" name="Instructions" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Cover" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Assumptions" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Drivers" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="5-Year P&amp;L" state="visible" r:id="rId8"/>
@@ -22,15 +22,102 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="192">
   <si>
+    <t>How to Use This Workbook</t>
+  </si>
+  <si>
+    <t>Civic Scholars Charter</t>
+  </si>
+  <si>
+    <t>Generated March 26, 2026</t>
+  </si>
+  <si>
+    <t>Cell Color Legend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Blue cells are editable inputs — change these to update your model.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  White cells contain formulas — do not edit (they recalculate automatically).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Green cells are key outputs and summary metrics.</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Navigation</t>
+  </si>
+  <si>
+    <t>The Assumptions tab is the central control panel — all other tabs reference it.</t>
+  </si>
+  <si>
+    <t>Structure</t>
+  </si>
+  <si>
+    <t>Assumptions &amp; Drivers: Model inputs and calculations</t>
+  </si>
+  <si>
+    <t>5-Year P&amp;L &amp; Cash Flow: Financial projections</t>
+  </si>
+  <si>
+    <t>Staffing &amp; Loan Snapshot: Personnel and debt detail</t>
+  </si>
+  <si>
+    <t>Summary &amp; Financial Health: Key metrics dashboard</t>
+  </si>
+  <si>
+    <t>Debt Service Convention</t>
+  </si>
+  <si>
+    <t>operating expense on the Operating Statement. This is a standard</t>
+  </si>
+  <si>
+    <t>simplification used in school financial underwriting that ensures internal</t>
+  </si>
+  <si>
+    <t>consistency across all tabs.</t>
+  </si>
+  <si>
+    <t>Tips</t>
+  </si>
+  <si>
+    <t>Check the Financial Health dashboard for an at-a-glance assessment.</t>
+  </si>
+  <si>
+    <t>Review key metrics: net margin, cash runway, and DSCR.</t>
+  </si>
+  <si>
+    <t>Next Steps</t>
+  </si>
+  <si>
+    <t>2. Verify enrollment and revenue projections match your plan.</t>
+  </si>
+  <si>
+    <t>3. Check the Financial Health dashboard for risk signals.</t>
+  </si>
+  <si>
+    <t>4. Share this workbook with your lender or financial advisor.</t>
+  </si>
+  <si>
+    <t>5. Update inputs as your school's plan evolves.</t>
+  </si>
+  <si>
+    <t>Disclaimer</t>
+  </si>
+  <si>
+    <t>a loan commitment, or a guarantee of funding. All projections are based on</t>
+  </si>
+  <si>
+    <t>user-provided assumptions and should be independently verified.</t>
+  </si>
+  <si>
     <t>SCHOOLSTACK BUDGET</t>
   </si>
   <si>
     <t>Lender-Ready Pro Forma</t>
   </si>
   <si>
-    <t>Civic Scholars Charter</t>
-  </si>
-  <si>
     <t>TABLE OF CONTENTS</t>
   </si>
   <si>
@@ -55,94 +142,7 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>Generated March 26, 2026</t>
-  </si>
-  <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>
-  </si>
-  <si>
-    <t>How to Use This Workbook</t>
-  </si>
-  <si>
-    <t>Cell Color Legend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Blue cells are editable inputs — change these to update your model.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  White cells contain formulas — do not edit (they recalculate automatically).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Green cells are key outputs and summary metrics.</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Navigation</t>
-  </si>
-  <si>
-    <t>The Assumptions tab is the central control panel — all other tabs reference it.</t>
-  </si>
-  <si>
-    <t>Structure</t>
-  </si>
-  <si>
-    <t>Assumptions &amp; Drivers: Model inputs and calculations</t>
-  </si>
-  <si>
-    <t>5-Year P&amp;L &amp; Cash Flow: Financial projections</t>
-  </si>
-  <si>
-    <t>Staffing &amp; Loan Snapshot: Personnel and debt detail</t>
-  </si>
-  <si>
-    <t>Summary &amp; Financial Health: Key metrics dashboard</t>
-  </si>
-  <si>
-    <t>Debt Service Convention</t>
-  </si>
-  <si>
-    <t>operating expense on the Operating Statement. This is a standard</t>
-  </si>
-  <si>
-    <t>simplification used in school financial underwriting that ensures internal</t>
-  </si>
-  <si>
-    <t>consistency across all tabs.</t>
-  </si>
-  <si>
-    <t>Tips</t>
-  </si>
-  <si>
-    <t>Check the Financial Health dashboard for an at-a-glance assessment.</t>
-  </si>
-  <si>
-    <t>Review key metrics: net margin, cash runway, and DSCR.</t>
-  </si>
-  <si>
-    <t>Next Steps</t>
-  </si>
-  <si>
-    <t>2. Verify enrollment and revenue projections match your plan.</t>
-  </si>
-  <si>
-    <t>3. Check the Financial Health dashboard for risk signals.</t>
-  </si>
-  <si>
-    <t>4. Share this workbook with your lender or financial advisor.</t>
-  </si>
-  <si>
-    <t>5. Update inputs as your school's plan evolves.</t>
-  </si>
-  <si>
-    <t>Disclaimer</t>
-  </si>
-  <si>
-    <t>a loan commitment, or a guarantee of funding. All projections are based on</t>
-  </si>
-  <si>
-    <t>user-provided assumptions and should be independently verified.</t>
   </si>
   <si>
     <t>SchoolStack Budget - Lender Pro Forma Assumptions</t>
@@ -619,36 +619,7 @@
     <font>
       <b/>
       <color rgb="FF1E293B"/>
-      <sz val="22"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF328555"/>
-      <sz val="14"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF1E293B"/>
       <sz val="16"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF1E293B"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <u/>
-      <color rgb="FF0563C1"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <color rgb="FF6B7280"/>
-      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -663,11 +634,40 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <b/>
+      <color rgb="FF1E293B"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <color rgb="FF1E3A5F"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF1E293B"/>
+      <sz val="22"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF328555"/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0563C1"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF6B7280"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -827,15 +827,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -843,27 +843,27 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -873,7 +873,7 @@
     <xf numFmtId="165" fontId="15" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="15" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -909,10 +909,10 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1412,107 +1412,192 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FF1E293B"/>
+    <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B3:C19"/>
+  <dimension ref="B2:B37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="5" customWidth="1"/>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="1" t="s">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="1"/>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="2"/>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="3"/>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="4" t="s">
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="4"/>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B8" s="6" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B9" s="5" t="s">
-        <v>4</v>
+      <c r="B9" s="7" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="5" t="s">
-        <v>5</v>
+      <c r="B10" s="6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="5" t="s">
-        <v>6</v>
+      <c r="B11" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B13" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="5" t="s">
-        <v>9</v>
+      <c r="B14" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B15" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B16" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="6"/>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="6"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B22" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B30" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B31" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B32" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="6" t="s">
+        <v>29</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="B9" r:id="rId1" location="#'Assumptions'!A1"/>
-    <hyperlink ref="B10" r:id="rId2" location="#'Drivers'!A1"/>
-    <hyperlink ref="B11" r:id="rId3" location="#'5-Year P&amp;L'!A1"/>
-    <hyperlink ref="B12" r:id="rId4" location="#'Cash Flow &amp; DSCR'!A1"/>
-    <hyperlink ref="B13" r:id="rId5" location="#'Staffing'!A1"/>
-    <hyperlink ref="B14" r:id="rId6" location="#'Loan Snapshot'!A1"/>
-    <hyperlink ref="B15" r:id="rId7" location="#'Summary'!A1"/>
-  </hyperlinks>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
@@ -1537,24 +1622,24 @@
   </cols>
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="35" t="s">
@@ -1990,7 +2075,7 @@
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B31" s="42" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="C31" s="27" t="s">
         <v>190</v>
@@ -2121,192 +2206,107 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FF328555"/>
+    <tabColor rgb="FF1E293B"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B37"/>
+  <dimension ref="B3:C19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="80" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B3" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B8" s="11" t="s">
-        <v>16</v>
-      </c>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B3" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="8"/>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="9"/>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1"/>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="10"/>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B9" s="12" t="s">
-        <v>17</v>
+      <c r="B9" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="9" t="s">
-        <v>19</v>
+      <c r="B11" s="11" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B12" s="11" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B13" s="11" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="9" t="s">
-        <v>21</v>
+      <c r="B14" s="11" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B15" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B16" s="11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B19" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B21" s="11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B22" s="11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B24" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B26" s="11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B27" s="11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B28" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B29" s="9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B30" s="11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B31" s="11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B32" s="11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B33" s="11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B34" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B35" s="9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B36" s="11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B37" s="11" t="s">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="12"/>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="12" t="s">
         <v>40</v>
       </c>
+      <c r="C19" s="12"/>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="B9" r:id="rId1" location="#'Assumptions'!A1"/>
+    <hyperlink ref="B10" r:id="rId2" location="#'Drivers'!A1"/>
+    <hyperlink ref="B11" r:id="rId3" location="#'5-Year P&amp;L'!A1"/>
+    <hyperlink ref="B12" r:id="rId4" location="#'Cash Flow &amp; DSCR'!A1"/>
+    <hyperlink ref="B13" r:id="rId5" location="#'Staffing'!A1"/>
+    <hyperlink ref="B14" r:id="rId6" location="#'Loan Snapshot'!A1"/>
+    <hyperlink ref="B15" r:id="rId7" location="#'Summary'!A1"/>
+  </hyperlinks>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
@@ -2339,7 +2339,7 @@
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="14" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>42</v>
@@ -2357,7 +2357,7 @@
         <v>44</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
@@ -4068,10 +4068,10 @@
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="C12" s="6"/>
+      <c r="C12" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="193">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -28,118 +28,121 @@
     <t>Civic Scholars Charter</t>
   </si>
   <si>
+    <t>Generated March 26, 2026 · nonprofit_501c3</t>
+  </si>
+  <si>
+    <t>Cell Color Legend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Blue cells are editable inputs — change these to update your model.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  White cells contain formulas — do not edit (they recalculate automatically).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Green cells are key outputs and summary metrics.</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Navigation</t>
+  </si>
+  <si>
+    <t>The Assumptions tab is the central control panel — all other tabs reference it.</t>
+  </si>
+  <si>
+    <t>Structure</t>
+  </si>
+  <si>
+    <t>Assumptions &amp; Drivers: Model inputs and calculations</t>
+  </si>
+  <si>
+    <t>5-Year P&amp;L &amp; Cash Flow: Financial projections</t>
+  </si>
+  <si>
+    <t>Staffing &amp; Loan Snapshot: Personnel and debt detail</t>
+  </si>
+  <si>
+    <t>Summary &amp; Financial Health: Key metrics dashboard</t>
+  </si>
+  <si>
+    <t>Debt Service Convention</t>
+  </si>
+  <si>
+    <t>operating expense on the Operating Statement. This is a standard</t>
+  </si>
+  <si>
+    <t>simplification used in school financial underwriting that ensures internal</t>
+  </si>
+  <si>
+    <t>consistency across all tabs.</t>
+  </si>
+  <si>
+    <t>Tips</t>
+  </si>
+  <si>
+    <t>Check the Financial Health dashboard for an at-a-glance assessment.</t>
+  </si>
+  <si>
+    <t>Review key metrics: net margin, cash runway, and DSCR.</t>
+  </si>
+  <si>
+    <t>Next Steps</t>
+  </si>
+  <si>
+    <t>2. Verify enrollment and revenue projections match your plan.</t>
+  </si>
+  <si>
+    <t>3. Check the Financial Health dashboard for risk signals.</t>
+  </si>
+  <si>
+    <t>4. Share this workbook with your lender or financial advisor.</t>
+  </si>
+  <si>
+    <t>5. Update inputs as your school's plan evolves.</t>
+  </si>
+  <si>
+    <t>Disclaimer</t>
+  </si>
+  <si>
+    <t>a loan commitment, or a guarantee of funding. All projections are based on</t>
+  </si>
+  <si>
+    <t>user-provided assumptions and should be independently verified.</t>
+  </si>
+  <si>
+    <t>SCHOOLSTACK BUDGET</t>
+  </si>
+  <si>
+    <t>Lender-Ready Pro Forma</t>
+  </si>
+  <si>
+    <t>TABLE OF CONTENTS</t>
+  </si>
+  <si>
+    <t>Assumptions</t>
+  </si>
+  <si>
+    <t>Drivers</t>
+  </si>
+  <si>
+    <t>5-Year P&amp;L</t>
+  </si>
+  <si>
+    <t>Cash Flow &amp; DSCR</t>
+  </si>
+  <si>
+    <t>Staffing</t>
+  </si>
+  <si>
+    <t>Loan Snapshot</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
     <t>Generated March 26, 2026</t>
-  </si>
-  <si>
-    <t>Cell Color Legend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Blue cells are editable inputs — change these to update your model.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  White cells contain formulas — do not edit (they recalculate automatically).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Green cells are key outputs and summary metrics.</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Navigation</t>
-  </si>
-  <si>
-    <t>The Assumptions tab is the central control panel — all other tabs reference it.</t>
-  </si>
-  <si>
-    <t>Structure</t>
-  </si>
-  <si>
-    <t>Assumptions &amp; Drivers: Model inputs and calculations</t>
-  </si>
-  <si>
-    <t>5-Year P&amp;L &amp; Cash Flow: Financial projections</t>
-  </si>
-  <si>
-    <t>Staffing &amp; Loan Snapshot: Personnel and debt detail</t>
-  </si>
-  <si>
-    <t>Summary &amp; Financial Health: Key metrics dashboard</t>
-  </si>
-  <si>
-    <t>Debt Service Convention</t>
-  </si>
-  <si>
-    <t>operating expense on the Operating Statement. This is a standard</t>
-  </si>
-  <si>
-    <t>simplification used in school financial underwriting that ensures internal</t>
-  </si>
-  <si>
-    <t>consistency across all tabs.</t>
-  </si>
-  <si>
-    <t>Tips</t>
-  </si>
-  <si>
-    <t>Check the Financial Health dashboard for an at-a-glance assessment.</t>
-  </si>
-  <si>
-    <t>Review key metrics: net margin, cash runway, and DSCR.</t>
-  </si>
-  <si>
-    <t>Next Steps</t>
-  </si>
-  <si>
-    <t>2. Verify enrollment and revenue projections match your plan.</t>
-  </si>
-  <si>
-    <t>3. Check the Financial Health dashboard for risk signals.</t>
-  </si>
-  <si>
-    <t>4. Share this workbook with your lender or financial advisor.</t>
-  </si>
-  <si>
-    <t>5. Update inputs as your school's plan evolves.</t>
-  </si>
-  <si>
-    <t>Disclaimer</t>
-  </si>
-  <si>
-    <t>a loan commitment, or a guarantee of funding. All projections are based on</t>
-  </si>
-  <si>
-    <t>user-provided assumptions and should be independently verified.</t>
-  </si>
-  <si>
-    <t>SCHOOLSTACK BUDGET</t>
-  </si>
-  <si>
-    <t>Lender-Ready Pro Forma</t>
-  </si>
-  <si>
-    <t>TABLE OF CONTENTS</t>
-  </si>
-  <si>
-    <t>Assumptions</t>
-  </si>
-  <si>
-    <t>Drivers</t>
-  </si>
-  <si>
-    <t>5-Year P&amp;L</t>
-  </si>
-  <si>
-    <t>Cash Flow &amp; DSCR</t>
-  </si>
-  <si>
-    <t>Staffing</t>
-  </si>
-  <si>
-    <t>Loan Snapshot</t>
-  </si>
-  <si>
-    <t>Summary</t>
   </si>
   <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>
@@ -1623,7 +1626,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1633,7 +1636,7 @@
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="12" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
@@ -1643,27 +1646,27 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="35" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="24" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C6" s="25">
         <v>120</v>
@@ -1683,7 +1686,7 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="24" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C7" s="26">
         <v>1546000</v>
@@ -1703,7 +1706,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="24" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C8" s="26">
         <v>1200167.1888888888</v>
@@ -1723,7 +1726,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="24" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C9" s="26">
         <v>654000</v>
@@ -1743,7 +1746,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="24" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C10" s="26">
         <v>164824.60522117943</v>
@@ -1763,7 +1766,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="27" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C11" s="29">
         <v>-472991.79411006824</v>
@@ -1783,7 +1786,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="27" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C12" s="29">
         <v>-472991.79411006824</v>
@@ -1803,7 +1806,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="27" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C13" s="37">
         <v>-0.3059455330595525</v>
@@ -1823,7 +1826,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="27" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C14" s="26">
         <v>12883.333333333334</v>
@@ -1843,7 +1846,7 @@
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="27" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C15" s="37">
         <v>0.7763047793589191</v>
@@ -1863,7 +1866,7 @@
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="27" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C16" s="39">
         <v>0.12690815006468306</v>
@@ -1883,7 +1886,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="27" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C17" s="37">
         <v>-0.19933194624119585</v>
@@ -1903,7 +1906,7 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="27" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C18" s="40">
         <v>-1.8696673865856184</v>
@@ -1923,10 +1926,10 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="27" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C19" s="41" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D19" s="41"/>
       <c r="E19" s="41"/>
@@ -1935,10 +1938,10 @@
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="27" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C20" s="41" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D20" s="41"/>
       <c r="E20" s="41"/>
@@ -1947,129 +1950,129 @@
     </row>
     <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="35" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D22" s="35" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E22" s="35"/>
       <c r="F22" s="35" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G22" s="35"/>
     </row>
     <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="42" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C23" s="43" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D23" s="44" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E23" s="44"/>
       <c r="F23" s="45" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G23" s="45"/>
     </row>
     <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="42" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C24" s="43" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D24" s="44" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E24" s="44"/>
       <c r="F24" s="45" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G24" s="45"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="42" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C25" s="46" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D25" s="44" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E25" s="44"/>
       <c r="F25" s="45" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G25" s="45"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B26" s="42" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C26" s="43" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D26" s="44" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E26" s="44"/>
       <c r="F26" s="45" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G26" s="45"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27" s="42" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C27" s="43" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D27" s="44" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E27" s="44"/>
       <c r="F27" s="45" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G27" s="45"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B28" s="42" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C28" s="47" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D28" s="44" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E28" s="44"/>
       <c r="F28" s="45" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G28" s="45"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B29" s="42" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C29" s="43" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D29" s="44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E29" s="44"/>
       <c r="F29" s="45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G29" s="45"/>
     </row>
@@ -2078,14 +2081,14 @@
         <v>39</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D31" s="27"/>
       <c r="E31" s="27"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B33" s="48" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C33" s="48"/>
       <c r="D33" s="48"/>
@@ -2279,13 +2282,13 @@
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="12" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C18" s="12"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C19" s="12"/>
     </row>
@@ -2332,7 +2335,7 @@
   <sheetData>
     <row r="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -2342,19 +2345,19 @@
         <v>7</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" s="16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C3" s="16"/>
       <c r="D3" s="16"/>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D5" s="18" t="s">
         <v>1</v>
@@ -2362,23 +2365,23 @@
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" s="17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" s="17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" s="17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D8" s="18">
         <v>2026</v>
@@ -2386,14 +2389,14 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="16"/>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D12" s="19">
         <v>120</v>
@@ -2401,7 +2404,7 @@
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D13" s="19">
         <v>200</v>
@@ -2409,7 +2412,7 @@
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" s="17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" s="19">
         <v>300</v>
@@ -2417,7 +2420,7 @@
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" s="17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15" s="19">
         <v>375</v>
@@ -2425,7 +2428,7 @@
     </row>
     <row r="16" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C16" s="17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D16" s="19">
         <v>400</v>
@@ -2433,14 +2436,14 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C18" s="16"/>
       <c r="D18" s="16"/>
     </row>
     <row r="20" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C20" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D20" s="20">
         <v>0</v>
@@ -2448,7 +2451,7 @@
     </row>
     <row r="21" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C21" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D21" s="21">
         <v>0.03</v>
@@ -2456,7 +2459,7 @@
     </row>
     <row r="22" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C22" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D22" s="20">
         <v>11500</v>
@@ -2464,7 +2467,7 @@
     </row>
     <row r="23" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C23" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D23" s="21">
         <v>0.02</v>
@@ -2472,7 +2475,7 @@
     </row>
     <row r="24" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C24" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D24" s="20">
         <v>300</v>
@@ -2480,7 +2483,7 @@
     </row>
     <row r="25" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C25" s="17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D25" s="21">
         <v>0.03</v>
@@ -2488,7 +2491,7 @@
     </row>
     <row r="26" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C26" s="17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D26" s="21">
         <v>0.95</v>
@@ -2496,7 +2499,7 @@
     </row>
     <row r="27" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C27" s="17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D27" s="20">
         <v>130000</v>
@@ -2504,7 +2507,7 @@
     </row>
     <row r="28" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C28" s="17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D28" s="21">
         <v>0</v>
@@ -2512,14 +2515,14 @@
     </row>
     <row r="30" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
     </row>
     <row r="32" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C32" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D32" s="19">
         <v>12</v>
@@ -2527,7 +2530,7 @@
     </row>
     <row r="33" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C33" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D33" s="20">
         <v>45667</v>
@@ -2535,7 +2538,7 @@
     </row>
     <row r="34" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C34" s="17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D34" s="21">
         <v>0.03</v>
@@ -2543,7 +2546,7 @@
     </row>
     <row r="35" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C35" s="17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D35" s="19">
         <v>7</v>
@@ -2551,7 +2554,7 @@
     </row>
     <row r="36" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C36" s="17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D36" s="19">
         <v>7</v>
@@ -2559,7 +2562,7 @@
     </row>
     <row r="37" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C37" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D37" s="19">
         <v>7</v>
@@ -2567,7 +2570,7 @@
     </row>
     <row r="38" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C38" s="17" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D38" s="19">
         <v>7</v>
@@ -2575,7 +2578,7 @@
     </row>
     <row r="39" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C39" s="17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D39" s="19">
         <v>7</v>
@@ -2583,7 +2586,7 @@
     </row>
     <row r="40" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C40" s="17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D40" s="20">
         <v>70000</v>
@@ -2591,7 +2594,7 @@
     </row>
     <row r="41" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C41" s="17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D41" s="21">
         <v>0.03</v>
@@ -2599,7 +2602,7 @@
     </row>
     <row r="42" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C42" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D42" s="21">
         <v>0.2677777777777778</v>
@@ -2607,14 +2610,14 @@
     </row>
     <row r="44" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B44" s="16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C44" s="16"/>
       <c r="D44" s="16"/>
     </row>
     <row r="46" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C46" s="17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D46" s="20">
         <v>282000</v>
@@ -2622,7 +2625,7 @@
     </row>
     <row r="47" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C47" s="17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D47" s="21">
         <v>0.03</v>
@@ -2630,7 +2633,7 @@
     </row>
     <row r="48" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C48" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D48" s="20">
         <v>0</v>
@@ -2638,7 +2641,7 @@
     </row>
     <row r="49" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C49" s="17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D49" s="21">
         <v>0.03</v>
@@ -2646,7 +2649,7 @@
     </row>
     <row r="50" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C50" s="17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D50" s="20">
         <v>700</v>
@@ -2654,7 +2657,7 @@
     </row>
     <row r="51" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C51" s="17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D51" s="21">
         <v>0.7166666666666667</v>
@@ -2662,7 +2665,7 @@
     </row>
     <row r="52" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C52" s="17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D52" s="20">
         <v>288000</v>
@@ -2670,7 +2673,7 @@
     </row>
     <row r="53" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C53" s="17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D53" s="21">
         <v>0.5736111111111111</v>
@@ -2678,14 +2681,14 @@
     </row>
     <row r="55" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B55" s="16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C55" s="16"/>
       <c r="D55" s="16"/>
     </row>
     <row r="57" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C57" s="17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D57" s="20">
         <v>0</v>
@@ -2693,7 +2696,7 @@
     </row>
     <row r="58" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C58" s="17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D58" s="20">
         <v>115000</v>
@@ -2701,7 +2704,7 @@
     </row>
     <row r="59" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C59" s="17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D59" s="20">
         <v>500000</v>
@@ -2709,7 +2712,7 @@
     </row>
     <row r="60" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C60" s="17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D60" s="21">
         <v>0.0575</v>
@@ -2717,7 +2720,7 @@
     </row>
     <row r="61" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C61" s="17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D61" s="19">
         <v>15</v>
@@ -2757,7 +2760,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -2768,24 +2771,24 @@
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="22"/>
       <c r="C3" s="23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E3" s="23" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F3" s="23" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="24" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" s="25">
         <f>Assumptions!D12</f>
@@ -2810,7 +2813,7 @@
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="24" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C5" s="26" t="str">
         <f>Assumptions!D12*Assumptions!D20</f>
@@ -2835,7 +2838,7 @@
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="24" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C6" s="26" t="str">
         <f>C5*Assumptions!D26</f>
@@ -2860,7 +2863,7 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="24" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C7" s="26">
         <f>Assumptions!D12*Assumptions!D22</f>
@@ -2885,7 +2888,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C8" s="26">
         <f>Assumptions!D12*Assumptions!D24</f>
@@ -2910,7 +2913,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="24" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C9" s="26">
         <f>Assumptions!D27</f>
@@ -2935,7 +2938,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="27" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C10" s="28">
         <f>C6+C7+C8+C9</f>
@@ -2960,7 +2963,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="24" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C12" s="25">
         <f>CEILING(Assumptions!D12/Assumptions!D32,1)</f>
@@ -2985,7 +2988,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="24" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C13" s="26">
         <f>C12*Assumptions!D33</f>
@@ -3010,7 +3013,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C14" s="26">
         <f>Assumptions!D35*Assumptions!D40</f>
@@ -3035,7 +3038,7 @@
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C15" s="26">
         <f>(C13+C14)*Assumptions!D42</f>
@@ -3060,7 +3063,7 @@
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C16" s="28">
         <f>C13+C14+C15</f>
@@ -3085,7 +3088,7 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C18" s="26">
         <f>Assumptions!D46</f>
@@ -3110,7 +3113,7 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="24" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C19" s="26" t="str">
         <f>Assumptions!D48</f>
@@ -3135,7 +3138,7 @@
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="24" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C20" s="26">
         <f>Assumptions!D12*Assumptions!D50</f>
@@ -3160,7 +3163,7 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="24" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C21" s="26">
         <f>Assumptions!D52</f>
@@ -3185,7 +3188,7 @@
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C22" s="28">
         <f>C18+C19+C20+C21</f>
@@ -3236,7 +3239,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -3247,24 +3250,24 @@
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="22"/>
       <c r="C3" s="23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E3" s="23" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F3" s="23" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="24" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C5" s="25">
         <f>Drivers!C4</f>
@@ -3289,7 +3292,7 @@
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="24" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C6" s="26" t="str">
         <f>Drivers!C6</f>
@@ -3314,7 +3317,7 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="24" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C7" s="26">
         <f>Drivers!C7</f>
@@ -3339,7 +3342,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="24" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C8" s="26">
         <f>Drivers!C8</f>
@@ -3364,7 +3367,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="24" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C9" s="26">
         <f>Drivers!C9</f>
@@ -3389,7 +3392,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="27" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C10" s="28">
         <f>Drivers!C10</f>
@@ -3414,7 +3417,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C12" s="26">
         <f>Drivers!C16</f>
@@ -3439,7 +3442,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="24" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C13" s="26">
         <f>Drivers!C22</f>
@@ -3464,7 +3467,7 @@
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="27" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C15" s="28">
         <f>C12+C13</f>
@@ -3489,7 +3492,7 @@
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="27" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C16" s="29">
         <f>C10-C15</f>
@@ -3514,7 +3517,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="24" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C17" s="30">
         <f>IF(C10&gt;0,C16/C10,0)</f>
@@ -3565,7 +3568,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -3576,24 +3579,24 @@
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="22"/>
       <c r="C3" s="23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E3" s="23" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F3" s="23" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="24" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C4" s="26">
         <f>'5-Year P&amp;L'!C16</f>
@@ -3618,7 +3621,7 @@
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="24" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C6" s="26">
         <f>Assumptions!D58</f>
@@ -3643,7 +3646,7 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C7" s="26">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
@@ -3668,7 +3671,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="27" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C8" s="28">
         <f>C6+C7</f>
@@ -3693,7 +3696,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="27" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C10" s="31">
         <f>IF(C8&gt;0,C4/C8,IF(C4&gt;0,99.9,0))</f>
@@ -3718,7 +3721,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="24" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C12" s="26">
         <f>C4-C8</f>
@@ -3743,7 +3746,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="27" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C14" s="32">
         <f>Assumptions!D57+C12</f>
@@ -3794,7 +3797,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -3805,24 +3808,24 @@
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="22"/>
       <c r="C3" s="23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E3" s="23" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F3" s="23" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="24" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C4" s="25">
         <f>Drivers!C12</f>
@@ -3847,7 +3850,7 @@
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="24" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C5" s="25">
         <f>Assumptions!D35</f>
@@ -3872,7 +3875,7 @@
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="27" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C6" s="33">
         <f>C4+C5</f>
@@ -3923,13 +3926,13 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C1" s="13"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="24" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C3" s="26">
         <f>Assumptions!D59</f>
@@ -3938,7 +3941,7 @@
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="24" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C4" s="30">
         <f>Assumptions!D60</f>
@@ -3947,7 +3950,7 @@
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C5" s="25">
         <f>Assumptions!D61</f>
@@ -3956,7 +3959,7 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="24" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C6" s="34">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
@@ -3965,7 +3968,7 @@
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="24" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C8" s="31">
         <f>'Cash Flow &amp; DSCR'!C10</f>
@@ -4000,13 +4003,13 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C1" s="13"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" s="24" t="str">
         <f>Assumptions!D5</f>
@@ -4015,7 +4018,7 @@
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4" s="24" t="str">
         <f>Assumptions!D7</f>
@@ -4024,7 +4027,7 @@
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C5" s="24" t="str">
         <f>Assumptions!D6</f>
@@ -4033,7 +4036,7 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="24" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C6" s="24">
         <f>Assumptions!D8</f>
@@ -4042,7 +4045,7 @@
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="24" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C8" s="25">
         <f>Assumptions!D16</f>
@@ -4051,7 +4054,7 @@
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="24" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C9" s="26">
         <f>Drivers!G10</f>
@@ -4060,7 +4063,7 @@
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="24" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C10" s="32">
         <f>'5-Year P&amp;L'!G16</f>
@@ -4069,7 +4072,7 @@
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C12" s="12"/>
     </row>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
@@ -611,7 +611,7 @@
     <numFmt numFmtId="166" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -679,6 +679,9 @@
       <color rgb="FF1E293B"/>
       <sz val="14"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF1E3A5F"/>
     </font>
     <font>
       <i/>
@@ -840,26 +843,26 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -869,47 +872,47 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="16" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="16" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="16" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="16" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -918,13 +921,13 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="194">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -151,7 +151,10 @@
     <t>SchoolStack Budget - Lender Pro Forma Assumptions</t>
   </si>
   <si>
-    <t>Blue cells are editable inputs</t>
+    <t>Editable assumption — change this value</t>
+  </si>
+  <si>
+    <t>Calculated — driven by formula</t>
   </si>
   <si>
     <t>SCHOOL PROFILE</t>
@@ -730,7 +733,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -745,6 +748,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -768,7 +776,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -782,6 +790,15 @@
       <top/>
       <bottom style="medium">
         <color rgb="FF328555"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
       </bottom>
       <diagonal/>
     </border>
@@ -828,7 +845,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -845,86 +862,87 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="165" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="16" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1629,7 +1647,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1648,456 +1666,456 @@
       <c r="G3" s="12"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="35" t="s">
-        <v>147</v>
-      </c>
-      <c r="C5" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="D5" s="36" t="s">
+      <c r="B5" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="C5" s="37" t="s">
         <v>96</v>
       </c>
-      <c r="E5" s="36" t="s">
+      <c r="D5" s="37" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="36" t="s">
+      <c r="E5" s="37" t="s">
         <v>98</v>
       </c>
-      <c r="G5" s="36" t="s">
+      <c r="F5" s="37" t="s">
         <v>99</v>
       </c>
+      <c r="G5" s="37" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="C6" s="25">
+      <c r="B6" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="26">
         <v>120</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="26">
         <v>200</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="26">
         <v>300</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="26">
         <v>375</v>
       </c>
-      <c r="G6" s="25">
+      <c r="G6" s="26">
         <v>400</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="C7" s="26">
+      <c r="B7" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="C7" s="27">
         <v>1546000</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="27">
         <v>2537800</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="27">
         <v>3814861</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="27">
         <v>4829391.287500001</v>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="27">
         <v>5244248.993199999</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="C8" s="26">
+      <c r="B8" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="C8" s="27">
         <v>1200167.1888888888</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="27">
         <v>1653599.5366333332</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="27">
         <v>2194579.1250638887</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="27">
         <v>2703265.15541712</v>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="27">
         <v>2914687.143308021</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="C9" s="26">
+      <c r="B9" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="C9" s="27">
         <v>654000</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="27">
         <v>983993.3333333334</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="27">
         <v>1631192.688888889</v>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="27">
         <v>2758353.228506173</v>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="27">
         <v>4515013.522229714</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="24" t="s">
-        <v>151</v>
-      </c>
-      <c r="C10" s="26">
+      <c r="B10" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="C10" s="27">
         <v>164824.60522117943</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="27">
         <v>164824.60522117943</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="27">
         <v>164824.60522117943</v>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="27">
         <v>164824.60522117943</v>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="27">
         <v>164824.60522117943</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="27" t="s">
-        <v>152</v>
-      </c>
-      <c r="C11" s="29">
+      <c r="B11" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="C11" s="30">
         <v>-472991.79411006824</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="30">
         <v>-264617.4751878461</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="30">
         <v>-175735.41917395697</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="30">
         <v>-797051.701644472</v>
       </c>
-      <c r="G11" s="29">
+      <c r="G11" s="30">
         <v>-2350276.2775589153</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="27" t="s">
-        <v>153</v>
-      </c>
-      <c r="C12" s="29">
+      <c r="B12" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="C12" s="30">
         <v>-472991.79411006824</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="30">
         <v>-737609.2692979143</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="30">
         <v>-913344.6884718713</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="30">
         <v>-1710396.3901163433</v>
       </c>
-      <c r="G12" s="29">
+      <c r="G12" s="30">
         <v>-4060672.6676752586</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="C13" s="37">
+      <c r="B13" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="C13" s="38">
         <v>-0.3059455330595525</v>
       </c>
-      <c r="D13" s="37">
+      <c r="D13" s="38">
         <v>-0.10427042130500674</v>
       </c>
-      <c r="E13" s="37">
+      <c r="E13" s="38">
         <v>-0.046066008479458874</v>
       </c>
-      <c r="F13" s="37">
+      <c r="F13" s="38">
         <v>-0.16504185604249857</v>
       </c>
-      <c r="G13" s="37">
+      <c r="G13" s="38">
         <v>-0.44816260261601254</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="27" t="s">
-        <v>155</v>
-      </c>
-      <c r="C14" s="26">
+      <c r="B14" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="C14" s="27">
         <v>12883.333333333334</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="27">
         <v>12689</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="27">
         <v>12716.203333333333</v>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="27">
         <v>12878.376766666668</v>
       </c>
-      <c r="G14" s="26">
+      <c r="G14" s="27">
         <v>13110.622483</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="27" t="s">
-        <v>156</v>
-      </c>
-      <c r="C15" s="37">
+      <c r="B15" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="C15" s="38">
         <v>0.7763047793589191</v>
       </c>
-      <c r="D15" s="37">
+      <c r="D15" s="38">
         <v>0.6515878070113221</v>
       </c>
-      <c r="E15" s="38">
+      <c r="E15" s="39">
         <v>0.5752710583855843</v>
       </c>
-      <c r="F15" s="38">
+      <c r="F15" s="39">
         <v>0.5597527709991174</v>
       </c>
-      <c r="G15" s="38">
+      <c r="G15" s="39">
         <v>0.5557873295275215</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="27" t="s">
-        <v>157</v>
-      </c>
-      <c r="C16" s="39">
+      <c r="B16" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="C16" s="40">
         <v>0.12690815006468306</v>
       </c>
-      <c r="D16" s="39">
+      <c r="D16" s="40">
         <v>0.1163204350224604</v>
       </c>
-      <c r="E16" s="39">
+      <c r="E16" s="40">
         <v>0.1282767069800621</v>
       </c>
-      <c r="F16" s="38">
+      <c r="F16" s="39">
         <v>0.1713478820185269</v>
       </c>
-      <c r="G16" s="37">
+      <c r="G16" s="38">
         <v>0.25828370438269493</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="27" t="s">
-        <v>123</v>
-      </c>
-      <c r="C17" s="37">
+      <c r="B17" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="C17" s="38">
         <v>-0.19933194624119585</v>
       </c>
-      <c r="D17" s="37">
+      <c r="D17" s="38">
         <v>-0.039322590419523434</v>
       </c>
-      <c r="E17" s="37">
+      <c r="E17" s="38">
         <v>-0.0028600816524580494</v>
       </c>
-      <c r="F17" s="37">
+      <c r="F17" s="38">
         <v>-0.13091237772754036</v>
       </c>
-      <c r="G17" s="37">
+      <c r="G17" s="38">
         <v>-0.4167330108031714</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="C18" s="40">
+      <c r="B18" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="C18" s="41">
         <v>-1.8696673865856184</v>
       </c>
-      <c r="D18" s="40">
+      <c r="D18" s="41">
         <v>-0.6054488638559378</v>
       </c>
-      <c r="E18" s="40">
+      <c r="E18" s="41">
         <v>-0.06619651197184098</v>
       </c>
-      <c r="F18" s="40">
+      <c r="F18" s="41">
         <v>-3.8357567765741165</v>
       </c>
-      <c r="G18" s="40">
+      <c r="G18" s="41">
         <v>-13.259256222122064</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="27" t="s">
-        <v>159</v>
-      </c>
-      <c r="C19" s="41" t="s">
+      <c r="B19" s="28" t="s">
         <v>160</v>
       </c>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
+      <c r="C19" s="42" t="s">
+        <v>161</v>
+      </c>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="27" t="s">
-        <v>161</v>
-      </c>
-      <c r="C20" s="41" t="s">
+      <c r="B20" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="D20" s="41"/>
-      <c r="E20" s="41"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="41"/>
+      <c r="C20" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
     </row>
     <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="35" t="s">
-        <v>163</v>
-      </c>
-      <c r="C22" s="35" t="s">
+      <c r="B22" s="36" t="s">
         <v>164</v>
       </c>
-      <c r="D22" s="35" t="s">
+      <c r="C22" s="36" t="s">
         <v>165</v>
       </c>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35" t="s">
+      <c r="D22" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="G22" s="35"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36" t="s">
+        <v>167</v>
+      </c>
+      <c r="G22" s="36"/>
     </row>
     <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="42" t="s">
-        <v>167</v>
-      </c>
-      <c r="C23" s="43" t="s">
+      <c r="B23" s="43" t="s">
         <v>168</v>
       </c>
-      <c r="D23" s="44" t="s">
+      <c r="C23" s="44" t="s">
         <v>169</v>
       </c>
-      <c r="E23" s="44"/>
-      <c r="F23" s="45" t="s">
+      <c r="D23" s="45" t="s">
         <v>170</v>
       </c>
-      <c r="G23" s="45"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="46" t="s">
+        <v>171</v>
+      </c>
+      <c r="G23" s="46"/>
     </row>
     <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="42" t="s">
-        <v>171</v>
-      </c>
-      <c r="C24" s="43" t="s">
-        <v>168</v>
-      </c>
-      <c r="D24" s="44" t="s">
+      <c r="B24" s="43" t="s">
         <v>172</v>
       </c>
-      <c r="E24" s="44"/>
-      <c r="F24" s="45" t="s">
+      <c r="C24" s="44" t="s">
+        <v>169</v>
+      </c>
+      <c r="D24" s="45" t="s">
         <v>173</v>
       </c>
-      <c r="G24" s="45"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="46" t="s">
+        <v>174</v>
+      </c>
+      <c r="G24" s="46"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="42" t="s">
-        <v>174</v>
-      </c>
-      <c r="C25" s="46" t="s">
+      <c r="B25" s="43" t="s">
         <v>175</v>
       </c>
-      <c r="D25" s="44" t="s">
+      <c r="C25" s="47" t="s">
         <v>176</v>
       </c>
-      <c r="E25" s="44"/>
-      <c r="F25" s="45" t="s">
+      <c r="D25" s="45" t="s">
         <v>177</v>
       </c>
-      <c r="G25" s="45"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="46" t="s">
+        <v>178</v>
+      </c>
+      <c r="G25" s="46"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="42" t="s">
-        <v>178</v>
-      </c>
-      <c r="C26" s="43" t="s">
-        <v>168</v>
-      </c>
-      <c r="D26" s="44" t="s">
+      <c r="B26" s="43" t="s">
         <v>179</v>
       </c>
-      <c r="E26" s="44"/>
-      <c r="F26" s="45" t="s">
+      <c r="C26" s="44" t="s">
+        <v>169</v>
+      </c>
+      <c r="D26" s="45" t="s">
         <v>180</v>
       </c>
-      <c r="G26" s="45"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="G26" s="46"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="42" t="s">
-        <v>181</v>
-      </c>
-      <c r="C27" s="43" t="s">
-        <v>168</v>
-      </c>
-      <c r="D27" s="44" t="s">
+      <c r="B27" s="43" t="s">
         <v>182</v>
       </c>
-      <c r="E27" s="44"/>
-      <c r="F27" s="45" t="s">
+      <c r="C27" s="44" t="s">
+        <v>169</v>
+      </c>
+      <c r="D27" s="45" t="s">
         <v>183</v>
       </c>
-      <c r="G27" s="45"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="46" t="s">
+        <v>184</v>
+      </c>
+      <c r="G27" s="46"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="42" t="s">
-        <v>184</v>
-      </c>
-      <c r="C28" s="47" t="s">
+      <c r="B28" s="43" t="s">
         <v>185</v>
       </c>
-      <c r="D28" s="44" t="s">
+      <c r="C28" s="48" t="s">
         <v>186</v>
       </c>
-      <c r="E28" s="44"/>
-      <c r="F28" s="45" t="s">
+      <c r="D28" s="45" t="s">
         <v>187</v>
       </c>
-      <c r="G28" s="45"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="46" t="s">
+        <v>188</v>
+      </c>
+      <c r="G28" s="46"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="42" t="s">
-        <v>188</v>
-      </c>
-      <c r="C29" s="43" t="s">
-        <v>168</v>
-      </c>
-      <c r="D29" s="44" t="s">
+      <c r="B29" s="43" t="s">
         <v>189</v>
       </c>
-      <c r="E29" s="44"/>
-      <c r="F29" s="45" t="s">
+      <c r="C29" s="44" t="s">
+        <v>169</v>
+      </c>
+      <c r="D29" s="45" t="s">
         <v>190</v>
       </c>
-      <c r="G29" s="45"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="46" t="s">
+        <v>191</v>
+      </c>
+      <c r="G29" s="46"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B31" s="42" t="s">
+      <c r="B31" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="C31" s="27" t="s">
-        <v>191</v>
-      </c>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
+      <c r="C31" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="48" t="s">
-        <v>192</v>
-      </c>
-      <c r="C33" s="48"/>
-      <c r="D33" s="48"/>
-      <c r="E33" s="48"/>
-      <c r="F33" s="48"/>
-      <c r="G33" s="48"/>
+      <c r="B33" s="49" t="s">
+        <v>193</v>
+      </c>
+      <c r="C33" s="49"/>
+      <c r="D33" s="49"/>
+      <c r="E33" s="49"/>
+      <c r="F33" s="49"/>
+      <c r="G33" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -2343,389 +2361,392 @@
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
     </row>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B2" s="14" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>43</v>
       </c>
+      <c r="D2" s="16" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
+      <c r="B3" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C5" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="18" t="s">
+      <c r="C5" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="19" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C6" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="18" t="s">
+      <c r="C6" s="18" t="s">
         <v>47</v>
       </c>
+      <c r="D6" s="19" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C7" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="18" t="s">
+      <c r="C7" s="18" t="s">
         <v>49</v>
       </c>
+      <c r="D7" s="19" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C8" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="18">
+      <c r="C8" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="19">
         <v>2026</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
+      <c r="B10" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C12" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="19">
+      <c r="C12" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="20">
         <v>120</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C13" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" s="19">
+      <c r="C13" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="20">
         <v>200</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C14" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="D14" s="19">
+      <c r="C14" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="20">
         <v>300</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C15" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15" s="19">
+      <c r="C15" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="20">
         <v>375</v>
       </c>
     </row>
     <row r="16" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C16" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D16" s="19">
+      <c r="C16" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="20">
         <v>400</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
+      <c r="B18" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
     </row>
     <row r="20" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C20" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20" s="20">
+      <c r="C20" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C21" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="D21" s="21">
+      <c r="C21" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="22">
         <v>0.03</v>
       </c>
     </row>
     <row r="22" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C22" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="D22" s="20">
+      <c r="C22" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="21">
         <v>11500</v>
       </c>
     </row>
     <row r="23" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C23" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D23" s="21">
+      <c r="C23" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" s="22">
         <v>0.02</v>
       </c>
     </row>
     <row r="24" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C24" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="D24" s="20">
+      <c r="C24" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" s="21">
         <v>300</v>
       </c>
     </row>
     <row r="25" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C25" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="D25" s="21">
+      <c r="C25" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" s="22">
         <v>0.03</v>
       </c>
     </row>
     <row r="26" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C26" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="D26" s="21">
+      <c r="C26" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" s="22">
         <v>0.95</v>
       </c>
     </row>
     <row r="27" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C27" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="D27" s="20">
+      <c r="C27" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="21">
         <v>130000</v>
       </c>
     </row>
     <row r="28" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C28" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="D28" s="21">
+      <c r="C28" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B30" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
+      <c r="B30" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
     </row>
     <row r="32" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C32" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="D32" s="19">
+      <c r="C32" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D32" s="20">
         <v>12</v>
       </c>
     </row>
     <row r="33" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C33" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="D33" s="20">
+      <c r="C33" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="D33" s="21">
         <v>45667</v>
       </c>
     </row>
     <row r="34" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C34" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D34" s="21">
+      <c r="C34" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="D34" s="22">
         <v>0.03</v>
       </c>
     </row>
     <row r="35" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C35" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="D35" s="19">
+      <c r="C35" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="D35" s="20">
         <v>7</v>
       </c>
     </row>
     <row r="36" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C36" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="D36" s="19">
+      <c r="C36" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="D36" s="20">
         <v>7</v>
       </c>
     </row>
     <row r="37" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C37" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="D37" s="19">
+      <c r="C37" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="D37" s="20">
         <v>7</v>
       </c>
     </row>
     <row r="38" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C38" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="D38" s="19">
+      <c r="C38" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="D38" s="20">
         <v>7</v>
       </c>
     </row>
     <row r="39" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C39" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="D39" s="19">
+      <c r="C39" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="D39" s="20">
         <v>7</v>
       </c>
     </row>
     <row r="40" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C40" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="D40" s="20">
+      <c r="C40" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D40" s="21">
         <v>70000</v>
       </c>
     </row>
     <row r="41" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C41" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="D41" s="21">
+      <c r="C41" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="D41" s="22">
         <v>0.03</v>
       </c>
     </row>
     <row r="42" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C42" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="D42" s="21">
+      <c r="C42" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="D42" s="22">
         <v>0.2677777777777778</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B44" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C44" s="16"/>
-      <c r="D44" s="16"/>
+      <c r="B44" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
     </row>
     <row r="46" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C46" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="D46" s="20">
+      <c r="C46" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="D46" s="21">
         <v>282000</v>
       </c>
     </row>
     <row r="47" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C47" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="D47" s="21">
+      <c r="C47" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="D47" s="22">
         <v>0.03</v>
       </c>
     </row>
     <row r="48" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C48" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="D48" s="20">
+      <c r="C48" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="D48" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C49" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="D49" s="21">
+      <c r="C49" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="D49" s="22">
         <v>0.03</v>
       </c>
     </row>
     <row r="50" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C50" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="D50" s="20">
+      <c r="C50" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="D50" s="21">
         <v>700</v>
       </c>
     </row>
     <row r="51" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C51" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="D51" s="21">
+      <c r="C51" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="D51" s="22">
         <v>0.7166666666666667</v>
       </c>
     </row>
     <row r="52" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C52" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="D52" s="20">
+      <c r="C52" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D52" s="21">
         <v>288000</v>
       </c>
     </row>
     <row r="53" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C53" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="D53" s="21">
+      <c r="C53" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="D53" s="22">
         <v>0.5736111111111111</v>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B55" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="C55" s="16"/>
-      <c r="D55" s="16"/>
+      <c r="B55" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C55" s="17"/>
+      <c r="D55" s="17"/>
     </row>
     <row r="57" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C57" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="D57" s="20">
+      <c r="C57" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="D57" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C58" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="D58" s="20">
+      <c r="C58" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="D58" s="21">
         <v>115000</v>
       </c>
     </row>
     <row r="59" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C59" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="D59" s="20">
+      <c r="C59" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="D59" s="21">
         <v>500000</v>
       </c>
     </row>
     <row r="60" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C60" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="D60" s="21">
+      <c r="C60" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="D60" s="22">
         <v>0.0575</v>
       </c>
     </row>
     <row r="61" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C61" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="D61" s="19">
+      <c r="C61" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="D61" s="20">
         <v>15</v>
       </c>
     </row>
@@ -2763,7 +2784,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -2772,444 +2793,444 @@
       <c r="G1" s="13"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="22"/>
-      <c r="C3" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" s="23" t="s">
+      <c r="B3" s="23"/>
+      <c r="C3" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="D3" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="E3" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="G3" s="23" t="s">
+      <c r="F3" s="24" t="s">
         <v>99</v>
       </c>
+      <c r="G3" s="24" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="C4" s="25">
+      <c r="B4" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="26">
         <f>Assumptions!D12</f>
         <v>120</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="26">
         <f>Assumptions!D13</f>
         <v>200</v>
       </c>
-      <c r="E4" s="25">
+      <c r="E4" s="26">
         <f>Assumptions!D14</f>
         <v>300</v>
       </c>
-      <c r="F4" s="25">
+      <c r="F4" s="26">
         <f>Assumptions!D15</f>
         <v>375</v>
       </c>
-      <c r="G4" s="25">
+      <c r="G4" s="26">
         <f>Assumptions!D16</f>
         <v>400</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="C5" s="26" t="str">
+      <c r="B5" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="27" t="str">
         <f>Assumptions!D12*Assumptions!D20</f>
         <v>0</v>
       </c>
-      <c r="D5" s="26" t="str">
+      <c r="D5" s="27" t="str">
         <f>Assumptions!D13*Assumptions!D20*(1+Assumptions!D21)^1</f>
         <v>0</v>
       </c>
-      <c r="E5" s="26" t="str">
+      <c r="E5" s="27" t="str">
         <f>Assumptions!D14*Assumptions!D20*(1+Assumptions!D21)^2</f>
         <v>0</v>
       </c>
-      <c r="F5" s="26" t="str">
+      <c r="F5" s="27" t="str">
         <f>Assumptions!D15*Assumptions!D20*(1+Assumptions!D21)^3</f>
         <v>0</v>
       </c>
-      <c r="G5" s="26" t="str">
+      <c r="G5" s="27" t="str">
         <f>Assumptions!D16*Assumptions!D20*(1+Assumptions!D21)^4</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" s="26" t="str">
+      <c r="B6" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" s="27" t="str">
         <f>C5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="D6" s="26" t="str">
+      <c r="D6" s="27" t="str">
         <f>D5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="E6" s="26" t="str">
+      <c r="E6" s="27" t="str">
         <f>E5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="F6" s="26" t="str">
+      <c r="F6" s="27" t="str">
         <f>F5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="G6" s="26" t="str">
+      <c r="G6" s="27" t="str">
         <f>G5*Assumptions!D26</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="C7" s="26">
+      <c r="B7" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="27">
         <f>Assumptions!D12*Assumptions!D22</f>
         <v>1380000</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="27">
         <f>Assumptions!D13*Assumptions!D22*(1+Assumptions!D23)^1</f>
         <v>2346000</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="27">
         <f>Assumptions!D14*Assumptions!D22*(1+Assumptions!D23)^2</f>
         <v>3589380</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="27">
         <f>Assumptions!D15*Assumptions!D22*(1+Assumptions!D23)^3</f>
         <v>4576459.5</v>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="27">
         <f>Assumptions!D16*Assumptions!D22*(1+Assumptions!D23)^4</f>
         <v>4979187.936</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="C8" s="26">
+      <c r="B8" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8" s="27">
         <f>Assumptions!D12*Assumptions!D24</f>
         <v>36000</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="27">
         <f>Assumptions!D13*Assumptions!D24*(1+Assumptions!D25)^1</f>
         <v>61800</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="27">
         <f>Assumptions!D14*Assumptions!D24*(1+Assumptions!D25)^2</f>
         <v>95481</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="27">
         <f>Assumptions!D15*Assumptions!D24*(1+Assumptions!D25)^3</f>
         <v>122931.7875</v>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="27">
         <f>Assumptions!D16*Assumptions!D24*(1+Assumptions!D25)^4</f>
         <v>135061.0572</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="C9" s="26">
+      <c r="B9" s="25" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="27">
         <f>Assumptions!D27</f>
         <v>130000</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="27">
         <f>Assumptions!D27*(1+Assumptions!D28)^1</f>
         <v>130000</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="27">
         <f>Assumptions!D27*(1+Assumptions!D28)^2</f>
         <v>130000</v>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="27">
         <f>Assumptions!D27*(1+Assumptions!D28)^3</f>
         <v>130000</v>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="27">
         <f>Assumptions!D27*(1+Assumptions!D28)^4</f>
         <v>130000</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="27" t="s">
-        <v>106</v>
-      </c>
-      <c r="C10" s="28">
+      <c r="B10" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="29">
         <f>C6+C7+C8+C9</f>
         <v>1546000</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="29">
         <f>D6+D7+D8+D9</f>
         <v>2537800</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="29">
         <f>E6+E7+E8+E9</f>
         <v>3814861</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="29">
         <f>F6+F7+F8+F9</f>
         <v>4829391.2875</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="29">
         <f>G6+G7+G8+G9</f>
         <v>5244248.9932</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="24" t="s">
-        <v>107</v>
-      </c>
-      <c r="C12" s="25">
+      <c r="B12" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="26">
         <f>CEILING(Assumptions!D12/Assumptions!D32,1)</f>
         <v>10</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="26">
         <f>CEILING(Assumptions!D13/Assumptions!D32,1)</f>
         <v>17</v>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="26">
         <f>CEILING(Assumptions!D14/Assumptions!D32,1)</f>
         <v>25</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="26">
         <f>CEILING(Assumptions!D15/Assumptions!D32,1)</f>
         <v>32</v>
       </c>
-      <c r="G12" s="25">
+      <c r="G12" s="26">
         <f>CEILING(Assumptions!D16/Assumptions!D32,1)</f>
         <v>34</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="C13" s="26">
+      <c r="B13" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="C13" s="27">
         <f>C12*Assumptions!D33</f>
         <v>456670</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="27">
         <f>D12*Assumptions!D33*(1+Assumptions!D34)^1</f>
         <v>799629.17</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="27">
         <f>E12*Assumptions!D33*(1+Assumptions!D34)^2</f>
         <v>1211203.0075</v>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="27">
         <f>F12*Assumptions!D33*(1+Assumptions!D34)^3</f>
         <v>1596850.045088</v>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="27">
         <f>G12*Assumptions!D33*(1+Assumptions!D34)^4</f>
         <v>1747552.76809318</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="C14" s="26">
+      <c r="B14" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="C14" s="27">
         <f>Assumptions!D35*Assumptions!D40</f>
         <v>490000</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="27">
         <f>Assumptions!D36*Assumptions!D40*(1+Assumptions!D41)^1</f>
         <v>504700</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="27">
         <f>Assumptions!D37*Assumptions!D40*(1+Assumptions!D41)^2</f>
         <v>519841</v>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="27">
         <f>Assumptions!D38*Assumptions!D40*(1+Assumptions!D41)^3</f>
         <v>535436.23</v>
       </c>
-      <c r="G14" s="26">
+      <c r="G14" s="27">
         <f>Assumptions!D39*Assumptions!D40*(1+Assumptions!D41)^4</f>
         <v>551499.3169</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="24" t="s">
-        <v>110</v>
-      </c>
-      <c r="C15" s="26">
+      <c r="B15" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" s="27">
         <f>(C13+C14)*Assumptions!D42</f>
         <v>253497.18888889</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="27">
         <f>(D13+D14)*Assumptions!D42</f>
         <v>349270.36663333</v>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="27">
         <f>(E13+E14)*Assumptions!D42</f>
         <v>463535.11756389</v>
       </c>
-      <c r="F15" s="26">
+      <c r="F15" s="27">
         <f>(F13+F14)*Assumptions!D42</f>
         <v>570978.88032912</v>
       </c>
-      <c r="G15" s="26">
+      <c r="G15" s="27">
         <f>(G13+G14)*Assumptions!D42</f>
         <v>615635.05831484</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="C16" s="28">
+      <c r="B16" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="C16" s="29">
         <f>C13+C14+C15</f>
         <v>1200167.18888889</v>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="29">
         <f>D13+D14+D15</f>
         <v>1653599.53663333</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="29">
         <f>E13+E14+E15</f>
         <v>2194579.12506389</v>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="29">
         <f>F13+F14+F15</f>
         <v>2703265.15541712</v>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="29">
         <f>G13+G14+G15</f>
         <v>2914687.14330802</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="24" t="s">
-        <v>112</v>
-      </c>
-      <c r="C18" s="26">
+      <c r="B18" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="C18" s="27">
         <f>Assumptions!D46</f>
         <v>282000</v>
       </c>
-      <c r="D18" s="26">
+      <c r="D18" s="27">
         <f>Assumptions!D46*(1+Assumptions!D47)^1</f>
         <v>290460</v>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="27">
         <f>Assumptions!D46*(1+Assumptions!D47)^2</f>
         <v>299173.8</v>
       </c>
-      <c r="F18" s="26">
+      <c r="F18" s="27">
         <f>Assumptions!D46*(1+Assumptions!D47)^3</f>
         <v>308149.014</v>
       </c>
-      <c r="G18" s="26">
+      <c r="G18" s="27">
         <f>Assumptions!D46*(1+Assumptions!D47)^4</f>
         <v>317393.48442</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="C19" s="26" t="str">
+      <c r="B19" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="C19" s="27" t="str">
         <f>Assumptions!D48</f>
         <v>0</v>
       </c>
-      <c r="D19" s="26" t="str">
+      <c r="D19" s="27" t="str">
         <f>Assumptions!D48*(1+Assumptions!D49)^1</f>
         <v>0</v>
       </c>
-      <c r="E19" s="26" t="str">
+      <c r="E19" s="27" t="str">
         <f>Assumptions!D48*(1+Assumptions!D49)^2</f>
         <v>0</v>
       </c>
-      <c r="F19" s="26" t="str">
+      <c r="F19" s="27" t="str">
         <f>Assumptions!D48*(1+Assumptions!D49)^3</f>
         <v>0</v>
       </c>
-      <c r="G19" s="26" t="str">
+      <c r="G19" s="27" t="str">
         <f>Assumptions!D48*(1+Assumptions!D49)^4</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="C20" s="26">
+      <c r="B20" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="C20" s="27">
         <f>Assumptions!D12*Assumptions!D50</f>
         <v>84000</v>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="27">
         <f>Assumptions!D13*Assumptions!D50*(1+Assumptions!D51)^1</f>
         <v>240333.33333333</v>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="27">
         <f>Assumptions!D14*Assumptions!D50*(1+Assumptions!D51)^2</f>
         <v>618858.33333333</v>
       </c>
-      <c r="F20" s="26">
+      <c r="F20" s="27">
         <f>Assumptions!D15*Assumptions!D50*(1+Assumptions!D51)^3</f>
         <v>1327966.84027778</v>
       </c>
-      <c r="G20" s="26">
+      <c r="G20" s="27">
         <f>Assumptions!D16*Assumptions!D50*(1+Assumptions!D51)^4</f>
         <v>2431654.83641975</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="C21" s="26">
+      <c r="B21" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="C21" s="27">
         <f>Assumptions!D52</f>
         <v>288000</v>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="27">
         <f>Assumptions!D52*(1+Assumptions!D53)^1</f>
         <v>453200</v>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="27">
         <f>Assumptions!D52*(1+Assumptions!D53)^2</f>
         <v>713160.55555556</v>
       </c>
-      <c r="F21" s="26">
+      <c r="F21" s="27">
         <f>Assumptions!D52*(1+Assumptions!D53)^3</f>
         <v>1122237.3742284</v>
       </c>
-      <c r="G21" s="26">
+      <c r="G21" s="27">
         <f>Assumptions!D52*(1+Assumptions!D53)^4</f>
         <v>1765965.20138996</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="C22" s="28">
+      <c r="B22" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="C22" s="29">
         <f>C18+C19+C20+C21</f>
         <v>654000</v>
       </c>
-      <c r="D22" s="28">
+      <c r="D22" s="29">
         <f>D18+D19+D20+D21</f>
         <v>983993.33333333</v>
       </c>
-      <c r="E22" s="28">
+      <c r="E22" s="29">
         <f>E18+E19+E20+E21</f>
         <v>1631192.68888889</v>
       </c>
-      <c r="F22" s="28">
+      <c r="F22" s="29">
         <f>F18+F19+F20+F21</f>
         <v>2758353.22850617</v>
       </c>
-      <c r="G22" s="28">
+      <c r="G22" s="29">
         <f>G18+G19+G20+G21</f>
         <v>4515013.52222971</v>
       </c>
@@ -3242,7 +3263,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -3251,294 +3272,294 @@
       <c r="G1" s="13"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="22"/>
-      <c r="C3" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" s="23" t="s">
+      <c r="B3" s="23"/>
+      <c r="C3" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="D3" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="E3" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="G3" s="23" t="s">
+      <c r="F3" s="24" t="s">
         <v>99</v>
       </c>
+      <c r="G3" s="24" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="C5" s="25">
+      <c r="B5" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="26">
         <f>Drivers!C4</f>
         <v>120</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="26">
         <f>Drivers!D4</f>
         <v>200</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="26">
         <f>Drivers!E4</f>
         <v>300</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="26">
         <f>Drivers!F4</f>
         <v>375</v>
       </c>
-      <c r="G5" s="25">
+      <c r="G5" s="26">
         <f>Drivers!G4</f>
         <v>400</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="C6" s="26" t="str">
+      <c r="B6" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="27" t="str">
         <f>Drivers!C6</f>
         <v>0</v>
       </c>
-      <c r="D6" s="26" t="str">
+      <c r="D6" s="27" t="str">
         <f>Drivers!D6</f>
         <v>0</v>
       </c>
-      <c r="E6" s="26" t="str">
+      <c r="E6" s="27" t="str">
         <f>Drivers!E6</f>
         <v>0</v>
       </c>
-      <c r="F6" s="26" t="str">
+      <c r="F6" s="27" t="str">
         <f>Drivers!F6</f>
         <v>0</v>
       </c>
-      <c r="G6" s="26" t="str">
+      <c r="G6" s="27" t="str">
         <f>Drivers!G6</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="C7" s="26">
+      <c r="B7" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" s="27">
         <f>Drivers!C7</f>
         <v>1380000</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="27">
         <f>Drivers!D7</f>
         <v>2346000</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="27">
         <f>Drivers!E7</f>
         <v>3589380</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="27">
         <f>Drivers!F7</f>
         <v>4576459.5</v>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="27">
         <f>Drivers!G7</f>
         <v>4979187.936</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="C8" s="26">
+      <c r="B8" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="C8" s="27">
         <f>Drivers!C8</f>
         <v>36000</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="27">
         <f>Drivers!D8</f>
         <v>61800</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="27">
         <f>Drivers!E8</f>
         <v>95481</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="27">
         <f>Drivers!F8</f>
         <v>122931.7875</v>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="27">
         <f>Drivers!G8</f>
         <v>135061.0572</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="C9" s="26">
+      <c r="B9" s="25" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="27">
         <f>Drivers!C9</f>
         <v>130000</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="27">
         <f>Drivers!D9</f>
         <v>130000</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="27">
         <f>Drivers!E9</f>
         <v>130000</v>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="27">
         <f>Drivers!F9</f>
         <v>130000</v>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="27">
         <f>Drivers!G9</f>
         <v>130000</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="27" t="s">
-        <v>106</v>
-      </c>
-      <c r="C10" s="28">
+      <c r="B10" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="29">
         <f>Drivers!C10</f>
         <v>1546000</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="29">
         <f>Drivers!D10</f>
         <v>2537800</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="29">
         <f>Drivers!E10</f>
         <v>3814861</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="29">
         <f>Drivers!F10</f>
         <v>4829391.2875</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="29">
         <f>Drivers!G10</f>
         <v>5244248.9932</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="C12" s="26">
+      <c r="B12" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="C12" s="27">
         <f>Drivers!C16</f>
         <v>1200167.18888889</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="27">
         <f>Drivers!D16</f>
         <v>1653599.53663333</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="27">
         <f>Drivers!E16</f>
         <v>2194579.12506389</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="27">
         <f>Drivers!F16</f>
         <v>2703265.15541712</v>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="27">
         <f>Drivers!G16</f>
         <v>2914687.14330802</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="C13" s="26">
+      <c r="B13" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="C13" s="27">
         <f>Drivers!C22</f>
         <v>654000</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="27">
         <f>Drivers!D22</f>
         <v>983993.33333333</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="27">
         <f>Drivers!E22</f>
         <v>1631192.68888889</v>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="27">
         <f>Drivers!F22</f>
         <v>2758353.22850617</v>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="27">
         <f>Drivers!G22</f>
         <v>4515013.52222971</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="27" t="s">
-        <v>121</v>
-      </c>
-      <c r="C15" s="28">
+      <c r="B15" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="C15" s="29">
         <f>C12+C13</f>
         <v>1854167.18888889</v>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="29">
         <f>D12+D13</f>
         <v>2637592.86996667</v>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="29">
         <f>E12+E13</f>
         <v>3825771.81395278</v>
       </c>
-      <c r="F15" s="28">
+      <c r="F15" s="29">
         <f>F12+F13</f>
         <v>5461618.38392329</v>
       </c>
-      <c r="G15" s="28">
+      <c r="G15" s="29">
         <f>G12+G13</f>
         <v>7429700.66553774</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="C16" s="29">
+      <c r="B16" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="C16" s="30">
         <f>C10-C15</f>
         <v>-308167.18888889</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="30">
         <f>D10-D15</f>
         <v>-99792.86996667</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="30">
         <f>E10-E15</f>
         <v>-10910.81395278</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="30">
         <f>F10-F15</f>
         <v>-632227.09642329</v>
       </c>
-      <c r="G16" s="29">
+      <c r="G16" s="30">
         <f>G10-G15</f>
         <v>-2185451.67233774</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="24" t="s">
-        <v>123</v>
-      </c>
-      <c r="C17" s="30">
+      <c r="B17" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="C17" s="31">
         <f>IF(C10&gt;0,C16/C10,0)</f>
         <v>-0.19933195</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="31">
         <f>IF(D10&gt;0,D16/D10,0)</f>
         <v>-0.03932259</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="31">
         <f>IF(E10&gt;0,E16/E10,0)</f>
         <v>-0.00286008</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="31">
         <f>IF(F10&gt;0,F16/F10,0)</f>
         <v>-0.13091238</v>
       </c>
-      <c r="G17" s="30">
+      <c r="G17" s="31">
         <f>IF(G10&gt;0,G16/G10,0)</f>
         <v>-0.41673301</v>
       </c>
@@ -3571,7 +3592,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -3580,194 +3601,194 @@
       <c r="G1" s="13"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="22"/>
-      <c r="C3" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" s="23" t="s">
+      <c r="B3" s="23"/>
+      <c r="C3" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="D3" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="E3" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="G3" s="23" t="s">
+      <c r="F3" s="24" t="s">
         <v>99</v>
       </c>
+      <c r="G3" s="24" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="C4" s="26">
+      <c r="B4" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" s="27">
         <f>'5-Year P&amp;L'!C16</f>
         <v>-308167.18888889</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="27">
         <f>'5-Year P&amp;L'!D16</f>
         <v>-99792.86996667</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="27">
         <f>'5-Year P&amp;L'!E16</f>
         <v>-10910.81395278</v>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="27">
         <f>'5-Year P&amp;L'!F16</f>
         <v>-632227.09642329</v>
       </c>
-      <c r="G4" s="26">
+      <c r="G4" s="27">
         <f>'5-Year P&amp;L'!G16</f>
         <v>-2185451.67233774</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="24" t="s">
-        <v>126</v>
-      </c>
-      <c r="C6" s="26">
+      <c r="B6" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="C6" s="27">
         <f>Assumptions!D58</f>
         <v>115000</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="27">
         <f>Assumptions!D58</f>
         <v>115000</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="27">
         <f>Assumptions!D58</f>
         <v>115000</v>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="27">
         <f>Assumptions!D58</f>
         <v>115000</v>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="27">
         <f>Assumptions!D58</f>
         <v>115000</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="C7" s="26">
+      <c r="B7" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="C7" s="27">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>49824.60522118</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="27">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>49824.60522118</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="27">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>49824.60522118</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="27">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>49824.60522118</v>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="27">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>49824.60522118</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="C8" s="28">
+      <c r="B8" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="C8" s="29">
         <f>C6+C7</f>
         <v>164824.60522118</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="29">
         <f>D6+D7</f>
         <v>164824.60522118</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="29">
         <f>E6+E7</f>
         <v>164824.60522118</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="29">
         <f>F6+F7</f>
         <v>164824.60522118</v>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="29">
         <f>G6+G7</f>
         <v>164824.60522118</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="27" t="s">
-        <v>129</v>
-      </c>
-      <c r="C10" s="31">
+      <c r="B10" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="C10" s="32">
         <f>IF(C8&gt;0,C4/C8,IF(C4&gt;0,99.9,0))</f>
         <v>-1.86966739</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="32">
         <f>IF(D8&gt;0,D4/D8,IF(D4&gt;0,99.9,0))</f>
         <v>-0.60544886</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="32">
         <f>IF(E8&gt;0,E4/E8,IF(E4&gt;0,99.9,0))</f>
         <v>-0.06619651</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="32">
         <f>IF(F8&gt;0,F4/F8,IF(F4&gt;0,99.9,0))</f>
         <v>-3.83575678</v>
       </c>
-      <c r="G10" s="31">
+      <c r="G10" s="32">
         <f>IF(G8&gt;0,G4/G8,IF(G4&gt;0,99.9,0))</f>
         <v>-13.25925622</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="24" t="s">
-        <v>130</v>
-      </c>
-      <c r="C12" s="26">
+      <c r="B12" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="C12" s="27">
         <f>C4-C8</f>
         <v>-472991.79411007</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="27">
         <f>D4-D8</f>
         <v>-264617.47518785</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="27">
         <f>E4-E8</f>
         <v>-175735.41917396</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="27">
         <f>F4-F8</f>
         <v>-797051.70164447</v>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="27">
         <f>G4-G8</f>
         <v>-2350276.27755892</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="C14" s="32">
+      <c r="B14" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" s="33">
         <f>Assumptions!D57+C12</f>
         <v>-472991.79411007</v>
       </c>
-      <c r="D14" s="32">
+      <c r="D14" s="33">
         <f>C14+D12</f>
         <v>-737609.26929791</v>
       </c>
-      <c r="E14" s="32">
+      <c r="E14" s="33">
         <f>D14+E12</f>
         <v>-913344.68847187</v>
       </c>
-      <c r="F14" s="32">
+      <c r="F14" s="33">
         <f>E14+F12</f>
         <v>-1710396.39011634</v>
       </c>
-      <c r="G14" s="32">
+      <c r="G14" s="33">
         <f>F14+G12</f>
         <v>-4060672.66767526</v>
       </c>
@@ -3800,7 +3821,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -3809,94 +3830,94 @@
       <c r="G1" s="13"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="22"/>
-      <c r="C3" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" s="23" t="s">
+      <c r="B3" s="23"/>
+      <c r="C3" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="D3" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="E3" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="G3" s="23" t="s">
+      <c r="F3" s="24" t="s">
         <v>99</v>
       </c>
+      <c r="G3" s="24" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="C4" s="25">
+      <c r="B4" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="C4" s="26">
         <f>Drivers!C12</f>
         <v>10</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="26">
         <f>Drivers!D12</f>
         <v>17</v>
       </c>
-      <c r="E4" s="25">
+      <c r="E4" s="26">
         <f>Drivers!E12</f>
         <v>25</v>
       </c>
-      <c r="F4" s="25">
+      <c r="F4" s="26">
         <f>Drivers!F12</f>
         <v>32</v>
       </c>
-      <c r="G4" s="25">
+      <c r="G4" s="26">
         <f>Drivers!G12</f>
         <v>34</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="C5" s="25">
+      <c r="B5" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5" s="26">
         <f>Assumptions!D35</f>
         <v>7</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="26">
         <f>Assumptions!D36</f>
         <v>7</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="26">
         <f>Assumptions!D37</f>
         <v>7</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="26">
         <f>Assumptions!D38</f>
         <v>7</v>
       </c>
-      <c r="G5" s="25">
+      <c r="G5" s="26">
         <f>Assumptions!D39</f>
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="C6" s="33">
+      <c r="B6" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="C6" s="34">
         <f>C4+C5</f>
         <v>17</v>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="34">
         <f>D4+D5</f>
         <v>24</v>
       </c>
-      <c r="E6" s="33">
+      <c r="E6" s="34">
         <f>E4+E5</f>
         <v>32</v>
       </c>
-      <c r="F6" s="33">
+      <c r="F6" s="34">
         <f>F4+F5</f>
         <v>39</v>
       </c>
-      <c r="G6" s="33">
+      <c r="G6" s="34">
         <f>G4+G5</f>
         <v>41</v>
       </c>
@@ -3929,51 +3950,51 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C1" s="13"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="C3" s="26">
+      <c r="B3" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="C3" s="27">
         <f>Assumptions!D59</f>
         <v>500000</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="C4" s="30">
+      <c r="B4" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4" s="31">
         <f>Assumptions!D60</f>
         <v>0.0575</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="C5" s="25">
+      <c r="B5" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" s="26">
         <f>Assumptions!D61</f>
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="24" t="s">
-        <v>139</v>
-      </c>
-      <c r="C6" s="34">
+      <c r="B6" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="C6" s="35">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>49824.60522118</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="C8" s="31">
+      <c r="B8" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="C8" s="32">
         <f>'Cash Flow &amp; DSCR'!C10</f>
         <v>-1.86966739</v>
       </c>
@@ -4006,76 +4027,76 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C1" s="13"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" s="24" t="str">
+      <c r="B3" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="25" t="str">
         <f>Assumptions!D5</f>
         <v>Civic Scholars Charter</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="24" t="str">
+      <c r="B4" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="25" t="str">
         <f>Assumptions!D7</f>
         <v>Charter School</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="24" t="str">
+      <c r="B5" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="25" t="str">
         <f>Assumptions!D6</f>
         <v>OH</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="C6" s="24">
+      <c r="B6" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" s="25">
         <f>Assumptions!D8</f>
         <v>2026</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="C8" s="25">
+      <c r="B8" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="26">
         <f>Assumptions!D16</f>
         <v>400</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="C9" s="26">
+      <c r="B9" s="25" t="s">
+        <v>144</v>
+      </c>
+      <c r="C9" s="27">
         <f>Drivers!G10</f>
         <v>5244248.9932</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="C10" s="32">
+      <c r="B10" s="25" t="s">
+        <v>145</v>
+      </c>
+      <c r="C10" s="33">
         <f>'5-Year P&amp;L'!G16</f>
         <v>-2185451.67233774</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C12" s="12"/>
     </row>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="194">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -862,7 +862,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2345,7 +2345,7 @@
     <tabColor rgb="FFD97706"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:D61"/>
+  <dimension ref="B1:E61"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -2361,7 +2361,7 @@
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
     </row>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" s="14" t="s">
         <v>7</v>
       </c>
@@ -2369,6 +2369,9 @@
         <v>43</v>
       </c>
       <c r="D2" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="15" t="s">
         <v>44</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="206">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -466,9 +466,21 @@
     <t>Civic Scholars Charter — Financial Health Dashboard</t>
   </si>
   <si>
+    <t>● Green = healthy</t>
+  </si>
+  <si>
+    <t>◐ Yellow = monitor</t>
+  </si>
+  <si>
+    <t>○ Red = action needed</t>
+  </si>
+  <si>
     <t>Metric</t>
   </si>
   <si>
+    <t>Benchmark</t>
+  </si>
+  <si>
     <t>Revenue</t>
   </si>
   <si>
@@ -493,15 +505,36 @@
     <t>Revenue per Student</t>
   </si>
   <si>
+    <t>≥ $10,000</t>
+  </si>
+  <si>
     <t>Payroll %</t>
   </si>
   <si>
+    <t>≤ 55%</t>
+  </si>
+  <si>
     <t>Facility %</t>
   </si>
   <si>
+    <t>≤ 15%</t>
+  </si>
+  <si>
+    <t>≥ 10%</t>
+  </si>
+  <si>
+    <t>Revenue Sources</t>
+  </si>
+  <si>
+    <t>≥ 3 sources</t>
+  </si>
+  <si>
     <t>DSCR</t>
   </si>
   <si>
+    <t>≥ 1.25x</t>
+  </si>
+  <si>
     <t>Break-even Year</t>
   </si>
   <si>
@@ -512,6 +545,9 @@
   </si>
   <si>
     <t>0 months</t>
+  </si>
+  <si>
+    <t>60+ months</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -710,7 +746,7 @@
     </font>
     <font>
       <b/>
-      <color rgb="FFDC2626"/>
+      <color rgb="FF16A34A"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -722,7 +758,7 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF16A34A"/>
+      <color rgb="FFDC2626"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -845,7 +881,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -912,6 +948,9 @@
     <xf numFmtId="165" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -919,18 +958,23 @@
     <xf numFmtId="166" fontId="16" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="16" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="16" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="16" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -942,7 +986,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -952,7 +996,28 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="24">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1633,19 +1698,20 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FF0D9488"/>
+    <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:G33"/>
+  <dimension ref="B2:H35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>147</v>
       </c>
@@ -1654,8 +1720,9 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="12" t="s">
         <v>40</v>
       </c>
@@ -1664,559 +1731,632 @@
       <c r="E3" s="12"/>
       <c r="F3" s="12"/>
       <c r="G3" s="12"/>
-    </row>
-    <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="36" t="s">
+      <c r="H3" s="12"/>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="36" t="s">
         <v>148</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="D4" s="37" t="s">
+        <v>149</v>
+      </c>
+      <c r="F4" s="38" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="39" t="s">
+        <v>151</v>
+      </c>
+      <c r="C6" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="D5" s="37" t="s">
+      <c r="D6" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="E5" s="37" t="s">
+      <c r="E6" s="40" t="s">
         <v>98</v>
       </c>
-      <c r="F5" s="37" t="s">
+      <c r="F6" s="40" t="s">
         <v>99</v>
       </c>
-      <c r="G5" s="37" t="s">
+      <c r="G6" s="40" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="25" t="s">
-        <v>101</v>
-      </c>
-      <c r="C6" s="26">
-        <v>120</v>
-      </c>
-      <c r="D6" s="26">
-        <v>200</v>
-      </c>
-      <c r="E6" s="26">
-        <v>300</v>
-      </c>
-      <c r="F6" s="26">
-        <v>375</v>
-      </c>
-      <c r="G6" s="26">
-        <v>400</v>
+      <c r="H6" s="40" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="C7" s="27">
-        <v>1546000</v>
-      </c>
-      <c r="D7" s="27">
-        <v>2537800</v>
-      </c>
-      <c r="E7" s="27">
-        <v>3814861</v>
-      </c>
-      <c r="F7" s="27">
-        <v>4829391.287500001</v>
-      </c>
-      <c r="G7" s="27">
-        <v>5244248.993199999</v>
+        <v>101</v>
+      </c>
+      <c r="C7" s="26">
+        <v>120</v>
+      </c>
+      <c r="D7" s="26">
+        <v>200</v>
+      </c>
+      <c r="E7" s="26">
+        <v>300</v>
+      </c>
+      <c r="F7" s="26">
+        <v>375</v>
+      </c>
+      <c r="G7" s="26">
+        <v>400</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="25" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C8" s="27">
-        <v>1200167.1888888888</v>
+        <v>1546000</v>
       </c>
       <c r="D8" s="27">
-        <v>1653599.5366333332</v>
+        <v>2537800</v>
       </c>
       <c r="E8" s="27">
-        <v>2194579.1250638887</v>
+        <v>3814861</v>
       </c>
       <c r="F8" s="27">
-        <v>2703265.15541712</v>
+        <v>4829391.287500001</v>
       </c>
       <c r="G8" s="27">
-        <v>2914687.143308021</v>
+        <v>5244248.993199999</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="25" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C9" s="27">
-        <v>654000</v>
+        <v>1200167.1888888888</v>
       </c>
       <c r="D9" s="27">
-        <v>983993.3333333334</v>
+        <v>1653599.5366333332</v>
       </c>
       <c r="E9" s="27">
-        <v>1631192.688888889</v>
+        <v>2194579.1250638887</v>
       </c>
       <c r="F9" s="27">
-        <v>2758353.228506173</v>
+        <v>2703265.15541712</v>
       </c>
       <c r="G9" s="27">
-        <v>4515013.522229714</v>
+        <v>2914687.143308021</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="25" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C10" s="27">
+        <v>654000</v>
+      </c>
+      <c r="D10" s="27">
+        <v>983993.3333333334</v>
+      </c>
+      <c r="E10" s="27">
+        <v>1631192.688888889</v>
+      </c>
+      <c r="F10" s="27">
+        <v>2758353.228506173</v>
+      </c>
+      <c r="G10" s="27">
+        <v>4515013.522229714</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="C11" s="27">
         <v>164824.60522117943</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D11" s="27">
         <v>164824.60522117943</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E11" s="27">
         <v>164824.60522117943</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F11" s="27">
         <v>164824.60522117943</v>
       </c>
-      <c r="G10" s="27">
+      <c r="G11" s="27">
         <v>164824.60522117943</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="28" t="s">
-        <v>153</v>
-      </c>
-      <c r="C11" s="30">
-        <v>-472991.79411006824</v>
-      </c>
-      <c r="D11" s="30">
-        <v>-264617.4751878461</v>
-      </c>
-      <c r="E11" s="30">
-        <v>-175735.41917395697</v>
-      </c>
-      <c r="F11" s="30">
-        <v>-797051.701644472</v>
-      </c>
-      <c r="G11" s="30">
-        <v>-2350276.2775589153</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="28" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C12" s="30">
         <v>-472991.79411006824</v>
       </c>
       <c r="D12" s="30">
-        <v>-737609.2692979143</v>
+        <v>-264617.4751878461</v>
       </c>
       <c r="E12" s="30">
-        <v>-913344.6884718713</v>
+        <v>-175735.41917395697</v>
       </c>
       <c r="F12" s="30">
-        <v>-1710396.3901163433</v>
+        <v>-797051.701644472</v>
       </c>
       <c r="G12" s="30">
-        <v>-4060672.6676752586</v>
+        <v>-2350276.2775589153</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="28" t="s">
-        <v>155</v>
-      </c>
-      <c r="C13" s="38">
-        <v>-0.3059455330595525</v>
-      </c>
-      <c r="D13" s="38">
-        <v>-0.10427042130500674</v>
-      </c>
-      <c r="E13" s="38">
-        <v>-0.046066008479458874</v>
-      </c>
-      <c r="F13" s="38">
-        <v>-0.16504185604249857</v>
-      </c>
-      <c r="G13" s="38">
-        <v>-0.44816260261601254</v>
+        <v>158</v>
+      </c>
+      <c r="C13" s="30">
+        <v>-472991.79411006824</v>
+      </c>
+      <c r="D13" s="30">
+        <v>-737609.2692979143</v>
+      </c>
+      <c r="E13" s="30">
+        <v>-913344.6884718713</v>
+      </c>
+      <c r="F13" s="30">
+        <v>-1710396.3901163433</v>
+      </c>
+      <c r="G13" s="30">
+        <v>-4060672.6676752586</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="28" t="s">
-        <v>156</v>
-      </c>
-      <c r="C14" s="27">
+        <v>159</v>
+      </c>
+      <c r="C14" s="41">
+        <v>-0.3059455330595525</v>
+      </c>
+      <c r="D14" s="41">
+        <v>-0.10427042130500674</v>
+      </c>
+      <c r="E14" s="41">
+        <v>-0.046066008479458874</v>
+      </c>
+      <c r="F14" s="41">
+        <v>-0.16504185604249857</v>
+      </c>
+      <c r="G14" s="41">
+        <v>-0.44816260261601254</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="C15" s="42">
         <v>12883.333333333334</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D15" s="42">
         <v>12689</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E15" s="42">
         <v>12716.203333333333</v>
       </c>
-      <c r="F14" s="27">
+      <c r="F15" s="42">
         <v>12878.376766666668</v>
       </c>
-      <c r="G14" s="27">
+      <c r="G15" s="42">
         <v>13110.622483</v>
       </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="28" t="s">
-        <v>157</v>
-      </c>
-      <c r="C15" s="38">
+      <c r="H15" s="43" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="C16" s="41">
         <v>0.7763047793589191</v>
       </c>
-      <c r="D15" s="38">
+      <c r="D16" s="41">
         <v>0.6515878070113221</v>
       </c>
-      <c r="E15" s="39">
+      <c r="E16" s="44">
         <v>0.5752710583855843</v>
       </c>
-      <c r="F15" s="39">
+      <c r="F16" s="44">
         <v>0.5597527709991174</v>
       </c>
-      <c r="G15" s="39">
+      <c r="G16" s="44">
         <v>0.5557873295275215</v>
       </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="28" t="s">
-        <v>158</v>
-      </c>
-      <c r="C16" s="40">
+      <c r="H16" s="43" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="C17" s="45">
         <v>0.12690815006468306</v>
       </c>
-      <c r="D16" s="40">
+      <c r="D17" s="45">
         <v>0.1163204350224604</v>
       </c>
-      <c r="E16" s="40">
+      <c r="E17" s="45">
         <v>0.1282767069800621</v>
       </c>
-      <c r="F16" s="39">
+      <c r="F17" s="44">
         <v>0.1713478820185269</v>
       </c>
-      <c r="G16" s="38">
+      <c r="G17" s="41">
         <v>0.25828370438269493</v>
       </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="28" t="s">
+      <c r="H17" s="43" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="C17" s="38">
+      <c r="C18" s="41">
         <v>-0.19933194624119585</v>
       </c>
-      <c r="D17" s="38">
+      <c r="D18" s="41">
         <v>-0.039322590419523434</v>
       </c>
-      <c r="E17" s="38">
+      <c r="E18" s="41">
         <v>-0.0028600816524580494</v>
       </c>
-      <c r="F17" s="38">
+      <c r="F18" s="41">
         <v>-0.13091237772754036</v>
       </c>
-      <c r="G17" s="38">
+      <c r="G18" s="41">
         <v>-0.4167330108031714</v>
       </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="28" t="s">
-        <v>159</v>
-      </c>
-      <c r="C18" s="41">
+      <c r="H18" s="43" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="C19" s="46">
+        <v>1</v>
+      </c>
+      <c r="D19" s="46"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="46"/>
+      <c r="G19" s="46"/>
+      <c r="H19" s="43" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="C20" s="47">
         <v>-1.8696673865856184</v>
       </c>
-      <c r="D18" s="41">
+      <c r="D20" s="47">
         <v>-0.6054488638559378</v>
       </c>
-      <c r="E18" s="41">
+      <c r="E20" s="47">
         <v>-0.06619651197184098</v>
       </c>
-      <c r="F18" s="41">
+      <c r="F20" s="47">
         <v>-3.8357567765741165</v>
       </c>
-      <c r="G18" s="41">
+      <c r="G20" s="47">
         <v>-13.259256222122064</v>
       </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="28" t="s">
-        <v>160</v>
-      </c>
-      <c r="C19" s="42" t="s">
-        <v>161</v>
-      </c>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="28" t="s">
-        <v>162</v>
-      </c>
-      <c r="C20" s="42" t="s">
-        <v>163</v>
-      </c>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="36" t="s">
-        <v>164</v>
-      </c>
-      <c r="C22" s="36" t="s">
-        <v>165</v>
-      </c>
-      <c r="D22" s="36" t="s">
-        <v>166</v>
-      </c>
-      <c r="E22" s="36"/>
-      <c r="F22" s="36" t="s">
-        <v>167</v>
-      </c>
-      <c r="G22" s="36"/>
-    </row>
-    <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="43" t="s">
-        <v>168</v>
-      </c>
-      <c r="C23" s="44" t="s">
-        <v>169</v>
-      </c>
-      <c r="D23" s="45" t="s">
+      <c r="H20" s="43" t="s">
         <v>170</v>
       </c>
-      <c r="E23" s="45"/>
-      <c r="F23" s="46" t="s">
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="28" t="s">
         <v>171</v>
       </c>
-      <c r="G23" s="46"/>
-    </row>
-    <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="43" t="s">
+      <c r="C21" s="48" t="s">
         <v>172</v>
       </c>
-      <c r="C24" s="44" t="s">
-        <v>169</v>
-      </c>
-      <c r="D24" s="45" t="s">
+      <c r="D21" s="48"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="48"/>
+      <c r="H21" s="43" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="E24" s="45"/>
-      <c r="F24" s="46" t="s">
+      <c r="C22" s="48" t="s">
         <v>174</v>
       </c>
-      <c r="G24" s="46"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="43" t="s">
+      <c r="D22" s="48"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="48"/>
+      <c r="H22" s="43" t="s">
         <v>175</v>
       </c>
-      <c r="C25" s="47" t="s">
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="39" t="s">
         <v>176</v>
       </c>
-      <c r="D25" s="45" t="s">
+      <c r="C24" s="39" t="s">
         <v>177</v>
       </c>
-      <c r="E25" s="45"/>
-      <c r="F25" s="46" t="s">
+      <c r="D24" s="39" t="s">
         <v>178</v>
       </c>
-      <c r="G25" s="46"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="43" t="s">
+      <c r="E24" s="39"/>
+      <c r="F24" s="39" t="s">
         <v>179</v>
       </c>
-      <c r="C26" s="44" t="s">
-        <v>169</v>
-      </c>
-      <c r="D26" s="45" t="s">
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="49" t="s">
         <v>180</v>
       </c>
-      <c r="E26" s="45"/>
-      <c r="F26" s="46" t="s">
+      <c r="C25" s="50" t="s">
         <v>181</v>
       </c>
-      <c r="G26" s="46"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="43" t="s">
+      <c r="D25" s="51" t="s">
         <v>182</v>
       </c>
-      <c r="C27" s="44" t="s">
-        <v>169</v>
-      </c>
-      <c r="D27" s="45" t="s">
+      <c r="E25" s="51"/>
+      <c r="F25" s="52" t="s">
         <v>183</v>
       </c>
-      <c r="E27" s="45"/>
-      <c r="F27" s="46" t="s">
+      <c r="G25" s="52"/>
+      <c r="H25" s="52"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="49" t="s">
         <v>184</v>
       </c>
-      <c r="G27" s="46"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="43" t="s">
+      <c r="C26" s="50" t="s">
+        <v>181</v>
+      </c>
+      <c r="D26" s="51" t="s">
         <v>185</v>
       </c>
-      <c r="C28" s="48" t="s">
+      <c r="E26" s="51"/>
+      <c r="F26" s="52" t="s">
         <v>186</v>
       </c>
-      <c r="D28" s="45" t="s">
+      <c r="G26" s="52"/>
+      <c r="H26" s="52"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="49" t="s">
         <v>187</v>
       </c>
-      <c r="E28" s="45"/>
-      <c r="F28" s="46" t="s">
+      <c r="C27" s="53" t="s">
         <v>188</v>
       </c>
-      <c r="G28" s="46"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="43" t="s">
+      <c r="D27" s="51" t="s">
         <v>189</v>
       </c>
-      <c r="C29" s="44" t="s">
-        <v>169</v>
-      </c>
-      <c r="D29" s="45" t="s">
+      <c r="E27" s="51"/>
+      <c r="F27" s="52" t="s">
         <v>190</v>
       </c>
-      <c r="E29" s="45"/>
-      <c r="F29" s="46" t="s">
+      <c r="G27" s="52"/>
+      <c r="H27" s="52"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="49" t="s">
         <v>191</v>
       </c>
-      <c r="G29" s="46"/>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B31" s="43" t="s">
+      <c r="C28" s="50" t="s">
+        <v>181</v>
+      </c>
+      <c r="D28" s="51" t="s">
+        <v>192</v>
+      </c>
+      <c r="E28" s="51"/>
+      <c r="F28" s="52" t="s">
+        <v>193</v>
+      </c>
+      <c r="G28" s="52"/>
+      <c r="H28" s="52"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="C29" s="50" t="s">
+        <v>181</v>
+      </c>
+      <c r="D29" s="51" t="s">
+        <v>195</v>
+      </c>
+      <c r="E29" s="51"/>
+      <c r="F29" s="52" t="s">
+        <v>196</v>
+      </c>
+      <c r="G29" s="52"/>
+      <c r="H29" s="52"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="49" t="s">
+        <v>197</v>
+      </c>
+      <c r="C30" s="54" t="s">
+        <v>198</v>
+      </c>
+      <c r="D30" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="E30" s="51"/>
+      <c r="F30" s="52" t="s">
+        <v>200</v>
+      </c>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="49" t="s">
+        <v>201</v>
+      </c>
+      <c r="C31" s="50" t="s">
+        <v>181</v>
+      </c>
+      <c r="D31" s="51" t="s">
+        <v>202</v>
+      </c>
+      <c r="E31" s="51"/>
+      <c r="F31" s="52" t="s">
+        <v>203</v>
+      </c>
+      <c r="G31" s="52"/>
+      <c r="H31" s="52"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="C31" s="28" t="s">
-        <v>192</v>
-      </c>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="49" t="s">
-        <v>193</v>
-      </c>
-      <c r="C33" s="49"/>
-      <c r="D33" s="49"/>
-      <c r="E33" s="49"/>
-      <c r="F33" s="49"/>
-      <c r="G33" s="49"/>
+      <c r="C33" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="55" t="s">
+        <v>205</v>
+      </c>
+      <c r="C35" s="55"/>
+      <c r="D35" s="55"/>
+      <c r="E35" s="55"/>
+      <c r="F35" s="55"/>
+      <c r="G35" s="55"/>
+      <c r="H35" s="55"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B3:G3"/>
+  <mergeCells count="23">
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
     <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F25:H25"/>
     <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F26:H26"/>
     <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F27:H27"/>
     <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B35:H35"/>
   </mergeCells>
-  <conditionalFormatting sqref="C11:G11">
+  <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>C11&gt;=0</formula>
+      <formula>C12&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="2">
-      <formula>C11&gt;=-1</formula>
+      <formula>C12&gt;=-1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="3">
-      <formula>C11&lt;-1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C12:G12">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>C12&gt;=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
-      <formula>C12&gt;=-1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="3">
       <formula>C12&lt;-1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:G13">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>C13&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>C13&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>C13&lt;-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14:G14">
     <cfRule type="expression" dxfId="6" priority="1">
-      <formula>C13&gt;=0.05</formula>
+      <formula>C14&gt;=0.05</formula>
     </cfRule>
     <cfRule type="expression" dxfId="7" priority="2">
-      <formula>C13&gt;=0</formula>
+      <formula>C14&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="8" priority="3">
-      <formula>C13&lt;0</formula>
+      <formula>C14&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:G15">
     <cfRule type="expression" dxfId="9" priority="1">
-      <formula>C15&lt;=0.55</formula>
+      <formula>C15&gt;=10000</formula>
     </cfRule>
     <cfRule type="expression" dxfId="10" priority="2">
-      <formula>C15&lt;=0.65</formula>
+      <formula>C15&gt;=7000</formula>
     </cfRule>
     <cfRule type="expression" dxfId="11" priority="3">
-      <formula>C15&gt;0.65</formula>
+      <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.15</formula>
+      <formula>C16&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.25</formula>
+      <formula>C16&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.25</formula>
+      <formula>C16&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17:G17">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&gt;=0.10</formula>
+      <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&gt;=0</formula>
+      <formula>C17&lt;=0.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&lt;0</formula>
+      <formula>C17&gt;0.25</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:G18">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=1.25</formula>
+      <formula>C18&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=1.0</formula>
+      <formula>C18&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;1.0</formula>
+      <formula>C18&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C20:G20">
+    <cfRule type="expression" dxfId="21" priority="1">
+      <formula>C20&gt;=1.25</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="2">
+      <formula>C20&gt;=1.0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="3">
+      <formula>C20&lt;1.0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="208">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -395,6 +395,12 @@
   </si>
   <si>
     <t>Operating Margin</t>
+  </si>
+  <si>
+    <t>Cumulative Net Income</t>
+  </si>
+  <si>
+    <t>Break-even</t>
   </si>
   <si>
     <t>Cash Flow &amp; Debt Service Coverage</t>
@@ -881,7 +887,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -936,6 +942,12 @@
     <xf numFmtId="166" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="167" fontId="16" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -943,9 +955,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -968,7 +977,7 @@
     <xf numFmtId="166" fontId="16" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="16" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1713,7 +1722,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1734,37 +1743,37 @@
       <c r="H3" s="12"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="D4" s="37" t="s">
-        <v>149</v>
-      </c>
-      <c r="F4" s="38" t="s">
+      <c r="B4" s="37" t="s">
         <v>150</v>
       </c>
+      <c r="D4" s="38" t="s">
+        <v>151</v>
+      </c>
+      <c r="F4" s="39" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="39" t="s">
-        <v>151</v>
-      </c>
-      <c r="C6" s="40" t="s">
+      <c r="B6" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="C6" s="41" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="40" t="s">
+      <c r="D6" s="41" t="s">
         <v>97</v>
       </c>
-      <c r="E6" s="40" t="s">
+      <c r="E6" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="F6" s="40" t="s">
+      <c r="F6" s="41" t="s">
         <v>99</v>
       </c>
-      <c r="G6" s="40" t="s">
+      <c r="G6" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="H6" s="40" t="s">
-        <v>152</v>
+      <c r="H6" s="41" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -1789,7 +1798,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="25" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C8" s="27">
         <v>1546000</v>
@@ -1809,7 +1818,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="25" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C9" s="27">
         <v>1200167.1888888888</v>
@@ -1829,7 +1838,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="25" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C10" s="27">
         <v>654000</v>
@@ -1849,7 +1858,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="25" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C11" s="27">
         <v>164824.60522117943</v>
@@ -1869,7 +1878,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="28" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C12" s="30">
         <v>-472991.79411006824</v>
@@ -1889,7 +1898,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="28" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C13" s="30">
         <v>-472991.79411006824</v>
@@ -1909,341 +1918,341 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="28" t="s">
-        <v>159</v>
-      </c>
-      <c r="C14" s="41">
+        <v>161</v>
+      </c>
+      <c r="C14" s="42">
         <v>-0.3059455330595525</v>
       </c>
-      <c r="D14" s="41">
+      <c r="D14" s="42">
         <v>-0.10427042130500674</v>
       </c>
-      <c r="E14" s="41">
+      <c r="E14" s="42">
         <v>-0.046066008479458874</v>
       </c>
-      <c r="F14" s="41">
+      <c r="F14" s="42">
         <v>-0.16504185604249857</v>
       </c>
-      <c r="G14" s="41">
+      <c r="G14" s="42">
         <v>-0.44816260261601254</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="28" t="s">
-        <v>160</v>
-      </c>
-      <c r="C15" s="42">
+        <v>162</v>
+      </c>
+      <c r="C15" s="43">
         <v>12883.333333333334</v>
       </c>
-      <c r="D15" s="42">
+      <c r="D15" s="43">
         <v>12689</v>
       </c>
-      <c r="E15" s="42">
+      <c r="E15" s="43">
         <v>12716.203333333333</v>
       </c>
-      <c r="F15" s="42">
+      <c r="F15" s="43">
         <v>12878.376766666668</v>
       </c>
-      <c r="G15" s="42">
+      <c r="G15" s="43">
         <v>13110.622483</v>
       </c>
-      <c r="H15" s="43" t="s">
-        <v>161</v>
+      <c r="H15" s="44" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="28" t="s">
-        <v>162</v>
-      </c>
-      <c r="C16" s="41">
+        <v>164</v>
+      </c>
+      <c r="C16" s="42">
         <v>0.7763047793589191</v>
       </c>
-      <c r="D16" s="41">
+      <c r="D16" s="42">
         <v>0.6515878070113221</v>
       </c>
-      <c r="E16" s="44">
+      <c r="E16" s="45">
         <v>0.5752710583855843</v>
       </c>
-      <c r="F16" s="44">
+      <c r="F16" s="45">
         <v>0.5597527709991174</v>
       </c>
-      <c r="G16" s="44">
+      <c r="G16" s="45">
         <v>0.5557873295275215</v>
       </c>
-      <c r="H16" s="43" t="s">
-        <v>163</v>
+      <c r="H16" s="44" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="28" t="s">
-        <v>164</v>
-      </c>
-      <c r="C17" s="45">
+        <v>166</v>
+      </c>
+      <c r="C17" s="46">
         <v>0.12690815006468306</v>
       </c>
-      <c r="D17" s="45">
+      <c r="D17" s="46">
         <v>0.1163204350224604</v>
       </c>
-      <c r="E17" s="45">
+      <c r="E17" s="46">
         <v>0.1282767069800621</v>
       </c>
-      <c r="F17" s="44">
+      <c r="F17" s="45">
         <v>0.1713478820185269</v>
       </c>
-      <c r="G17" s="41">
+      <c r="G17" s="42">
         <v>0.25828370438269493</v>
       </c>
-      <c r="H17" s="43" t="s">
-        <v>165</v>
+      <c r="H17" s="44" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="C18" s="41">
+      <c r="C18" s="42">
         <v>-0.19933194624119585</v>
       </c>
-      <c r="D18" s="41">
+      <c r="D18" s="42">
         <v>-0.039322590419523434</v>
       </c>
-      <c r="E18" s="41">
+      <c r="E18" s="42">
         <v>-0.0028600816524580494</v>
       </c>
-      <c r="F18" s="41">
+      <c r="F18" s="42">
         <v>-0.13091237772754036</v>
       </c>
-      <c r="G18" s="41">
+      <c r="G18" s="42">
         <v>-0.4167330108031714</v>
       </c>
-      <c r="H18" s="43" t="s">
-        <v>166</v>
+      <c r="H18" s="44" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="28" t="s">
-        <v>167</v>
-      </c>
-      <c r="C19" s="46">
-        <v>1</v>
-      </c>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="46"/>
-      <c r="H19" s="43" t="s">
-        <v>168</v>
+        <v>169</v>
+      </c>
+      <c r="C19" s="47">
+        <v>3</v>
+      </c>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="44" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="28" t="s">
-        <v>169</v>
-      </c>
-      <c r="C20" s="47">
+        <v>171</v>
+      </c>
+      <c r="C20" s="48">
         <v>-1.8696673865856184</v>
       </c>
-      <c r="D20" s="47">
+      <c r="D20" s="48">
         <v>-0.6054488638559378</v>
       </c>
-      <c r="E20" s="47">
+      <c r="E20" s="48">
         <v>-0.06619651197184098</v>
       </c>
-      <c r="F20" s="47">
+      <c r="F20" s="48">
         <v>-3.8357567765741165</v>
       </c>
-      <c r="G20" s="47">
+      <c r="G20" s="48">
         <v>-13.259256222122064</v>
       </c>
-      <c r="H20" s="43" t="s">
-        <v>170</v>
+      <c r="H20" s="44" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="C21" s="48" t="s">
-        <v>172</v>
-      </c>
-      <c r="D21" s="48"/>
-      <c r="E21" s="48"/>
-      <c r="F21" s="48"/>
-      <c r="G21" s="48"/>
-      <c r="H21" s="43" t="s">
+        <v>173</v>
+      </c>
+      <c r="C21" s="49" t="s">
+        <v>174</v>
+      </c>
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="49"/>
+      <c r="H21" s="44" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="C22" s="48" t="s">
-        <v>174</v>
-      </c>
-      <c r="D22" s="48"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="48"/>
-      <c r="H22" s="43" t="s">
         <v>175</v>
       </c>
+      <c r="C22" s="49" t="s">
+        <v>176</v>
+      </c>
+      <c r="D22" s="49"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="49"/>
+      <c r="G22" s="49"/>
+      <c r="H22" s="44" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="39" t="s">
-        <v>176</v>
-      </c>
-      <c r="C24" s="39" t="s">
-        <v>177</v>
-      </c>
-      <c r="D24" s="39" t="s">
+      <c r="B24" s="40" t="s">
         <v>178</v>
       </c>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39" t="s">
+      <c r="C24" s="40" t="s">
         <v>179</v>
       </c>
-      <c r="G24" s="39"/>
-      <c r="H24" s="39"/>
+      <c r="D24" s="40" t="s">
+        <v>180</v>
+      </c>
+      <c r="E24" s="40"/>
+      <c r="F24" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="G24" s="40"/>
+      <c r="H24" s="40"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="49" t="s">
-        <v>180</v>
-      </c>
-      <c r="C25" s="50" t="s">
-        <v>181</v>
-      </c>
-      <c r="D25" s="51" t="s">
+      <c r="B25" s="50" t="s">
         <v>182</v>
       </c>
-      <c r="E25" s="51"/>
-      <c r="F25" s="52" t="s">
+      <c r="C25" s="51" t="s">
         <v>183</v>
       </c>
-      <c r="G25" s="52"/>
-      <c r="H25" s="52"/>
+      <c r="D25" s="52" t="s">
+        <v>184</v>
+      </c>
+      <c r="E25" s="52"/>
+      <c r="F25" s="53" t="s">
+        <v>185</v>
+      </c>
+      <c r="G25" s="53"/>
+      <c r="H25" s="53"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="49" t="s">
-        <v>184</v>
-      </c>
-      <c r="C26" s="50" t="s">
-        <v>181</v>
-      </c>
-      <c r="D26" s="51" t="s">
-        <v>185</v>
-      </c>
-      <c r="E26" s="51"/>
-      <c r="F26" s="52" t="s">
+      <c r="B26" s="50" t="s">
         <v>186</v>
       </c>
-      <c r="G26" s="52"/>
-      <c r="H26" s="52"/>
+      <c r="C26" s="51" t="s">
+        <v>183</v>
+      </c>
+      <c r="D26" s="52" t="s">
+        <v>187</v>
+      </c>
+      <c r="E26" s="52"/>
+      <c r="F26" s="53" t="s">
+        <v>188</v>
+      </c>
+      <c r="G26" s="53"/>
+      <c r="H26" s="53"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="49" t="s">
-        <v>187</v>
-      </c>
-      <c r="C27" s="53" t="s">
-        <v>188</v>
-      </c>
-      <c r="D27" s="51" t="s">
+      <c r="B27" s="50" t="s">
         <v>189</v>
       </c>
-      <c r="E27" s="51"/>
-      <c r="F27" s="52" t="s">
+      <c r="C27" s="54" t="s">
         <v>190</v>
       </c>
-      <c r="G27" s="52"/>
-      <c r="H27" s="52"/>
+      <c r="D27" s="52" t="s">
+        <v>191</v>
+      </c>
+      <c r="E27" s="52"/>
+      <c r="F27" s="53" t="s">
+        <v>192</v>
+      </c>
+      <c r="G27" s="53"/>
+      <c r="H27" s="53"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="49" t="s">
-        <v>191</v>
-      </c>
-      <c r="C28" s="50" t="s">
-        <v>181</v>
-      </c>
-      <c r="D28" s="51" t="s">
-        <v>192</v>
-      </c>
-      <c r="E28" s="51"/>
-      <c r="F28" s="52" t="s">
+      <c r="B28" s="50" t="s">
         <v>193</v>
       </c>
-      <c r="G28" s="52"/>
-      <c r="H28" s="52"/>
+      <c r="C28" s="51" t="s">
+        <v>183</v>
+      </c>
+      <c r="D28" s="52" t="s">
+        <v>194</v>
+      </c>
+      <c r="E28" s="52"/>
+      <c r="F28" s="53" t="s">
+        <v>195</v>
+      </c>
+      <c r="G28" s="53"/>
+      <c r="H28" s="53"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="49" t="s">
-        <v>194</v>
-      </c>
-      <c r="C29" s="50" t="s">
-        <v>181</v>
-      </c>
-      <c r="D29" s="51" t="s">
-        <v>195</v>
-      </c>
-      <c r="E29" s="51"/>
-      <c r="F29" s="52" t="s">
+      <c r="B29" s="50" t="s">
         <v>196</v>
       </c>
-      <c r="G29" s="52"/>
-      <c r="H29" s="52"/>
+      <c r="C29" s="51" t="s">
+        <v>183</v>
+      </c>
+      <c r="D29" s="52" t="s">
+        <v>197</v>
+      </c>
+      <c r="E29" s="52"/>
+      <c r="F29" s="53" t="s">
+        <v>198</v>
+      </c>
+      <c r="G29" s="53"/>
+      <c r="H29" s="53"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="49" t="s">
-        <v>197</v>
-      </c>
-      <c r="C30" s="54" t="s">
-        <v>198</v>
-      </c>
-      <c r="D30" s="51" t="s">
+      <c r="B30" s="50" t="s">
         <v>199</v>
       </c>
-      <c r="E30" s="51"/>
-      <c r="F30" s="52" t="s">
+      <c r="C30" s="55" t="s">
         <v>200</v>
       </c>
-      <c r="G30" s="52"/>
-      <c r="H30" s="52"/>
+      <c r="D30" s="52" t="s">
+        <v>201</v>
+      </c>
+      <c r="E30" s="52"/>
+      <c r="F30" s="53" t="s">
+        <v>202</v>
+      </c>
+      <c r="G30" s="53"/>
+      <c r="H30" s="53"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="49" t="s">
-        <v>201</v>
-      </c>
-      <c r="C31" s="50" t="s">
-        <v>181</v>
-      </c>
-      <c r="D31" s="51" t="s">
-        <v>202</v>
-      </c>
-      <c r="E31" s="51"/>
-      <c r="F31" s="52" t="s">
+      <c r="B31" s="50" t="s">
         <v>203</v>
       </c>
-      <c r="G31" s="52"/>
-      <c r="H31" s="52"/>
+      <c r="C31" s="51" t="s">
+        <v>183</v>
+      </c>
+      <c r="D31" s="52" t="s">
+        <v>204</v>
+      </c>
+      <c r="E31" s="52"/>
+      <c r="F31" s="53" t="s">
+        <v>205</v>
+      </c>
+      <c r="G31" s="53"/>
+      <c r="H31" s="53"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="49" t="s">
+      <c r="B33" s="50" t="s">
         <v>39</v>
       </c>
       <c r="C33" s="28" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D33" s="28"/>
       <c r="E33" s="28"/>
       <c r="F33" s="28"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="55" t="s">
-        <v>205</v>
-      </c>
-      <c r="C35" s="55"/>
-      <c r="D35" s="55"/>
-      <c r="E35" s="55"/>
-      <c r="F35" s="55"/>
-      <c r="G35" s="55"/>
-      <c r="H35" s="55"/>
+      <c r="B35" s="56" t="s">
+        <v>207</v>
+      </c>
+      <c r="C35" s="56"/>
+      <c r="D35" s="56"/>
+      <c r="E35" s="56"/>
+      <c r="F35" s="56"/>
+      <c r="G35" s="56"/>
+      <c r="H35" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -3396,7 +3405,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:G17"/>
+  <dimension ref="B1:G20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -3705,6 +3714,51 @@
       <c r="G17" s="31">
         <f>IF(G10&gt;0,G16/G10,0)</f>
         <v>-0.41673301</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="C19" s="32">
+        <f>C16</f>
+        <v>-308167.18888889</v>
+      </c>
+      <c r="D19" s="32">
+        <f>C19+D16</f>
+        <v>-407960.05885556</v>
+      </c>
+      <c r="E19" s="32">
+        <f>D19+E16</f>
+        <v>-418870.87280833</v>
+      </c>
+      <c r="F19" s="32">
+        <f>E19+F16</f>
+        <v>-1051097.96923163</v>
+      </c>
+      <c r="G19" s="32">
+        <f>F19+G16</f>
+        <v>-3236549.64156936</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="C20" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="G20" s="33" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3735,7 +3789,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -3763,7 +3817,7 @@
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="25" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C4" s="27">
         <f>'5-Year P&amp;L'!C16</f>
@@ -3788,7 +3842,7 @@
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="25" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C6" s="27">
         <f>Assumptions!D58</f>
@@ -3813,7 +3867,7 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="25" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C7" s="27">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
@@ -3838,7 +3892,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="28" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C8" s="29">
         <f>C6+C7</f>
@@ -3863,32 +3917,32 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="C10" s="32">
+        <v>132</v>
+      </c>
+      <c r="C10" s="34">
         <f>IF(C8&gt;0,C4/C8,IF(C4&gt;0,99.9,0))</f>
         <v>-1.86966739</v>
       </c>
-      <c r="D10" s="32">
+      <c r="D10" s="34">
         <f>IF(D8&gt;0,D4/D8,IF(D4&gt;0,99.9,0))</f>
         <v>-0.60544886</v>
       </c>
-      <c r="E10" s="32">
+      <c r="E10" s="34">
         <f>IF(E8&gt;0,E4/E8,IF(E4&gt;0,99.9,0))</f>
         <v>-0.06619651</v>
       </c>
-      <c r="F10" s="32">
+      <c r="F10" s="34">
         <f>IF(F8&gt;0,F4/F8,IF(F4&gt;0,99.9,0))</f>
         <v>-3.83575678</v>
       </c>
-      <c r="G10" s="32">
+      <c r="G10" s="34">
         <f>IF(G8&gt;0,G4/G8,IF(G4&gt;0,99.9,0))</f>
         <v>-13.25925622</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="25" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C12" s="27">
         <f>C4-C8</f>
@@ -3913,25 +3967,25 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="C14" s="33">
+        <v>134</v>
+      </c>
+      <c r="C14" s="35">
         <f>Assumptions!D57+C12</f>
         <v>-472991.79411007</v>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="35">
         <f>C14+D12</f>
         <v>-737609.26929791</v>
       </c>
-      <c r="E14" s="33">
+      <c r="E14" s="35">
         <f>D14+E12</f>
         <v>-913344.68847187</v>
       </c>
-      <c r="F14" s="33">
+      <c r="F14" s="35">
         <f>E14+F12</f>
         <v>-1710396.39011634</v>
       </c>
-      <c r="G14" s="33">
+      <c r="G14" s="35">
         <f>F14+G12</f>
         <v>-4060672.66767526</v>
       </c>
@@ -3964,7 +4018,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -3992,7 +4046,7 @@
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="25" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C4" s="26">
         <f>Drivers!C12</f>
@@ -4017,7 +4071,7 @@
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="25" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C5" s="26">
         <f>Assumptions!D35</f>
@@ -4042,25 +4096,25 @@
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="28" t="s">
-        <v>136</v>
-      </c>
-      <c r="C6" s="34">
+        <v>138</v>
+      </c>
+      <c r="C6" s="36">
         <f>C4+C5</f>
         <v>17</v>
       </c>
-      <c r="D6" s="34">
+      <c r="D6" s="36">
         <f>D4+D5</f>
         <v>24</v>
       </c>
-      <c r="E6" s="34">
+      <c r="E6" s="36">
         <f>E4+E5</f>
         <v>32</v>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="36">
         <f>F4+F5</f>
         <v>39</v>
       </c>
-      <c r="G6" s="34">
+      <c r="G6" s="36">
         <f>G4+G5</f>
         <v>41</v>
       </c>
@@ -4093,13 +4147,13 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C1" s="13"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="25" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C3" s="27">
         <f>Assumptions!D59</f>
@@ -4108,7 +4162,7 @@
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="25" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C4" s="31">
         <f>Assumptions!D60</f>
@@ -4126,18 +4180,18 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="25" t="s">
-        <v>140</v>
-      </c>
-      <c r="C6" s="35">
+        <v>142</v>
+      </c>
+      <c r="C6" s="32">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>49824.60522118</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="C8" s="32">
+        <v>143</v>
+      </c>
+      <c r="C8" s="34">
         <f>'Cash Flow &amp; DSCR'!C10</f>
         <v>-1.86966739</v>
       </c>
@@ -4170,7 +4224,7 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C1" s="13"/>
     </row>
@@ -4203,7 +4257,7 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="25" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C6" s="25">
         <f>Assumptions!D8</f>
@@ -4221,7 +4275,7 @@
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="25" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C9" s="27">
         <f>Drivers!G10</f>
@@ -4230,16 +4284,16 @@
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="25" t="s">
-        <v>145</v>
-      </c>
-      <c r="C10" s="33">
+        <v>147</v>
+      </c>
+      <c r="C10" s="35">
         <f>'5-Year P&amp;L'!G16</f>
         <v>-2185451.67233774</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="12" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C12" s="12"/>
     </row>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
@@ -2362,10 +2362,10 @@
       <formula>C20&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1.0</formula>
+      <formula>C20&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1.0</formula>
+      <formula>C20&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="207">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -542,9 +542,6 @@
   </si>
   <si>
     <t>Break-even Year</t>
-  </si>
-  <si>
-    <t>Not reached</t>
   </si>
   <si>
     <t>Cash Runway</t>
@@ -887,7 +884,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -980,6 +977,9 @@
     <xf numFmtId="164" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="16" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2070,196 +2070,208 @@
       <c r="B21" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="C21" s="49" t="s">
-        <v>174</v>
-      </c>
-      <c r="D21" s="49"/>
-      <c r="E21" s="49"/>
-      <c r="F21" s="49"/>
-      <c r="G21" s="49"/>
+      <c r="C21" s="49" t="str">
+        <f>IF('5-Year P&amp;L'!C19&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="49" t="str">
+        <f>IF('5-Year P&amp;L'!D19&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="49" t="str">
+        <f>IF('5-Year P&amp;L'!E19&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="49" t="str">
+        <f>IF('5-Year P&amp;L'!F19&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="49" t="str">
+        <f>IF('5-Year P&amp;L'!G19&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
       <c r="H21" s="44" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="C22" s="50" t="s">
         <v>175</v>
       </c>
-      <c r="C22" s="49" t="s">
+      <c r="D22" s="50"/>
+      <c r="E22" s="50"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="50"/>
+      <c r="H22" s="44" t="s">
         <v>176</v>
-      </c>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="49"/>
-      <c r="G22" s="49"/>
-      <c r="H22" s="44" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="40" t="s">
+        <v>177</v>
+      </c>
+      <c r="C24" s="40" t="s">
         <v>178</v>
       </c>
-      <c r="C24" s="40" t="s">
+      <c r="D24" s="40" t="s">
         <v>179</v>
-      </c>
-      <c r="D24" s="40" t="s">
-        <v>180</v>
       </c>
       <c r="E24" s="40"/>
       <c r="F24" s="40" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G24" s="40"/>
       <c r="H24" s="40"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="50" t="s">
+      <c r="B25" s="51" t="s">
+        <v>181</v>
+      </c>
+      <c r="C25" s="52" t="s">
         <v>182</v>
       </c>
-      <c r="C25" s="51" t="s">
+      <c r="D25" s="53" t="s">
         <v>183</v>
       </c>
-      <c r="D25" s="52" t="s">
+      <c r="E25" s="53"/>
+      <c r="F25" s="54" t="s">
         <v>184</v>
       </c>
-      <c r="E25" s="52"/>
-      <c r="F25" s="53" t="s">
+      <c r="G25" s="54"/>
+      <c r="H25" s="54"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="51" t="s">
         <v>185</v>
       </c>
-      <c r="G25" s="53"/>
-      <c r="H25" s="53"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="50" t="s">
+      <c r="C26" s="52" t="s">
+        <v>182</v>
+      </c>
+      <c r="D26" s="53" t="s">
         <v>186</v>
       </c>
-      <c r="C26" s="51" t="s">
-        <v>183</v>
-      </c>
-      <c r="D26" s="52" t="s">
+      <c r="E26" s="53"/>
+      <c r="F26" s="54" t="s">
         <v>187</v>
       </c>
-      <c r="E26" s="52"/>
-      <c r="F26" s="53" t="s">
+      <c r="G26" s="54"/>
+      <c r="H26" s="54"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="51" t="s">
         <v>188</v>
       </c>
-      <c r="G26" s="53"/>
-      <c r="H26" s="53"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="50" t="s">
+      <c r="C27" s="55" t="s">
         <v>189</v>
       </c>
-      <c r="C27" s="54" t="s">
+      <c r="D27" s="53" t="s">
         <v>190</v>
       </c>
-      <c r="D27" s="52" t="s">
+      <c r="E27" s="53"/>
+      <c r="F27" s="54" t="s">
         <v>191</v>
       </c>
-      <c r="E27" s="52"/>
-      <c r="F27" s="53" t="s">
+      <c r="G27" s="54"/>
+      <c r="H27" s="54"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="51" t="s">
         <v>192</v>
       </c>
-      <c r="G27" s="53"/>
-      <c r="H27" s="53"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="50" t="s">
+      <c r="C28" s="52" t="s">
+        <v>182</v>
+      </c>
+      <c r="D28" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="C28" s="51" t="s">
-        <v>183</v>
-      </c>
-      <c r="D28" s="52" t="s">
+      <c r="E28" s="53"/>
+      <c r="F28" s="54" t="s">
         <v>194</v>
       </c>
-      <c r="E28" s="52"/>
-      <c r="F28" s="53" t="s">
+      <c r="G28" s="54"/>
+      <c r="H28" s="54"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="51" t="s">
         <v>195</v>
       </c>
-      <c r="G28" s="53"/>
-      <c r="H28" s="53"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="50" t="s">
+      <c r="C29" s="52" t="s">
+        <v>182</v>
+      </c>
+      <c r="D29" s="53" t="s">
         <v>196</v>
       </c>
-      <c r="C29" s="51" t="s">
-        <v>183</v>
-      </c>
-      <c r="D29" s="52" t="s">
+      <c r="E29" s="53"/>
+      <c r="F29" s="54" t="s">
         <v>197</v>
       </c>
-      <c r="E29" s="52"/>
-      <c r="F29" s="53" t="s">
+      <c r="G29" s="54"/>
+      <c r="H29" s="54"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="51" t="s">
         <v>198</v>
       </c>
-      <c r="G29" s="53"/>
-      <c r="H29" s="53"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="50" t="s">
+      <c r="C30" s="56" t="s">
         <v>199</v>
       </c>
-      <c r="C30" s="55" t="s">
+      <c r="D30" s="53" t="s">
         <v>200</v>
       </c>
-      <c r="D30" s="52" t="s">
+      <c r="E30" s="53"/>
+      <c r="F30" s="54" t="s">
         <v>201</v>
       </c>
-      <c r="E30" s="52"/>
-      <c r="F30" s="53" t="s">
+      <c r="G30" s="54"/>
+      <c r="H30" s="54"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="51" t="s">
         <v>202</v>
       </c>
-      <c r="G30" s="53"/>
-      <c r="H30" s="53"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="50" t="s">
+      <c r="C31" s="52" t="s">
+        <v>182</v>
+      </c>
+      <c r="D31" s="53" t="s">
         <v>203</v>
       </c>
-      <c r="C31" s="51" t="s">
-        <v>183</v>
-      </c>
-      <c r="D31" s="52" t="s">
+      <c r="E31" s="53"/>
+      <c r="F31" s="54" t="s">
         <v>204</v>
       </c>
-      <c r="E31" s="52"/>
-      <c r="F31" s="53" t="s">
+      <c r="G31" s="54"/>
+      <c r="H31" s="54"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="28" t="s">
         <v>205</v>
-      </c>
-      <c r="G31" s="53"/>
-      <c r="H31" s="53"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="50" t="s">
-        <v>39</v>
-      </c>
-      <c r="C33" s="28" t="s">
-        <v>206</v>
       </c>
       <c r="D33" s="28"/>
       <c r="E33" s="28"/>
       <c r="F33" s="28"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="56" t="s">
-        <v>207</v>
-      </c>
-      <c r="C35" s="56"/>
-      <c r="D35" s="56"/>
-      <c r="E35" s="56"/>
-      <c r="F35" s="56"/>
-      <c r="G35" s="56"/>
-      <c r="H35" s="56"/>
+      <c r="B35" s="57" t="s">
+        <v>206</v>
+      </c>
+      <c r="C35" s="57"/>
+      <c r="D35" s="57"/>
+      <c r="E35" s="57"/>
+      <c r="F35" s="57"/>
+      <c r="G35" s="57"/>
+      <c r="H35" s="57"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="22">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C21:G21"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:H24"/>
@@ -2340,10 +2352,10 @@
       <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.25</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.25</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:G18">

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="206">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -544,13 +544,10 @@
     <t>Break-even Year</t>
   </si>
   <si>
-    <t>Cash Runway</t>
-  </si>
-  <si>
-    <t>0 months</t>
-  </si>
-  <si>
-    <t>60+ months</t>
+    <t>Cash Runway (Months)</t>
+  </si>
+  <si>
+    <t>≥ 24 months</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -974,14 +971,18 @@
     <xf numFmtId="166" fontId="16" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="167" fontId="16" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2035,10 +2036,18 @@
       <c r="C19" s="47">
         <v>3</v>
       </c>
-      <c r="D19" s="47"/>
-      <c r="E19" s="47"/>
-      <c r="F19" s="47"/>
-      <c r="G19" s="47"/>
+      <c r="D19" s="47">
+        <v>3</v>
+      </c>
+      <c r="E19" s="47">
+        <v>3</v>
+      </c>
+      <c r="F19" s="47">
+        <v>3</v>
+      </c>
+      <c r="G19" s="47">
+        <v>3</v>
+      </c>
       <c r="H19" s="44" t="s">
         <v>170</v>
       </c>
@@ -2075,19 +2084,19 @@
         <v>0</v>
       </c>
       <c r="D21" s="49" t="str">
-        <f>IF('5-Year P&amp;L'!D19&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year P&amp;L'!D19&gt;=0,'5-Year P&amp;L'!C19&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="E21" s="49" t="str">
-        <f>IF('5-Year P&amp;L'!E19&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year P&amp;L'!E19&gt;=0,'5-Year P&amp;L'!D19&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="F21" s="49" t="str">
-        <f>IF('5-Year P&amp;L'!F19&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year P&amp;L'!F19&gt;=0,'5-Year P&amp;L'!E19&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="G21" s="49" t="str">
-        <f>IF('5-Year P&amp;L'!G19&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year P&amp;L'!G19&gt;=0,'5-Year P&amp;L'!F19&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="H21" s="44" t="s">
@@ -2098,149 +2107,157 @@
       <c r="B22" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="C22" s="50" t="s">
+      <c r="C22" s="50">
+        <v>-3</v>
+      </c>
+      <c r="D22" s="50">
+        <v>-3</v>
+      </c>
+      <c r="E22" s="50">
+        <v>-3</v>
+      </c>
+      <c r="F22" s="50">
+        <v>-4</v>
+      </c>
+      <c r="G22" s="50">
+        <v>-6</v>
+      </c>
+      <c r="H22" s="44" t="s">
         <v>175</v>
-      </c>
-      <c r="D22" s="50"/>
-      <c r="E22" s="50"/>
-      <c r="F22" s="50"/>
-      <c r="G22" s="50"/>
-      <c r="H22" s="44" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="40" t="s">
+        <v>176</v>
+      </c>
+      <c r="C24" s="40" t="s">
         <v>177</v>
       </c>
-      <c r="C24" s="40" t="s">
+      <c r="D24" s="40" t="s">
         <v>178</v>
-      </c>
-      <c r="D24" s="40" t="s">
-        <v>179</v>
       </c>
       <c r="E24" s="40"/>
       <c r="F24" s="40" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G24" s="40"/>
       <c r="H24" s="40"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="51" t="s">
+        <v>180</v>
+      </c>
+      <c r="C25" s="52" t="s">
         <v>181</v>
       </c>
-      <c r="C25" s="52" t="s">
+      <c r="D25" s="53" t="s">
         <v>182</v>
-      </c>
-      <c r="D25" s="53" t="s">
-        <v>183</v>
       </c>
       <c r="E25" s="53"/>
       <c r="F25" s="54" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G25" s="54"/>
       <c r="H25" s="54"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="51" t="s">
+        <v>184</v>
+      </c>
+      <c r="C26" s="52" t="s">
+        <v>181</v>
+      </c>
+      <c r="D26" s="53" t="s">
         <v>185</v>
-      </c>
-      <c r="C26" s="52" t="s">
-        <v>182</v>
-      </c>
-      <c r="D26" s="53" t="s">
-        <v>186</v>
       </c>
       <c r="E26" s="53"/>
       <c r="F26" s="54" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G26" s="54"/>
       <c r="H26" s="54"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="51" t="s">
+        <v>187</v>
+      </c>
+      <c r="C27" s="55" t="s">
         <v>188</v>
       </c>
-      <c r="C27" s="55" t="s">
+      <c r="D27" s="53" t="s">
         <v>189</v>
-      </c>
-      <c r="D27" s="53" t="s">
-        <v>190</v>
       </c>
       <c r="E27" s="53"/>
       <c r="F27" s="54" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G27" s="54"/>
       <c r="H27" s="54"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="51" t="s">
+        <v>191</v>
+      </c>
+      <c r="C28" s="52" t="s">
+        <v>181</v>
+      </c>
+      <c r="D28" s="53" t="s">
         <v>192</v>
-      </c>
-      <c r="C28" s="52" t="s">
-        <v>182</v>
-      </c>
-      <c r="D28" s="53" t="s">
-        <v>193</v>
       </c>
       <c r="E28" s="53"/>
       <c r="F28" s="54" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G28" s="54"/>
       <c r="H28" s="54"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="51" t="s">
+        <v>194</v>
+      </c>
+      <c r="C29" s="52" t="s">
+        <v>181</v>
+      </c>
+      <c r="D29" s="53" t="s">
         <v>195</v>
-      </c>
-      <c r="C29" s="52" t="s">
-        <v>182</v>
-      </c>
-      <c r="D29" s="53" t="s">
-        <v>196</v>
       </c>
       <c r="E29" s="53"/>
       <c r="F29" s="54" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G29" s="54"/>
       <c r="H29" s="54"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="51" t="s">
+        <v>197</v>
+      </c>
+      <c r="C30" s="56" t="s">
         <v>198</v>
       </c>
-      <c r="C30" s="56" t="s">
+      <c r="D30" s="53" t="s">
         <v>199</v>
-      </c>
-      <c r="D30" s="53" t="s">
-        <v>200</v>
       </c>
       <c r="E30" s="53"/>
       <c r="F30" s="54" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G30" s="54"/>
       <c r="H30" s="54"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="51" t="s">
+        <v>201</v>
+      </c>
+      <c r="C31" s="52" t="s">
+        <v>181</v>
+      </c>
+      <c r="D31" s="53" t="s">
         <v>202</v>
-      </c>
-      <c r="C31" s="52" t="s">
-        <v>182</v>
-      </c>
-      <c r="D31" s="53" t="s">
-        <v>203</v>
       </c>
       <c r="E31" s="53"/>
       <c r="F31" s="54" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G31" s="54"/>
       <c r="H31" s="54"/>
@@ -2250,7 +2267,7 @@
         <v>39</v>
       </c>
       <c r="C33" s="28" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D33" s="28"/>
       <c r="E33" s="28"/>
@@ -2258,7 +2275,7 @@
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="57" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C35" s="57"/>
       <c r="D35" s="57"/>
@@ -2268,11 +2285,9 @@
       <c r="H35" s="57"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
@@ -598,10 +598,13 @@
     <t>Facility Burden</t>
   </si>
   <si>
-    <t>Facility costs at 26% of revenue are high. Fixed costs this size create rigidity in your budget.</t>
-  </si>
-  <si>
-    <t>Explore shared space, renegotiate terms, or consider a smaller facility.</t>
+    <t>● Healthy</t>
+  </si>
+  <si>
+    <t>Facility costs at 6% of revenue are well-managed and leave budget for programs.</t>
+  </si>
+  <si>
+    <t>Watch for rent escalation clauses that could push this higher over time.</t>
   </si>
   <si>
     <t>Debt Affordability</t>
@@ -616,9 +619,6 @@
     <t>Revenue Concentration</t>
   </si>
   <si>
-    <t>● Healthy</t>
-  </si>
-  <si>
     <t>Revenue is anchored to enrollment-driven income — the strongest foundation for a school model. A focused revenue stream is a strength when backed by dependable demand.</t>
   </si>
   <si>
@@ -634,7 +634,7 @@
     <t>Prioritize building reserves — even a small surplus each year compounds into meaningful protection.</t>
   </si>
   <si>
-    <t>1 Healthy  |  1 Watch  |  5 Needs Attention</t>
+    <t>2 Healthy  |  1 Watch  |  4 Needs Attention</t>
   </si>
   <si>
     <t>Built by SchoolStack Budget  •  budget.schoolstack.ai</t>
@@ -1987,20 +1987,20 @@
       <c r="B17" s="28" t="s">
         <v>166</v>
       </c>
-      <c r="C17" s="46">
-        <v>0.12690815006468306</v>
+      <c r="C17" s="45">
+        <v>0.18240620957309184</v>
       </c>
       <c r="D17" s="46">
-        <v>0.1163204350224604</v>
+        <v>0.11445346362991568</v>
       </c>
       <c r="E17" s="46">
-        <v>0.1282767069800621</v>
-      </c>
-      <c r="F17" s="45">
-        <v>0.1713478820185269</v>
-      </c>
-      <c r="G17" s="42">
-        <v>0.25828370438269493</v>
+        <v>0.07842325054569485</v>
+      </c>
+      <c r="F17" s="46">
+        <v>0.06380700913541373</v>
+      </c>
+      <c r="G17" s="46">
+        <v>0.06052219961934512</v>
       </c>
       <c r="H17" s="44" t="s">
         <v>167</v>
@@ -2198,42 +2198,42 @@
       <c r="B28" s="51" t="s">
         <v>191</v>
       </c>
-      <c r="C28" s="52" t="s">
-        <v>181</v>
+      <c r="C28" s="56" t="s">
+        <v>192</v>
       </c>
       <c r="D28" s="53" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E28" s="53"/>
       <c r="F28" s="54" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G28" s="54"/>
       <c r="H28" s="54"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="51" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C29" s="52" t="s">
         <v>181</v>
       </c>
       <c r="D29" s="53" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E29" s="53"/>
       <c r="F29" s="54" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G29" s="54"/>
       <c r="H29" s="54"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="51" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C30" s="56" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="D30" s="53" t="s">
         <v>199</v>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="215">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -397,6 +397,15 @@
     <t>Operating Margin</t>
   </si>
   <si>
+    <t>Capital &amp; Debt Service</t>
+  </si>
+  <si>
+    <t>Net Income</t>
+  </si>
+  <si>
+    <t>Net Margin</t>
+  </si>
+  <si>
     <t>Cumulative Net Income</t>
   </si>
   <si>
@@ -406,6 +415,9 @@
     <t>Cash Flow &amp; Debt Service Coverage</t>
   </si>
   <si>
+    <t>Beginning Cash</t>
+  </si>
+  <si>
     <t>Net Operating Income</t>
   </si>
   <si>
@@ -424,7 +436,10 @@
     <t>Net Income After Debt</t>
   </si>
   <si>
-    <t>Cumulative Cash</t>
+    <t>Net Cash Flow</t>
+  </si>
+  <si>
+    <t>Ending Cash</t>
   </si>
   <si>
     <t>Staffing Detail</t>
@@ -466,6 +481,27 @@
     <t>Year 5 NOI</t>
   </si>
   <si>
+    <t>KEY RATIOS</t>
+  </si>
+  <si>
+    <t>Net Margin (Year 5)</t>
+  </si>
+  <si>
+    <t>Personnel % of Revenue (Year 5)</t>
+  </si>
+  <si>
+    <t>Revenue per Student (Year 5)</t>
+  </si>
+  <si>
+    <t>Expense per Student (Year 5)</t>
+  </si>
+  <si>
+    <t>DSCR (Year 1)</t>
+  </si>
+  <si>
+    <t>DSCR (Year 5)</t>
+  </si>
+  <si>
     <t>Generated by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
@@ -497,15 +533,6 @@
   </si>
   <si>
     <t>Debt Service</t>
-  </si>
-  <si>
-    <t>Net Income</t>
-  </si>
-  <si>
-    <t>Ending Cash</t>
-  </si>
-  <si>
-    <t>Net Margin</t>
   </si>
   <si>
     <t>Revenue per Student</t>
@@ -881,7 +908,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -945,10 +972,14 @@
     <xf numFmtId="167" fontId="16" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="165" fontId="16" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1723,7 +1754,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1744,37 +1775,37 @@
       <c r="H3" s="12"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="37" t="s">
-        <v>150</v>
-      </c>
-      <c r="D4" s="38" t="s">
-        <v>151</v>
-      </c>
-      <c r="F4" s="39" t="s">
-        <v>152</v>
+      <c r="B4" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="D4" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="F4" s="41" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="40" t="s">
-        <v>153</v>
-      </c>
-      <c r="C6" s="41" t="s">
+      <c r="B6" s="42" t="s">
+        <v>165</v>
+      </c>
+      <c r="C6" s="43" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="41" t="s">
+      <c r="D6" s="43" t="s">
         <v>97</v>
       </c>
-      <c r="E6" s="41" t="s">
+      <c r="E6" s="43" t="s">
         <v>98</v>
       </c>
-      <c r="F6" s="41" t="s">
+      <c r="F6" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="G6" s="41" t="s">
+      <c r="G6" s="43" t="s">
         <v>100</v>
       </c>
-      <c r="H6" s="41" t="s">
-        <v>154</v>
+      <c r="H6" s="43" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -1799,7 +1830,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="C8" s="27">
         <v>1546000</v>
@@ -1819,7 +1850,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="25" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="C9" s="27">
         <v>1200167.1888888888</v>
@@ -1839,7 +1870,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="25" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C10" s="27">
         <v>654000</v>
@@ -1859,7 +1890,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="25" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="C11" s="27">
         <v>164824.60522117943</v>
@@ -1879,7 +1910,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="28" t="s">
-        <v>159</v>
+        <v>126</v>
       </c>
       <c r="C12" s="30">
         <v>-472991.79411006824</v>
@@ -1899,7 +1930,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="28" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="C13" s="30">
         <v>-472991.79411006824</v>
@@ -1919,370 +1950,370 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="C14" s="42">
+        <v>127</v>
+      </c>
+      <c r="C14" s="44">
         <v>-0.3059455330595525</v>
       </c>
-      <c r="D14" s="42">
+      <c r="D14" s="44">
         <v>-0.10427042130500674</v>
       </c>
-      <c r="E14" s="42">
+      <c r="E14" s="44">
         <v>-0.046066008479458874</v>
       </c>
-      <c r="F14" s="42">
+      <c r="F14" s="44">
         <v>-0.16504185604249857</v>
       </c>
-      <c r="G14" s="42">
+      <c r="G14" s="44">
         <v>-0.44816260261601254</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="28" t="s">
-        <v>162</v>
-      </c>
-      <c r="C15" s="43">
+        <v>171</v>
+      </c>
+      <c r="C15" s="45">
         <v>12883.333333333334</v>
       </c>
-      <c r="D15" s="43">
+      <c r="D15" s="45">
         <v>12689</v>
       </c>
-      <c r="E15" s="43">
+      <c r="E15" s="45">
         <v>12716.203333333333</v>
       </c>
-      <c r="F15" s="43">
+      <c r="F15" s="45">
         <v>12878.376766666668</v>
       </c>
-      <c r="G15" s="43">
+      <c r="G15" s="45">
         <v>13110.622483</v>
       </c>
-      <c r="H15" s="44" t="s">
-        <v>163</v>
+      <c r="H15" s="46" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="28" t="s">
-        <v>164</v>
-      </c>
-      <c r="C16" s="42">
+        <v>173</v>
+      </c>
+      <c r="C16" s="44">
         <v>0.7763047793589191</v>
       </c>
-      <c r="D16" s="42">
+      <c r="D16" s="44">
         <v>0.6515878070113221</v>
       </c>
-      <c r="E16" s="45">
+      <c r="E16" s="47">
         <v>0.5752710583855843</v>
       </c>
-      <c r="F16" s="45">
+      <c r="F16" s="47">
         <v>0.5597527709991174</v>
       </c>
-      <c r="G16" s="45">
+      <c r="G16" s="47">
         <v>0.5557873295275215</v>
       </c>
-      <c r="H16" s="44" t="s">
-        <v>165</v>
+      <c r="H16" s="46" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="28" t="s">
-        <v>166</v>
-      </c>
-      <c r="C17" s="45">
+        <v>175</v>
+      </c>
+      <c r="C17" s="47">
         <v>0.18240620957309184</v>
       </c>
-      <c r="D17" s="46">
+      <c r="D17" s="48">
         <v>0.11445346362991568</v>
       </c>
-      <c r="E17" s="46">
+      <c r="E17" s="48">
         <v>0.07842325054569485</v>
       </c>
-      <c r="F17" s="46">
+      <c r="F17" s="48">
         <v>0.06380700913541373</v>
       </c>
-      <c r="G17" s="46">
+      <c r="G17" s="48">
         <v>0.06052219961934512</v>
       </c>
-      <c r="H17" s="44" t="s">
-        <v>167</v>
+      <c r="H17" s="46" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="C18" s="42">
+      <c r="C18" s="44">
         <v>-0.19933194624119585</v>
       </c>
-      <c r="D18" s="42">
+      <c r="D18" s="44">
         <v>-0.039322590419523434</v>
       </c>
-      <c r="E18" s="42">
+      <c r="E18" s="44">
         <v>-0.0028600816524580494</v>
       </c>
-      <c r="F18" s="42">
+      <c r="F18" s="44">
         <v>-0.13091237772754036</v>
       </c>
-      <c r="G18" s="42">
+      <c r="G18" s="44">
         <v>-0.4167330108031714</v>
       </c>
-      <c r="H18" s="44" t="s">
-        <v>168</v>
+      <c r="H18" s="46" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="28" t="s">
-        <v>169</v>
-      </c>
-      <c r="C19" s="47">
+        <v>178</v>
+      </c>
+      <c r="C19" s="49">
         <v>3</v>
       </c>
-      <c r="D19" s="47">
+      <c r="D19" s="49">
         <v>3</v>
       </c>
-      <c r="E19" s="47">
+      <c r="E19" s="49">
         <v>3</v>
       </c>
-      <c r="F19" s="47">
+      <c r="F19" s="49">
         <v>3</v>
       </c>
-      <c r="G19" s="47">
+      <c r="G19" s="49">
         <v>3</v>
       </c>
-      <c r="H19" s="44" t="s">
-        <v>170</v>
+      <c r="H19" s="46" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="C20" s="48">
+        <v>180</v>
+      </c>
+      <c r="C20" s="50">
         <v>-1.8696673865856184</v>
       </c>
-      <c r="D20" s="48">
+      <c r="D20" s="50">
         <v>-0.6054488638559378</v>
       </c>
-      <c r="E20" s="48">
+      <c r="E20" s="50">
         <v>-0.06619651197184098</v>
       </c>
-      <c r="F20" s="48">
+      <c r="F20" s="50">
         <v>-3.8357567765741165</v>
       </c>
-      <c r="G20" s="48">
+      <c r="G20" s="50">
         <v>-13.259256222122064</v>
       </c>
-      <c r="H20" s="44" t="s">
-        <v>172</v>
+      <c r="H20" s="46" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="C21" s="49" t="str">
-        <f>IF('5-Year P&amp;L'!C19&gt;=0,"✓ Break-even","")</f>
+        <v>182</v>
+      </c>
+      <c r="C21" s="51" t="str">
+        <f>IF('5-Year P&amp;L'!C24&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D21" s="49" t="str">
-        <f>IF(AND('5-Year P&amp;L'!D19&gt;=0,'5-Year P&amp;L'!C19&lt;0),"✓ Break-even","")</f>
+      <c r="D21" s="51" t="str">
+        <f>IF(AND('5-Year P&amp;L'!D24&gt;=0,'5-Year P&amp;L'!C24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="49" t="str">
-        <f>IF(AND('5-Year P&amp;L'!E19&gt;=0,'5-Year P&amp;L'!D19&lt;0),"✓ Break-even","")</f>
+      <c r="E21" s="51" t="str">
+        <f>IF(AND('5-Year P&amp;L'!E24&gt;=0,'5-Year P&amp;L'!D24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="49" t="str">
-        <f>IF(AND('5-Year P&amp;L'!F19&gt;=0,'5-Year P&amp;L'!E19&lt;0),"✓ Break-even","")</f>
+      <c r="F21" s="51" t="str">
+        <f>IF(AND('5-Year P&amp;L'!F24&gt;=0,'5-Year P&amp;L'!E24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="49" t="str">
-        <f>IF(AND('5-Year P&amp;L'!G19&gt;=0,'5-Year P&amp;L'!F19&lt;0),"✓ Break-even","")</f>
+      <c r="G21" s="51" t="str">
+        <f>IF(AND('5-Year P&amp;L'!G24&gt;=0,'5-Year P&amp;L'!F24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="44" t="s">
+      <c r="H21" s="46" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="C22" s="50">
+        <v>183</v>
+      </c>
+      <c r="C22" s="52">
         <v>-3</v>
       </c>
-      <c r="D22" s="50">
+      <c r="D22" s="52">
         <v>-3</v>
       </c>
-      <c r="E22" s="50">
+      <c r="E22" s="52">
         <v>-3</v>
       </c>
-      <c r="F22" s="50">
+      <c r="F22" s="52">
         <v>-4</v>
       </c>
-      <c r="G22" s="50">
+      <c r="G22" s="52">
         <v>-6</v>
       </c>
-      <c r="H22" s="44" t="s">
-        <v>175</v>
+      <c r="H22" s="46" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="40" t="s">
-        <v>176</v>
-      </c>
-      <c r="C24" s="40" t="s">
-        <v>177</v>
-      </c>
-      <c r="D24" s="40" t="s">
-        <v>178</v>
-      </c>
-      <c r="E24" s="40"/>
-      <c r="F24" s="40" t="s">
-        <v>179</v>
-      </c>
-      <c r="G24" s="40"/>
-      <c r="H24" s="40"/>
+      <c r="B24" s="42" t="s">
+        <v>185</v>
+      </c>
+      <c r="C24" s="42" t="s">
+        <v>186</v>
+      </c>
+      <c r="D24" s="42" t="s">
+        <v>187</v>
+      </c>
+      <c r="E24" s="42"/>
+      <c r="F24" s="42" t="s">
+        <v>188</v>
+      </c>
+      <c r="G24" s="42"/>
+      <c r="H24" s="42"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="51" t="s">
-        <v>180</v>
-      </c>
-      <c r="C25" s="52" t="s">
-        <v>181</v>
-      </c>
-      <c r="D25" s="53" t="s">
-        <v>182</v>
-      </c>
-      <c r="E25" s="53"/>
-      <c r="F25" s="54" t="s">
-        <v>183</v>
-      </c>
-      <c r="G25" s="54"/>
-      <c r="H25" s="54"/>
+      <c r="B25" s="53" t="s">
+        <v>189</v>
+      </c>
+      <c r="C25" s="54" t="s">
+        <v>190</v>
+      </c>
+      <c r="D25" s="55" t="s">
+        <v>191</v>
+      </c>
+      <c r="E25" s="55"/>
+      <c r="F25" s="56" t="s">
+        <v>192</v>
+      </c>
+      <c r="G25" s="56"/>
+      <c r="H25" s="56"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="51" t="s">
-        <v>184</v>
-      </c>
-      <c r="C26" s="52" t="s">
-        <v>181</v>
-      </c>
-      <c r="D26" s="53" t="s">
-        <v>185</v>
-      </c>
-      <c r="E26" s="53"/>
-      <c r="F26" s="54" t="s">
-        <v>186</v>
-      </c>
-      <c r="G26" s="54"/>
-      <c r="H26" s="54"/>
+      <c r="B26" s="53" t="s">
+        <v>193</v>
+      </c>
+      <c r="C26" s="54" t="s">
+        <v>190</v>
+      </c>
+      <c r="D26" s="55" t="s">
+        <v>194</v>
+      </c>
+      <c r="E26" s="55"/>
+      <c r="F26" s="56" t="s">
+        <v>195</v>
+      </c>
+      <c r="G26" s="56"/>
+      <c r="H26" s="56"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="51" t="s">
-        <v>187</v>
-      </c>
-      <c r="C27" s="55" t="s">
-        <v>188</v>
-      </c>
-      <c r="D27" s="53" t="s">
-        <v>189</v>
-      </c>
-      <c r="E27" s="53"/>
-      <c r="F27" s="54" t="s">
+      <c r="B27" s="53" t="s">
+        <v>196</v>
+      </c>
+      <c r="C27" s="57" t="s">
+        <v>197</v>
+      </c>
+      <c r="D27" s="55" t="s">
+        <v>198</v>
+      </c>
+      <c r="E27" s="55"/>
+      <c r="F27" s="56" t="s">
+        <v>199</v>
+      </c>
+      <c r="G27" s="56"/>
+      <c r="H27" s="56"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="53" t="s">
+        <v>200</v>
+      </c>
+      <c r="C28" s="58" t="s">
+        <v>201</v>
+      </c>
+      <c r="D28" s="55" t="s">
+        <v>202</v>
+      </c>
+      <c r="E28" s="55"/>
+      <c r="F28" s="56" t="s">
+        <v>203</v>
+      </c>
+      <c r="G28" s="56"/>
+      <c r="H28" s="56"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="C29" s="54" t="s">
         <v>190</v>
       </c>
-      <c r="G27" s="54"/>
-      <c r="H27" s="54"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="51" t="s">
-        <v>191</v>
-      </c>
-      <c r="C28" s="56" t="s">
-        <v>192</v>
-      </c>
-      <c r="D28" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="E28" s="53"/>
-      <c r="F28" s="54" t="s">
-        <v>194</v>
-      </c>
-      <c r="G28" s="54"/>
-      <c r="H28" s="54"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="51" t="s">
-        <v>195</v>
-      </c>
-      <c r="C29" s="52" t="s">
-        <v>181</v>
-      </c>
-      <c r="D29" s="53" t="s">
-        <v>196</v>
-      </c>
-      <c r="E29" s="53"/>
-      <c r="F29" s="54" t="s">
-        <v>197</v>
-      </c>
-      <c r="G29" s="54"/>
-      <c r="H29" s="54"/>
+      <c r="D29" s="55" t="s">
+        <v>205</v>
+      </c>
+      <c r="E29" s="55"/>
+      <c r="F29" s="56" t="s">
+        <v>206</v>
+      </c>
+      <c r="G29" s="56"/>
+      <c r="H29" s="56"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="51" t="s">
-        <v>198</v>
-      </c>
-      <c r="C30" s="56" t="s">
-        <v>192</v>
-      </c>
-      <c r="D30" s="53" t="s">
-        <v>199</v>
-      </c>
-      <c r="E30" s="53"/>
-      <c r="F30" s="54" t="s">
-        <v>200</v>
-      </c>
-      <c r="G30" s="54"/>
-      <c r="H30" s="54"/>
+      <c r="B30" s="53" t="s">
+        <v>207</v>
+      </c>
+      <c r="C30" s="58" t="s">
+        <v>201</v>
+      </c>
+      <c r="D30" s="55" t="s">
+        <v>208</v>
+      </c>
+      <c r="E30" s="55"/>
+      <c r="F30" s="56" t="s">
+        <v>209</v>
+      </c>
+      <c r="G30" s="56"/>
+      <c r="H30" s="56"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="51" t="s">
-        <v>201</v>
-      </c>
-      <c r="C31" s="52" t="s">
-        <v>181</v>
-      </c>
-      <c r="D31" s="53" t="s">
-        <v>202</v>
-      </c>
-      <c r="E31" s="53"/>
-      <c r="F31" s="54" t="s">
-        <v>203</v>
-      </c>
-      <c r="G31" s="54"/>
-      <c r="H31" s="54"/>
+      <c r="B31" s="53" t="s">
+        <v>210</v>
+      </c>
+      <c r="C31" s="54" t="s">
+        <v>190</v>
+      </c>
+      <c r="D31" s="55" t="s">
+        <v>211</v>
+      </c>
+      <c r="E31" s="55"/>
+      <c r="F31" s="56" t="s">
+        <v>212</v>
+      </c>
+      <c r="G31" s="56"/>
+      <c r="H31" s="56"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="51" t="s">
+      <c r="B33" s="53" t="s">
         <v>39</v>
       </c>
       <c r="C33" s="28" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="D33" s="28"/>
       <c r="E33" s="28"/>
       <c r="F33" s="28"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="57" t="s">
-        <v>205</v>
-      </c>
-      <c r="C35" s="57"/>
-      <c r="D35" s="57"/>
-      <c r="E35" s="57"/>
-      <c r="F35" s="57"/>
-      <c r="G35" s="57"/>
-      <c r="H35" s="57"/>
+      <c r="B35" s="59" t="s">
+        <v>214</v>
+      </c>
+      <c r="C35" s="59"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="59"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -3432,7 +3463,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:G20"/>
+  <dimension ref="B1:G25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -3744,47 +3775,122 @@
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="C19" s="32">
-        <f>C16</f>
-        <v>-308167.18888889</v>
-      </c>
-      <c r="D19" s="32">
-        <f>C19+D16</f>
-        <v>-407960.05885556</v>
-      </c>
-      <c r="E19" s="32">
-        <f>D19+E16</f>
-        <v>-418870.87280833</v>
-      </c>
-      <c r="F19" s="32">
-        <f>E19+F16</f>
-        <v>-1051097.96923163</v>
-      </c>
-      <c r="G19" s="32">
-        <f>F19+G16</f>
-        <v>-3236549.64156936</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="28" t="s">
+      <c r="C19" s="27">
+        <f>'Cash Flow &amp; DSCR'!C9</f>
+        <v>164824.60522118</v>
+      </c>
+      <c r="D19" s="27">
+        <f>'Cash Flow &amp; DSCR'!D9</f>
+        <v>164824.60522118</v>
+      </c>
+      <c r="E19" s="27">
+        <f>'Cash Flow &amp; DSCR'!E9</f>
+        <v>164824.60522118</v>
+      </c>
+      <c r="F19" s="27">
+        <f>'Cash Flow &amp; DSCR'!F9</f>
+        <v>164824.60522118</v>
+      </c>
+      <c r="G19" s="27">
+        <f>'Cash Flow &amp; DSCR'!G9</f>
+        <v>164824.60522118</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="C20" s="33" t="s">
+      <c r="C21" s="30">
+        <f>C16-C19</f>
+        <v>-472991.79411007</v>
+      </c>
+      <c r="D21" s="30">
+        <f>D16-D19</f>
+        <v>-264617.47518785</v>
+      </c>
+      <c r="E21" s="30">
+        <f>E16-E19</f>
+        <v>-175735.41917396</v>
+      </c>
+      <c r="F21" s="30">
+        <f>F16-F19</f>
+        <v>-797051.70164447</v>
+      </c>
+      <c r="G21" s="30">
+        <f>G16-G19</f>
+        <v>-2350276.27755892</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="C22" s="31">
+        <f>IF(C10&gt;0,C21/C10,0)</f>
+        <v>-0.30594553</v>
+      </c>
+      <c r="D22" s="31">
+        <f>IF(D10&gt;0,D21/D10,0)</f>
+        <v>-0.10427042</v>
+      </c>
+      <c r="E22" s="31">
+        <f>IF(E10&gt;0,E21/E10,0)</f>
+        <v>-0.04606601</v>
+      </c>
+      <c r="F22" s="31">
+        <f>IF(F10&gt;0,F21/F10,0)</f>
+        <v>-0.16504186</v>
+      </c>
+      <c r="G22" s="31">
+        <f>IF(G10&gt;0,G21/G10,0)</f>
+        <v>-0.4481626</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="C24" s="32">
+        <f>C21</f>
+        <v>-472991.79411007</v>
+      </c>
+      <c r="D24" s="32">
+        <f>C24+D21</f>
+        <v>-737609.26929791</v>
+      </c>
+      <c r="E24" s="32">
+        <f>D24+E21</f>
+        <v>-913344.68847187</v>
+      </c>
+      <c r="F24" s="32">
+        <f>E24+F21</f>
+        <v>-1710396.39011634</v>
+      </c>
+      <c r="G24" s="32">
+        <f>F24+G21</f>
+        <v>-4060672.66767526</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="C25" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="33" t="s">
+      <c r="D25" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="33" t="s">
+      <c r="E25" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="F20" s="33" t="s">
+      <c r="F25" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="G20" s="33" t="s">
+      <c r="G25" s="33" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3806,7 +3912,7 @@
     <tabColor rgb="FFD97706"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:G14"/>
+  <dimension ref="B1:G16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -3816,7 +3922,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -3843,177 +3949,227 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="25" t="s">
-        <v>128</v>
-      </c>
-      <c r="C4" s="27">
+      <c r="B4" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" s="32" t="str">
+        <f>Assumptions!D57</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="32">
+        <f>C16</f>
+        <v>-472991.79411007</v>
+      </c>
+      <c r="E4" s="32">
+        <f>D16</f>
+        <v>-737609.26929791</v>
+      </c>
+      <c r="F4" s="32">
+        <f>E16</f>
+        <v>-913344.68847187</v>
+      </c>
+      <c r="G4" s="32">
+        <f>F16</f>
+        <v>-1710396.39011634</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="C5" s="27">
         <f>'5-Year P&amp;L'!C16</f>
         <v>-308167.18888889</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D5" s="27">
         <f>'5-Year P&amp;L'!D16</f>
         <v>-99792.86996667</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E5" s="27">
         <f>'5-Year P&amp;L'!E16</f>
         <v>-10910.81395278</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F5" s="27">
         <f>'5-Year P&amp;L'!F16</f>
         <v>-632227.09642329</v>
       </c>
-      <c r="G4" s="27">
+      <c r="G5" s="27">
         <f>'5-Year P&amp;L'!G16</f>
         <v>-2185451.67233774</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="25" t="s">
-        <v>129</v>
-      </c>
-      <c r="C6" s="27">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="C7" s="27">
         <f>Assumptions!D58</f>
         <v>115000</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D7" s="27">
         <f>Assumptions!D58</f>
         <v>115000</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E7" s="27">
         <f>Assumptions!D58</f>
         <v>115000</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F7" s="27">
         <f>Assumptions!D58</f>
         <v>115000</v>
       </c>
-      <c r="G6" s="27">
+      <c r="G7" s="27">
         <f>Assumptions!D58</f>
         <v>115000</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="25" t="s">
-        <v>130</v>
-      </c>
-      <c r="C7" s="27">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="C8" s="27">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>49824.60522118</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D8" s="27">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>49824.60522118</v>
       </c>
-      <c r="E7" s="27">
+      <c r="E8" s="27">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>49824.60522118</v>
       </c>
-      <c r="F7" s="27">
+      <c r="F8" s="27">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>49824.60522118</v>
       </c>
-      <c r="G7" s="27">
+      <c r="G8" s="27">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>49824.60522118</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="C8" s="29">
-        <f>C6+C7</f>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="C9" s="29">
+        <f>C7+C8</f>
         <v>164824.60522118</v>
       </c>
-      <c r="D8" s="29">
-        <f>D6+D7</f>
+      <c r="D9" s="29">
+        <f>D7+D8</f>
         <v>164824.60522118</v>
       </c>
-      <c r="E8" s="29">
-        <f>E6+E7</f>
+      <c r="E9" s="29">
+        <f>E7+E8</f>
         <v>164824.60522118</v>
       </c>
-      <c r="F8" s="29">
-        <f>F6+F7</f>
+      <c r="F9" s="29">
+        <f>F7+F8</f>
         <v>164824.60522118</v>
       </c>
-      <c r="G8" s="29">
-        <f>G6+G7</f>
+      <c r="G9" s="29">
+        <f>G7+G8</f>
         <v>164824.60522118</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="C10" s="34">
-        <f>IF(C8&gt;0,C4/C8,IF(C4&gt;0,99.9,0))</f>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="C11" s="34">
+        <f>IF(C9&gt;0,C5/C9,IF(C5&gt;0,99.9,0))</f>
         <v>-1.86966739</v>
       </c>
-      <c r="D10" s="34">
-        <f>IF(D8&gt;0,D4/D8,IF(D4&gt;0,99.9,0))</f>
+      <c r="D11" s="34">
+        <f>IF(D9&gt;0,D5/D9,IF(D5&gt;0,99.9,0))</f>
         <v>-0.60544886</v>
       </c>
-      <c r="E10" s="34">
-        <f>IF(E8&gt;0,E4/E8,IF(E4&gt;0,99.9,0))</f>
+      <c r="E11" s="34">
+        <f>IF(E9&gt;0,E5/E9,IF(E5&gt;0,99.9,0))</f>
         <v>-0.06619651</v>
       </c>
-      <c r="F10" s="34">
-        <f>IF(F8&gt;0,F4/F8,IF(F4&gt;0,99.9,0))</f>
+      <c r="F11" s="34">
+        <f>IF(F9&gt;0,F5/F9,IF(F5&gt;0,99.9,0))</f>
         <v>-3.83575678</v>
       </c>
-      <c r="G10" s="34">
-        <f>IF(G8&gt;0,G4/G8,IF(G4&gt;0,99.9,0))</f>
+      <c r="G11" s="34">
+        <f>IF(G9&gt;0,G5/G9,IF(G5&gt;0,99.9,0))</f>
         <v>-13.25925622</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="C12" s="27">
-        <f>C4-C8</f>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="C13" s="27">
+        <f>C5-C9</f>
         <v>-472991.79411007</v>
       </c>
-      <c r="D12" s="27">
-        <f>D4-D8</f>
+      <c r="D13" s="27">
+        <f>D5-D9</f>
         <v>-264617.47518785</v>
       </c>
-      <c r="E12" s="27">
-        <f>E4-E8</f>
+      <c r="E13" s="27">
+        <f>E5-E9</f>
         <v>-175735.41917396</v>
       </c>
-      <c r="F12" s="27">
-        <f>F4-F8</f>
+      <c r="F13" s="27">
+        <f>F5-F9</f>
         <v>-797051.70164447</v>
       </c>
-      <c r="G12" s="27">
-        <f>G4-G8</f>
+      <c r="G13" s="27">
+        <f>G5-G9</f>
         <v>-2350276.27755892</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="C14" s="35">
-        <f>Assumptions!D57+C12</f>
+        <v>138</v>
+      </c>
+      <c r="C14" s="32">
+        <f>C5-C9</f>
         <v>-472991.79411007</v>
       </c>
-      <c r="D14" s="35">
-        <f>C14+D12</f>
+      <c r="D14" s="32">
+        <f>D5-D9</f>
+        <v>-264617.47518785</v>
+      </c>
+      <c r="E14" s="32">
+        <f>E5-E9</f>
+        <v>-175735.41917396</v>
+      </c>
+      <c r="F14" s="32">
+        <f>F5-F9</f>
+        <v>-797051.70164447</v>
+      </c>
+      <c r="G14" s="32">
+        <f>G5-G9</f>
+        <v>-2350276.27755892</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="C16" s="30">
+        <f>C4+C14</f>
+        <v>-472991.79411007</v>
+      </c>
+      <c r="D16" s="30">
+        <f>D4+D14</f>
         <v>-737609.26929791</v>
       </c>
-      <c r="E14" s="35">
-        <f>D14+E12</f>
+      <c r="E16" s="30">
+        <f>E4+E14</f>
         <v>-913344.68847187</v>
       </c>
-      <c r="F14" s="35">
-        <f>E14+F12</f>
+      <c r="F16" s="30">
+        <f>F4+F14</f>
         <v>-1710396.39011634</v>
       </c>
-      <c r="G14" s="35">
-        <f>F14+G12</f>
+      <c r="G16" s="30">
+        <f>G4+G14</f>
         <v>-4060672.66767526</v>
       </c>
     </row>
@@ -4045,7 +4201,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -4073,7 +4229,7 @@
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="25" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C4" s="26">
         <f>Drivers!C12</f>
@@ -4098,7 +4254,7 @@
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="25" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C5" s="26">
         <f>Assumptions!D35</f>
@@ -4123,25 +4279,25 @@
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="C6" s="36">
+        <v>143</v>
+      </c>
+      <c r="C6" s="35">
         <f>C4+C5</f>
         <v>17</v>
       </c>
-      <c r="D6" s="36">
+      <c r="D6" s="35">
         <f>D4+D5</f>
         <v>24</v>
       </c>
-      <c r="E6" s="36">
+      <c r="E6" s="35">
         <f>E4+E5</f>
         <v>32</v>
       </c>
-      <c r="F6" s="36">
+      <c r="F6" s="35">
         <f>F4+F5</f>
         <v>39</v>
       </c>
-      <c r="G6" s="36">
+      <c r="G6" s="35">
         <f>G4+G5</f>
         <v>41</v>
       </c>
@@ -4174,13 +4330,13 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C1" s="13"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="25" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C3" s="27">
         <f>Assumptions!D59</f>
@@ -4189,7 +4345,7 @@
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="25" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C4" s="31">
         <f>Assumptions!D60</f>
@@ -4207,7 +4363,7 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="25" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C6" s="32">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
@@ -4216,10 +4372,10 @@
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="25" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C8" s="34">
-        <f>'Cash Flow &amp; DSCR'!C10</f>
+        <f>'Cash Flow &amp; DSCR'!C11</f>
         <v>-1.86966739</v>
       </c>
     </row>
@@ -4241,7 +4397,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:C12"/>
+  <dimension ref="B1:C20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -4251,7 +4407,7 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C1" s="13"/>
     </row>
@@ -4284,7 +4440,7 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="25" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C6" s="25">
         <f>Assumptions!D8</f>
@@ -4302,7 +4458,7 @@
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="25" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C9" s="27">
         <f>Drivers!G10</f>
@@ -4311,23 +4467,83 @@
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="25" t="s">
-        <v>147</v>
-      </c>
-      <c r="C10" s="35">
+        <v>152</v>
+      </c>
+      <c r="C10" s="36">
         <f>'5-Year P&amp;L'!G16</f>
         <v>-2185451.67233774</v>
       </c>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="C12" s="12"/>
+    <row r="12" ht="24" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="C12" s="23"/>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="C13" s="38">
+        <f>IF(Drivers!G10&gt;0,'5-Year P&amp;L'!G21/Drivers!G10,0)</f>
+        <v>-0.4481626</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="C14" s="31">
+        <f>IF(Drivers!G10&gt;0,Drivers!G16/Drivers!G10,0)</f>
+        <v>0.55578733</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="C15" s="27">
+        <f>IF(Assumptions!D16&gt;0,Drivers!G10/Assumptions!D16,0)</f>
+        <v>13111</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="C16" s="27">
+        <f>IF(Assumptions!D16&gt;0,('5-Year P&amp;L'!G12+'5-Year P&amp;L'!G13)/Assumptions!D16,0)</f>
+        <v>18574</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="25" t="s">
+        <v>158</v>
+      </c>
+      <c r="C17" s="34">
+        <f>'Cash Flow &amp; DSCR'!C11</f>
+        <v>-1.86966739</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="C18" s="34">
+        <f>'Cash Flow &amp; DSCR'!G11</f>
+        <v>-13.25925622</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="C20" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B20:C20"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
@@ -28,7 +28,7 @@
     <t>Civic Scholars Charter</t>
   </si>
   <si>
-    <t>Generated March 26, 2026 · nonprofit_501c3</t>
+    <t>Generated March 27, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -142,7 +142,7 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>Generated March 26, 2026</t>
+    <t>Generated March 27, 2026</t>
   </si>
   <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="218">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -502,6 +502,9 @@
     <t>DSCR (Year 5)</t>
   </si>
   <si>
+    <t>Days Cash on Hand (Year 1)</t>
+  </si>
+  <si>
     <t>Generated by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
@@ -575,6 +578,12 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>Days Cash on Hand</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -908,7 +917,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -980,6 +989,9 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1742,7 +1754,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1754,7 +1766,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1775,37 +1787,37 @@
       <c r="H3" s="12"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="39" t="s">
-        <v>162</v>
-      </c>
-      <c r="D4" s="40" t="s">
+      <c r="B4" s="40" t="s">
         <v>163</v>
       </c>
-      <c r="F4" s="41" t="s">
+      <c r="D4" s="41" t="s">
         <v>164</v>
       </c>
+      <c r="F4" s="42" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="42" t="s">
-        <v>165</v>
-      </c>
-      <c r="C6" s="43" t="s">
+      <c r="B6" s="43" t="s">
+        <v>166</v>
+      </c>
+      <c r="C6" s="44" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="44" t="s">
         <v>97</v>
       </c>
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="44" t="s">
         <v>98</v>
       </c>
-      <c r="F6" s="43" t="s">
+      <c r="F6" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="G6" s="43" t="s">
+      <c r="G6" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="H6" s="43" t="s">
-        <v>166</v>
+      <c r="H6" s="44" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -1830,7 +1842,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="25" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C8" s="27">
         <v>1546000</v>
@@ -1850,7 +1862,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="25" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C9" s="27">
         <v>1200167.1888888888</v>
@@ -1870,7 +1882,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C10" s="27">
         <v>654000</v>
@@ -1890,7 +1902,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="25" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C11" s="27">
         <v>164824.60522117943</v>
@@ -1952,375 +1964,396 @@
       <c r="B14" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="C14" s="44">
+      <c r="C14" s="45">
         <v>-0.3059455330595525</v>
       </c>
-      <c r="D14" s="44">
+      <c r="D14" s="45">
         <v>-0.10427042130500674</v>
       </c>
-      <c r="E14" s="44">
+      <c r="E14" s="45">
         <v>-0.046066008479458874</v>
       </c>
-      <c r="F14" s="44">
+      <c r="F14" s="45">
         <v>-0.16504185604249857</v>
       </c>
-      <c r="G14" s="44">
+      <c r="G14" s="45">
         <v>-0.44816260261601254</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="C15" s="45">
+        <v>172</v>
+      </c>
+      <c r="C15" s="46">
         <v>12883.333333333334</v>
       </c>
-      <c r="D15" s="45">
+      <c r="D15" s="46">
         <v>12689</v>
       </c>
-      <c r="E15" s="45">
+      <c r="E15" s="46">
         <v>12716.203333333333</v>
       </c>
-      <c r="F15" s="45">
+      <c r="F15" s="46">
         <v>12878.376766666668</v>
       </c>
-      <c r="G15" s="45">
+      <c r="G15" s="46">
         <v>13110.622483</v>
       </c>
-      <c r="H15" s="46" t="s">
-        <v>172</v>
+      <c r="H15" s="47" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="C16" s="44">
+        <v>174</v>
+      </c>
+      <c r="C16" s="45">
         <v>0.7763047793589191</v>
       </c>
-      <c r="D16" s="44">
+      <c r="D16" s="45">
         <v>0.6515878070113221</v>
       </c>
-      <c r="E16" s="47">
+      <c r="E16" s="48">
         <v>0.5752710583855843</v>
       </c>
-      <c r="F16" s="47">
+      <c r="F16" s="48">
         <v>0.5597527709991174</v>
       </c>
-      <c r="G16" s="47">
+      <c r="G16" s="48">
         <v>0.5557873295275215</v>
       </c>
-      <c r="H16" s="46" t="s">
-        <v>174</v>
+      <c r="H16" s="47" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="28" t="s">
-        <v>175</v>
-      </c>
-      <c r="C17" s="47">
+        <v>176</v>
+      </c>
+      <c r="C17" s="48">
         <v>0.18240620957309184</v>
       </c>
-      <c r="D17" s="48">
+      <c r="D17" s="49">
         <v>0.11445346362991568</v>
       </c>
-      <c r="E17" s="48">
+      <c r="E17" s="49">
         <v>0.07842325054569485</v>
       </c>
-      <c r="F17" s="48">
+      <c r="F17" s="49">
         <v>0.06380700913541373</v>
       </c>
-      <c r="G17" s="48">
+      <c r="G17" s="49">
         <v>0.06052219961934512</v>
       </c>
-      <c r="H17" s="46" t="s">
-        <v>176</v>
+      <c r="H17" s="47" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="C18" s="44">
+      <c r="C18" s="45">
         <v>-0.19933194624119585</v>
       </c>
-      <c r="D18" s="44">
+      <c r="D18" s="45">
         <v>-0.039322590419523434</v>
       </c>
-      <c r="E18" s="44">
+      <c r="E18" s="45">
         <v>-0.0028600816524580494</v>
       </c>
-      <c r="F18" s="44">
+      <c r="F18" s="45">
         <v>-0.13091237772754036</v>
       </c>
-      <c r="G18" s="44">
+      <c r="G18" s="45">
         <v>-0.4167330108031714</v>
       </c>
-      <c r="H18" s="46" t="s">
-        <v>177</v>
+      <c r="H18" s="47" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="28" t="s">
-        <v>178</v>
-      </c>
-      <c r="C19" s="49">
+        <v>179</v>
+      </c>
+      <c r="C19" s="50">
         <v>3</v>
       </c>
-      <c r="D19" s="49">
+      <c r="D19" s="50">
         <v>3</v>
       </c>
-      <c r="E19" s="49">
+      <c r="E19" s="50">
         <v>3</v>
       </c>
-      <c r="F19" s="49">
+      <c r="F19" s="50">
         <v>3</v>
       </c>
-      <c r="G19" s="49">
+      <c r="G19" s="50">
         <v>3</v>
       </c>
-      <c r="H19" s="46" t="s">
-        <v>179</v>
+      <c r="H19" s="47" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="28" t="s">
-        <v>180</v>
-      </c>
-      <c r="C20" s="50">
+        <v>181</v>
+      </c>
+      <c r="C20" s="51">
         <v>-1.8696673865856184</v>
       </c>
-      <c r="D20" s="50">
+      <c r="D20" s="51">
         <v>-0.6054488638559378</v>
       </c>
-      <c r="E20" s="50">
+      <c r="E20" s="51">
         <v>-0.06619651197184098</v>
       </c>
-      <c r="F20" s="50">
+      <c r="F20" s="51">
         <v>-3.8357567765741165</v>
       </c>
-      <c r="G20" s="50">
+      <c r="G20" s="51">
         <v>-13.259256222122064</v>
       </c>
-      <c r="H20" s="46" t="s">
-        <v>181</v>
+      <c r="H20" s="47" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="C21" s="51" t="str">
+        <v>183</v>
+      </c>
+      <c r="C21" s="52" t="str">
         <f>IF('5-Year P&amp;L'!C24&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D21" s="51" t="str">
+      <c r="D21" s="52" t="str">
         <f>IF(AND('5-Year P&amp;L'!D24&gt;=0,'5-Year P&amp;L'!C24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="51" t="str">
+      <c r="E21" s="52" t="str">
         <f>IF(AND('5-Year P&amp;L'!E24&gt;=0,'5-Year P&amp;L'!D24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="51" t="str">
+      <c r="F21" s="52" t="str">
         <f>IF(AND('5-Year P&amp;L'!F24&gt;=0,'5-Year P&amp;L'!E24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="51" t="str">
+      <c r="G21" s="52" t="str">
         <f>IF(AND('5-Year P&amp;L'!G24&gt;=0,'5-Year P&amp;L'!F24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="46" t="s">
+      <c r="H21" s="47" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="C22" s="52">
+        <v>184</v>
+      </c>
+      <c r="C22" s="53">
         <v>-3</v>
       </c>
-      <c r="D22" s="52">
+      <c r="D22" s="53">
         <v>-3</v>
       </c>
-      <c r="E22" s="52">
+      <c r="E22" s="53">
         <v>-3</v>
       </c>
-      <c r="F22" s="52">
+      <c r="F22" s="53">
         <v>-4</v>
       </c>
-      <c r="G22" s="52">
+      <c r="G22" s="53">
         <v>-6</v>
       </c>
-      <c r="H22" s="46" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="42" t="s">
+      <c r="H22" s="47" t="s">
         <v>185</v>
       </c>
-      <c r="C24" s="42" t="s">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="28" t="s">
         <v>186</v>
       </c>
-      <c r="D24" s="42" t="s">
+      <c r="C23" s="53">
+        <v>0</v>
+      </c>
+      <c r="D23" s="53">
+        <v>0</v>
+      </c>
+      <c r="E23" s="53">
+        <v>0</v>
+      </c>
+      <c r="F23" s="53">
+        <v>0</v>
+      </c>
+      <c r="G23" s="53">
+        <v>0</v>
+      </c>
+      <c r="H23" s="47" t="s">
         <v>187</v>
       </c>
-      <c r="E24" s="42"/>
-      <c r="F24" s="42" t="s">
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="43" t="s">
         <v>188</v>
       </c>
-      <c r="G24" s="42"/>
-      <c r="H24" s="42"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="53" t="s">
+      <c r="C25" s="43" t="s">
         <v>189</v>
       </c>
-      <c r="C25" s="54" t="s">
+      <c r="D25" s="43" t="s">
         <v>190</v>
       </c>
-      <c r="D25" s="55" t="s">
+      <c r="E25" s="43"/>
+      <c r="F25" s="43" t="s">
         <v>191</v>
       </c>
-      <c r="E25" s="55"/>
-      <c r="F25" s="56" t="s">
+      <c r="G25" s="43"/>
+      <c r="H25" s="43"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="54" t="s">
         <v>192</v>
       </c>
-      <c r="G25" s="56"/>
-      <c r="H25" s="56"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="53" t="s">
+      <c r="C26" s="55" t="s">
         <v>193</v>
       </c>
-      <c r="C26" s="54" t="s">
-        <v>190</v>
-      </c>
-      <c r="D26" s="55" t="s">
+      <c r="D26" s="56" t="s">
         <v>194</v>
       </c>
-      <c r="E26" s="55"/>
-      <c r="F26" s="56" t="s">
+      <c r="E26" s="56"/>
+      <c r="F26" s="57" t="s">
         <v>195</v>
       </c>
-      <c r="G26" s="56"/>
-      <c r="H26" s="56"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="57"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="53" t="s">
+      <c r="B27" s="54" t="s">
         <v>196</v>
       </c>
-      <c r="C27" s="57" t="s">
+      <c r="C27" s="55" t="s">
+        <v>193</v>
+      </c>
+      <c r="D27" s="56" t="s">
         <v>197</v>
       </c>
-      <c r="D27" s="55" t="s">
+      <c r="E27" s="56"/>
+      <c r="F27" s="57" t="s">
         <v>198</v>
       </c>
-      <c r="E27" s="55"/>
-      <c r="F27" s="56" t="s">
+      <c r="G27" s="57"/>
+      <c r="H27" s="57"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="G27" s="56"/>
-      <c r="H27" s="56"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="53" t="s">
+      <c r="C28" s="58" t="s">
         <v>200</v>
       </c>
-      <c r="C28" s="58" t="s">
+      <c r="D28" s="56" t="s">
         <v>201</v>
       </c>
-      <c r="D28" s="55" t="s">
+      <c r="E28" s="56"/>
+      <c r="F28" s="57" t="s">
         <v>202</v>
       </c>
-      <c r="E28" s="55"/>
-      <c r="F28" s="56" t="s">
+      <c r="G28" s="57"/>
+      <c r="H28" s="57"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="54" t="s">
         <v>203</v>
       </c>
-      <c r="G28" s="56"/>
-      <c r="H28" s="56"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="53" t="s">
+      <c r="C29" s="59" t="s">
         <v>204</v>
       </c>
-      <c r="C29" s="54" t="s">
-        <v>190</v>
-      </c>
-      <c r="D29" s="55" t="s">
+      <c r="D29" s="56" t="s">
         <v>205</v>
       </c>
-      <c r="E29" s="55"/>
-      <c r="F29" s="56" t="s">
+      <c r="E29" s="56"/>
+      <c r="F29" s="57" t="s">
         <v>206</v>
       </c>
-      <c r="G29" s="56"/>
-      <c r="H29" s="56"/>
+      <c r="G29" s="57"/>
+      <c r="H29" s="57"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="53" t="s">
+      <c r="B30" s="54" t="s">
         <v>207</v>
       </c>
-      <c r="C30" s="58" t="s">
-        <v>201</v>
-      </c>
-      <c r="D30" s="55" t="s">
+      <c r="C30" s="55" t="s">
+        <v>193</v>
+      </c>
+      <c r="D30" s="56" t="s">
         <v>208</v>
       </c>
-      <c r="E30" s="55"/>
-      <c r="F30" s="56" t="s">
+      <c r="E30" s="56"/>
+      <c r="F30" s="57" t="s">
         <v>209</v>
       </c>
-      <c r="G30" s="56"/>
-      <c r="H30" s="56"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="53" t="s">
+      <c r="B31" s="54" t="s">
         <v>210</v>
       </c>
-      <c r="C31" s="54" t="s">
-        <v>190</v>
-      </c>
-      <c r="D31" s="55" t="s">
+      <c r="C31" s="59" t="s">
+        <v>204</v>
+      </c>
+      <c r="D31" s="56" t="s">
         <v>211</v>
       </c>
-      <c r="E31" s="55"/>
-      <c r="F31" s="56" t="s">
+      <c r="E31" s="56"/>
+      <c r="F31" s="57" t="s">
         <v>212</v>
       </c>
-      <c r="G31" s="56"/>
-      <c r="H31" s="56"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="53" t="s">
+      <c r="G31" s="57"/>
+      <c r="H31" s="57"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="54" t="s">
+        <v>213</v>
+      </c>
+      <c r="C32" s="55" t="s">
+        <v>193</v>
+      </c>
+      <c r="D32" s="56" t="s">
+        <v>214</v>
+      </c>
+      <c r="E32" s="56"/>
+      <c r="F32" s="57" t="s">
+        <v>215</v>
+      </c>
+      <c r="G32" s="57"/>
+      <c r="H32" s="57"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B34" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="28" t="s">
-        <v>213</v>
-      </c>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="59" t="s">
-        <v>214</v>
-      </c>
-      <c r="C35" s="59"/>
-      <c r="D35" s="59"/>
-      <c r="E35" s="59"/>
-      <c r="F35" s="59"/>
-      <c r="G35" s="59"/>
-      <c r="H35" s="59"/>
+      <c r="C34" s="28" t="s">
+        <v>216</v>
+      </c>
+      <c r="D34" s="28"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="60" t="s">
+        <v>217</v>
+      </c>
+      <c r="C36" s="60"/>
+      <c r="D36" s="60"/>
+      <c r="E36" s="60"/>
+      <c r="F36" s="60"/>
+      <c r="G36" s="60"/>
+      <c r="H36" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="F25:H25"/>
     <mergeCell ref="D26:E26"/>
@@ -2335,8 +2368,10 @@
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="B36:H36"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -4397,7 +4432,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:C20"/>
+  <dimension ref="B1:C21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -4534,16 +4569,24 @@
         <v>-13.25925622</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="12" t="s">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="25" t="s">
         <v>160</v>
       </c>
-      <c r="C20" s="12"/>
+      <c r="C19" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="C21" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="223">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -542,6 +542,21 @@
   </si>
   <si>
     <t>≥ $10,000</t>
+  </si>
+  <si>
+    <t>Cost per Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
   </si>
   <si>
     <t>Payroll %</t>
@@ -917,7 +932,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1008,6 +1023,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="166" fontId="16" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1754,7 +1772,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H36"/>
+  <dimension ref="B2:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -2003,365 +2021,440 @@
         <v>173</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="C16" s="45">
-        <v>0.7763047793589191</v>
-      </c>
-      <c r="D16" s="45">
-        <v>0.6515878070113221</v>
-      </c>
-      <c r="E16" s="48">
-        <v>0.5752710583855843</v>
-      </c>
-      <c r="F16" s="48">
-        <v>0.5597527709991174</v>
-      </c>
-      <c r="G16" s="48">
-        <v>0.5557873295275215</v>
-      </c>
-      <c r="H16" s="47" t="s">
+      <c r="C16" s="32">
+        <v>16824.9316175839</v>
+      </c>
+      <c r="D16" s="32">
+        <v>14012.08737593923</v>
+      </c>
+      <c r="E16" s="32">
+        <v>13301.98806391319</v>
+      </c>
+      <c r="F16" s="32">
+        <v>15003.847971051926</v>
+      </c>
+      <c r="G16" s="32">
+        <v>18986.313176897285</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="25" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="28" t="s">
+      <c r="C17" s="27">
+        <v>700</v>
+      </c>
+      <c r="D17" s="27">
+        <v>1201.6666666666667</v>
+      </c>
+      <c r="E17" s="27">
+        <v>2062.8611111111118</v>
+      </c>
+      <c r="F17" s="27">
+        <v>3541.244907407408</v>
+      </c>
+      <c r="G17" s="27">
+        <v>6079.137091049384</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="25" t="s">
         <v>176</v>
       </c>
-      <c r="C17" s="48">
-        <v>0.18240620957309184</v>
-      </c>
-      <c r="D17" s="49">
-        <v>0.11445346362991568</v>
-      </c>
-      <c r="E17" s="49">
-        <v>0.07842325054569485</v>
-      </c>
-      <c r="F17" s="49">
-        <v>0.06380700913541373</v>
-      </c>
-      <c r="G17" s="49">
-        <v>0.06052219961934512</v>
-      </c>
-      <c r="H17" s="47" t="s">
+      <c r="C18" s="48">
+        <v>2350</v>
+      </c>
+      <c r="D18" s="46">
+        <v>1452.3</v>
+      </c>
+      <c r="E18" s="46">
+        <v>997.246</v>
+      </c>
+      <c r="F18" s="46">
+        <v>821.7307040000001</v>
+      </c>
+      <c r="G18" s="46">
+        <v>793.4837110500001</v>
+      </c>
+      <c r="H18" s="47" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="C18" s="45">
-        <v>-0.19933194624119585</v>
-      </c>
-      <c r="D18" s="45">
-        <v>-0.039322590419523434</v>
-      </c>
-      <c r="E18" s="45">
-        <v>-0.0028600816524580494</v>
-      </c>
-      <c r="F18" s="45">
-        <v>-0.13091237772754036</v>
-      </c>
-      <c r="G18" s="45">
-        <v>-0.4167330108031714</v>
-      </c>
-      <c r="H18" s="47" t="s">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="28" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="28" t="s">
-        <v>179</v>
-      </c>
-      <c r="C19" s="50">
-        <v>3</v>
-      </c>
-      <c r="D19" s="50">
-        <v>3</v>
-      </c>
-      <c r="E19" s="50">
-        <v>3</v>
-      </c>
-      <c r="F19" s="50">
-        <v>3</v>
-      </c>
-      <c r="G19" s="50">
-        <v>3</v>
-      </c>
-      <c r="H19" s="47" t="s">
-        <v>180</v>
+      <c r="C19" s="36">
+        <v>-3941.5982842505687</v>
+      </c>
+      <c r="D19" s="36">
+        <v>-1323.0873759392305</v>
+      </c>
+      <c r="E19" s="36">
+        <v>-585.7847305798565</v>
+      </c>
+      <c r="F19" s="36">
+        <v>-2125.4712043852587</v>
+      </c>
+      <c r="G19" s="36">
+        <v>-5875.690693897288</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="28" t="s">
-        <v>181</v>
-      </c>
-      <c r="C20" s="51">
-        <v>-1.8696673865856184</v>
-      </c>
-      <c r="D20" s="51">
-        <v>-0.6054488638559378</v>
-      </c>
-      <c r="E20" s="51">
-        <v>-0.06619651197184098</v>
-      </c>
-      <c r="F20" s="51">
-        <v>-3.8357567765741165</v>
-      </c>
-      <c r="G20" s="51">
-        <v>-13.259256222122064</v>
+        <v>179</v>
+      </c>
+      <c r="C20" s="45">
+        <v>0.7763047793589191</v>
+      </c>
+      <c r="D20" s="45">
+        <v>0.6515878070113221</v>
+      </c>
+      <c r="E20" s="49">
+        <v>0.5752710583855843</v>
+      </c>
+      <c r="F20" s="49">
+        <v>0.5597527709991174</v>
+      </c>
+      <c r="G20" s="49">
+        <v>0.5557873295275215</v>
       </c>
       <c r="H20" s="47" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="C21" s="49">
+        <v>0.18240620957309184</v>
+      </c>
+      <c r="D21" s="50">
+        <v>0.11445346362991568</v>
+      </c>
+      <c r="E21" s="50">
+        <v>0.07842325054569485</v>
+      </c>
+      <c r="F21" s="50">
+        <v>0.06380700913541373</v>
+      </c>
+      <c r="G21" s="50">
+        <v>0.06052219961934512</v>
+      </c>
+      <c r="H21" s="47" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="C22" s="45">
+        <v>-0.19933194624119585</v>
+      </c>
+      <c r="D22" s="45">
+        <v>-0.039322590419523434</v>
+      </c>
+      <c r="E22" s="45">
+        <v>-0.0028600816524580494</v>
+      </c>
+      <c r="F22" s="45">
+        <v>-0.13091237772754036</v>
+      </c>
+      <c r="G22" s="45">
+        <v>-0.4167330108031714</v>
+      </c>
+      <c r="H22" s="47" t="s">
         <v>183</v>
       </c>
-      <c r="C21" s="52" t="str">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="C23" s="51">
+        <v>3</v>
+      </c>
+      <c r="D23" s="51">
+        <v>3</v>
+      </c>
+      <c r="E23" s="51">
+        <v>3</v>
+      </c>
+      <c r="F23" s="51">
+        <v>3</v>
+      </c>
+      <c r="G23" s="51">
+        <v>3</v>
+      </c>
+      <c r="H23" s="47" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="C24" s="52">
+        <v>-1.8696673865856184</v>
+      </c>
+      <c r="D24" s="52">
+        <v>-0.6054488638559378</v>
+      </c>
+      <c r="E24" s="52">
+        <v>-0.06619651197184098</v>
+      </c>
+      <c r="F24" s="52">
+        <v>-3.8357567765741165</v>
+      </c>
+      <c r="G24" s="52">
+        <v>-13.259256222122064</v>
+      </c>
+      <c r="H24" s="47" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="28" t="s">
+        <v>188</v>
+      </c>
+      <c r="C25" s="53" t="str">
         <f>IF('5-Year P&amp;L'!C24&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D21" s="52" t="str">
+      <c r="D25" s="53" t="str">
         <f>IF(AND('5-Year P&amp;L'!D24&gt;=0,'5-Year P&amp;L'!C24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="52" t="str">
+      <c r="E25" s="53" t="str">
         <f>IF(AND('5-Year P&amp;L'!E24&gt;=0,'5-Year P&amp;L'!D24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="52" t="str">
+      <c r="F25" s="53" t="str">
         <f>IF(AND('5-Year P&amp;L'!F24&gt;=0,'5-Year P&amp;L'!E24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="52" t="str">
+      <c r="G25" s="53" t="str">
         <f>IF(AND('5-Year P&amp;L'!G24&gt;=0,'5-Year P&amp;L'!F24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="47" t="s">
+      <c r="H25" s="47" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="C22" s="53">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="C26" s="54">
         <v>-3</v>
       </c>
-      <c r="D22" s="53">
+      <c r="D26" s="54">
         <v>-3</v>
       </c>
-      <c r="E22" s="53">
+      <c r="E26" s="54">
         <v>-3</v>
       </c>
-      <c r="F22" s="53">
+      <c r="F26" s="54">
         <v>-4</v>
       </c>
-      <c r="G22" s="53">
+      <c r="G26" s="54">
         <v>-6</v>
       </c>
-      <c r="H22" s="47" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="28" t="s">
-        <v>186</v>
-      </c>
-      <c r="C23" s="53">
+      <c r="H26" s="47" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="C27" s="54">
         <v>0</v>
       </c>
-      <c r="D23" s="53">
+      <c r="D27" s="54">
         <v>0</v>
       </c>
-      <c r="E23" s="53">
+      <c r="E27" s="54">
         <v>0</v>
       </c>
-      <c r="F23" s="53">
+      <c r="F27" s="54">
         <v>0</v>
       </c>
-      <c r="G23" s="53">
+      <c r="G27" s="54">
         <v>0</v>
       </c>
-      <c r="H23" s="47" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="43" t="s">
-        <v>188</v>
-      </c>
-      <c r="C25" s="43" t="s">
-        <v>189</v>
-      </c>
-      <c r="D25" s="43" t="s">
-        <v>190</v>
-      </c>
-      <c r="E25" s="43"/>
-      <c r="F25" s="43" t="s">
-        <v>191</v>
-      </c>
-      <c r="G25" s="43"/>
-      <c r="H25" s="43"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="54" t="s">
+      <c r="H27" s="47" t="s">
         <v>192</v>
       </c>
-      <c r="C26" s="55" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="43" t="s">
         <v>193</v>
       </c>
-      <c r="D26" s="56" t="s">
+      <c r="C29" s="43" t="s">
         <v>194</v>
       </c>
-      <c r="E26" s="56"/>
-      <c r="F26" s="57" t="s">
+      <c r="D29" s="43" t="s">
         <v>195</v>
       </c>
-      <c r="G26" s="57"/>
-      <c r="H26" s="57"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="54" t="s">
+      <c r="E29" s="43"/>
+      <c r="F29" s="43" t="s">
         <v>196</v>
       </c>
-      <c r="C27" s="55" t="s">
-        <v>193</v>
-      </c>
-      <c r="D27" s="56" t="s">
+      <c r="G29" s="43"/>
+      <c r="H29" s="43"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="55" t="s">
         <v>197</v>
       </c>
-      <c r="E27" s="56"/>
-      <c r="F27" s="57" t="s">
+      <c r="C30" s="56" t="s">
         <v>198</v>
       </c>
-      <c r="G27" s="57"/>
-      <c r="H27" s="57"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="54" t="s">
+      <c r="D30" s="57" t="s">
         <v>199</v>
       </c>
-      <c r="C28" s="58" t="s">
+      <c r="E30" s="57"/>
+      <c r="F30" s="58" t="s">
         <v>200</v>
       </c>
-      <c r="D28" s="56" t="s">
+      <c r="G30" s="58"/>
+      <c r="H30" s="58"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="55" t="s">
         <v>201</v>
       </c>
-      <c r="E28" s="56"/>
-      <c r="F28" s="57" t="s">
+      <c r="C31" s="56" t="s">
+        <v>198</v>
+      </c>
+      <c r="D31" s="57" t="s">
         <v>202</v>
       </c>
-      <c r="G28" s="57"/>
-      <c r="H28" s="57"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="54" t="s">
+      <c r="E31" s="57"/>
+      <c r="F31" s="58" t="s">
         <v>203</v>
       </c>
-      <c r="C29" s="59" t="s">
+      <c r="G31" s="58"/>
+      <c r="H31" s="58"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="55" t="s">
         <v>204</v>
       </c>
-      <c r="D29" s="56" t="s">
+      <c r="C32" s="59" t="s">
         <v>205</v>
       </c>
-      <c r="E29" s="56"/>
-      <c r="F29" s="57" t="s">
+      <c r="D32" s="57" t="s">
         <v>206</v>
       </c>
-      <c r="G29" s="57"/>
-      <c r="H29" s="57"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="54" t="s">
+      <c r="E32" s="57"/>
+      <c r="F32" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="C30" s="55" t="s">
-        <v>193</v>
-      </c>
-      <c r="D30" s="56" t="s">
+      <c r="G32" s="58"/>
+      <c r="H32" s="58"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="55" t="s">
         <v>208</v>
       </c>
-      <c r="E30" s="56"/>
-      <c r="F30" s="57" t="s">
+      <c r="C33" s="60" t="s">
         <v>209</v>
       </c>
-      <c r="G30" s="57"/>
-      <c r="H30" s="57"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="54" t="s">
+      <c r="D33" s="57" t="s">
         <v>210</v>
       </c>
-      <c r="C31" s="59" t="s">
-        <v>204</v>
-      </c>
-      <c r="D31" s="56" t="s">
+      <c r="E33" s="57"/>
+      <c r="F33" s="58" t="s">
         <v>211</v>
       </c>
-      <c r="E31" s="56"/>
-      <c r="F31" s="57" t="s">
+      <c r="G33" s="58"/>
+      <c r="H33" s="58"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="55" t="s">
         <v>212</v>
       </c>
-      <c r="G31" s="57"/>
-      <c r="H31" s="57"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="54" t="s">
+      <c r="C34" s="56" t="s">
+        <v>198</v>
+      </c>
+      <c r="D34" s="57" t="s">
         <v>213</v>
       </c>
-      <c r="C32" s="55" t="s">
-        <v>193</v>
-      </c>
-      <c r="D32" s="56" t="s">
+      <c r="E34" s="57"/>
+      <c r="F34" s="58" t="s">
         <v>214</v>
       </c>
-      <c r="E32" s="56"/>
-      <c r="F32" s="57" t="s">
+      <c r="G34" s="58"/>
+      <c r="H34" s="58"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="55" t="s">
         <v>215</v>
       </c>
-      <c r="G32" s="57"/>
-      <c r="H32" s="57"/>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B34" s="54" t="s">
+      <c r="C35" s="60" t="s">
+        <v>209</v>
+      </c>
+      <c r="D35" s="57" t="s">
+        <v>216</v>
+      </c>
+      <c r="E35" s="57"/>
+      <c r="F35" s="58" t="s">
+        <v>217</v>
+      </c>
+      <c r="G35" s="58"/>
+      <c r="H35" s="58"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="55" t="s">
+        <v>218</v>
+      </c>
+      <c r="C36" s="56" t="s">
+        <v>198</v>
+      </c>
+      <c r="D36" s="57" t="s">
+        <v>219</v>
+      </c>
+      <c r="E36" s="57"/>
+      <c r="F36" s="58" t="s">
+        <v>220</v>
+      </c>
+      <c r="G36" s="58"/>
+      <c r="H36" s="58"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="28" t="s">
-        <v>216</v>
-      </c>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="60" t="s">
-        <v>217</v>
-      </c>
-      <c r="C36" s="60"/>
-      <c r="D36" s="60"/>
-      <c r="E36" s="60"/>
-      <c r="F36" s="60"/>
-      <c r="G36" s="60"/>
-      <c r="H36" s="60"/>
+      <c r="C38" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="D38" s="28"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="28"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="61" t="s">
+        <v>222</v>
+      </c>
+      <c r="C40" s="61"/>
+      <c r="D40" s="61"/>
+      <c r="E40" s="61"/>
+      <c r="F40" s="61"/>
+      <c r="G40" s="61"/>
+      <c r="H40" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
@@ -2370,8 +2463,16 @@
     <mergeCell ref="F31:H31"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="F32:H32"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -2417,48 +2518,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C24:G24">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C20&gt;=1.25</formula>
+      <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1</formula>
+      <formula>C24&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1</formula>
+      <formula>C24&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="215">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -502,9 +502,6 @@
     <t>DSCR (Year 5)</t>
   </si>
   <si>
-    <t>Days Cash on Hand (Year 1)</t>
-  </si>
-  <si>
     <t>Generated by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
@@ -544,21 +541,6 @@
     <t>≥ $10,000</t>
   </si>
   <si>
-    <t>Cost per Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Instructional / Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Facility / Student</t>
-  </si>
-  <si>
-    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
-  </si>
-  <si>
-    <t>Surplus per Student</t>
-  </si>
-  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -593,12 +575,6 @@
   </si>
   <si>
     <t>≥ 24 months</t>
-  </si>
-  <si>
-    <t>Days Cash on Hand</t>
-  </si>
-  <si>
-    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -932,7 +908,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1006,9 +982,6 @@
     <xf numFmtId="166" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="16" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1023,9 +996,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="166" fontId="16" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1772,7 +1742,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H40"/>
+  <dimension ref="B2:H35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1784,7 +1754,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1805,37 +1775,37 @@
       <c r="H3" s="12"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="D4" s="40" t="s">
         <v>163</v>
       </c>
-      <c r="D4" s="41" t="s">
+      <c r="F4" s="41" t="s">
         <v>164</v>
       </c>
-      <c r="F4" s="42" t="s">
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="42" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="43" t="s">
+      <c r="C6" s="43" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" s="43" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" s="43" t="s">
+        <v>98</v>
+      </c>
+      <c r="F6" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="G6" s="43" t="s">
+        <v>100</v>
+      </c>
+      <c r="H6" s="43" t="s">
         <v>166</v>
-      </c>
-      <c r="C6" s="44" t="s">
-        <v>96</v>
-      </c>
-      <c r="D6" s="44" t="s">
-        <v>97</v>
-      </c>
-      <c r="E6" s="44" t="s">
-        <v>98</v>
-      </c>
-      <c r="F6" s="44" t="s">
-        <v>99</v>
-      </c>
-      <c r="G6" s="44" t="s">
-        <v>100</v>
-      </c>
-      <c r="H6" s="44" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -1860,7 +1830,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="25" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C8" s="27">
         <v>1546000</v>
@@ -1880,7 +1850,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="25" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C9" s="27">
         <v>1200167.1888888888</v>
@@ -1900,7 +1870,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="25" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C10" s="27">
         <v>654000</v>
@@ -1920,7 +1890,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="25" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C11" s="27">
         <v>164824.60522117943</v>
@@ -1982,497 +1952,391 @@
       <c r="B14" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="C14" s="45">
+      <c r="C14" s="44">
         <v>-0.3059455330595525</v>
       </c>
-      <c r="D14" s="45">
+      <c r="D14" s="44">
         <v>-0.10427042130500674</v>
       </c>
-      <c r="E14" s="45">
+      <c r="E14" s="44">
         <v>-0.046066008479458874</v>
       </c>
-      <c r="F14" s="45">
+      <c r="F14" s="44">
         <v>-0.16504185604249857</v>
       </c>
-      <c r="G14" s="45">
+      <c r="G14" s="44">
         <v>-0.44816260261601254</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="C15" s="45">
+        <v>12883.333333333334</v>
+      </c>
+      <c r="D15" s="45">
+        <v>12689</v>
+      </c>
+      <c r="E15" s="45">
+        <v>12716.203333333333</v>
+      </c>
+      <c r="F15" s="45">
+        <v>12878.376766666668</v>
+      </c>
+      <c r="G15" s="45">
+        <v>13110.622483</v>
+      </c>
+      <c r="H15" s="46" t="s">
         <v>172</v>
       </c>
-      <c r="C15" s="46">
-        <v>12883.333333333334</v>
-      </c>
-      <c r="D15" s="46">
-        <v>12689</v>
-      </c>
-      <c r="E15" s="46">
-        <v>12716.203333333333</v>
-      </c>
-      <c r="F15" s="46">
-        <v>12878.376766666668</v>
-      </c>
-      <c r="G15" s="46">
-        <v>13110.622483</v>
-      </c>
-      <c r="H15" s="47" t="s">
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="28" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="28" t="s">
+      <c r="C16" s="44">
+        <v>0.7763047793589191</v>
+      </c>
+      <c r="D16" s="44">
+        <v>0.6515878070113221</v>
+      </c>
+      <c r="E16" s="47">
+        <v>0.5752710583855843</v>
+      </c>
+      <c r="F16" s="47">
+        <v>0.5597527709991174</v>
+      </c>
+      <c r="G16" s="47">
+        <v>0.5557873295275215</v>
+      </c>
+      <c r="H16" s="46" t="s">
         <v>174</v>
       </c>
-      <c r="C16" s="32">
-        <v>16824.9316175839</v>
-      </c>
-      <c r="D16" s="32">
-        <v>14012.08737593923</v>
-      </c>
-      <c r="E16" s="32">
-        <v>13301.98806391319</v>
-      </c>
-      <c r="F16" s="32">
-        <v>15003.847971051926</v>
-      </c>
-      <c r="G16" s="32">
-        <v>18986.313176897285</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="25" t="s">
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="C17" s="27">
-        <v>700</v>
-      </c>
-      <c r="D17" s="27">
-        <v>1201.6666666666667</v>
-      </c>
-      <c r="E17" s="27">
-        <v>2062.8611111111118</v>
-      </c>
-      <c r="F17" s="27">
-        <v>3541.244907407408</v>
-      </c>
-      <c r="G17" s="27">
-        <v>6079.137091049384</v>
+      <c r="C17" s="47">
+        <v>0.18240620957309184</v>
+      </c>
+      <c r="D17" s="48">
+        <v>0.11445346362991568</v>
+      </c>
+      <c r="E17" s="48">
+        <v>0.07842325054569485</v>
+      </c>
+      <c r="F17" s="48">
+        <v>0.06380700913541373</v>
+      </c>
+      <c r="G17" s="48">
+        <v>0.06052219961934512</v>
+      </c>
+      <c r="H17" s="46" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="25" t="s">
-        <v>176</v>
-      </c>
-      <c r="C18" s="48">
-        <v>2350</v>
-      </c>
-      <c r="D18" s="46">
-        <v>1452.3</v>
-      </c>
-      <c r="E18" s="46">
-        <v>997.246</v>
-      </c>
-      <c r="F18" s="46">
-        <v>821.7307040000001</v>
-      </c>
-      <c r="G18" s="46">
-        <v>793.4837110500001</v>
-      </c>
-      <c r="H18" s="47" t="s">
+      <c r="B18" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="C18" s="44">
+        <v>-0.19933194624119585</v>
+      </c>
+      <c r="D18" s="44">
+        <v>-0.039322590419523434</v>
+      </c>
+      <c r="E18" s="44">
+        <v>-0.0028600816524580494</v>
+      </c>
+      <c r="F18" s="44">
+        <v>-0.13091237772754036</v>
+      </c>
+      <c r="G18" s="44">
+        <v>-0.4167330108031714</v>
+      </c>
+      <c r="H18" s="46" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="C19" s="36">
-        <v>-3941.5982842505687</v>
-      </c>
-      <c r="D19" s="36">
-        <v>-1323.0873759392305</v>
-      </c>
-      <c r="E19" s="36">
-        <v>-585.7847305798565</v>
-      </c>
-      <c r="F19" s="36">
-        <v>-2125.4712043852587</v>
-      </c>
-      <c r="G19" s="36">
-        <v>-5875.690693897288</v>
+      <c r="C19" s="49">
+        <v>3</v>
+      </c>
+      <c r="D19" s="49">
+        <v>3</v>
+      </c>
+      <c r="E19" s="49">
+        <v>3</v>
+      </c>
+      <c r="F19" s="49">
+        <v>3</v>
+      </c>
+      <c r="G19" s="49">
+        <v>3</v>
+      </c>
+      <c r="H19" s="46" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="28" t="s">
-        <v>179</v>
-      </c>
-      <c r="C20" s="45">
-        <v>0.7763047793589191</v>
-      </c>
-      <c r="D20" s="45">
-        <v>0.6515878070113221</v>
-      </c>
-      <c r="E20" s="49">
-        <v>0.5752710583855843</v>
-      </c>
-      <c r="F20" s="49">
-        <v>0.5597527709991174</v>
-      </c>
-      <c r="G20" s="49">
-        <v>0.5557873295275215</v>
-      </c>
-      <c r="H20" s="47" t="s">
         <v>180</v>
+      </c>
+      <c r="C20" s="50">
+        <v>-1.8696673865856184</v>
+      </c>
+      <c r="D20" s="50">
+        <v>-0.6054488638559378</v>
+      </c>
+      <c r="E20" s="50">
+        <v>-0.06619651197184098</v>
+      </c>
+      <c r="F20" s="50">
+        <v>-3.8357567765741165</v>
+      </c>
+      <c r="G20" s="50">
+        <v>-13.259256222122064</v>
+      </c>
+      <c r="H20" s="46" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="28" t="s">
-        <v>181</v>
-      </c>
-      <c r="C21" s="49">
-        <v>0.18240620957309184</v>
-      </c>
-      <c r="D21" s="50">
-        <v>0.11445346362991568</v>
-      </c>
-      <c r="E21" s="50">
-        <v>0.07842325054569485</v>
-      </c>
-      <c r="F21" s="50">
-        <v>0.06380700913541373</v>
-      </c>
-      <c r="G21" s="50">
-        <v>0.06052219961934512</v>
-      </c>
-      <c r="H21" s="47" t="s">
         <v>182</v>
+      </c>
+      <c r="C21" s="51" t="str">
+        <f>IF('5-Year P&amp;L'!C24&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="51" t="str">
+        <f>IF(AND('5-Year P&amp;L'!D24&gt;=0,'5-Year P&amp;L'!C24&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="51" t="str">
+        <f>IF(AND('5-Year P&amp;L'!E24&gt;=0,'5-Year P&amp;L'!D24&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="51" t="str">
+        <f>IF(AND('5-Year P&amp;L'!F24&gt;=0,'5-Year P&amp;L'!E24&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="51" t="str">
+        <f>IF(AND('5-Year P&amp;L'!G24&gt;=0,'5-Year P&amp;L'!F24&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="46" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="C22" s="45">
-        <v>-0.19933194624119585</v>
-      </c>
-      <c r="D22" s="45">
-        <v>-0.039322590419523434</v>
-      </c>
-      <c r="E22" s="45">
-        <v>-0.0028600816524580494</v>
-      </c>
-      <c r="F22" s="45">
-        <v>-0.13091237772754036</v>
-      </c>
-      <c r="G22" s="45">
-        <v>-0.4167330108031714</v>
-      </c>
-      <c r="H22" s="47" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="28" t="s">
+      <c r="C22" s="52">
+        <v>-3</v>
+      </c>
+      <c r="D22" s="52">
+        <v>-3</v>
+      </c>
+      <c r="E22" s="52">
+        <v>-3</v>
+      </c>
+      <c r="F22" s="52">
+        <v>-4</v>
+      </c>
+      <c r="G22" s="52">
+        <v>-6</v>
+      </c>
+      <c r="H22" s="46" t="s">
         <v>184</v>
       </c>
-      <c r="C23" s="51">
-        <v>3</v>
-      </c>
-      <c r="D23" s="51">
-        <v>3</v>
-      </c>
-      <c r="E23" s="51">
-        <v>3</v>
-      </c>
-      <c r="F23" s="51">
-        <v>3</v>
-      </c>
-      <c r="G23" s="51">
-        <v>3</v>
-      </c>
-      <c r="H23" s="47" t="s">
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="42" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="28" t="s">
+      <c r="C24" s="42" t="s">
         <v>186</v>
       </c>
-      <c r="C24" s="52">
-        <v>-1.8696673865856184</v>
-      </c>
-      <c r="D24" s="52">
-        <v>-0.6054488638559378</v>
-      </c>
-      <c r="E24" s="52">
-        <v>-0.06619651197184098</v>
-      </c>
-      <c r="F24" s="52">
-        <v>-3.8357567765741165</v>
-      </c>
-      <c r="G24" s="52">
-        <v>-13.259256222122064</v>
-      </c>
-      <c r="H24" s="47" t="s">
+      <c r="D24" s="42" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="28" t="s">
+      <c r="E24" s="42"/>
+      <c r="F24" s="42" t="s">
         <v>188</v>
       </c>
-      <c r="C25" s="53" t="str">
-        <f>IF('5-Year P&amp;L'!C24&gt;=0,"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="D25" s="53" t="str">
-        <f>IF(AND('5-Year P&amp;L'!D24&gt;=0,'5-Year P&amp;L'!C24&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="53" t="str">
-        <f>IF(AND('5-Year P&amp;L'!E24&gt;=0,'5-Year P&amp;L'!D24&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="53" t="str">
-        <f>IF(AND('5-Year P&amp;L'!F24&gt;=0,'5-Year P&amp;L'!E24&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="53" t="str">
-        <f>IF(AND('5-Year P&amp;L'!G24&gt;=0,'5-Year P&amp;L'!F24&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="47" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="28" t="s">
+      <c r="G24" s="42"/>
+      <c r="H24" s="42"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="53" t="s">
         <v>189</v>
       </c>
-      <c r="C26" s="54">
-        <v>-3</v>
-      </c>
-      <c r="D26" s="54">
-        <v>-3</v>
-      </c>
-      <c r="E26" s="54">
-        <v>-3</v>
-      </c>
-      <c r="F26" s="54">
-        <v>-4</v>
-      </c>
-      <c r="G26" s="54">
-        <v>-6</v>
-      </c>
-      <c r="H26" s="47" t="s">
+      <c r="C25" s="54" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="28" t="s">
+      <c r="D25" s="55" t="s">
         <v>191</v>
       </c>
-      <c r="C27" s="54">
-        <v>0</v>
-      </c>
-      <c r="D27" s="54">
-        <v>0</v>
-      </c>
-      <c r="E27" s="54">
-        <v>0</v>
-      </c>
-      <c r="F27" s="54">
-        <v>0</v>
-      </c>
-      <c r="G27" s="54">
-        <v>0</v>
-      </c>
-      <c r="H27" s="47" t="s">
+      <c r="E25" s="55"/>
+      <c r="F25" s="56" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="43" t="s">
+      <c r="G25" s="56"/>
+      <c r="H25" s="56"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="C29" s="43" t="s">
+      <c r="C26" s="54" t="s">
+        <v>190</v>
+      </c>
+      <c r="D26" s="55" t="s">
         <v>194</v>
       </c>
-      <c r="D29" s="43" t="s">
+      <c r="E26" s="55"/>
+      <c r="F26" s="56" t="s">
         <v>195</v>
       </c>
-      <c r="E29" s="43"/>
-      <c r="F29" s="43" t="s">
+      <c r="G26" s="56"/>
+      <c r="H26" s="56"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="53" t="s">
         <v>196</v>
       </c>
-      <c r="G29" s="43"/>
-      <c r="H29" s="43"/>
+      <c r="C27" s="57" t="s">
+        <v>197</v>
+      </c>
+      <c r="D27" s="55" t="s">
+        <v>198</v>
+      </c>
+      <c r="E27" s="55"/>
+      <c r="F27" s="56" t="s">
+        <v>199</v>
+      </c>
+      <c r="G27" s="56"/>
+      <c r="H27" s="56"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="53" t="s">
+        <v>200</v>
+      </c>
+      <c r="C28" s="58" t="s">
+        <v>201</v>
+      </c>
+      <c r="D28" s="55" t="s">
+        <v>202</v>
+      </c>
+      <c r="E28" s="55"/>
+      <c r="F28" s="56" t="s">
+        <v>203</v>
+      </c>
+      <c r="G28" s="56"/>
+      <c r="H28" s="56"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="C29" s="54" t="s">
+        <v>190</v>
+      </c>
+      <c r="D29" s="55" t="s">
+        <v>205</v>
+      </c>
+      <c r="E29" s="55"/>
+      <c r="F29" s="56" t="s">
+        <v>206</v>
+      </c>
+      <c r="G29" s="56"/>
+      <c r="H29" s="56"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="55" t="s">
-        <v>197</v>
-      </c>
-      <c r="C30" s="56" t="s">
-        <v>198</v>
-      </c>
-      <c r="D30" s="57" t="s">
-        <v>199</v>
-      </c>
-      <c r="E30" s="57"/>
-      <c r="F30" s="58" t="s">
-        <v>200</v>
-      </c>
-      <c r="G30" s="58"/>
-      <c r="H30" s="58"/>
+      <c r="B30" s="53" t="s">
+        <v>207</v>
+      </c>
+      <c r="C30" s="58" t="s">
+        <v>201</v>
+      </c>
+      <c r="D30" s="55" t="s">
+        <v>208</v>
+      </c>
+      <c r="E30" s="55"/>
+      <c r="F30" s="56" t="s">
+        <v>209</v>
+      </c>
+      <c r="G30" s="56"/>
+      <c r="H30" s="56"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="55" t="s">
-        <v>201</v>
-      </c>
-      <c r="C31" s="56" t="s">
-        <v>198</v>
-      </c>
-      <c r="D31" s="57" t="s">
-        <v>202</v>
-      </c>
-      <c r="E31" s="57"/>
-      <c r="F31" s="58" t="s">
-        <v>203</v>
-      </c>
-      <c r="G31" s="58"/>
-      <c r="H31" s="58"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="55" t="s">
-        <v>204</v>
-      </c>
-      <c r="C32" s="59" t="s">
-        <v>205</v>
-      </c>
-      <c r="D32" s="57" t="s">
-        <v>206</v>
-      </c>
-      <c r="E32" s="57"/>
-      <c r="F32" s="58" t="s">
-        <v>207</v>
-      </c>
-      <c r="G32" s="58"/>
-      <c r="H32" s="58"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="55" t="s">
-        <v>208</v>
-      </c>
-      <c r="C33" s="60" t="s">
-        <v>209</v>
-      </c>
-      <c r="D33" s="57" t="s">
+      <c r="B31" s="53" t="s">
         <v>210</v>
       </c>
-      <c r="E33" s="57"/>
-      <c r="F33" s="58" t="s">
+      <c r="C31" s="54" t="s">
+        <v>190</v>
+      </c>
+      <c r="D31" s="55" t="s">
         <v>211</v>
       </c>
-      <c r="G33" s="58"/>
-      <c r="H33" s="58"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="55" t="s">
+      <c r="E31" s="55"/>
+      <c r="F31" s="56" t="s">
         <v>212</v>
       </c>
-      <c r="C34" s="56" t="s">
-        <v>198</v>
-      </c>
-      <c r="D34" s="57" t="s">
+      <c r="G31" s="56"/>
+      <c r="H31" s="56"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="28" t="s">
         <v>213</v>
       </c>
-      <c r="E34" s="57"/>
-      <c r="F34" s="58" t="s">
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="59" t="s">
         <v>214</v>
       </c>
-      <c r="G34" s="58"/>
-      <c r="H34" s="58"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="55" t="s">
-        <v>215</v>
-      </c>
-      <c r="C35" s="60" t="s">
-        <v>209</v>
-      </c>
-      <c r="D35" s="57" t="s">
-        <v>216</v>
-      </c>
-      <c r="E35" s="57"/>
-      <c r="F35" s="58" t="s">
-        <v>217</v>
-      </c>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-    </row>
-    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="55" t="s">
-        <v>218</v>
-      </c>
-      <c r="C36" s="56" t="s">
-        <v>198</v>
-      </c>
-      <c r="D36" s="57" t="s">
-        <v>219</v>
-      </c>
-      <c r="E36" s="57"/>
-      <c r="F36" s="58" t="s">
-        <v>220</v>
-      </c>
-      <c r="G36" s="58"/>
-      <c r="H36" s="58"/>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="55" t="s">
-        <v>39</v>
-      </c>
-      <c r="C38" s="28" t="s">
-        <v>221</v>
-      </c>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="28"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="61" t="s">
-        <v>222</v>
-      </c>
-      <c r="C40" s="61"/>
-      <c r="D40" s="61"/>
-      <c r="E40" s="61"/>
-      <c r="F40" s="61"/>
-      <c r="G40" s="61"/>
-      <c r="H40" s="61"/>
+      <c r="C35" s="59"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="59"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B35:H35"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -2518,48 +2382,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C20&lt;=0.55</formula>
+      <formula>C16&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C20&lt;=0.65</formula>
+      <formula>C16&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C20&gt;0.65</formula>
+      <formula>C16&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C21:G21">
+  <conditionalFormatting sqref="C17:G17">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C21&lt;=0.15</formula>
+      <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C21&lt;=0.22</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C21&gt;0.22</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C22:G22">
+  <conditionalFormatting sqref="C18:G18">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C22&gt;=0.10</formula>
+      <formula>C18&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C22&gt;=0</formula>
+      <formula>C18&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C22&lt;0</formula>
+      <formula>C18&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C24:G24">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C24&gt;=1.25</formula>
+      <formula>C20&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C24&gt;=1</formula>
+      <formula>C20&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C24&lt;1</formula>
+      <formula>C20&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4533,7 +4397,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:C21"/>
+  <dimension ref="B1:C20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -4670,24 +4534,16 @@
         <v>-13.25925622</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="25" t="s">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="C19" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="C21" s="12"/>
+      <c r="C20" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B20:C20"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="223">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -502,6 +502,9 @@
     <t>DSCR (Year 5)</t>
   </si>
   <si>
+    <t>Days Cash on Hand (Year 1)</t>
+  </si>
+  <si>
     <t>Generated by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
@@ -541,6 +544,21 @@
     <t>≥ $10,000</t>
   </si>
   <si>
+    <t>Cost per Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
+  </si>
+  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -575,6 +593,12 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>Days Cash on Hand</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -908,7 +932,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -982,6 +1006,9 @@
     <xf numFmtId="166" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="3" fontId="16" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -996,6 +1023,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="166" fontId="16" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1742,7 +1772,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1754,7 +1784,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1775,37 +1805,37 @@
       <c r="H3" s="12"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="39" t="s">
-        <v>162</v>
-      </c>
-      <c r="D4" s="40" t="s">
+      <c r="B4" s="40" t="s">
         <v>163</v>
       </c>
-      <c r="F4" s="41" t="s">
+      <c r="D4" s="41" t="s">
         <v>164</v>
       </c>
+      <c r="F4" s="42" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="42" t="s">
-        <v>165</v>
-      </c>
-      <c r="C6" s="43" t="s">
+      <c r="B6" s="43" t="s">
+        <v>166</v>
+      </c>
+      <c r="C6" s="44" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="44" t="s">
         <v>97</v>
       </c>
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="44" t="s">
         <v>98</v>
       </c>
-      <c r="F6" s="43" t="s">
+      <c r="F6" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="G6" s="43" t="s">
+      <c r="G6" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="H6" s="43" t="s">
-        <v>166</v>
+      <c r="H6" s="44" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -1830,7 +1860,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="25" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C8" s="27">
         <v>1546000</v>
@@ -1850,7 +1880,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="25" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C9" s="27">
         <v>1200167.1888888888</v>
@@ -1870,7 +1900,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C10" s="27">
         <v>654000</v>
@@ -1890,7 +1920,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="25" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C11" s="27">
         <v>164824.60522117943</v>
@@ -1952,391 +1982,497 @@
       <c r="B14" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="C14" s="44">
+      <c r="C14" s="45">
         <v>-0.3059455330595525</v>
       </c>
-      <c r="D14" s="44">
+      <c r="D14" s="45">
         <v>-0.10427042130500674</v>
       </c>
-      <c r="E14" s="44">
+      <c r="E14" s="45">
         <v>-0.046066008479458874</v>
       </c>
-      <c r="F14" s="44">
+      <c r="F14" s="45">
         <v>-0.16504185604249857</v>
       </c>
-      <c r="G14" s="44">
+      <c r="G14" s="45">
         <v>-0.44816260261601254</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="C15" s="45">
+        <v>172</v>
+      </c>
+      <c r="C15" s="46">
         <v>12883.333333333334</v>
       </c>
-      <c r="D15" s="45">
+      <c r="D15" s="46">
         <v>12689</v>
       </c>
-      <c r="E15" s="45">
+      <c r="E15" s="46">
         <v>12716.203333333333</v>
       </c>
-      <c r="F15" s="45">
+      <c r="F15" s="46">
         <v>12878.376766666668</v>
       </c>
-      <c r="G15" s="45">
+      <c r="G15" s="46">
         <v>13110.622483</v>
       </c>
-      <c r="H15" s="46" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H15" s="47" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="C16" s="44">
-        <v>0.7763047793589191</v>
-      </c>
-      <c r="D16" s="44">
-        <v>0.6515878070113221</v>
-      </c>
-      <c r="E16" s="47">
-        <v>0.5752710583855843</v>
-      </c>
-      <c r="F16" s="47">
-        <v>0.5597527709991174</v>
-      </c>
-      <c r="G16" s="47">
-        <v>0.5557873295275215</v>
-      </c>
-      <c r="H16" s="46" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="28" t="s">
+      <c r="C16" s="32">
+        <v>16824.9316175839</v>
+      </c>
+      <c r="D16" s="32">
+        <v>14012.08737593923</v>
+      </c>
+      <c r="E16" s="32">
+        <v>13301.98806391319</v>
+      </c>
+      <c r="F16" s="32">
+        <v>15003.847971051926</v>
+      </c>
+      <c r="G16" s="32">
+        <v>18986.313176897285</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="C17" s="47">
-        <v>0.18240620957309184</v>
-      </c>
-      <c r="D17" s="48">
-        <v>0.11445346362991568</v>
-      </c>
-      <c r="E17" s="48">
-        <v>0.07842325054569485</v>
-      </c>
-      <c r="F17" s="48">
-        <v>0.06380700913541373</v>
-      </c>
-      <c r="G17" s="48">
-        <v>0.06052219961934512</v>
-      </c>
-      <c r="H17" s="46" t="s">
+      <c r="C17" s="27">
+        <v>700</v>
+      </c>
+      <c r="D17" s="27">
+        <v>1201.6666666666667</v>
+      </c>
+      <c r="E17" s="27">
+        <v>2062.8611111111118</v>
+      </c>
+      <c r="F17" s="27">
+        <v>3541.244907407408</v>
+      </c>
+      <c r="G17" s="27">
+        <v>6079.137091049384</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="25" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="C18" s="44">
-        <v>-0.19933194624119585</v>
-      </c>
-      <c r="D18" s="44">
-        <v>-0.039322590419523434</v>
-      </c>
-      <c r="E18" s="44">
-        <v>-0.0028600816524580494</v>
-      </c>
-      <c r="F18" s="44">
-        <v>-0.13091237772754036</v>
-      </c>
-      <c r="G18" s="44">
-        <v>-0.4167330108031714</v>
-      </c>
-      <c r="H18" s="46" t="s">
+      <c r="C18" s="48">
+        <v>2350</v>
+      </c>
+      <c r="D18" s="46">
+        <v>1452.3</v>
+      </c>
+      <c r="E18" s="46">
+        <v>997.246</v>
+      </c>
+      <c r="F18" s="46">
+        <v>821.7307040000001</v>
+      </c>
+      <c r="G18" s="46">
+        <v>793.4837110500001</v>
+      </c>
+      <c r="H18" s="47" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="C19" s="49">
-        <v>3</v>
-      </c>
-      <c r="D19" s="49">
-        <v>3</v>
-      </c>
-      <c r="E19" s="49">
-        <v>3</v>
-      </c>
-      <c r="F19" s="49">
-        <v>3</v>
-      </c>
-      <c r="G19" s="49">
-        <v>3</v>
-      </c>
-      <c r="H19" s="46" t="s">
-        <v>179</v>
+      <c r="C19" s="36">
+        <v>-3941.5982842505687</v>
+      </c>
+      <c r="D19" s="36">
+        <v>-1323.0873759392305</v>
+      </c>
+      <c r="E19" s="36">
+        <v>-585.7847305798565</v>
+      </c>
+      <c r="F19" s="36">
+        <v>-2125.4712043852587</v>
+      </c>
+      <c r="G19" s="36">
+        <v>-5875.690693897288</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="C20" s="45">
+        <v>0.7763047793589191</v>
+      </c>
+      <c r="D20" s="45">
+        <v>0.6515878070113221</v>
+      </c>
+      <c r="E20" s="49">
+        <v>0.5752710583855843</v>
+      </c>
+      <c r="F20" s="49">
+        <v>0.5597527709991174</v>
+      </c>
+      <c r="G20" s="49">
+        <v>0.5557873295275215</v>
+      </c>
+      <c r="H20" s="47" t="s">
         <v>180</v>
-      </c>
-      <c r="C20" s="50">
-        <v>-1.8696673865856184</v>
-      </c>
-      <c r="D20" s="50">
-        <v>-0.6054488638559378</v>
-      </c>
-      <c r="E20" s="50">
-        <v>-0.06619651197184098</v>
-      </c>
-      <c r="F20" s="50">
-        <v>-3.8357567765741165</v>
-      </c>
-      <c r="G20" s="50">
-        <v>-13.259256222122064</v>
-      </c>
-      <c r="H20" s="46" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="C21" s="49">
+        <v>0.18240620957309184</v>
+      </c>
+      <c r="D21" s="50">
+        <v>0.11445346362991568</v>
+      </c>
+      <c r="E21" s="50">
+        <v>0.07842325054569485</v>
+      </c>
+      <c r="F21" s="50">
+        <v>0.06380700913541373</v>
+      </c>
+      <c r="G21" s="50">
+        <v>0.06052219961934512</v>
+      </c>
+      <c r="H21" s="47" t="s">
         <v>182</v>
       </c>
-      <c r="C21" s="51" t="str">
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="C22" s="45">
+        <v>-0.19933194624119585</v>
+      </c>
+      <c r="D22" s="45">
+        <v>-0.039322590419523434</v>
+      </c>
+      <c r="E22" s="45">
+        <v>-0.0028600816524580494</v>
+      </c>
+      <c r="F22" s="45">
+        <v>-0.13091237772754036</v>
+      </c>
+      <c r="G22" s="45">
+        <v>-0.4167330108031714</v>
+      </c>
+      <c r="H22" s="47" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="C23" s="51">
+        <v>3</v>
+      </c>
+      <c r="D23" s="51">
+        <v>3</v>
+      </c>
+      <c r="E23" s="51">
+        <v>3</v>
+      </c>
+      <c r="F23" s="51">
+        <v>3</v>
+      </c>
+      <c r="G23" s="51">
+        <v>3</v>
+      </c>
+      <c r="H23" s="47" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="C24" s="52">
+        <v>-1.8696673865856184</v>
+      </c>
+      <c r="D24" s="52">
+        <v>-0.6054488638559378</v>
+      </c>
+      <c r="E24" s="52">
+        <v>-0.06619651197184098</v>
+      </c>
+      <c r="F24" s="52">
+        <v>-3.8357567765741165</v>
+      </c>
+      <c r="G24" s="52">
+        <v>-13.259256222122064</v>
+      </c>
+      <c r="H24" s="47" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="28" t="s">
+        <v>188</v>
+      </c>
+      <c r="C25" s="53" t="str">
         <f>IF('5-Year P&amp;L'!C24&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D21" s="51" t="str">
+      <c r="D25" s="53" t="str">
         <f>IF(AND('5-Year P&amp;L'!D24&gt;=0,'5-Year P&amp;L'!C24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="51" t="str">
+      <c r="E25" s="53" t="str">
         <f>IF(AND('5-Year P&amp;L'!E24&gt;=0,'5-Year P&amp;L'!D24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="51" t="str">
+      <c r="F25" s="53" t="str">
         <f>IF(AND('5-Year P&amp;L'!F24&gt;=0,'5-Year P&amp;L'!E24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="51" t="str">
+      <c r="G25" s="53" t="str">
         <f>IF(AND('5-Year P&amp;L'!G24&gt;=0,'5-Year P&amp;L'!F24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="46" t="s">
+      <c r="H25" s="47" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="C22" s="52">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="C26" s="54">
         <v>-3</v>
       </c>
-      <c r="D22" s="52">
+      <c r="D26" s="54">
         <v>-3</v>
       </c>
-      <c r="E22" s="52">
+      <c r="E26" s="54">
         <v>-3</v>
       </c>
-      <c r="F22" s="52">
+      <c r="F26" s="54">
         <v>-4</v>
       </c>
-      <c r="G22" s="52">
+      <c r="G26" s="54">
         <v>-6</v>
       </c>
-      <c r="H22" s="46" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="42" t="s">
-        <v>185</v>
-      </c>
-      <c r="C24" s="42" t="s">
-        <v>186</v>
-      </c>
-      <c r="D24" s="42" t="s">
-        <v>187</v>
-      </c>
-      <c r="E24" s="42"/>
-      <c r="F24" s="42" t="s">
-        <v>188</v>
-      </c>
-      <c r="G24" s="42"/>
-      <c r="H24" s="42"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="53" t="s">
-        <v>189</v>
-      </c>
-      <c r="C25" s="54" t="s">
+      <c r="H26" s="47" t="s">
         <v>190</v>
       </c>
-      <c r="D25" s="55" t="s">
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="28" t="s">
         <v>191</v>
       </c>
-      <c r="E25" s="55"/>
-      <c r="F25" s="56" t="s">
+      <c r="C27" s="54">
+        <v>0</v>
+      </c>
+      <c r="D27" s="54">
+        <v>0</v>
+      </c>
+      <c r="E27" s="54">
+        <v>0</v>
+      </c>
+      <c r="F27" s="54">
+        <v>0</v>
+      </c>
+      <c r="G27" s="54">
+        <v>0</v>
+      </c>
+      <c r="H27" s="47" t="s">
         <v>192</v>
       </c>
-      <c r="G25" s="56"/>
-      <c r="H25" s="56"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="53" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="43" t="s">
         <v>193</v>
       </c>
-      <c r="C26" s="54" t="s">
-        <v>190</v>
-      </c>
-      <c r="D26" s="55" t="s">
+      <c r="C29" s="43" t="s">
         <v>194</v>
       </c>
-      <c r="E26" s="55"/>
-      <c r="F26" s="56" t="s">
+      <c r="D29" s="43" t="s">
         <v>195</v>
       </c>
-      <c r="G26" s="56"/>
-      <c r="H26" s="56"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="53" t="s">
+      <c r="E29" s="43"/>
+      <c r="F29" s="43" t="s">
         <v>196</v>
       </c>
-      <c r="C27" s="57" t="s">
+      <c r="G29" s="43"/>
+      <c r="H29" s="43"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="55" t="s">
         <v>197</v>
       </c>
-      <c r="D27" s="55" t="s">
+      <c r="C30" s="56" t="s">
         <v>198</v>
       </c>
-      <c r="E27" s="55"/>
-      <c r="F27" s="56" t="s">
+      <c r="D30" s="57" t="s">
         <v>199</v>
       </c>
-      <c r="G27" s="56"/>
-      <c r="H27" s="56"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="53" t="s">
+      <c r="E30" s="57"/>
+      <c r="F30" s="58" t="s">
         <v>200</v>
       </c>
-      <c r="C28" s="58" t="s">
+      <c r="G30" s="58"/>
+      <c r="H30" s="58"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="55" t="s">
         <v>201</v>
       </c>
-      <c r="D28" s="55" t="s">
+      <c r="C31" s="56" t="s">
+        <v>198</v>
+      </c>
+      <c r="D31" s="57" t="s">
         <v>202</v>
       </c>
-      <c r="E28" s="55"/>
-      <c r="F28" s="56" t="s">
+      <c r="E31" s="57"/>
+      <c r="F31" s="58" t="s">
         <v>203</v>
       </c>
-      <c r="G28" s="56"/>
-      <c r="H28" s="56"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="53" t="s">
+      <c r="G31" s="58"/>
+      <c r="H31" s="58"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="55" t="s">
         <v>204</v>
       </c>
-      <c r="C29" s="54" t="s">
-        <v>190</v>
-      </c>
-      <c r="D29" s="55" t="s">
+      <c r="C32" s="59" t="s">
         <v>205</v>
       </c>
-      <c r="E29" s="55"/>
-      <c r="F29" s="56" t="s">
+      <c r="D32" s="57" t="s">
         <v>206</v>
       </c>
-      <c r="G29" s="56"/>
-      <c r="H29" s="56"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="53" t="s">
+      <c r="E32" s="57"/>
+      <c r="F32" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="C30" s="58" t="s">
-        <v>201</v>
-      </c>
-      <c r="D30" s="55" t="s">
+      <c r="G32" s="58"/>
+      <c r="H32" s="58"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="55" t="s">
         <v>208</v>
       </c>
-      <c r="E30" s="55"/>
-      <c r="F30" s="56" t="s">
+      <c r="C33" s="60" t="s">
         <v>209</v>
       </c>
-      <c r="G30" s="56"/>
-      <c r="H30" s="56"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="53" t="s">
+      <c r="D33" s="57" t="s">
         <v>210</v>
       </c>
-      <c r="C31" s="54" t="s">
-        <v>190</v>
-      </c>
-      <c r="D31" s="55" t="s">
+      <c r="E33" s="57"/>
+      <c r="F33" s="58" t="s">
         <v>211</v>
       </c>
-      <c r="E31" s="55"/>
-      <c r="F31" s="56" t="s">
+      <c r="G33" s="58"/>
+      <c r="H33" s="58"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="55" t="s">
         <v>212</v>
       </c>
-      <c r="G31" s="56"/>
-      <c r="H31" s="56"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="53" t="s">
+      <c r="C34" s="56" t="s">
+        <v>198</v>
+      </c>
+      <c r="D34" s="57" t="s">
+        <v>213</v>
+      </c>
+      <c r="E34" s="57"/>
+      <c r="F34" s="58" t="s">
+        <v>214</v>
+      </c>
+      <c r="G34" s="58"/>
+      <c r="H34" s="58"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="55" t="s">
+        <v>215</v>
+      </c>
+      <c r="C35" s="60" t="s">
+        <v>209</v>
+      </c>
+      <c r="D35" s="57" t="s">
+        <v>216</v>
+      </c>
+      <c r="E35" s="57"/>
+      <c r="F35" s="58" t="s">
+        <v>217</v>
+      </c>
+      <c r="G35" s="58"/>
+      <c r="H35" s="58"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="55" t="s">
+        <v>218</v>
+      </c>
+      <c r="C36" s="56" t="s">
+        <v>198</v>
+      </c>
+      <c r="D36" s="57" t="s">
+        <v>219</v>
+      </c>
+      <c r="E36" s="57"/>
+      <c r="F36" s="58" t="s">
+        <v>220</v>
+      </c>
+      <c r="G36" s="58"/>
+      <c r="H36" s="58"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="28" t="s">
-        <v>213</v>
-      </c>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="59" t="s">
-        <v>214</v>
-      </c>
-      <c r="C35" s="59"/>
-      <c r="D35" s="59"/>
-      <c r="E35" s="59"/>
-      <c r="F35" s="59"/>
-      <c r="G35" s="59"/>
-      <c r="H35" s="59"/>
+      <c r="C38" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="D38" s="28"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="28"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="61" t="s">
+        <v>222</v>
+      </c>
+      <c r="C40" s="61"/>
+      <c r="D40" s="61"/>
+      <c r="E40" s="61"/>
+      <c r="F40" s="61"/>
+      <c r="G40" s="61"/>
+      <c r="H40" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -2382,48 +2518,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C24:G24">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C20&gt;=1.25</formula>
+      <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1</formula>
+      <formula>C24&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1</formula>
+      <formula>C24&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4397,7 +4533,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:C20"/>
+  <dimension ref="B1:C21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -4534,16 +4670,24 @@
         <v>-13.25925622</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="12" t="s">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="25" t="s">
         <v>160</v>
       </c>
-      <c r="C20" s="12"/>
+      <c r="C19" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="C21" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
@@ -13,14 +13,15 @@
     <sheet sheetId="7" name="Staffing" state="visible" r:id="rId10"/>
     <sheet sheetId="8" name="Loan Snapshot" state="visible" r:id="rId11"/>
     <sheet sheetId="9" name="Summary" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="Financial Health" state="visible" r:id="rId13"/>
+    <sheet sheetId="10" name="Decision History" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="Financial Health" state="visible" r:id="rId14"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="226">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -28,7 +29,7 @@
     <t>Civic Scholars Charter</t>
   </si>
   <si>
-    <t>Generated March 27, 2026 · nonprofit_501c3</t>
+    <t>Generated April 29, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -142,7 +143,7 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>Generated March 27, 2026</t>
+    <t>Generated April 29, 2026</t>
   </si>
   <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>
@@ -508,6 +509,15 @@
     <t>Generated by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
+    <t>Decision History</t>
+  </si>
+  <si>
+    <t>No decisions have been tracked with an outcome yet. As the team marks saved scenarios as Pursued, Declined, or On hold, those outcomes (and any retrospective notes) will appear here so reviewers can see what actually happened versus what was modeled.</t>
+  </si>
+  <si>
+    <t>Once decisions are saved with a Pursued / Declined / On hold outcome inside the planner, they will be summarized here.</t>
+  </si>
+  <si>
     <t>Civic Scholars Charter — Financial Health Dashboard</t>
   </si>
   <si>
@@ -628,7 +638,7 @@
     <t>Liquidity</t>
   </si>
   <si>
-    <t>Cash goes negative in month 0. The school will need outside funding to continue operating.</t>
+    <t>Cash goes negative in month 1. The school will need outside funding to continue operating.</t>
   </si>
   <si>
     <t>Secure a line of credit or bridge funding before operations begin.</t>
@@ -661,7 +671,7 @@
     <t>Debt Affordability</t>
   </si>
   <si>
-    <t>DSCR of -13.26x means operating income does not cover debt payments. This must be resolved.</t>
+    <t>DSCR of -13.26x is below the 1.15x amber threshold. Any shortfall in revenue makes debt unaffordable.</t>
   </si>
   <si>
     <t>Reduce loan amounts, extend terms, or increase revenue before committing to this debt.</t>
@@ -932,7 +942,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1008,6 +1018,12 @@
     </xf>
     <xf numFmtId="3" fontId="16" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1772,6 +1788,72 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="B1:H4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+    </row>
+    <row r="2" ht="60" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>164</v>
+      </c>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B4:H4"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF328555"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="B2:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -1784,7 +1866,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1805,37 +1887,37 @@
       <c r="H3" s="12"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="D4" s="41" t="s">
-        <v>164</v>
-      </c>
-      <c r="F4" s="42" t="s">
-        <v>165</v>
+      <c r="B4" s="42" t="s">
+        <v>166</v>
+      </c>
+      <c r="D4" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="F4" s="44" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="43" t="s">
-        <v>166</v>
-      </c>
-      <c r="C6" s="44" t="s">
+      <c r="B6" s="45" t="s">
+        <v>169</v>
+      </c>
+      <c r="C6" s="46" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="44" t="s">
+      <c r="D6" s="46" t="s">
         <v>97</v>
       </c>
-      <c r="E6" s="44" t="s">
+      <c r="E6" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="F6" s="44" t="s">
+      <c r="F6" s="46" t="s">
         <v>99</v>
       </c>
-      <c r="G6" s="44" t="s">
+      <c r="G6" s="46" t="s">
         <v>100</v>
       </c>
-      <c r="H6" s="44" t="s">
-        <v>167</v>
+      <c r="H6" s="46" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -1860,7 +1942,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="25" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C8" s="27">
         <v>1546000</v>
@@ -1880,7 +1962,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="25" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C9" s="27">
         <v>1200167.1888888888</v>
@@ -1900,7 +1982,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="25" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C10" s="27">
         <v>654000</v>
@@ -1920,7 +2002,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="25" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C11" s="27">
         <v>164824.60522117943</v>
@@ -1982,48 +2064,48 @@
       <c r="B14" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="C14" s="45">
+      <c r="C14" s="47">
         <v>-0.3059455330595525</v>
       </c>
-      <c r="D14" s="45">
+      <c r="D14" s="47">
         <v>-0.10427042130500674</v>
       </c>
-      <c r="E14" s="45">
+      <c r="E14" s="47">
         <v>-0.046066008479458874</v>
       </c>
-      <c r="F14" s="45">
+      <c r="F14" s="47">
         <v>-0.16504185604249857</v>
       </c>
-      <c r="G14" s="45">
+      <c r="G14" s="47">
         <v>-0.44816260261601254</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="28" t="s">
-        <v>172</v>
-      </c>
-      <c r="C15" s="46">
+        <v>175</v>
+      </c>
+      <c r="C15" s="48">
         <v>12883.333333333334</v>
       </c>
-      <c r="D15" s="46">
+      <c r="D15" s="48">
         <v>12689</v>
       </c>
-      <c r="E15" s="46">
+      <c r="E15" s="48">
         <v>12716.203333333333</v>
       </c>
-      <c r="F15" s="46">
+      <c r="F15" s="48">
         <v>12878.376766666668</v>
       </c>
-      <c r="G15" s="46">
+      <c r="G15" s="48">
         <v>13110.622483</v>
       </c>
-      <c r="H15" s="47" t="s">
-        <v>173</v>
+      <c r="H15" s="49" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="28" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C16" s="32">
         <v>16824.9316175839</v>
@@ -2043,7 +2125,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="25" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C17" s="27">
         <v>700</v>
@@ -2063,30 +2145,30 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="25" t="s">
-        <v>176</v>
-      </c>
-      <c r="C18" s="48">
+        <v>179</v>
+      </c>
+      <c r="C18" s="50">
         <v>2350</v>
       </c>
-      <c r="D18" s="46">
+      <c r="D18" s="48">
         <v>1452.3</v>
       </c>
-      <c r="E18" s="46">
+      <c r="E18" s="48">
         <v>997.246</v>
       </c>
-      <c r="F18" s="46">
+      <c r="F18" s="48">
         <v>821.7307040000001</v>
       </c>
-      <c r="G18" s="46">
+      <c r="G18" s="48">
         <v>793.4837110500001</v>
       </c>
-      <c r="H18" s="47" t="s">
-        <v>177</v>
+      <c r="H18" s="49" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="28" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C19" s="36">
         <v>-3941.5982842505687</v>
@@ -2106,350 +2188,350 @@
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="28" t="s">
-        <v>179</v>
-      </c>
-      <c r="C20" s="45">
+        <v>182</v>
+      </c>
+      <c r="C20" s="47">
         <v>0.7763047793589191</v>
       </c>
-      <c r="D20" s="45">
+      <c r="D20" s="47">
         <v>0.6515878070113221</v>
       </c>
-      <c r="E20" s="49">
+      <c r="E20" s="51">
         <v>0.5752710583855843</v>
       </c>
-      <c r="F20" s="49">
+      <c r="F20" s="51">
         <v>0.5597527709991174</v>
       </c>
-      <c r="G20" s="49">
+      <c r="G20" s="51">
         <v>0.5557873295275215</v>
       </c>
-      <c r="H20" s="47" t="s">
-        <v>180</v>
+      <c r="H20" s="49" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="28" t="s">
-        <v>181</v>
-      </c>
-      <c r="C21" s="49">
+        <v>184</v>
+      </c>
+      <c r="C21" s="51">
         <v>0.18240620957309184</v>
       </c>
-      <c r="D21" s="50">
+      <c r="D21" s="52">
         <v>0.11445346362991568</v>
       </c>
-      <c r="E21" s="50">
+      <c r="E21" s="52">
         <v>0.07842325054569485</v>
       </c>
-      <c r="F21" s="50">
+      <c r="F21" s="52">
         <v>0.06380700913541373</v>
       </c>
-      <c r="G21" s="50">
+      <c r="G21" s="52">
         <v>0.06052219961934512</v>
       </c>
-      <c r="H21" s="47" t="s">
-        <v>182</v>
+      <c r="H21" s="49" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="C22" s="45">
+      <c r="C22" s="47">
         <v>-0.19933194624119585</v>
       </c>
-      <c r="D22" s="45">
+      <c r="D22" s="47">
         <v>-0.039322590419523434</v>
       </c>
-      <c r="E22" s="45">
+      <c r="E22" s="47">
         <v>-0.0028600816524580494</v>
       </c>
-      <c r="F22" s="45">
+      <c r="F22" s="47">
         <v>-0.13091237772754036</v>
       </c>
-      <c r="G22" s="45">
+      <c r="G22" s="47">
         <v>-0.4167330108031714</v>
       </c>
-      <c r="H22" s="47" t="s">
-        <v>183</v>
+      <c r="H22" s="49" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="C23" s="51">
+        <v>187</v>
+      </c>
+      <c r="C23" s="53">
         <v>3</v>
       </c>
-      <c r="D23" s="51">
+      <c r="D23" s="53">
         <v>3</v>
       </c>
-      <c r="E23" s="51">
+      <c r="E23" s="53">
         <v>3</v>
       </c>
-      <c r="F23" s="51">
+      <c r="F23" s="53">
         <v>3</v>
       </c>
-      <c r="G23" s="51">
+      <c r="G23" s="53">
         <v>3</v>
       </c>
-      <c r="H23" s="47" t="s">
-        <v>185</v>
+      <c r="H23" s="49" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="28" t="s">
-        <v>186</v>
-      </c>
-      <c r="C24" s="52">
+        <v>189</v>
+      </c>
+      <c r="C24" s="54">
         <v>-1.8696673865856184</v>
       </c>
-      <c r="D24" s="52">
+      <c r="D24" s="54">
         <v>-0.6054488638559378</v>
       </c>
-      <c r="E24" s="52">
+      <c r="E24" s="54">
         <v>-0.06619651197184098</v>
       </c>
-      <c r="F24" s="52">
+      <c r="F24" s="54">
         <v>-3.8357567765741165</v>
       </c>
-      <c r="G24" s="52">
+      <c r="G24" s="54">
         <v>-13.259256222122064</v>
       </c>
-      <c r="H24" s="47" t="s">
-        <v>187</v>
+      <c r="H24" s="49" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="28" t="s">
-        <v>188</v>
-      </c>
-      <c r="C25" s="53" t="str">
+        <v>191</v>
+      </c>
+      <c r="C25" s="55" t="str">
         <f>IF('5-Year P&amp;L'!C24&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D25" s="53" t="str">
+      <c r="D25" s="55" t="str">
         <f>IF(AND('5-Year P&amp;L'!D24&gt;=0,'5-Year P&amp;L'!C24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E25" s="53" t="str">
+      <c r="E25" s="55" t="str">
         <f>IF(AND('5-Year P&amp;L'!E24&gt;=0,'5-Year P&amp;L'!D24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F25" s="53" t="str">
+      <c r="F25" s="55" t="str">
         <f>IF(AND('5-Year P&amp;L'!F24&gt;=0,'5-Year P&amp;L'!E24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G25" s="53" t="str">
+      <c r="G25" s="55" t="str">
         <f>IF(AND('5-Year P&amp;L'!G24&gt;=0,'5-Year P&amp;L'!F24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H25" s="47" t="s">
+      <c r="H25" s="49" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="28" t="s">
-        <v>189</v>
-      </c>
-      <c r="C26" s="54">
+        <v>192</v>
+      </c>
+      <c r="C26" s="56">
         <v>-3</v>
       </c>
-      <c r="D26" s="54">
+      <c r="D26" s="56">
         <v>-3</v>
       </c>
-      <c r="E26" s="54">
+      <c r="E26" s="56">
         <v>-3</v>
       </c>
-      <c r="F26" s="54">
+      <c r="F26" s="56">
         <v>-4</v>
       </c>
-      <c r="G26" s="54">
+      <c r="G26" s="56">
         <v>-6</v>
       </c>
-      <c r="H26" s="47" t="s">
-        <v>190</v>
+      <c r="H26" s="49" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="28" t="s">
-        <v>191</v>
-      </c>
-      <c r="C27" s="54">
+        <v>194</v>
+      </c>
+      <c r="C27" s="56">
         <v>0</v>
       </c>
-      <c r="D27" s="54">
+      <c r="D27" s="56">
         <v>0</v>
       </c>
-      <c r="E27" s="54">
+      <c r="E27" s="56">
         <v>0</v>
       </c>
-      <c r="F27" s="54">
+      <c r="F27" s="56">
         <v>0</v>
       </c>
-      <c r="G27" s="54">
+      <c r="G27" s="56">
         <v>0</v>
       </c>
-      <c r="H27" s="47" t="s">
-        <v>192</v>
+      <c r="H27" s="49" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="43" t="s">
-        <v>193</v>
-      </c>
-      <c r="C29" s="43" t="s">
-        <v>194</v>
-      </c>
-      <c r="D29" s="43" t="s">
-        <v>195</v>
-      </c>
-      <c r="E29" s="43"/>
-      <c r="F29" s="43" t="s">
+      <c r="B29" s="45" t="s">
         <v>196</v>
       </c>
-      <c r="G29" s="43"/>
-      <c r="H29" s="43"/>
+      <c r="C29" s="45" t="s">
+        <v>197</v>
+      </c>
+      <c r="D29" s="45" t="s">
+        <v>198</v>
+      </c>
+      <c r="E29" s="45"/>
+      <c r="F29" s="45" t="s">
+        <v>199</v>
+      </c>
+      <c r="G29" s="45"/>
+      <c r="H29" s="45"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="55" t="s">
-        <v>197</v>
-      </c>
-      <c r="C30" s="56" t="s">
-        <v>198</v>
-      </c>
-      <c r="D30" s="57" t="s">
-        <v>199</v>
-      </c>
-      <c r="E30" s="57"/>
-      <c r="F30" s="58" t="s">
+      <c r="B30" s="57" t="s">
         <v>200</v>
       </c>
-      <c r="G30" s="58"/>
-      <c r="H30" s="58"/>
+      <c r="C30" s="58" t="s">
+        <v>201</v>
+      </c>
+      <c r="D30" s="59" t="s">
+        <v>202</v>
+      </c>
+      <c r="E30" s="59"/>
+      <c r="F30" s="60" t="s">
+        <v>203</v>
+      </c>
+      <c r="G30" s="60"/>
+      <c r="H30" s="60"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="55" t="s">
+      <c r="B31" s="57" t="s">
+        <v>204</v>
+      </c>
+      <c r="C31" s="58" t="s">
         <v>201</v>
       </c>
-      <c r="C31" s="56" t="s">
-        <v>198</v>
-      </c>
-      <c r="D31" s="57" t="s">
-        <v>202</v>
-      </c>
-      <c r="E31" s="57"/>
-      <c r="F31" s="58" t="s">
-        <v>203</v>
-      </c>
-      <c r="G31" s="58"/>
-      <c r="H31" s="58"/>
+      <c r="D31" s="59" t="s">
+        <v>205</v>
+      </c>
+      <c r="E31" s="59"/>
+      <c r="F31" s="60" t="s">
+        <v>206</v>
+      </c>
+      <c r="G31" s="60"/>
+      <c r="H31" s="60"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="55" t="s">
-        <v>204</v>
-      </c>
-      <c r="C32" s="59" t="s">
-        <v>205</v>
-      </c>
-      <c r="D32" s="57" t="s">
-        <v>206</v>
-      </c>
-      <c r="E32" s="57"/>
-      <c r="F32" s="58" t="s">
+      <c r="B32" s="57" t="s">
         <v>207</v>
       </c>
-      <c r="G32" s="58"/>
-      <c r="H32" s="58"/>
+      <c r="C32" s="61" t="s">
+        <v>208</v>
+      </c>
+      <c r="D32" s="59" t="s">
+        <v>209</v>
+      </c>
+      <c r="E32" s="59"/>
+      <c r="F32" s="60" t="s">
+        <v>210</v>
+      </c>
+      <c r="G32" s="60"/>
+      <c r="H32" s="60"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="55" t="s">
-        <v>208</v>
-      </c>
-      <c r="C33" s="60" t="s">
-        <v>209</v>
-      </c>
-      <c r="D33" s="57" t="s">
-        <v>210</v>
-      </c>
-      <c r="E33" s="57"/>
-      <c r="F33" s="58" t="s">
+      <c r="B33" s="57" t="s">
         <v>211</v>
       </c>
-      <c r="G33" s="58"/>
-      <c r="H33" s="58"/>
+      <c r="C33" s="62" t="s">
+        <v>212</v>
+      </c>
+      <c r="D33" s="59" t="s">
+        <v>213</v>
+      </c>
+      <c r="E33" s="59"/>
+      <c r="F33" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="G33" s="60"/>
+      <c r="H33" s="60"/>
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="55" t="s">
+      <c r="B34" s="57" t="s">
+        <v>215</v>
+      </c>
+      <c r="C34" s="58" t="s">
+        <v>201</v>
+      </c>
+      <c r="D34" s="59" t="s">
+        <v>216</v>
+      </c>
+      <c r="E34" s="59"/>
+      <c r="F34" s="60" t="s">
+        <v>217</v>
+      </c>
+      <c r="G34" s="60"/>
+      <c r="H34" s="60"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="57" t="s">
+        <v>218</v>
+      </c>
+      <c r="C35" s="62" t="s">
         <v>212</v>
       </c>
-      <c r="C34" s="56" t="s">
-        <v>198</v>
-      </c>
-      <c r="D34" s="57" t="s">
-        <v>213</v>
-      </c>
-      <c r="E34" s="57"/>
-      <c r="F34" s="58" t="s">
-        <v>214</v>
-      </c>
-      <c r="G34" s="58"/>
-      <c r="H34" s="58"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="55" t="s">
-        <v>215</v>
-      </c>
-      <c r="C35" s="60" t="s">
-        <v>209</v>
-      </c>
-      <c r="D35" s="57" t="s">
-        <v>216</v>
-      </c>
-      <c r="E35" s="57"/>
-      <c r="F35" s="58" t="s">
-        <v>217</v>
-      </c>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
+      <c r="D35" s="59" t="s">
+        <v>219</v>
+      </c>
+      <c r="E35" s="59"/>
+      <c r="F35" s="60" t="s">
+        <v>220</v>
+      </c>
+      <c r="G35" s="60"/>
+      <c r="H35" s="60"/>
     </row>
     <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="55" t="s">
-        <v>218</v>
-      </c>
-      <c r="C36" s="56" t="s">
-        <v>198</v>
-      </c>
-      <c r="D36" s="57" t="s">
-        <v>219</v>
-      </c>
-      <c r="E36" s="57"/>
-      <c r="F36" s="58" t="s">
-        <v>220</v>
-      </c>
-      <c r="G36" s="58"/>
-      <c r="H36" s="58"/>
+      <c r="B36" s="57" t="s">
+        <v>221</v>
+      </c>
+      <c r="C36" s="58" t="s">
+        <v>201</v>
+      </c>
+      <c r="D36" s="59" t="s">
+        <v>222</v>
+      </c>
+      <c r="E36" s="59"/>
+      <c r="F36" s="60" t="s">
+        <v>223</v>
+      </c>
+      <c r="G36" s="60"/>
+      <c r="H36" s="60"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="55" t="s">
+      <c r="B38" s="57" t="s">
         <v>39</v>
       </c>
       <c r="C38" s="28" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D38" s="28"/>
       <c r="E38" s="28"/>
       <c r="F38" s="28"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="61" t="s">
-        <v>222</v>
-      </c>
-      <c r="C40" s="61"/>
-      <c r="D40" s="61"/>
-      <c r="E40" s="61"/>
-      <c r="F40" s="61"/>
-      <c r="G40" s="61"/>
-      <c r="H40" s="61"/>
+      <c r="B40" s="63" t="s">
+        <v>225</v>
+      </c>
+      <c r="C40" s="63"/>
+      <c r="D40" s="63"/>
+      <c r="E40" s="63"/>
+      <c r="F40" s="63"/>
+      <c r="G40" s="63"/>
+      <c r="H40" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -2556,10 +2638,10 @@
       <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C24&gt;=1</formula>
+      <formula>C24&gt;=1.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C24&lt;1</formula>
+      <formula>C24&lt;1.15</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
@@ -29,7 +29,7 @@
     <t>Civic Scholars Charter</t>
   </si>
   <si>
-    <t>Generated April 29, 2026 · nonprofit_501c3</t>
+    <t>Generated May 1, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -143,7 +143,7 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>Generated April 29, 2026</t>
+    <t>Generated May 1, 2026</t>
   </si>
   <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
@@ -29,7 +29,7 @@
     <t>Civic Scholars Charter</t>
   </si>
   <si>
-    <t>Generated May 1, 2026 · nonprofit_501c3</t>
+    <t>Generated May 7, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -143,7 +143,7 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>Generated May 1, 2026</t>
+    <t>Generated May 7, 2026</t>
   </si>
   <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>
@@ -1854,7 +1854,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H40"/>
+  <dimension ref="B2:I40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1864,7 +1864,7 @@
     <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>165</v>
       </c>
@@ -1874,8 +1874,9 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="12" t="s">
         <v>40</v>
       </c>
@@ -1885,6 +1886,7 @@
       <c r="F3" s="12"/>
       <c r="G3" s="12"/>
       <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="42" t="s">
@@ -2375,7 +2377,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="45" t="s">
         <v>196</v>
       </c>
@@ -2391,8 +2393,9 @@
       </c>
       <c r="G29" s="45"/>
       <c r="H29" s="45"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I29" s="45"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="57" t="s">
         <v>200</v>
       </c>
@@ -2408,8 +2411,9 @@
       </c>
       <c r="G30" s="60"/>
       <c r="H30" s="60"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I30" s="60"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="57" t="s">
         <v>204</v>
       </c>
@@ -2425,8 +2429,9 @@
       </c>
       <c r="G31" s="60"/>
       <c r="H31" s="60"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I31" s="60"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="57" t="s">
         <v>207</v>
       </c>
@@ -2442,8 +2447,9 @@
       </c>
       <c r="G32" s="60"/>
       <c r="H32" s="60"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I32" s="60"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33" s="57" t="s">
         <v>211</v>
       </c>
@@ -2459,8 +2465,9 @@
       </c>
       <c r="G33" s="60"/>
       <c r="H33" s="60"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I33" s="60"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="57" t="s">
         <v>215</v>
       </c>
@@ -2476,8 +2483,9 @@
       </c>
       <c r="G34" s="60"/>
       <c r="H34" s="60"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I34" s="60"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="57" t="s">
         <v>218</v>
       </c>
@@ -2493,8 +2501,9 @@
       </c>
       <c r="G35" s="60"/>
       <c r="H35" s="60"/>
-    </row>
-    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I35" s="60"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B36" s="57" t="s">
         <v>221</v>
       </c>
@@ -2510,6 +2519,7 @@
       </c>
       <c r="G36" s="60"/>
       <c r="H36" s="60"/>
+      <c r="I36" s="60"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" s="57" t="s">
@@ -2522,7 +2532,7 @@
       <c r="E38" s="28"/>
       <c r="F38" s="28"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B40" s="63" t="s">
         <v>225</v>
       </c>
@@ -2532,29 +2542,30 @@
       <c r="F40" s="63"/>
       <c r="G40" s="63"/>
       <c r="H40" s="63"/>
+      <c r="I40" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
     <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F29:I29"/>
     <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F30:I30"/>
     <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="F31:I31"/>
     <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F32:I32"/>
     <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F33:I33"/>
     <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F34:I34"/>
     <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F35:I35"/>
     <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="F36:I36"/>
     <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="B40:I40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -2946,7 +2957,7 @@
         <v>65</v>
       </c>
       <c r="D26" s="22">
-        <v>0.95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="3:4" x14ac:dyDescent="0.25">

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_Public_Funding.xlsx
@@ -10,18 +10,20 @@
     <sheet sheetId="4" name="Drivers" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="5-Year P&amp;L" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="Cash Flow &amp; DSCR" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Staffing" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="Loan Snapshot" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="Summary" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="Decision History" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="Financial Health" state="visible" r:id="rId14"/>
+    <sheet sheetId="7" name="AR &amp; Restricted Recon" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Staffing" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Loan Snapshot" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="Summary" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="Stress Tests" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="Decision History" state="visible" r:id="rId15"/>
+    <sheet sheetId="13" name="Financial Health" state="visible" r:id="rId16"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="261">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -29,7 +31,7 @@
     <t>Civic Scholars Charter</t>
   </si>
   <si>
-    <t>Generated May 7, 2026 · nonprofit_501c3</t>
+    <t>Generated May 9, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -143,7 +145,7 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>Generated May 7, 2026</t>
+    <t>Generated May 9, 2026</t>
   </si>
   <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>
@@ -398,7 +400,10 @@
     <t>Operating Margin</t>
   </si>
   <si>
-    <t>Capital &amp; Debt Service</t>
+    <t>Interest Expense</t>
+  </si>
+  <si>
+    <t>Principal &amp; Capital Outlays</t>
   </si>
   <si>
     <t>Net Income</t>
@@ -443,6 +448,42 @@
     <t>Ending Cash</t>
   </si>
   <si>
+    <t>AR Schedule &amp; Restricted-vs-Unrestricted Cash Recon</t>
+  </si>
+  <si>
+    <t>AR = year's collected tuition × 30-day weighted delay ÷ 365. Bad debt = contracted − collected.</t>
+  </si>
+  <si>
+    <t>Accounts Receivable Schedule</t>
+  </si>
+  <si>
+    <t>Contracted Tuition (gross)</t>
+  </si>
+  <si>
+    <t>Collected Tuition (cash-basis)</t>
+  </si>
+  <si>
+    <t>Bad Debt (contracted − collected)</t>
+  </si>
+  <si>
+    <t>Year-end AR Balance (30-day delay)</t>
+  </si>
+  <si>
+    <t>Restricted vs Unrestricted Cash</t>
+  </si>
+  <si>
+    <t>Total Cash Position (accrual)</t>
+  </si>
+  <si>
+    <t>Restricted Cash (capital/program-restricted)</t>
+  </si>
+  <si>
+    <t>Unrestricted Cash (DSCR/runway basis)</t>
+  </si>
+  <si>
+    <t>Note: DSCR and cash-runway covenants in this packet are computed off Unrestricted Cash (row 14). Restricted gifts cannot legally service debt and are excluded from coverage tests.</t>
+  </si>
+  <si>
     <t>Staffing Detail</t>
   </si>
   <si>
@@ -509,6 +550,78 @@
     <t>Generated by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
+    <t>Standard Lender Stress Tests</t>
+  </si>
+  <si>
+    <t>Five fixed downside scenarios re-run on the canonical engine. Identical figures appear on the founder dashboard, consultant view, and lender packet PDF.</t>
+  </si>
+  <si>
+    <t>Scenario</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Δ vs Base (Y1)</t>
+  </si>
+  <si>
+    <t>Base Case</t>
+  </si>
+  <si>
+    <t>Canonical engine output. All scenarios below are deltas vs this row.</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>DSCR</t>
+  </si>
+  <si>
+    <t>Break-Even Students</t>
+  </si>
+  <si>
+    <t>Cash Runway (mo)</t>
+  </si>
+  <si>
+    <t>Break-Even Year</t>
+  </si>
+  <si>
+    <t>Enrollment -10%</t>
+  </si>
+  <si>
+    <t>All five enrollment years scaled down by 10% — the standard lender enrollment-miss sensitivity.</t>
+  </si>
+  <si>
+    <t>+1y</t>
+  </si>
+  <si>
+    <t>Enrollment -20%</t>
+  </si>
+  <si>
+    <t>All five enrollment years scaled down by 20% — the stretch downside lenders use to confirm the school can survive a soft-launch.</t>
+  </si>
+  <si>
+    <t>ESA / Public Funding Delayed 3 Months</t>
+  </si>
+  <si>
+    <t>Year-1 ESA, school-choice, and public-funding receipts reduced by 25% (≈ 3 months delayed) to simulate a slow first disbursement.</t>
+  </si>
+  <si>
+    <t>0y</t>
+  </si>
+  <si>
+    <t>Rent Shock +25%</t>
+  </si>
+  <si>
+    <t>Occupancy &amp; facility expense rows escalated by 25% — covers a lease renewal, market-rate reset, or unbudgeted CAM/utilities surprise.</t>
+  </si>
+  <si>
+    <t>Founder Comp Normalized to Market</t>
+  </si>
+  <si>
+    <t>Founder compensation re-cast at the market-rate benchmark (with benefits + payroll tax). The lender / board view of true operating cost.</t>
+  </si>
+  <si>
     <t>Decision History</t>
   </si>
   <si>
@@ -530,9 +643,6 @@
     <t>○ Red = action needed</t>
   </si>
   <si>
-    <t>Metric</t>
-  </si>
-  <si>
     <t>Benchmark</t>
   </si>
   <si>
@@ -588,9 +698,6 @@
   </si>
   <si>
     <t>≥ 3 sources</t>
-  </si>
-  <si>
-    <t>DSCR</t>
   </si>
   <si>
     <t>≥ 1.25x</t>
@@ -711,7 +818,7 @@
     <numFmt numFmtId="166" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -803,6 +910,18 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF6B7280"/>
+      <sz val="9"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -942,7 +1061,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1006,6 +1125,13 @@
     <xf numFmtId="167" fontId="16" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="16" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1019,15 +1145,40 @@
     <xf numFmtId="3" fontId="16" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1061,7 +1212,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1070,13 +1221,13 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1788,6 +1939,1345 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="B1:C21"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="C1" s="13"/>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B3" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="25" t="str">
+        <f>Assumptions!D5</f>
+        <v>Civic Scholars Charter</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="25" t="str">
+        <f>Assumptions!D7</f>
+        <v>Charter School</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B5" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="25" t="str">
+        <f>Assumptions!D6</f>
+        <v>OH</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="25" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6" s="25">
+        <f>Assumptions!D8</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="26">
+        <f>Assumptions!D16</f>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="25" t="s">
+        <v>164</v>
+      </c>
+      <c r="C9" s="27">
+        <f>Drivers!G10</f>
+        <v>5244248.9932</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="C10" s="39">
+        <f>'5-Year P&amp;L'!G16</f>
+        <v>-2185451.67233774</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="40" t="s">
+        <v>166</v>
+      </c>
+      <c r="C12" s="23"/>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="25" t="s">
+        <v>167</v>
+      </c>
+      <c r="C13" s="41">
+        <f>IF(Drivers!G10&gt;0,'5-Year P&amp;L'!G21/Drivers!G10,0)</f>
+        <v>-0.4481626</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="25" t="s">
+        <v>168</v>
+      </c>
+      <c r="C14" s="31">
+        <f>IF(Drivers!G10&gt;0,Drivers!G16/Drivers!G10,0)</f>
+        <v>0.55578733</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="C15" s="27">
+        <f>IF(Assumptions!D16&gt;0,Drivers!G10/Assumptions!D16,0)</f>
+        <v>13111</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="C16" s="27">
+        <f>IF(Assumptions!D16&gt;0,('5-Year P&amp;L'!G12+'5-Year P&amp;L'!G13)/Assumptions!D16,0)</f>
+        <v>18574</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="C17" s="34">
+        <f>'Cash Flow &amp; DSCR'!C11</f>
+        <v>-1.86966739</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="C18" s="34">
+        <f>'Cash Flow &amp; DSCR'!G11</f>
+        <v>-13.25925622</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="25" t="s">
+        <v>173</v>
+      </c>
+      <c r="C19" s="42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="C21" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="B21:C21"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FFD97706"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H57"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="8" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="43" t="s">
+        <v>175</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="44" t="s">
+        <v>176</v>
+      </c>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="45" t="s">
+        <v>177</v>
+      </c>
+      <c r="B4" s="45" t="s">
+        <v>178</v>
+      </c>
+      <c r="C4" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" s="46" t="s">
+        <v>97</v>
+      </c>
+      <c r="E4" s="46" t="s">
+        <v>98</v>
+      </c>
+      <c r="F4" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="G4" s="46" t="s">
+        <v>100</v>
+      </c>
+      <c r="H4" s="46" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="48" t="s">
+        <v>181</v>
+      </c>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7" s="27">
+        <v>-418531.68855451304</v>
+      </c>
+      <c r="D7" s="27">
+        <v>66514.89477882069</v>
+      </c>
+      <c r="E7" s="27">
+        <v>708232.4947788208</v>
+      </c>
+      <c r="F7" s="27">
+        <v>1202306.8627788206</v>
+      </c>
+      <c r="G7" s="27">
+        <v>1446208.9918188206</v>
+      </c>
+      <c r="H7" s="49" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="C8" s="26">
+        <v>-7.4</v>
+      </c>
+      <c r="D8" s="26">
+        <v>2.33</v>
+      </c>
+      <c r="E8" s="26">
+        <v>15.21</v>
+      </c>
+      <c r="F8" s="26">
+        <v>25.13</v>
+      </c>
+      <c r="G8" s="26">
+        <v>30.03</v>
+      </c>
+      <c r="H8" s="49" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="C9" s="27">
+        <v>-368531.68855451304</v>
+      </c>
+      <c r="D9" s="27">
+        <v>-302016.79377569235</v>
+      </c>
+      <c r="E9" s="27">
+        <v>406215.70100312843</v>
+      </c>
+      <c r="F9" s="27">
+        <v>1608522.563781949</v>
+      </c>
+      <c r="G9" s="27">
+        <v>3054731.55560077</v>
+      </c>
+      <c r="H9" s="49" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="C10" s="26">
+        <v>156</v>
+      </c>
+      <c r="D10" s="26">
+        <v>190</v>
+      </c>
+      <c r="E10" s="26">
+        <v>225</v>
+      </c>
+      <c r="F10" s="26">
+        <v>251</v>
+      </c>
+      <c r="G10" s="26">
+        <v>254</v>
+      </c>
+      <c r="H10" s="49" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="C11" s="26">
+        <v>3</v>
+      </c>
+      <c r="D11" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="H11" s="51" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="C12" s="52" t="s">
+        <v>97</v>
+      </c>
+      <c r="D12" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="H12" s="49" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="47" t="s">
+        <v>187</v>
+      </c>
+      <c r="B14" s="47"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="47"/>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="48" t="s">
+        <v>188</v>
+      </c>
+      <c r="B15" s="48"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="48"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="C16" s="27">
+        <v>-481140.85522117955</v>
+      </c>
+      <c r="D16" s="27">
+        <v>-50167.105221179314</v>
+      </c>
+      <c r="E16" s="27">
+        <v>528349.4947788208</v>
+      </c>
+      <c r="F16" s="27">
+        <v>984852.8627788206</v>
+      </c>
+      <c r="G16" s="27">
+        <v>1192844.9918188206</v>
+      </c>
+      <c r="H16" s="32">
+        <v>-62609.16666666651</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="C17" s="26">
+        <v>-8.66</v>
+      </c>
+      <c r="D17" s="26">
+        <v>-0.01</v>
+      </c>
+      <c r="E17" s="26">
+        <v>11.6</v>
+      </c>
+      <c r="F17" s="26">
+        <v>20.77</v>
+      </c>
+      <c r="G17" s="26">
+        <v>24.94</v>
+      </c>
+      <c r="H17" s="51">
+        <v>-1.2599999999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="C18" s="27">
+        <v>-431140.85522117955</v>
+      </c>
+      <c r="D18" s="27">
+        <v>-481307.96044235886</v>
+      </c>
+      <c r="E18" s="27">
+        <v>47041.53433646192</v>
+      </c>
+      <c r="F18" s="27">
+        <v>1031894.3971152825</v>
+      </c>
+      <c r="G18" s="27">
+        <v>2224739.388934103</v>
+      </c>
+      <c r="H18" s="32">
+        <v>-62609.16666666651</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="C19" s="26">
+        <v>151</v>
+      </c>
+      <c r="D19" s="26">
+        <v>182</v>
+      </c>
+      <c r="E19" s="26">
+        <v>213</v>
+      </c>
+      <c r="F19" s="26">
+        <v>236</v>
+      </c>
+      <c r="G19" s="26">
+        <v>240</v>
+      </c>
+      <c r="H19" s="51">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="C20" s="26">
+        <v>3</v>
+      </c>
+      <c r="D20" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="G20" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="H20" s="51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="C21" s="52" t="s">
+        <v>98</v>
+      </c>
+      <c r="D21" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="G21" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="H21" s="49" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="47" t="s">
+        <v>190</v>
+      </c>
+      <c r="B23" s="47"/>
+      <c r="C23" s="47"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="47"/>
+      <c r="H23" s="47"/>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="48" t="s">
+        <v>191</v>
+      </c>
+      <c r="B24" s="48"/>
+      <c r="C24" s="48"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="48"/>
+      <c r="H24" s="48"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="C25" s="27">
+        <v>-543750.0218878458</v>
+      </c>
+      <c r="D25" s="27">
+        <v>-166849.1052211793</v>
+      </c>
+      <c r="E25" s="27">
+        <v>348466.4947788208</v>
+      </c>
+      <c r="F25" s="27">
+        <v>722439.8627788206</v>
+      </c>
+      <c r="G25" s="27">
+        <v>904211.9918188206</v>
+      </c>
+      <c r="H25" s="32">
+        <v>-125218.33333333279</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="C26" s="26">
+        <v>-9.91</v>
+      </c>
+      <c r="D26" s="26">
+        <v>-2.35</v>
+      </c>
+      <c r="E26" s="26">
+        <v>7.99</v>
+      </c>
+      <c r="F26" s="26">
+        <v>15.5</v>
+      </c>
+      <c r="G26" s="26">
+        <v>19.15</v>
+      </c>
+      <c r="H26" s="51">
+        <v>-2.51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="C27" s="27">
+        <v>-493750.0218878458</v>
+      </c>
+      <c r="D27" s="27">
+        <v>-660599.1271090251</v>
+      </c>
+      <c r="E27" s="27">
+        <v>-312132.63233020436</v>
+      </c>
+      <c r="F27" s="27">
+        <v>410307.2304486162</v>
+      </c>
+      <c r="G27" s="27">
+        <v>1314519.2222674368</v>
+      </c>
+      <c r="H27" s="32">
+        <v>-125218.33333333279</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="C28" s="26">
+        <v>145</v>
+      </c>
+      <c r="D28" s="26">
+        <v>173</v>
+      </c>
+      <c r="E28" s="26">
+        <v>201</v>
+      </c>
+      <c r="F28" s="26">
+        <v>225</v>
+      </c>
+      <c r="G28" s="26">
+        <v>229</v>
+      </c>
+      <c r="H28" s="51">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="C29" s="26">
+        <v>3</v>
+      </c>
+      <c r="D29" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="G29" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="H29" s="51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="C30" s="52" t="s">
+        <v>98</v>
+      </c>
+      <c r="D30" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="F30" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="G30" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="H30" s="49" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="47" t="s">
+        <v>192</v>
+      </c>
+      <c r="B32" s="47"/>
+      <c r="C32" s="47"/>
+      <c r="D32" s="47"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="47"/>
+      <c r="H32" s="47"/>
+    </row>
+    <row r="33" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="48" t="s">
+        <v>193</v>
+      </c>
+      <c r="B33" s="48"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="48"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="48"/>
+      <c r="G33" s="48"/>
+      <c r="H33" s="48"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="C34" s="27">
+        <v>-706031.6885545129</v>
+      </c>
+      <c r="D34" s="27">
+        <v>66514.89477882069</v>
+      </c>
+      <c r="E34" s="27">
+        <v>708232.4947788208</v>
+      </c>
+      <c r="F34" s="27">
+        <v>1202306.8627788206</v>
+      </c>
+      <c r="G34" s="27">
+        <v>1446208.9918188206</v>
+      </c>
+      <c r="H34" s="32">
+        <v>-287499.9999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="C35" s="26">
+        <v>-13.17</v>
+      </c>
+      <c r="D35" s="26">
+        <v>2.33</v>
+      </c>
+      <c r="E35" s="26">
+        <v>15.21</v>
+      </c>
+      <c r="F35" s="26">
+        <v>25.13</v>
+      </c>
+      <c r="G35" s="26">
+        <v>30.03</v>
+      </c>
+      <c r="H35" s="51">
+        <v>-5.77</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="C36" s="27">
+        <v>-656031.6885545129</v>
+      </c>
+      <c r="D36" s="27">
+        <v>-589516.7937756922</v>
+      </c>
+      <c r="E36" s="27">
+        <v>118715.70100312855</v>
+      </c>
+      <c r="F36" s="27">
+        <v>1321022.5637819492</v>
+      </c>
+      <c r="G36" s="27">
+        <v>2767231.55560077</v>
+      </c>
+      <c r="H36" s="32">
+        <v>-287499.9999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="C37" s="26">
+        <v>216</v>
+      </c>
+      <c r="D37" s="26">
+        <v>190</v>
+      </c>
+      <c r="E37" s="26">
+        <v>225</v>
+      </c>
+      <c r="F37" s="26">
+        <v>251</v>
+      </c>
+      <c r="G37" s="26">
+        <v>254</v>
+      </c>
+      <c r="H37" s="51">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="C38" s="26">
+        <v>2</v>
+      </c>
+      <c r="D38" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="F38" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="G38" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="H38" s="51">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="C39" s="52" t="s">
+        <v>97</v>
+      </c>
+      <c r="D39" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="E39" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="F39" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="G39" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="H39" s="49" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="47" t="s">
+        <v>195</v>
+      </c>
+      <c r="B41" s="47"/>
+      <c r="C41" s="47"/>
+      <c r="D41" s="47"/>
+      <c r="E41" s="47"/>
+      <c r="F41" s="47"/>
+      <c r="G41" s="47"/>
+      <c r="H41" s="47"/>
+    </row>
+    <row r="42" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="48" t="s">
+        <v>196</v>
+      </c>
+      <c r="B42" s="48"/>
+      <c r="C42" s="48"/>
+      <c r="D42" s="48"/>
+      <c r="E42" s="48"/>
+      <c r="F42" s="48"/>
+      <c r="G42" s="48"/>
+      <c r="H42" s="48"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="C43" s="27">
+        <v>-477281.68855451304</v>
+      </c>
+      <c r="D43" s="27">
+        <v>-6100.105221179314</v>
+      </c>
+      <c r="E43" s="27">
+        <v>633440.8947788207</v>
+      </c>
+      <c r="F43" s="27">
+        <v>1125269.3547788206</v>
+      </c>
+      <c r="G43" s="27">
+        <v>1366860.7660788205</v>
+      </c>
+      <c r="H43" s="32">
+        <v>-58750</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="C44" s="26">
+        <v>-8.58</v>
+      </c>
+      <c r="D44" s="26">
+        <v>0.88</v>
+      </c>
+      <c r="E44" s="26">
+        <v>13.71</v>
+      </c>
+      <c r="F44" s="26">
+        <v>23.58</v>
+      </c>
+      <c r="G44" s="26">
+        <v>28.43</v>
+      </c>
+      <c r="H44" s="51">
+        <v>-1.1799999999999997</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B45" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="C45" s="27">
+        <v>-427281.68855451304</v>
+      </c>
+      <c r="D45" s="27">
+        <v>-433381.79377569235</v>
+      </c>
+      <c r="E45" s="27">
+        <v>200059.10100312834</v>
+      </c>
+      <c r="F45" s="27">
+        <v>1325328.455781949</v>
+      </c>
+      <c r="G45" s="27">
+        <v>2692189.221860769</v>
+      </c>
+      <c r="H45" s="32">
+        <v>-58750</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="C46" s="26">
+        <v>163</v>
+      </c>
+      <c r="D46" s="26">
+        <v>197</v>
+      </c>
+      <c r="E46" s="26">
+        <v>232</v>
+      </c>
+      <c r="F46" s="26">
+        <v>259</v>
+      </c>
+      <c r="G46" s="26">
+        <v>262</v>
+      </c>
+      <c r="H46" s="51">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="B47" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="C47" s="26">
+        <v>3</v>
+      </c>
+      <c r="D47" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="E47" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="F47" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="G47" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="H47" s="51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="C48" s="52" t="s">
+        <v>98</v>
+      </c>
+      <c r="D48" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="E48" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="F48" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="G48" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="H48" s="49" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="47" t="s">
+        <v>197</v>
+      </c>
+      <c r="B50" s="47"/>
+      <c r="C50" s="47"/>
+      <c r="D50" s="47"/>
+      <c r="E50" s="47"/>
+      <c r="F50" s="47"/>
+      <c r="G50" s="47"/>
+      <c r="H50" s="47"/>
+    </row>
+    <row r="51" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="48" t="s">
+        <v>198</v>
+      </c>
+      <c r="B51" s="48"/>
+      <c r="C51" s="48"/>
+      <c r="D51" s="48"/>
+      <c r="E51" s="48"/>
+      <c r="F51" s="48"/>
+      <c r="G51" s="48"/>
+      <c r="H51" s="48"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="C52" s="27">
+        <v>-398184.18855451304</v>
+      </c>
+      <c r="D52" s="27">
+        <v>52949.894778820686</v>
+      </c>
+      <c r="E52" s="27">
+        <v>653972.4947788208</v>
+      </c>
+      <c r="F52" s="27">
+        <v>1148046.8627788206</v>
+      </c>
+      <c r="G52" s="27">
+        <v>1391948.9918188206</v>
+      </c>
+      <c r="H52" s="32">
+        <v>20347.5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B53" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="C53" s="26">
+        <v>-6.99</v>
+      </c>
+      <c r="D53" s="26">
+        <v>2.06</v>
+      </c>
+      <c r="E53" s="26">
+        <v>14.13</v>
+      </c>
+      <c r="F53" s="26">
+        <v>24.04</v>
+      </c>
+      <c r="G53" s="26">
+        <v>28.94</v>
+      </c>
+      <c r="H53" s="51">
+        <v>0.41000000000000014</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="C54" s="27">
+        <v>-368531.68855451304</v>
+      </c>
+      <c r="D54" s="27">
+        <v>-302016.79377569235</v>
+      </c>
+      <c r="E54" s="27">
+        <v>406215.70100312843</v>
+      </c>
+      <c r="F54" s="27">
+        <v>1608522.563781949</v>
+      </c>
+      <c r="G54" s="27">
+        <v>3054731.55560077</v>
+      </c>
+      <c r="H54" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="C55" s="26">
+        <v>156</v>
+      </c>
+      <c r="D55" s="26">
+        <v>190</v>
+      </c>
+      <c r="E55" s="26">
+        <v>225</v>
+      </c>
+      <c r="F55" s="26">
+        <v>251</v>
+      </c>
+      <c r="G55" s="26">
+        <v>254</v>
+      </c>
+      <c r="H55" s="51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="B56" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="C56" s="26">
+        <v>3</v>
+      </c>
+      <c r="D56" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="E56" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="F56" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="G56" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="H56" s="51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="B57" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="C57" s="52" t="s">
+        <v>97</v>
+      </c>
+      <c r="D57" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="E57" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="F57" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="G57" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="H57" s="49" t="s">
+        <v>194</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="A51:H51"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF328555"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="B1:H4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -1803,7 +3293,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>162</v>
+        <v>199</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -1813,26 +3303,26 @@
       <c r="H1" s="13"/>
     </row>
     <row r="2" ht="60" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
+      <c r="B2" s="53" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
     </row>
     <row r="4" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="41" t="s">
-        <v>164</v>
-      </c>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
+      <c r="B4" s="37" t="s">
+        <v>201</v>
+      </c>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1848,7 +3338,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF328555"/>
@@ -1866,7 +3356,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>165</v>
+        <v>202</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1889,37 +3379,37 @@
       <c r="I3" s="12"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="42" t="s">
-        <v>166</v>
-      </c>
-      <c r="D4" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="F4" s="44" t="s">
-        <v>168</v>
+      <c r="B4" s="54" t="s">
+        <v>203</v>
+      </c>
+      <c r="D4" s="55" t="s">
+        <v>204</v>
+      </c>
+      <c r="F4" s="56" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="45" t="s">
-        <v>169</v>
-      </c>
-      <c r="C6" s="46" t="s">
+      <c r="B6" s="57" t="s">
+        <v>178</v>
+      </c>
+      <c r="C6" s="58" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="46" t="s">
+      <c r="D6" s="58" t="s">
         <v>97</v>
       </c>
-      <c r="E6" s="46" t="s">
+      <c r="E6" s="58" t="s">
         <v>98</v>
       </c>
-      <c r="F6" s="46" t="s">
+      <c r="F6" s="58" t="s">
         <v>99</v>
       </c>
-      <c r="G6" s="46" t="s">
+      <c r="G6" s="58" t="s">
         <v>100</v>
       </c>
-      <c r="H6" s="46" t="s">
-        <v>170</v>
+      <c r="H6" s="58" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -1944,7 +3434,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="25" t="s">
-        <v>171</v>
+        <v>207</v>
       </c>
       <c r="C8" s="27">
         <v>1546000</v>
@@ -1964,7 +3454,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="25" t="s">
-        <v>172</v>
+        <v>208</v>
       </c>
       <c r="C9" s="27">
         <v>1200167.1888888888</v>
@@ -1984,7 +3474,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="25" t="s">
-        <v>173</v>
+        <v>209</v>
       </c>
       <c r="C10" s="27">
         <v>654000</v>
@@ -2004,7 +3494,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="25" t="s">
-        <v>174</v>
+        <v>210</v>
       </c>
       <c r="C11" s="27">
         <v>164824.60522117943</v>
@@ -2024,7 +3514,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C12" s="30">
         <v>-472991.79411006824</v>
@@ -2044,7 +3534,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="28" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C13" s="30">
         <v>-472991.79411006824</v>
@@ -2064,50 +3554,50 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="C14" s="47">
+        <v>128</v>
+      </c>
+      <c r="C14" s="59">
         <v>-0.3059455330595525</v>
       </c>
-      <c r="D14" s="47">
+      <c r="D14" s="59">
         <v>-0.10427042130500674</v>
       </c>
-      <c r="E14" s="47">
+      <c r="E14" s="59">
         <v>-0.046066008479458874</v>
       </c>
-      <c r="F14" s="47">
+      <c r="F14" s="59">
         <v>-0.16504185604249857</v>
       </c>
-      <c r="G14" s="47">
+      <c r="G14" s="59">
         <v>-0.44816260261601254</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="28" t="s">
-        <v>175</v>
-      </c>
-      <c r="C15" s="48">
+        <v>211</v>
+      </c>
+      <c r="C15" s="60">
         <v>12883.333333333334</v>
       </c>
-      <c r="D15" s="48">
+      <c r="D15" s="60">
         <v>12689</v>
       </c>
-      <c r="E15" s="48">
+      <c r="E15" s="60">
         <v>12716.203333333333</v>
       </c>
-      <c r="F15" s="48">
+      <c r="F15" s="60">
         <v>12878.376766666668</v>
       </c>
-      <c r="G15" s="48">
+      <c r="G15" s="60">
         <v>13110.622483</v>
       </c>
-      <c r="H15" s="49" t="s">
-        <v>176</v>
+      <c r="H15" s="61" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="28" t="s">
-        <v>177</v>
+        <v>213</v>
       </c>
       <c r="C16" s="32">
         <v>16824.9316175839</v>
@@ -2127,7 +3617,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="25" t="s">
-        <v>178</v>
+        <v>214</v>
       </c>
       <c r="C17" s="27">
         <v>700</v>
@@ -2147,402 +3637,402 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="25" t="s">
-        <v>179</v>
-      </c>
-      <c r="C18" s="50">
+        <v>215</v>
+      </c>
+      <c r="C18" s="62">
         <v>2350</v>
       </c>
-      <c r="D18" s="48">
+      <c r="D18" s="60">
         <v>1452.3</v>
       </c>
-      <c r="E18" s="48">
+      <c r="E18" s="60">
         <v>997.246</v>
       </c>
-      <c r="F18" s="48">
+      <c r="F18" s="60">
         <v>821.7307040000001</v>
       </c>
-      <c r="G18" s="48">
+      <c r="G18" s="60">
         <v>793.4837110500001</v>
       </c>
-      <c r="H18" s="49" t="s">
-        <v>180</v>
+      <c r="H18" s="61" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="28" t="s">
-        <v>181</v>
-      </c>
-      <c r="C19" s="36">
+        <v>217</v>
+      </c>
+      <c r="C19" s="39">
         <v>-3941.5982842505687</v>
       </c>
-      <c r="D19" s="36">
+      <c r="D19" s="39">
         <v>-1323.0873759392305</v>
       </c>
-      <c r="E19" s="36">
+      <c r="E19" s="39">
         <v>-585.7847305798565</v>
       </c>
-      <c r="F19" s="36">
+      <c r="F19" s="39">
         <v>-2125.4712043852587</v>
       </c>
-      <c r="G19" s="36">
+      <c r="G19" s="39">
         <v>-5875.690693897288</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="C20" s="47">
+        <v>218</v>
+      </c>
+      <c r="C20" s="59">
         <v>0.7763047793589191</v>
       </c>
-      <c r="D20" s="47">
+      <c r="D20" s="59">
         <v>0.6515878070113221</v>
       </c>
-      <c r="E20" s="51">
+      <c r="E20" s="63">
         <v>0.5752710583855843</v>
       </c>
-      <c r="F20" s="51">
+      <c r="F20" s="63">
         <v>0.5597527709991174</v>
       </c>
-      <c r="G20" s="51">
+      <c r="G20" s="63">
         <v>0.5557873295275215</v>
       </c>
-      <c r="H20" s="49" t="s">
-        <v>183</v>
+      <c r="H20" s="61" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="C21" s="51">
+        <v>220</v>
+      </c>
+      <c r="C21" s="63">
         <v>0.18240620957309184</v>
       </c>
-      <c r="D21" s="52">
+      <c r="D21" s="64">
         <v>0.11445346362991568</v>
       </c>
-      <c r="E21" s="52">
+      <c r="E21" s="64">
         <v>0.07842325054569485</v>
       </c>
-      <c r="F21" s="52">
+      <c r="F21" s="64">
         <v>0.06380700913541373</v>
       </c>
-      <c r="G21" s="52">
+      <c r="G21" s="64">
         <v>0.06052219961934512</v>
       </c>
-      <c r="H21" s="49" t="s">
-        <v>185</v>
+      <c r="H21" s="61" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="C22" s="47">
+      <c r="C22" s="59">
         <v>-0.19933194624119585</v>
       </c>
-      <c r="D22" s="47">
+      <c r="D22" s="59">
         <v>-0.039322590419523434</v>
       </c>
-      <c r="E22" s="47">
+      <c r="E22" s="59">
         <v>-0.0028600816524580494</v>
       </c>
-      <c r="F22" s="47">
+      <c r="F22" s="59">
         <v>-0.13091237772754036</v>
       </c>
-      <c r="G22" s="47">
+      <c r="G22" s="59">
         <v>-0.4167330108031714</v>
       </c>
-      <c r="H22" s="49" t="s">
-        <v>186</v>
+      <c r="H22" s="61" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="28" t="s">
-        <v>187</v>
-      </c>
-      <c r="C23" s="53">
+        <v>223</v>
+      </c>
+      <c r="C23" s="65">
         <v>3</v>
       </c>
-      <c r="D23" s="53">
+      <c r="D23" s="65">
         <v>3</v>
       </c>
-      <c r="E23" s="53">
+      <c r="E23" s="65">
         <v>3</v>
       </c>
-      <c r="F23" s="53">
+      <c r="F23" s="65">
         <v>3</v>
       </c>
-      <c r="G23" s="53">
+      <c r="G23" s="65">
         <v>3</v>
       </c>
-      <c r="H23" s="49" t="s">
-        <v>188</v>
+      <c r="H23" s="61" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="28" t="s">
-        <v>189</v>
-      </c>
-      <c r="C24" s="54">
+        <v>183</v>
+      </c>
+      <c r="C24" s="66">
         <v>-1.8696673865856184</v>
       </c>
-      <c r="D24" s="54">
+      <c r="D24" s="66">
         <v>-0.6054488638559378</v>
       </c>
-      <c r="E24" s="54">
+      <c r="E24" s="66">
         <v>-0.06619651197184098</v>
       </c>
-      <c r="F24" s="54">
+      <c r="F24" s="66">
         <v>-3.8357567765741165</v>
       </c>
-      <c r="G24" s="54">
+      <c r="G24" s="66">
         <v>-13.259256222122064</v>
       </c>
-      <c r="H24" s="49" t="s">
-        <v>190</v>
+      <c r="H24" s="61" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="28" t="s">
-        <v>191</v>
-      </c>
-      <c r="C25" s="55" t="str">
+        <v>226</v>
+      </c>
+      <c r="C25" s="67" t="str">
         <f>IF('5-Year P&amp;L'!C24&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D25" s="55" t="str">
+      <c r="D25" s="67" t="str">
         <f>IF(AND('5-Year P&amp;L'!D24&gt;=0,'5-Year P&amp;L'!C24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E25" s="55" t="str">
+      <c r="E25" s="67" t="str">
         <f>IF(AND('5-Year P&amp;L'!E24&gt;=0,'5-Year P&amp;L'!D24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F25" s="55" t="str">
+      <c r="F25" s="67" t="str">
         <f>IF(AND('5-Year P&amp;L'!F24&gt;=0,'5-Year P&amp;L'!E24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G25" s="55" t="str">
+      <c r="G25" s="67" t="str">
         <f>IF(AND('5-Year P&amp;L'!G24&gt;=0,'5-Year P&amp;L'!F24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H25" s="49" t="s">
+      <c r="H25" s="61" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="28" t="s">
-        <v>192</v>
-      </c>
-      <c r="C26" s="56">
+        <v>227</v>
+      </c>
+      <c r="C26" s="68">
         <v>-3</v>
       </c>
-      <c r="D26" s="56">
+      <c r="D26" s="68">
         <v>-3</v>
       </c>
-      <c r="E26" s="56">
+      <c r="E26" s="68">
         <v>-3</v>
       </c>
-      <c r="F26" s="56">
+      <c r="F26" s="68">
         <v>-4</v>
       </c>
-      <c r="G26" s="56">
+      <c r="G26" s="68">
         <v>-6</v>
       </c>
-      <c r="H26" s="49" t="s">
-        <v>193</v>
+      <c r="H26" s="61" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="28" t="s">
-        <v>194</v>
-      </c>
-      <c r="C27" s="56">
-        <v>0</v>
-      </c>
-      <c r="D27" s="56">
-        <v>0</v>
-      </c>
-      <c r="E27" s="56">
-        <v>0</v>
-      </c>
-      <c r="F27" s="56">
-        <v>0</v>
-      </c>
-      <c r="G27" s="56">
-        <v>0</v>
-      </c>
-      <c r="H27" s="49" t="s">
-        <v>195</v>
+        <v>229</v>
+      </c>
+      <c r="C27" s="68">
+        <v>0</v>
+      </c>
+      <c r="D27" s="68">
+        <v>0</v>
+      </c>
+      <c r="E27" s="68">
+        <v>0</v>
+      </c>
+      <c r="F27" s="68">
+        <v>0</v>
+      </c>
+      <c r="G27" s="68">
+        <v>0</v>
+      </c>
+      <c r="H27" s="61" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B29" s="45" t="s">
-        <v>196</v>
-      </c>
-      <c r="C29" s="45" t="s">
-        <v>197</v>
-      </c>
-      <c r="D29" s="45" t="s">
-        <v>198</v>
-      </c>
-      <c r="E29" s="45"/>
-      <c r="F29" s="45" t="s">
-        <v>199</v>
-      </c>
-      <c r="G29" s="45"/>
-      <c r="H29" s="45"/>
-      <c r="I29" s="45"/>
+      <c r="B29" s="57" t="s">
+        <v>231</v>
+      </c>
+      <c r="C29" s="57" t="s">
+        <v>232</v>
+      </c>
+      <c r="D29" s="57" t="s">
+        <v>233</v>
+      </c>
+      <c r="E29" s="57"/>
+      <c r="F29" s="57" t="s">
+        <v>234</v>
+      </c>
+      <c r="G29" s="57"/>
+      <c r="H29" s="57"/>
+      <c r="I29" s="57"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B30" s="57" t="s">
-        <v>200</v>
-      </c>
-      <c r="C30" s="58" t="s">
-        <v>201</v>
-      </c>
-      <c r="D30" s="59" t="s">
-        <v>202</v>
-      </c>
-      <c r="E30" s="59"/>
-      <c r="F30" s="60" t="s">
-        <v>203</v>
-      </c>
-      <c r="G30" s="60"/>
-      <c r="H30" s="60"/>
-      <c r="I30" s="60"/>
+      <c r="B30" s="69" t="s">
+        <v>235</v>
+      </c>
+      <c r="C30" s="70" t="s">
+        <v>236</v>
+      </c>
+      <c r="D30" s="71" t="s">
+        <v>237</v>
+      </c>
+      <c r="E30" s="71"/>
+      <c r="F30" s="72" t="s">
+        <v>238</v>
+      </c>
+      <c r="G30" s="72"/>
+      <c r="H30" s="72"/>
+      <c r="I30" s="72"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B31" s="57" t="s">
-        <v>204</v>
-      </c>
-      <c r="C31" s="58" t="s">
-        <v>201</v>
-      </c>
-      <c r="D31" s="59" t="s">
-        <v>205</v>
-      </c>
-      <c r="E31" s="59"/>
-      <c r="F31" s="60" t="s">
-        <v>206</v>
-      </c>
-      <c r="G31" s="60"/>
-      <c r="H31" s="60"/>
-      <c r="I31" s="60"/>
+      <c r="B31" s="69" t="s">
+        <v>239</v>
+      </c>
+      <c r="C31" s="70" t="s">
+        <v>236</v>
+      </c>
+      <c r="D31" s="71" t="s">
+        <v>240</v>
+      </c>
+      <c r="E31" s="71"/>
+      <c r="F31" s="72" t="s">
+        <v>241</v>
+      </c>
+      <c r="G31" s="72"/>
+      <c r="H31" s="72"/>
+      <c r="I31" s="72"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B32" s="57" t="s">
-        <v>207</v>
-      </c>
-      <c r="C32" s="61" t="s">
-        <v>208</v>
-      </c>
-      <c r="D32" s="59" t="s">
-        <v>209</v>
-      </c>
-      <c r="E32" s="59"/>
-      <c r="F32" s="60" t="s">
-        <v>210</v>
-      </c>
-      <c r="G32" s="60"/>
-      <c r="H32" s="60"/>
-      <c r="I32" s="60"/>
+      <c r="B32" s="69" t="s">
+        <v>242</v>
+      </c>
+      <c r="C32" s="73" t="s">
+        <v>243</v>
+      </c>
+      <c r="D32" s="71" t="s">
+        <v>244</v>
+      </c>
+      <c r="E32" s="71"/>
+      <c r="F32" s="72" t="s">
+        <v>245</v>
+      </c>
+      <c r="G32" s="72"/>
+      <c r="H32" s="72"/>
+      <c r="I32" s="72"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B33" s="57" t="s">
-        <v>211</v>
-      </c>
-      <c r="C33" s="62" t="s">
-        <v>212</v>
-      </c>
-      <c r="D33" s="59" t="s">
-        <v>213</v>
-      </c>
-      <c r="E33" s="59"/>
-      <c r="F33" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="G33" s="60"/>
-      <c r="H33" s="60"/>
-      <c r="I33" s="60"/>
+      <c r="B33" s="69" t="s">
+        <v>246</v>
+      </c>
+      <c r="C33" s="74" t="s">
+        <v>247</v>
+      </c>
+      <c r="D33" s="71" t="s">
+        <v>248</v>
+      </c>
+      <c r="E33" s="71"/>
+      <c r="F33" s="72" t="s">
+        <v>249</v>
+      </c>
+      <c r="G33" s="72"/>
+      <c r="H33" s="72"/>
+      <c r="I33" s="72"/>
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B34" s="57" t="s">
-        <v>215</v>
-      </c>
-      <c r="C34" s="58" t="s">
-        <v>201</v>
-      </c>
-      <c r="D34" s="59" t="s">
-        <v>216</v>
-      </c>
-      <c r="E34" s="59"/>
-      <c r="F34" s="60" t="s">
-        <v>217</v>
-      </c>
-      <c r="G34" s="60"/>
-      <c r="H34" s="60"/>
-      <c r="I34" s="60"/>
+      <c r="B34" s="69" t="s">
+        <v>250</v>
+      </c>
+      <c r="C34" s="70" t="s">
+        <v>236</v>
+      </c>
+      <c r="D34" s="71" t="s">
+        <v>251</v>
+      </c>
+      <c r="E34" s="71"/>
+      <c r="F34" s="72" t="s">
+        <v>252</v>
+      </c>
+      <c r="G34" s="72"/>
+      <c r="H34" s="72"/>
+      <c r="I34" s="72"/>
     </row>
     <row r="35" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B35" s="57" t="s">
-        <v>218</v>
-      </c>
-      <c r="C35" s="62" t="s">
-        <v>212</v>
-      </c>
-      <c r="D35" s="59" t="s">
-        <v>219</v>
-      </c>
-      <c r="E35" s="59"/>
-      <c r="F35" s="60" t="s">
-        <v>220</v>
-      </c>
-      <c r="G35" s="60"/>
-      <c r="H35" s="60"/>
-      <c r="I35" s="60"/>
+      <c r="B35" s="69" t="s">
+        <v>253</v>
+      </c>
+      <c r="C35" s="74" t="s">
+        <v>247</v>
+      </c>
+      <c r="D35" s="71" t="s">
+        <v>254</v>
+      </c>
+      <c r="E35" s="71"/>
+      <c r="F35" s="72" t="s">
+        <v>255</v>
+      </c>
+      <c r="G35" s="72"/>
+      <c r="H35" s="72"/>
+      <c r="I35" s="72"/>
     </row>
     <row r="36" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B36" s="57" t="s">
-        <v>221</v>
-      </c>
-      <c r="C36" s="58" t="s">
-        <v>201</v>
-      </c>
-      <c r="D36" s="59" t="s">
-        <v>222</v>
-      </c>
-      <c r="E36" s="59"/>
-      <c r="F36" s="60" t="s">
-        <v>223</v>
-      </c>
-      <c r="G36" s="60"/>
-      <c r="H36" s="60"/>
-      <c r="I36" s="60"/>
+      <c r="B36" s="69" t="s">
+        <v>256</v>
+      </c>
+      <c r="C36" s="70" t="s">
+        <v>236</v>
+      </c>
+      <c r="D36" s="71" t="s">
+        <v>257</v>
+      </c>
+      <c r="E36" s="71"/>
+      <c r="F36" s="72" t="s">
+        <v>258</v>
+      </c>
+      <c r="G36" s="72"/>
+      <c r="H36" s="72"/>
+      <c r="I36" s="72"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="57" t="s">
+      <c r="B38" s="69" t="s">
         <v>39</v>
       </c>
       <c r="C38" s="28" t="s">
-        <v>224</v>
+        <v>259</v>
       </c>
       <c r="D38" s="28"/>
       <c r="E38" s="28"/>
       <c r="F38" s="28"/>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="63" t="s">
-        <v>225</v>
-      </c>
-      <c r="C40" s="63"/>
-      <c r="D40" s="63"/>
-      <c r="E40" s="63"/>
-      <c r="F40" s="63"/>
-      <c r="G40" s="63"/>
-      <c r="H40" s="63"/>
-      <c r="I40" s="63"/>
+      <c r="B40" s="75" t="s">
+        <v>260</v>
+      </c>
+      <c r="C40" s="75"/>
+      <c r="D40" s="75"/>
+      <c r="E40" s="75"/>
+      <c r="F40" s="75"/>
+      <c r="G40" s="75"/>
+      <c r="H40" s="75"/>
+      <c r="I40" s="75"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -3692,7 +5182,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:G25"/>
+  <dimension ref="B1:G26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -4008,118 +5498,138 @@
         <v>125</v>
       </c>
       <c r="C19" s="27">
-        <f>'Cash Flow &amp; DSCR'!C9</f>
-        <v>164824.60522118</v>
+        <v>28186</v>
       </c>
       <c r="D19" s="27">
-        <f>'Cash Flow &amp; DSCR'!D9</f>
-        <v>164824.60522118</v>
+        <v>26908</v>
       </c>
       <c r="E19" s="27">
-        <f>'Cash Flow &amp; DSCR'!E9</f>
-        <v>164824.60522118</v>
+        <v>25555</v>
       </c>
       <c r="F19" s="27">
-        <f>'Cash Flow &amp; DSCR'!F9</f>
-        <v>164824.60522118</v>
+        <v>24122</v>
       </c>
       <c r="G19" s="27">
-        <f>'Cash Flow &amp; DSCR'!G9</f>
-        <v>164824.60522118</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="28" t="s">
+        <v>22605</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="25" t="s">
         <v>126</v>
       </c>
-      <c r="C21" s="30">
-        <f>C16-C19</f>
+      <c r="C20" s="27">
+        <f>'Cash Flow &amp; DSCR'!C9-C19</f>
+        <v>136638.97628843</v>
+      </c>
+      <c r="D20" s="27">
+        <f>'Cash Flow &amp; DSCR'!D9-D19</f>
+        <v>137916.5377976</v>
+      </c>
+      <c r="E20" s="27">
+        <f>'Cash Flow &amp; DSCR'!E9-E19</f>
+        <v>139269.52632273</v>
+      </c>
+      <c r="F20" s="27">
+        <f>'Cash Flow &amp; DSCR'!F9-F19</f>
+        <v>140702.39506211</v>
+      </c>
+      <c r="G20" s="27">
+        <f>'Cash Flow &amp; DSCR'!G9-G19</f>
+        <v>142219.86013011</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="C22" s="30">
+        <f>C16-C19-C20</f>
         <v>-472991.79411007</v>
       </c>
-      <c r="D21" s="30">
-        <f>D16-D19</f>
+      <c r="D22" s="30">
+        <f>D16-D19-D20</f>
         <v>-264617.47518785</v>
       </c>
-      <c r="E21" s="30">
-        <f>E16-E19</f>
+      <c r="E22" s="30">
+        <f>E16-E19-E20</f>
         <v>-175735.41917396</v>
       </c>
-      <c r="F21" s="30">
-        <f>F16-F19</f>
+      <c r="F22" s="30">
+        <f>F16-F19-F20</f>
         <v>-797051.70164447</v>
       </c>
-      <c r="G21" s="30">
-        <f>G16-G19</f>
+      <c r="G22" s="30">
+        <f>G16-G19-G20</f>
         <v>-2350276.27755892</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="C22" s="31">
-        <f>IF(C10&gt;0,C21/C10,0)</f>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="C23" s="31">
+        <f>IF(C10&gt;0,C22/C10,0)</f>
         <v>-0.30594553</v>
       </c>
-      <c r="D22" s="31">
-        <f>IF(D10&gt;0,D21/D10,0)</f>
+      <c r="D23" s="31">
+        <f>IF(D10&gt;0,D22/D10,0)</f>
         <v>-0.10427042</v>
       </c>
-      <c r="E22" s="31">
-        <f>IF(E10&gt;0,E21/E10,0)</f>
+      <c r="E23" s="31">
+        <f>IF(E10&gt;0,E22/E10,0)</f>
         <v>-0.04606601</v>
       </c>
-      <c r="F22" s="31">
-        <f>IF(F10&gt;0,F21/F10,0)</f>
+      <c r="F23" s="31">
+        <f>IF(F10&gt;0,F22/F10,0)</f>
         <v>-0.16504186</v>
       </c>
-      <c r="G22" s="31">
-        <f>IF(G10&gt;0,G21/G10,0)</f>
+      <c r="G23" s="31">
+        <f>IF(G10&gt;0,G22/G10,0)</f>
         <v>-0.4481626</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="C24" s="32">
-        <f>C21</f>
-        <v>-472991.79411007</v>
-      </c>
-      <c r="D24" s="32">
-        <f>C24+D21</f>
-        <v>-737609.26929791</v>
-      </c>
-      <c r="E24" s="32">
-        <f>D24+E21</f>
-        <v>-913344.68847187</v>
-      </c>
-      <c r="F24" s="32">
-        <f>E24+F21</f>
-        <v>-1710396.39011634</v>
-      </c>
-      <c r="G24" s="32">
-        <f>F24+G21</f>
-        <v>-4060672.66767526</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="C25" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="G25" s="33" t="s">
+      <c r="C25" s="32">
+        <f>C22</f>
+        <v>-472991.79411007</v>
+      </c>
+      <c r="D25" s="32">
+        <f>C25+D22</f>
+        <v>-737609.26929791</v>
+      </c>
+      <c r="E25" s="32">
+        <f>D25+E22</f>
+        <v>-913344.68847187</v>
+      </c>
+      <c r="F25" s="32">
+        <f>E25+F22</f>
+        <v>-1710396.39011634</v>
+      </c>
+      <c r="G25" s="32">
+        <f>F25+G22</f>
+        <v>-4060672.66767526</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="C26" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="G26" s="33" t="s">
         <v>7</v>
       </c>
     </row>
@@ -4151,7 +5661,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -4179,7 +5689,7 @@
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="28" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C4" s="32" t="str">
         <f>Assumptions!D57</f>
@@ -4204,7 +5714,7 @@
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="25" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C5" s="27">
         <f>'5-Year P&amp;L'!C16</f>
@@ -4229,7 +5739,7 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="25" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C7" s="27">
         <f>Assumptions!D58</f>
@@ -4254,7 +5764,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="25" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C8" s="27">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
@@ -4279,7 +5789,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="28" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C9" s="29">
         <f>C7+C8</f>
@@ -4304,7 +5814,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="28" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C11" s="34">
         <f>IF(C9&gt;0,C5/C9,IF(C5&gt;0,99.9,0))</f>
@@ -4329,7 +5839,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="25" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C13" s="27">
         <f>C5-C9</f>
@@ -4354,7 +5864,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="28" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C14" s="32">
         <f>C5-C9</f>
@@ -4379,7 +5889,7 @@
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="28" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C16" s="30">
         <f>C4+C14</f>
@@ -4417,6 +5927,267 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <tabColor rgb="FF7C3AED"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:G17"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="3" max="7" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B1" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+    </row>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="23"/>
+      <c r="C4" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="35" t="s">
+        <v>143</v>
+      </c>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="25" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" s="27">
+        <v>0</v>
+      </c>
+      <c r="D6" s="27">
+        <v>0</v>
+      </c>
+      <c r="E6" s="27">
+        <v>0</v>
+      </c>
+      <c r="F6" s="27">
+        <v>0</v>
+      </c>
+      <c r="G6" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="25" t="s">
+        <v>145</v>
+      </c>
+      <c r="C7" s="27">
+        <v>0</v>
+      </c>
+      <c r="D7" s="27">
+        <v>0</v>
+      </c>
+      <c r="E7" s="27">
+        <v>0</v>
+      </c>
+      <c r="F7" s="27">
+        <v>0</v>
+      </c>
+      <c r="G7" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="C8" s="36" t="str">
+        <f>C6-C7</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="36" t="str">
+        <f>D6-D7</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="36" t="str">
+        <f>E6-E7</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="36" t="str">
+        <f>F6-F7</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="36" t="str">
+        <f>G6-G7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="C9" s="29" t="str">
+        <f>C7*30/365</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="29" t="str">
+        <f>D7*30/365</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="29" t="str">
+        <f>E7*30/365</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="29" t="str">
+        <f>F7*30/365</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="29" t="str">
+        <f>G7*30/365</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="35" t="s">
+        <v>148</v>
+      </c>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="C12" s="27">
+        <v>-472991.79411006824</v>
+      </c>
+      <c r="D12" s="27">
+        <v>-737609.2692979143</v>
+      </c>
+      <c r="E12" s="27">
+        <v>-913344.6884718713</v>
+      </c>
+      <c r="F12" s="27">
+        <v>-1710396.3901163433</v>
+      </c>
+      <c r="G12" s="27">
+        <v>-4060672.6676752586</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="C13" s="27">
+        <v>0</v>
+      </c>
+      <c r="D13" s="27">
+        <v>0</v>
+      </c>
+      <c r="E13" s="27">
+        <v>0</v>
+      </c>
+      <c r="F13" s="27">
+        <v>0</v>
+      </c>
+      <c r="G13" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="C14" s="30">
+        <f>C12-C13</f>
+        <v>-472991.79411007</v>
+      </c>
+      <c r="D14" s="30">
+        <f>D12-D13</f>
+        <v>-737609.26929791</v>
+      </c>
+      <c r="E14" s="30">
+        <f>E12-E13</f>
+        <v>-913344.68847187</v>
+      </c>
+      <c r="F14" s="30">
+        <f>F12-F13</f>
+        <v>-1710396.39011634</v>
+      </c>
+      <c r="G14" s="30">
+        <f>G12-G13</f>
+        <v>-4060672.66767526</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="C16" s="37"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="37"/>
+      <c r="G16" s="37"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="37"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="37"/>
+      <c r="G17" s="37"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="B16:G17"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
     <tabColor rgb="FF0D9488"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4430,7 +6201,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -4458,7 +6229,7 @@
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="25" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="C4" s="26">
         <f>Drivers!C12</f>
@@ -4483,7 +6254,7 @@
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="25" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="C5" s="26">
         <f>Assumptions!D35</f>
@@ -4508,25 +6279,25 @@
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="28" t="s">
-        <v>143</v>
-      </c>
-      <c r="C6" s="35">
+        <v>156</v>
+      </c>
+      <c r="C6" s="38">
         <f>C4+C5</f>
         <v>17</v>
       </c>
-      <c r="D6" s="35">
+      <c r="D6" s="38">
         <f>D4+D5</f>
         <v>24</v>
       </c>
-      <c r="E6" s="35">
+      <c r="E6" s="38">
         <f>E4+E5</f>
         <v>32</v>
       </c>
-      <c r="F6" s="35">
+      <c r="F6" s="38">
         <f>F4+F5</f>
         <v>39</v>
       </c>
-      <c r="G6" s="35">
+      <c r="G6" s="38">
         <f>G4+G5</f>
         <v>41</v>
       </c>
@@ -4543,7 +6314,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFD97706"/>
@@ -4559,13 +6330,13 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="C1" s="13"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="25" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="C3" s="27">
         <f>Assumptions!D59</f>
@@ -4574,7 +6345,7 @@
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="25" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="C4" s="31">
         <f>Assumptions!D60</f>
@@ -4592,7 +6363,7 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="25" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="C6" s="32">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
@@ -4601,7 +6372,7 @@
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="25" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="C8" s="34">
         <f>'Cash Flow &amp; DSCR'!C11</f>
@@ -4618,174 +6389,4 @@
     <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor rgb="FF328555"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="B1:C21"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="C1" s="13"/>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" s="25" t="str">
-        <f>Assumptions!D5</f>
-        <v>Civic Scholars Charter</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4" s="25" t="str">
-        <f>Assumptions!D7</f>
-        <v>Charter School</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="25" t="str">
-        <f>Assumptions!D6</f>
-        <v>OH</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="C6" s="25">
-        <f>Assumptions!D8</f>
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" s="26">
-        <f>Assumptions!D16</f>
-        <v>400</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="C9" s="27">
-        <f>Drivers!G10</f>
-        <v>5244248.9932</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="C10" s="36">
-        <f>'5-Year P&amp;L'!G16</f>
-        <v>-2185451.67233774</v>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="37" t="s">
-        <v>153</v>
-      </c>
-      <c r="C12" s="23"/>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="C13" s="38">
-        <f>IF(Drivers!G10&gt;0,'5-Year P&amp;L'!G21/Drivers!G10,0)</f>
-        <v>-0.4481626</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="C14" s="31">
-        <f>IF(Drivers!G10&gt;0,Drivers!G16/Drivers!G10,0)</f>
-        <v>0.55578733</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="25" t="s">
-        <v>156</v>
-      </c>
-      <c r="C15" s="27">
-        <f>IF(Assumptions!D16&gt;0,Drivers!G10/Assumptions!D16,0)</f>
-        <v>13111</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="25" t="s">
-        <v>157</v>
-      </c>
-      <c r="C16" s="27">
-        <f>IF(Assumptions!D16&gt;0,('5-Year P&amp;L'!G12+'5-Year P&amp;L'!G13)/Assumptions!D16,0)</f>
-        <v>18574</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="25" t="s">
-        <v>158</v>
-      </c>
-      <c r="C17" s="34">
-        <f>'Cash Flow &amp; DSCR'!C11</f>
-        <v>-1.86966739</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="C18" s="34">
-        <f>'Cash Flow &amp; DSCR'!G11</f>
-        <v>-13.25925622</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="C19" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="C21" s="12"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B21:C21"/>
-  </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
-  <headerFooter>
-    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
-  </headerFooter>
-</worksheet>
 </file>